--- a/templates/classeum-vocab-week1.xlsx
+++ b/templates/classeum-vocab-week1.xlsx
@@ -680,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:K500"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="G2" s="6" t="n"/>
-      <c r="H2" s="6" t="n"/>
-      <c r="I2" s="6" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="8" t="n"/>
       <c r="J2" s="6" t="n"/>
-      <c r="K2" s="6" t="n"/>
+      <c r="K2" s="8" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="6" t="inlineStr">
@@ -818,10 +818,10 @@
         </is>
       </c>
       <c r="G3" s="6" t="n"/>
-      <c r="H3" s="6" t="n"/>
-      <c r="I3" s="6" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="8" t="n"/>
       <c r="J3" s="6" t="n"/>
-      <c r="K3" s="6" t="n"/>
+      <c r="K3" s="8" t="n"/>
     </row>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
@@ -855,10 +855,10 @@
         </is>
       </c>
       <c r="G4" s="6" t="n"/>
-      <c r="H4" s="6" t="n"/>
-      <c r="I4" s="6" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="8" t="n"/>
       <c r="J4" s="6" t="n"/>
-      <c r="K4" s="6" t="n"/>
+      <c r="K4" s="8" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -888,10 +888,10 @@
         </is>
       </c>
       <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="8" t="n"/>
       <c r="J5" s="6" t="n"/>
-      <c r="K5" s="6" t="n"/>
+      <c r="K5" s="8" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -925,10 +925,10 @@
         </is>
       </c>
       <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="8" t="n"/>
       <c r="J6" s="6" t="n"/>
-      <c r="K6" s="6" t="n"/>
+      <c r="K6" s="8" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -962,10 +962,10 @@
         </is>
       </c>
       <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="8" t="n"/>
       <c r="J7" s="6" t="n"/>
-      <c r="K7" s="6" t="n"/>
+      <c r="K7" s="8" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -999,10 +999,10 @@
         </is>
       </c>
       <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="8" t="n"/>
       <c r="J8" s="6" t="n"/>
-      <c r="K8" s="6" t="n"/>
+      <c r="K8" s="8" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -1032,10 +1032,10 @@
         </is>
       </c>
       <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="8" t="n"/>
       <c r="J9" s="6" t="n"/>
-      <c r="K9" s="6" t="n"/>
+      <c r="K9" s="8" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -1057,10 +1057,10 @@
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
       <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="8" t="n"/>
       <c r="J10" s="6" t="n"/>
-      <c r="K10" s="6" t="n"/>
+      <c r="K10" s="8" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
@@ -1082,10 +1082,10 @@
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
       <c r="G11" s="6" t="n"/>
-      <c r="H11" s="6" t="n"/>
-      <c r="I11" s="6" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="8" t="n"/>
       <c r="J11" s="6" t="n"/>
-      <c r="K11" s="6" t="n"/>
+      <c r="K11" s="8" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -1115,10 +1115,10 @@
         </is>
       </c>
       <c r="G12" s="6" t="n"/>
-      <c r="H12" s="6" t="n"/>
-      <c r="I12" s="6" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="8" t="n"/>
       <c r="J12" s="6" t="n"/>
-      <c r="K12" s="6" t="n"/>
+      <c r="K12" s="8" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -1152,10 +1152,10 @@
         </is>
       </c>
       <c r="G13" s="6" t="n"/>
-      <c r="H13" s="6" t="n"/>
-      <c r="I13" s="6" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="8" t="n"/>
       <c r="J13" s="6" t="n"/>
-      <c r="K13" s="6" t="n"/>
+      <c r="K13" s="8" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -1189,10 +1189,10 @@
         </is>
       </c>
       <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="8" t="n"/>
       <c r="J14" s="6" t="n"/>
-      <c r="K14" s="6" t="n"/>
+      <c r="K14" s="8" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -1218,10 +1218,10 @@
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
       <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="8" t="n"/>
       <c r="J15" s="6" t="n"/>
-      <c r="K15" s="6" t="n"/>
+      <c r="K15" s="8" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -1247,10 +1247,10 @@
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
       <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="8" t="n"/>
       <c r="J16" s="6" t="n"/>
-      <c r="K16" s="6" t="n"/>
+      <c r="K16" s="8" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -1276,10 +1276,10 @@
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
       <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="8" t="n"/>
       <c r="J17" s="6" t="n"/>
-      <c r="K17" s="6" t="n"/>
+      <c r="K17" s="8" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -1305,10 +1305,10 @@
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
       <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="8" t="n"/>
       <c r="J18" s="6" t="n"/>
-      <c r="K18" s="6" t="n"/>
+      <c r="K18" s="8" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -1338,10 +1338,10 @@
         </is>
       </c>
       <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="8" t="n"/>
       <c r="J19" s="6" t="n"/>
-      <c r="K19" s="6" t="n"/>
+      <c r="K19" s="8" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -1367,10 +1367,10 @@
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
       <c r="G20" s="6" t="n"/>
-      <c r="H20" s="6" t="n"/>
-      <c r="I20" s="6" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="8" t="n"/>
       <c r="J20" s="6" t="n"/>
-      <c r="K20" s="6" t="n"/>
+      <c r="K20" s="8" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -1400,10 +1400,2405 @@
         </is>
       </c>
       <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
-      <c r="I21" s="6" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="8" t="n"/>
       <c r="J21" s="6" t="n"/>
-      <c r="K21" s="6" t="n"/>
+      <c r="K21" s="8" t="n"/>
+    </row>
+    <row r="22">
+      <c r="H22" s="9" t="n"/>
+      <c r="I22" s="9" t="n"/>
+      <c r="K22" s="9" t="n"/>
+    </row>
+    <row r="23">
+      <c r="H23" s="9" t="n"/>
+      <c r="I23" s="9" t="n"/>
+      <c r="K23" s="9" t="n"/>
+    </row>
+    <row r="24">
+      <c r="H24" s="9" t="n"/>
+      <c r="I24" s="9" t="n"/>
+      <c r="K24" s="9" t="n"/>
+    </row>
+    <row r="25">
+      <c r="H25" s="9" t="n"/>
+      <c r="I25" s="9" t="n"/>
+      <c r="K25" s="9" t="n"/>
+    </row>
+    <row r="26">
+      <c r="H26" s="9" t="n"/>
+      <c r="I26" s="9" t="n"/>
+      <c r="K26" s="9" t="n"/>
+    </row>
+    <row r="27">
+      <c r="H27" s="9" t="n"/>
+      <c r="I27" s="9" t="n"/>
+      <c r="K27" s="9" t="n"/>
+    </row>
+    <row r="28">
+      <c r="H28" s="9" t="n"/>
+      <c r="I28" s="9" t="n"/>
+      <c r="K28" s="9" t="n"/>
+    </row>
+    <row r="29">
+      <c r="H29" s="9" t="n"/>
+      <c r="I29" s="9" t="n"/>
+      <c r="K29" s="9" t="n"/>
+    </row>
+    <row r="30">
+      <c r="H30" s="9" t="n"/>
+      <c r="I30" s="9" t="n"/>
+      <c r="K30" s="9" t="n"/>
+    </row>
+    <row r="31">
+      <c r="H31" s="9" t="n"/>
+      <c r="I31" s="9" t="n"/>
+      <c r="K31" s="9" t="n"/>
+    </row>
+    <row r="32">
+      <c r="H32" s="9" t="n"/>
+      <c r="I32" s="9" t="n"/>
+      <c r="K32" s="9" t="n"/>
+    </row>
+    <row r="33">
+      <c r="H33" s="9" t="n"/>
+      <c r="I33" s="9" t="n"/>
+      <c r="K33" s="9" t="n"/>
+    </row>
+    <row r="34">
+      <c r="H34" s="9" t="n"/>
+      <c r="I34" s="9" t="n"/>
+      <c r="K34" s="9" t="n"/>
+    </row>
+    <row r="35">
+      <c r="H35" s="9" t="n"/>
+      <c r="I35" s="9" t="n"/>
+      <c r="K35" s="9" t="n"/>
+    </row>
+    <row r="36">
+      <c r="H36" s="9" t="n"/>
+      <c r="I36" s="9" t="n"/>
+      <c r="K36" s="9" t="n"/>
+    </row>
+    <row r="37">
+      <c r="H37" s="9" t="n"/>
+      <c r="I37" s="9" t="n"/>
+      <c r="K37" s="9" t="n"/>
+    </row>
+    <row r="38">
+      <c r="H38" s="9" t="n"/>
+      <c r="I38" s="9" t="n"/>
+      <c r="K38" s="9" t="n"/>
+    </row>
+    <row r="39">
+      <c r="H39" s="9" t="n"/>
+      <c r="I39" s="9" t="n"/>
+      <c r="K39" s="9" t="n"/>
+    </row>
+    <row r="40">
+      <c r="H40" s="9" t="n"/>
+      <c r="I40" s="9" t="n"/>
+      <c r="K40" s="9" t="n"/>
+    </row>
+    <row r="41">
+      <c r="H41" s="9" t="n"/>
+      <c r="I41" s="9" t="n"/>
+      <c r="K41" s="9" t="n"/>
+    </row>
+    <row r="42">
+      <c r="H42" s="9" t="n"/>
+      <c r="I42" s="9" t="n"/>
+      <c r="K42" s="9" t="n"/>
+    </row>
+    <row r="43">
+      <c r="H43" s="9" t="n"/>
+      <c r="I43" s="9" t="n"/>
+      <c r="K43" s="9" t="n"/>
+    </row>
+    <row r="44">
+      <c r="H44" s="9" t="n"/>
+      <c r="I44" s="9" t="n"/>
+      <c r="K44" s="9" t="n"/>
+    </row>
+    <row r="45">
+      <c r="H45" s="9" t="n"/>
+      <c r="I45" s="9" t="n"/>
+      <c r="K45" s="9" t="n"/>
+    </row>
+    <row r="46">
+      <c r="H46" s="9" t="n"/>
+      <c r="I46" s="9" t="n"/>
+      <c r="K46" s="9" t="n"/>
+    </row>
+    <row r="47">
+      <c r="H47" s="9" t="n"/>
+      <c r="I47" s="9" t="n"/>
+      <c r="K47" s="9" t="n"/>
+    </row>
+    <row r="48">
+      <c r="H48" s="9" t="n"/>
+      <c r="I48" s="9" t="n"/>
+      <c r="K48" s="9" t="n"/>
+    </row>
+    <row r="49">
+      <c r="H49" s="9" t="n"/>
+      <c r="I49" s="9" t="n"/>
+      <c r="K49" s="9" t="n"/>
+    </row>
+    <row r="50">
+      <c r="H50" s="9" t="n"/>
+      <c r="I50" s="9" t="n"/>
+      <c r="K50" s="9" t="n"/>
+    </row>
+    <row r="51">
+      <c r="H51" s="9" t="n"/>
+      <c r="I51" s="9" t="n"/>
+      <c r="K51" s="9" t="n"/>
+    </row>
+    <row r="52">
+      <c r="H52" s="9" t="n"/>
+      <c r="I52" s="9" t="n"/>
+      <c r="K52" s="9" t="n"/>
+    </row>
+    <row r="53">
+      <c r="H53" s="9" t="n"/>
+      <c r="I53" s="9" t="n"/>
+      <c r="K53" s="9" t="n"/>
+    </row>
+    <row r="54">
+      <c r="H54" s="9" t="n"/>
+      <c r="I54" s="9" t="n"/>
+      <c r="K54" s="9" t="n"/>
+    </row>
+    <row r="55">
+      <c r="H55" s="9" t="n"/>
+      <c r="I55" s="9" t="n"/>
+      <c r="K55" s="9" t="n"/>
+    </row>
+    <row r="56">
+      <c r="H56" s="9" t="n"/>
+      <c r="I56" s="9" t="n"/>
+      <c r="K56" s="9" t="n"/>
+    </row>
+    <row r="57">
+      <c r="H57" s="9" t="n"/>
+      <c r="I57" s="9" t="n"/>
+      <c r="K57" s="9" t="n"/>
+    </row>
+    <row r="58">
+      <c r="H58" s="9" t="n"/>
+      <c r="I58" s="9" t="n"/>
+      <c r="K58" s="9" t="n"/>
+    </row>
+    <row r="59">
+      <c r="H59" s="9" t="n"/>
+      <c r="I59" s="9" t="n"/>
+      <c r="K59" s="9" t="n"/>
+    </row>
+    <row r="60">
+      <c r="H60" s="9" t="n"/>
+      <c r="I60" s="9" t="n"/>
+      <c r="K60" s="9" t="n"/>
+    </row>
+    <row r="61">
+      <c r="H61" s="9" t="n"/>
+      <c r="I61" s="9" t="n"/>
+      <c r="K61" s="9" t="n"/>
+    </row>
+    <row r="62">
+      <c r="H62" s="9" t="n"/>
+      <c r="I62" s="9" t="n"/>
+      <c r="K62" s="9" t="n"/>
+    </row>
+    <row r="63">
+      <c r="H63" s="9" t="n"/>
+      <c r="I63" s="9" t="n"/>
+      <c r="K63" s="9" t="n"/>
+    </row>
+    <row r="64">
+      <c r="H64" s="9" t="n"/>
+      <c r="I64" s="9" t="n"/>
+      <c r="K64" s="9" t="n"/>
+    </row>
+    <row r="65">
+      <c r="H65" s="9" t="n"/>
+      <c r="I65" s="9" t="n"/>
+      <c r="K65" s="9" t="n"/>
+    </row>
+    <row r="66">
+      <c r="H66" s="9" t="n"/>
+      <c r="I66" s="9" t="n"/>
+      <c r="K66" s="9" t="n"/>
+    </row>
+    <row r="67">
+      <c r="H67" s="9" t="n"/>
+      <c r="I67" s="9" t="n"/>
+      <c r="K67" s="9" t="n"/>
+    </row>
+    <row r="68">
+      <c r="H68" s="9" t="n"/>
+      <c r="I68" s="9" t="n"/>
+      <c r="K68" s="9" t="n"/>
+    </row>
+    <row r="69">
+      <c r="H69" s="9" t="n"/>
+      <c r="I69" s="9" t="n"/>
+      <c r="K69" s="9" t="n"/>
+    </row>
+    <row r="70">
+      <c r="H70" s="9" t="n"/>
+      <c r="I70" s="9" t="n"/>
+      <c r="K70" s="9" t="n"/>
+    </row>
+    <row r="71">
+      <c r="H71" s="9" t="n"/>
+      <c r="I71" s="9" t="n"/>
+      <c r="K71" s="9" t="n"/>
+    </row>
+    <row r="72">
+      <c r="H72" s="9" t="n"/>
+      <c r="I72" s="9" t="n"/>
+      <c r="K72" s="9" t="n"/>
+    </row>
+    <row r="73">
+      <c r="H73" s="9" t="n"/>
+      <c r="I73" s="9" t="n"/>
+      <c r="K73" s="9" t="n"/>
+    </row>
+    <row r="74">
+      <c r="H74" s="9" t="n"/>
+      <c r="I74" s="9" t="n"/>
+      <c r="K74" s="9" t="n"/>
+    </row>
+    <row r="75">
+      <c r="H75" s="9" t="n"/>
+      <c r="I75" s="9" t="n"/>
+      <c r="K75" s="9" t="n"/>
+    </row>
+    <row r="76">
+      <c r="H76" s="9" t="n"/>
+      <c r="I76" s="9" t="n"/>
+      <c r="K76" s="9" t="n"/>
+    </row>
+    <row r="77">
+      <c r="H77" s="9" t="n"/>
+      <c r="I77" s="9" t="n"/>
+      <c r="K77" s="9" t="n"/>
+    </row>
+    <row r="78">
+      <c r="H78" s="9" t="n"/>
+      <c r="I78" s="9" t="n"/>
+      <c r="K78" s="9" t="n"/>
+    </row>
+    <row r="79">
+      <c r="H79" s="9" t="n"/>
+      <c r="I79" s="9" t="n"/>
+      <c r="K79" s="9" t="n"/>
+    </row>
+    <row r="80">
+      <c r="H80" s="9" t="n"/>
+      <c r="I80" s="9" t="n"/>
+      <c r="K80" s="9" t="n"/>
+    </row>
+    <row r="81">
+      <c r="H81" s="9" t="n"/>
+      <c r="I81" s="9" t="n"/>
+      <c r="K81" s="9" t="n"/>
+    </row>
+    <row r="82">
+      <c r="H82" s="9" t="n"/>
+      <c r="I82" s="9" t="n"/>
+      <c r="K82" s="9" t="n"/>
+    </row>
+    <row r="83">
+      <c r="H83" s="9" t="n"/>
+      <c r="I83" s="9" t="n"/>
+      <c r="K83" s="9" t="n"/>
+    </row>
+    <row r="84">
+      <c r="H84" s="9" t="n"/>
+      <c r="I84" s="9" t="n"/>
+      <c r="K84" s="9" t="n"/>
+    </row>
+    <row r="85">
+      <c r="H85" s="9" t="n"/>
+      <c r="I85" s="9" t="n"/>
+      <c r="K85" s="9" t="n"/>
+    </row>
+    <row r="86">
+      <c r="H86" s="9" t="n"/>
+      <c r="I86" s="9" t="n"/>
+      <c r="K86" s="9" t="n"/>
+    </row>
+    <row r="87">
+      <c r="H87" s="9" t="n"/>
+      <c r="I87" s="9" t="n"/>
+      <c r="K87" s="9" t="n"/>
+    </row>
+    <row r="88">
+      <c r="H88" s="9" t="n"/>
+      <c r="I88" s="9" t="n"/>
+      <c r="K88" s="9" t="n"/>
+    </row>
+    <row r="89">
+      <c r="H89" s="9" t="n"/>
+      <c r="I89" s="9" t="n"/>
+      <c r="K89" s="9" t="n"/>
+    </row>
+    <row r="90">
+      <c r="H90" s="9" t="n"/>
+      <c r="I90" s="9" t="n"/>
+      <c r="K90" s="9" t="n"/>
+    </row>
+    <row r="91">
+      <c r="H91" s="9" t="n"/>
+      <c r="I91" s="9" t="n"/>
+      <c r="K91" s="9" t="n"/>
+    </row>
+    <row r="92">
+      <c r="H92" s="9" t="n"/>
+      <c r="I92" s="9" t="n"/>
+      <c r="K92" s="9" t="n"/>
+    </row>
+    <row r="93">
+      <c r="H93" s="9" t="n"/>
+      <c r="I93" s="9" t="n"/>
+      <c r="K93" s="9" t="n"/>
+    </row>
+    <row r="94">
+      <c r="H94" s="9" t="n"/>
+      <c r="I94" s="9" t="n"/>
+      <c r="K94" s="9" t="n"/>
+    </row>
+    <row r="95">
+      <c r="H95" s="9" t="n"/>
+      <c r="I95" s="9" t="n"/>
+      <c r="K95" s="9" t="n"/>
+    </row>
+    <row r="96">
+      <c r="H96" s="9" t="n"/>
+      <c r="I96" s="9" t="n"/>
+      <c r="K96" s="9" t="n"/>
+    </row>
+    <row r="97">
+      <c r="H97" s="9" t="n"/>
+      <c r="I97" s="9" t="n"/>
+      <c r="K97" s="9" t="n"/>
+    </row>
+    <row r="98">
+      <c r="H98" s="9" t="n"/>
+      <c r="I98" s="9" t="n"/>
+      <c r="K98" s="9" t="n"/>
+    </row>
+    <row r="99">
+      <c r="H99" s="9" t="n"/>
+      <c r="I99" s="9" t="n"/>
+      <c r="K99" s="9" t="n"/>
+    </row>
+    <row r="100">
+      <c r="H100" s="9" t="n"/>
+      <c r="I100" s="9" t="n"/>
+      <c r="K100" s="9" t="n"/>
+    </row>
+    <row r="101">
+      <c r="H101" s="9" t="n"/>
+      <c r="I101" s="9" t="n"/>
+      <c r="K101" s="9" t="n"/>
+    </row>
+    <row r="102">
+      <c r="H102" s="9" t="n"/>
+      <c r="I102" s="9" t="n"/>
+      <c r="K102" s="9" t="n"/>
+    </row>
+    <row r="103">
+      <c r="H103" s="9" t="n"/>
+      <c r="I103" s="9" t="n"/>
+      <c r="K103" s="9" t="n"/>
+    </row>
+    <row r="104">
+      <c r="H104" s="9" t="n"/>
+      <c r="I104" s="9" t="n"/>
+      <c r="K104" s="9" t="n"/>
+    </row>
+    <row r="105">
+      <c r="H105" s="9" t="n"/>
+      <c r="I105" s="9" t="n"/>
+      <c r="K105" s="9" t="n"/>
+    </row>
+    <row r="106">
+      <c r="H106" s="9" t="n"/>
+      <c r="I106" s="9" t="n"/>
+      <c r="K106" s="9" t="n"/>
+    </row>
+    <row r="107">
+      <c r="H107" s="9" t="n"/>
+      <c r="I107" s="9" t="n"/>
+      <c r="K107" s="9" t="n"/>
+    </row>
+    <row r="108">
+      <c r="H108" s="9" t="n"/>
+      <c r="I108" s="9" t="n"/>
+      <c r="K108" s="9" t="n"/>
+    </row>
+    <row r="109">
+      <c r="H109" s="9" t="n"/>
+      <c r="I109" s="9" t="n"/>
+      <c r="K109" s="9" t="n"/>
+    </row>
+    <row r="110">
+      <c r="H110" s="9" t="n"/>
+      <c r="I110" s="9" t="n"/>
+      <c r="K110" s="9" t="n"/>
+    </row>
+    <row r="111">
+      <c r="H111" s="9" t="n"/>
+      <c r="I111" s="9" t="n"/>
+      <c r="K111" s="9" t="n"/>
+    </row>
+    <row r="112">
+      <c r="H112" s="9" t="n"/>
+      <c r="I112" s="9" t="n"/>
+      <c r="K112" s="9" t="n"/>
+    </row>
+    <row r="113">
+      <c r="H113" s="9" t="n"/>
+      <c r="I113" s="9" t="n"/>
+      <c r="K113" s="9" t="n"/>
+    </row>
+    <row r="114">
+      <c r="H114" s="9" t="n"/>
+      <c r="I114" s="9" t="n"/>
+      <c r="K114" s="9" t="n"/>
+    </row>
+    <row r="115">
+      <c r="H115" s="9" t="n"/>
+      <c r="I115" s="9" t="n"/>
+      <c r="K115" s="9" t="n"/>
+    </row>
+    <row r="116">
+      <c r="H116" s="9" t="n"/>
+      <c r="I116" s="9" t="n"/>
+      <c r="K116" s="9" t="n"/>
+    </row>
+    <row r="117">
+      <c r="H117" s="9" t="n"/>
+      <c r="I117" s="9" t="n"/>
+      <c r="K117" s="9" t="n"/>
+    </row>
+    <row r="118">
+      <c r="H118" s="9" t="n"/>
+      <c r="I118" s="9" t="n"/>
+      <c r="K118" s="9" t="n"/>
+    </row>
+    <row r="119">
+      <c r="H119" s="9" t="n"/>
+      <c r="I119" s="9" t="n"/>
+      <c r="K119" s="9" t="n"/>
+    </row>
+    <row r="120">
+      <c r="H120" s="9" t="n"/>
+      <c r="I120" s="9" t="n"/>
+      <c r="K120" s="9" t="n"/>
+    </row>
+    <row r="121">
+      <c r="H121" s="9" t="n"/>
+      <c r="I121" s="9" t="n"/>
+      <c r="K121" s="9" t="n"/>
+    </row>
+    <row r="122">
+      <c r="H122" s="9" t="n"/>
+      <c r="I122" s="9" t="n"/>
+      <c r="K122" s="9" t="n"/>
+    </row>
+    <row r="123">
+      <c r="H123" s="9" t="n"/>
+      <c r="I123" s="9" t="n"/>
+      <c r="K123" s="9" t="n"/>
+    </row>
+    <row r="124">
+      <c r="H124" s="9" t="n"/>
+      <c r="I124" s="9" t="n"/>
+      <c r="K124" s="9" t="n"/>
+    </row>
+    <row r="125">
+      <c r="H125" s="9" t="n"/>
+      <c r="I125" s="9" t="n"/>
+      <c r="K125" s="9" t="n"/>
+    </row>
+    <row r="126">
+      <c r="H126" s="9" t="n"/>
+      <c r="I126" s="9" t="n"/>
+      <c r="K126" s="9" t="n"/>
+    </row>
+    <row r="127">
+      <c r="H127" s="9" t="n"/>
+      <c r="I127" s="9" t="n"/>
+      <c r="K127" s="9" t="n"/>
+    </row>
+    <row r="128">
+      <c r="H128" s="9" t="n"/>
+      <c r="I128" s="9" t="n"/>
+      <c r="K128" s="9" t="n"/>
+    </row>
+    <row r="129">
+      <c r="H129" s="9" t="n"/>
+      <c r="I129" s="9" t="n"/>
+      <c r="K129" s="9" t="n"/>
+    </row>
+    <row r="130">
+      <c r="H130" s="9" t="n"/>
+      <c r="I130" s="9" t="n"/>
+      <c r="K130" s="9" t="n"/>
+    </row>
+    <row r="131">
+      <c r="H131" s="9" t="n"/>
+      <c r="I131" s="9" t="n"/>
+      <c r="K131" s="9" t="n"/>
+    </row>
+    <row r="132">
+      <c r="H132" s="9" t="n"/>
+      <c r="I132" s="9" t="n"/>
+      <c r="K132" s="9" t="n"/>
+    </row>
+    <row r="133">
+      <c r="H133" s="9" t="n"/>
+      <c r="I133" s="9" t="n"/>
+      <c r="K133" s="9" t="n"/>
+    </row>
+    <row r="134">
+      <c r="H134" s="9" t="n"/>
+      <c r="I134" s="9" t="n"/>
+      <c r="K134" s="9" t="n"/>
+    </row>
+    <row r="135">
+      <c r="H135" s="9" t="n"/>
+      <c r="I135" s="9" t="n"/>
+      <c r="K135" s="9" t="n"/>
+    </row>
+    <row r="136">
+      <c r="H136" s="9" t="n"/>
+      <c r="I136" s="9" t="n"/>
+      <c r="K136" s="9" t="n"/>
+    </row>
+    <row r="137">
+      <c r="H137" s="9" t="n"/>
+      <c r="I137" s="9" t="n"/>
+      <c r="K137" s="9" t="n"/>
+    </row>
+    <row r="138">
+      <c r="H138" s="9" t="n"/>
+      <c r="I138" s="9" t="n"/>
+      <c r="K138" s="9" t="n"/>
+    </row>
+    <row r="139">
+      <c r="H139" s="9" t="n"/>
+      <c r="I139" s="9" t="n"/>
+      <c r="K139" s="9" t="n"/>
+    </row>
+    <row r="140">
+      <c r="H140" s="9" t="n"/>
+      <c r="I140" s="9" t="n"/>
+      <c r="K140" s="9" t="n"/>
+    </row>
+    <row r="141">
+      <c r="H141" s="9" t="n"/>
+      <c r="I141" s="9" t="n"/>
+      <c r="K141" s="9" t="n"/>
+    </row>
+    <row r="142">
+      <c r="H142" s="9" t="n"/>
+      <c r="I142" s="9" t="n"/>
+      <c r="K142" s="9" t="n"/>
+    </row>
+    <row r="143">
+      <c r="H143" s="9" t="n"/>
+      <c r="I143" s="9" t="n"/>
+      <c r="K143" s="9" t="n"/>
+    </row>
+    <row r="144">
+      <c r="H144" s="9" t="n"/>
+      <c r="I144" s="9" t="n"/>
+      <c r="K144" s="9" t="n"/>
+    </row>
+    <row r="145">
+      <c r="H145" s="9" t="n"/>
+      <c r="I145" s="9" t="n"/>
+      <c r="K145" s="9" t="n"/>
+    </row>
+    <row r="146">
+      <c r="H146" s="9" t="n"/>
+      <c r="I146" s="9" t="n"/>
+      <c r="K146" s="9" t="n"/>
+    </row>
+    <row r="147">
+      <c r="H147" s="9" t="n"/>
+      <c r="I147" s="9" t="n"/>
+      <c r="K147" s="9" t="n"/>
+    </row>
+    <row r="148">
+      <c r="H148" s="9" t="n"/>
+      <c r="I148" s="9" t="n"/>
+      <c r="K148" s="9" t="n"/>
+    </row>
+    <row r="149">
+      <c r="H149" s="9" t="n"/>
+      <c r="I149" s="9" t="n"/>
+      <c r="K149" s="9" t="n"/>
+    </row>
+    <row r="150">
+      <c r="H150" s="9" t="n"/>
+      <c r="I150" s="9" t="n"/>
+      <c r="K150" s="9" t="n"/>
+    </row>
+    <row r="151">
+      <c r="H151" s="9" t="n"/>
+      <c r="I151" s="9" t="n"/>
+      <c r="K151" s="9" t="n"/>
+    </row>
+    <row r="152">
+      <c r="H152" s="9" t="n"/>
+      <c r="I152" s="9" t="n"/>
+      <c r="K152" s="9" t="n"/>
+    </row>
+    <row r="153">
+      <c r="H153" s="9" t="n"/>
+      <c r="I153" s="9" t="n"/>
+      <c r="K153" s="9" t="n"/>
+    </row>
+    <row r="154">
+      <c r="H154" s="9" t="n"/>
+      <c r="I154" s="9" t="n"/>
+      <c r="K154" s="9" t="n"/>
+    </row>
+    <row r="155">
+      <c r="H155" s="9" t="n"/>
+      <c r="I155" s="9" t="n"/>
+      <c r="K155" s="9" t="n"/>
+    </row>
+    <row r="156">
+      <c r="H156" s="9" t="n"/>
+      <c r="I156" s="9" t="n"/>
+      <c r="K156" s="9" t="n"/>
+    </row>
+    <row r="157">
+      <c r="H157" s="9" t="n"/>
+      <c r="I157" s="9" t="n"/>
+      <c r="K157" s="9" t="n"/>
+    </row>
+    <row r="158">
+      <c r="H158" s="9" t="n"/>
+      <c r="I158" s="9" t="n"/>
+      <c r="K158" s="9" t="n"/>
+    </row>
+    <row r="159">
+      <c r="H159" s="9" t="n"/>
+      <c r="I159" s="9" t="n"/>
+      <c r="K159" s="9" t="n"/>
+    </row>
+    <row r="160">
+      <c r="H160" s="9" t="n"/>
+      <c r="I160" s="9" t="n"/>
+      <c r="K160" s="9" t="n"/>
+    </row>
+    <row r="161">
+      <c r="H161" s="9" t="n"/>
+      <c r="I161" s="9" t="n"/>
+      <c r="K161" s="9" t="n"/>
+    </row>
+    <row r="162">
+      <c r="H162" s="9" t="n"/>
+      <c r="I162" s="9" t="n"/>
+      <c r="K162" s="9" t="n"/>
+    </row>
+    <row r="163">
+      <c r="H163" s="9" t="n"/>
+      <c r="I163" s="9" t="n"/>
+      <c r="K163" s="9" t="n"/>
+    </row>
+    <row r="164">
+      <c r="H164" s="9" t="n"/>
+      <c r="I164" s="9" t="n"/>
+      <c r="K164" s="9" t="n"/>
+    </row>
+    <row r="165">
+      <c r="H165" s="9" t="n"/>
+      <c r="I165" s="9" t="n"/>
+      <c r="K165" s="9" t="n"/>
+    </row>
+    <row r="166">
+      <c r="H166" s="9" t="n"/>
+      <c r="I166" s="9" t="n"/>
+      <c r="K166" s="9" t="n"/>
+    </row>
+    <row r="167">
+      <c r="H167" s="9" t="n"/>
+      <c r="I167" s="9" t="n"/>
+      <c r="K167" s="9" t="n"/>
+    </row>
+    <row r="168">
+      <c r="H168" s="9" t="n"/>
+      <c r="I168" s="9" t="n"/>
+      <c r="K168" s="9" t="n"/>
+    </row>
+    <row r="169">
+      <c r="H169" s="9" t="n"/>
+      <c r="I169" s="9" t="n"/>
+      <c r="K169" s="9" t="n"/>
+    </row>
+    <row r="170">
+      <c r="H170" s="9" t="n"/>
+      <c r="I170" s="9" t="n"/>
+      <c r="K170" s="9" t="n"/>
+    </row>
+    <row r="171">
+      <c r="H171" s="9" t="n"/>
+      <c r="I171" s="9" t="n"/>
+      <c r="K171" s="9" t="n"/>
+    </row>
+    <row r="172">
+      <c r="H172" s="9" t="n"/>
+      <c r="I172" s="9" t="n"/>
+      <c r="K172" s="9" t="n"/>
+    </row>
+    <row r="173">
+      <c r="H173" s="9" t="n"/>
+      <c r="I173" s="9" t="n"/>
+      <c r="K173" s="9" t="n"/>
+    </row>
+    <row r="174">
+      <c r="H174" s="9" t="n"/>
+      <c r="I174" s="9" t="n"/>
+      <c r="K174" s="9" t="n"/>
+    </row>
+    <row r="175">
+      <c r="H175" s="9" t="n"/>
+      <c r="I175" s="9" t="n"/>
+      <c r="K175" s="9" t="n"/>
+    </row>
+    <row r="176">
+      <c r="H176" s="9" t="n"/>
+      <c r="I176" s="9" t="n"/>
+      <c r="K176" s="9" t="n"/>
+    </row>
+    <row r="177">
+      <c r="H177" s="9" t="n"/>
+      <c r="I177" s="9" t="n"/>
+      <c r="K177" s="9" t="n"/>
+    </row>
+    <row r="178">
+      <c r="H178" s="9" t="n"/>
+      <c r="I178" s="9" t="n"/>
+      <c r="K178" s="9" t="n"/>
+    </row>
+    <row r="179">
+      <c r="H179" s="9" t="n"/>
+      <c r="I179" s="9" t="n"/>
+      <c r="K179" s="9" t="n"/>
+    </row>
+    <row r="180">
+      <c r="H180" s="9" t="n"/>
+      <c r="I180" s="9" t="n"/>
+      <c r="K180" s="9" t="n"/>
+    </row>
+    <row r="181">
+      <c r="H181" s="9" t="n"/>
+      <c r="I181" s="9" t="n"/>
+      <c r="K181" s="9" t="n"/>
+    </row>
+    <row r="182">
+      <c r="H182" s="9" t="n"/>
+      <c r="I182" s="9" t="n"/>
+      <c r="K182" s="9" t="n"/>
+    </row>
+    <row r="183">
+      <c r="H183" s="9" t="n"/>
+      <c r="I183" s="9" t="n"/>
+      <c r="K183" s="9" t="n"/>
+    </row>
+    <row r="184">
+      <c r="H184" s="9" t="n"/>
+      <c r="I184" s="9" t="n"/>
+      <c r="K184" s="9" t="n"/>
+    </row>
+    <row r="185">
+      <c r="H185" s="9" t="n"/>
+      <c r="I185" s="9" t="n"/>
+      <c r="K185" s="9" t="n"/>
+    </row>
+    <row r="186">
+      <c r="H186" s="9" t="n"/>
+      <c r="I186" s="9" t="n"/>
+      <c r="K186" s="9" t="n"/>
+    </row>
+    <row r="187">
+      <c r="H187" s="9" t="n"/>
+      <c r="I187" s="9" t="n"/>
+      <c r="K187" s="9" t="n"/>
+    </row>
+    <row r="188">
+      <c r="H188" s="9" t="n"/>
+      <c r="I188" s="9" t="n"/>
+      <c r="K188" s="9" t="n"/>
+    </row>
+    <row r="189">
+      <c r="H189" s="9" t="n"/>
+      <c r="I189" s="9" t="n"/>
+      <c r="K189" s="9" t="n"/>
+    </row>
+    <row r="190">
+      <c r="H190" s="9" t="n"/>
+      <c r="I190" s="9" t="n"/>
+      <c r="K190" s="9" t="n"/>
+    </row>
+    <row r="191">
+      <c r="H191" s="9" t="n"/>
+      <c r="I191" s="9" t="n"/>
+      <c r="K191" s="9" t="n"/>
+    </row>
+    <row r="192">
+      <c r="H192" s="9" t="n"/>
+      <c r="I192" s="9" t="n"/>
+      <c r="K192" s="9" t="n"/>
+    </row>
+    <row r="193">
+      <c r="H193" s="9" t="n"/>
+      <c r="I193" s="9" t="n"/>
+      <c r="K193" s="9" t="n"/>
+    </row>
+    <row r="194">
+      <c r="H194" s="9" t="n"/>
+      <c r="I194" s="9" t="n"/>
+      <c r="K194" s="9" t="n"/>
+    </row>
+    <row r="195">
+      <c r="H195" s="9" t="n"/>
+      <c r="I195" s="9" t="n"/>
+      <c r="K195" s="9" t="n"/>
+    </row>
+    <row r="196">
+      <c r="H196" s="9" t="n"/>
+      <c r="I196" s="9" t="n"/>
+      <c r="K196" s="9" t="n"/>
+    </row>
+    <row r="197">
+      <c r="H197" s="9" t="n"/>
+      <c r="I197" s="9" t="n"/>
+      <c r="K197" s="9" t="n"/>
+    </row>
+    <row r="198">
+      <c r="H198" s="9" t="n"/>
+      <c r="I198" s="9" t="n"/>
+      <c r="K198" s="9" t="n"/>
+    </row>
+    <row r="199">
+      <c r="H199" s="9" t="n"/>
+      <c r="I199" s="9" t="n"/>
+      <c r="K199" s="9" t="n"/>
+    </row>
+    <row r="200">
+      <c r="H200" s="9" t="n"/>
+      <c r="I200" s="9" t="n"/>
+      <c r="K200" s="9" t="n"/>
+    </row>
+    <row r="201">
+      <c r="H201" s="9" t="n"/>
+      <c r="I201" s="9" t="n"/>
+      <c r="K201" s="9" t="n"/>
+    </row>
+    <row r="202">
+      <c r="H202" s="9" t="n"/>
+      <c r="I202" s="9" t="n"/>
+      <c r="K202" s="9" t="n"/>
+    </row>
+    <row r="203">
+      <c r="H203" s="9" t="n"/>
+      <c r="I203" s="9" t="n"/>
+      <c r="K203" s="9" t="n"/>
+    </row>
+    <row r="204">
+      <c r="H204" s="9" t="n"/>
+      <c r="I204" s="9" t="n"/>
+      <c r="K204" s="9" t="n"/>
+    </row>
+    <row r="205">
+      <c r="H205" s="9" t="n"/>
+      <c r="I205" s="9" t="n"/>
+      <c r="K205" s="9" t="n"/>
+    </row>
+    <row r="206">
+      <c r="H206" s="9" t="n"/>
+      <c r="I206" s="9" t="n"/>
+      <c r="K206" s="9" t="n"/>
+    </row>
+    <row r="207">
+      <c r="H207" s="9" t="n"/>
+      <c r="I207" s="9" t="n"/>
+      <c r="K207" s="9" t="n"/>
+    </row>
+    <row r="208">
+      <c r="H208" s="9" t="n"/>
+      <c r="I208" s="9" t="n"/>
+      <c r="K208" s="9" t="n"/>
+    </row>
+    <row r="209">
+      <c r="H209" s="9" t="n"/>
+      <c r="I209" s="9" t="n"/>
+      <c r="K209" s="9" t="n"/>
+    </row>
+    <row r="210">
+      <c r="H210" s="9" t="n"/>
+      <c r="I210" s="9" t="n"/>
+      <c r="K210" s="9" t="n"/>
+    </row>
+    <row r="211">
+      <c r="H211" s="9" t="n"/>
+      <c r="I211" s="9" t="n"/>
+      <c r="K211" s="9" t="n"/>
+    </row>
+    <row r="212">
+      <c r="H212" s="9" t="n"/>
+      <c r="I212" s="9" t="n"/>
+      <c r="K212" s="9" t="n"/>
+    </row>
+    <row r="213">
+      <c r="H213" s="9" t="n"/>
+      <c r="I213" s="9" t="n"/>
+      <c r="K213" s="9" t="n"/>
+    </row>
+    <row r="214">
+      <c r="H214" s="9" t="n"/>
+      <c r="I214" s="9" t="n"/>
+      <c r="K214" s="9" t="n"/>
+    </row>
+    <row r="215">
+      <c r="H215" s="9" t="n"/>
+      <c r="I215" s="9" t="n"/>
+      <c r="K215" s="9" t="n"/>
+    </row>
+    <row r="216">
+      <c r="H216" s="9" t="n"/>
+      <c r="I216" s="9" t="n"/>
+      <c r="K216" s="9" t="n"/>
+    </row>
+    <row r="217">
+      <c r="H217" s="9" t="n"/>
+      <c r="I217" s="9" t="n"/>
+      <c r="K217" s="9" t="n"/>
+    </row>
+    <row r="218">
+      <c r="H218" s="9" t="n"/>
+      <c r="I218" s="9" t="n"/>
+      <c r="K218" s="9" t="n"/>
+    </row>
+    <row r="219">
+      <c r="H219" s="9" t="n"/>
+      <c r="I219" s="9" t="n"/>
+      <c r="K219" s="9" t="n"/>
+    </row>
+    <row r="220">
+      <c r="H220" s="9" t="n"/>
+      <c r="I220" s="9" t="n"/>
+      <c r="K220" s="9" t="n"/>
+    </row>
+    <row r="221">
+      <c r="H221" s="9" t="n"/>
+      <c r="I221" s="9" t="n"/>
+      <c r="K221" s="9" t="n"/>
+    </row>
+    <row r="222">
+      <c r="H222" s="9" t="n"/>
+      <c r="I222" s="9" t="n"/>
+      <c r="K222" s="9" t="n"/>
+    </row>
+    <row r="223">
+      <c r="H223" s="9" t="n"/>
+      <c r="I223" s="9" t="n"/>
+      <c r="K223" s="9" t="n"/>
+    </row>
+    <row r="224">
+      <c r="H224" s="9" t="n"/>
+      <c r="I224" s="9" t="n"/>
+      <c r="K224" s="9" t="n"/>
+    </row>
+    <row r="225">
+      <c r="H225" s="9" t="n"/>
+      <c r="I225" s="9" t="n"/>
+      <c r="K225" s="9" t="n"/>
+    </row>
+    <row r="226">
+      <c r="H226" s="9" t="n"/>
+      <c r="I226" s="9" t="n"/>
+      <c r="K226" s="9" t="n"/>
+    </row>
+    <row r="227">
+      <c r="H227" s="9" t="n"/>
+      <c r="I227" s="9" t="n"/>
+      <c r="K227" s="9" t="n"/>
+    </row>
+    <row r="228">
+      <c r="H228" s="9" t="n"/>
+      <c r="I228" s="9" t="n"/>
+      <c r="K228" s="9" t="n"/>
+    </row>
+    <row r="229">
+      <c r="H229" s="9" t="n"/>
+      <c r="I229" s="9" t="n"/>
+      <c r="K229" s="9" t="n"/>
+    </row>
+    <row r="230">
+      <c r="H230" s="9" t="n"/>
+      <c r="I230" s="9" t="n"/>
+      <c r="K230" s="9" t="n"/>
+    </row>
+    <row r="231">
+      <c r="H231" s="9" t="n"/>
+      <c r="I231" s="9" t="n"/>
+      <c r="K231" s="9" t="n"/>
+    </row>
+    <row r="232">
+      <c r="H232" s="9" t="n"/>
+      <c r="I232" s="9" t="n"/>
+      <c r="K232" s="9" t="n"/>
+    </row>
+    <row r="233">
+      <c r="H233" s="9" t="n"/>
+      <c r="I233" s="9" t="n"/>
+      <c r="K233" s="9" t="n"/>
+    </row>
+    <row r="234">
+      <c r="H234" s="9" t="n"/>
+      <c r="I234" s="9" t="n"/>
+      <c r="K234" s="9" t="n"/>
+    </row>
+    <row r="235">
+      <c r="H235" s="9" t="n"/>
+      <c r="I235" s="9" t="n"/>
+      <c r="K235" s="9" t="n"/>
+    </row>
+    <row r="236">
+      <c r="H236" s="9" t="n"/>
+      <c r="I236" s="9" t="n"/>
+      <c r="K236" s="9" t="n"/>
+    </row>
+    <row r="237">
+      <c r="H237" s="9" t="n"/>
+      <c r="I237" s="9" t="n"/>
+      <c r="K237" s="9" t="n"/>
+    </row>
+    <row r="238">
+      <c r="H238" s="9" t="n"/>
+      <c r="I238" s="9" t="n"/>
+      <c r="K238" s="9" t="n"/>
+    </row>
+    <row r="239">
+      <c r="H239" s="9" t="n"/>
+      <c r="I239" s="9" t="n"/>
+      <c r="K239" s="9" t="n"/>
+    </row>
+    <row r="240">
+      <c r="H240" s="9" t="n"/>
+      <c r="I240" s="9" t="n"/>
+      <c r="K240" s="9" t="n"/>
+    </row>
+    <row r="241">
+      <c r="H241" s="9" t="n"/>
+      <c r="I241" s="9" t="n"/>
+      <c r="K241" s="9" t="n"/>
+    </row>
+    <row r="242">
+      <c r="H242" s="9" t="n"/>
+      <c r="I242" s="9" t="n"/>
+      <c r="K242" s="9" t="n"/>
+    </row>
+    <row r="243">
+      <c r="H243" s="9" t="n"/>
+      <c r="I243" s="9" t="n"/>
+      <c r="K243" s="9" t="n"/>
+    </row>
+    <row r="244">
+      <c r="H244" s="9" t="n"/>
+      <c r="I244" s="9" t="n"/>
+      <c r="K244" s="9" t="n"/>
+    </row>
+    <row r="245">
+      <c r="H245" s="9" t="n"/>
+      <c r="I245" s="9" t="n"/>
+      <c r="K245" s="9" t="n"/>
+    </row>
+    <row r="246">
+      <c r="H246" s="9" t="n"/>
+      <c r="I246" s="9" t="n"/>
+      <c r="K246" s="9" t="n"/>
+    </row>
+    <row r="247">
+      <c r="H247" s="9" t="n"/>
+      <c r="I247" s="9" t="n"/>
+      <c r="K247" s="9" t="n"/>
+    </row>
+    <row r="248">
+      <c r="H248" s="9" t="n"/>
+      <c r="I248" s="9" t="n"/>
+      <c r="K248" s="9" t="n"/>
+    </row>
+    <row r="249">
+      <c r="H249" s="9" t="n"/>
+      <c r="I249" s="9" t="n"/>
+      <c r="K249" s="9" t="n"/>
+    </row>
+    <row r="250">
+      <c r="H250" s="9" t="n"/>
+      <c r="I250" s="9" t="n"/>
+      <c r="K250" s="9" t="n"/>
+    </row>
+    <row r="251">
+      <c r="H251" s="9" t="n"/>
+      <c r="I251" s="9" t="n"/>
+      <c r="K251" s="9" t="n"/>
+    </row>
+    <row r="252">
+      <c r="H252" s="9" t="n"/>
+      <c r="I252" s="9" t="n"/>
+      <c r="K252" s="9" t="n"/>
+    </row>
+    <row r="253">
+      <c r="H253" s="9" t="n"/>
+      <c r="I253" s="9" t="n"/>
+      <c r="K253" s="9" t="n"/>
+    </row>
+    <row r="254">
+      <c r="H254" s="9" t="n"/>
+      <c r="I254" s="9" t="n"/>
+      <c r="K254" s="9" t="n"/>
+    </row>
+    <row r="255">
+      <c r="H255" s="9" t="n"/>
+      <c r="I255" s="9" t="n"/>
+      <c r="K255" s="9" t="n"/>
+    </row>
+    <row r="256">
+      <c r="H256" s="9" t="n"/>
+      <c r="I256" s="9" t="n"/>
+      <c r="K256" s="9" t="n"/>
+    </row>
+    <row r="257">
+      <c r="H257" s="9" t="n"/>
+      <c r="I257" s="9" t="n"/>
+      <c r="K257" s="9" t="n"/>
+    </row>
+    <row r="258">
+      <c r="H258" s="9" t="n"/>
+      <c r="I258" s="9" t="n"/>
+      <c r="K258" s="9" t="n"/>
+    </row>
+    <row r="259">
+      <c r="H259" s="9" t="n"/>
+      <c r="I259" s="9" t="n"/>
+      <c r="K259" s="9" t="n"/>
+    </row>
+    <row r="260">
+      <c r="H260" s="9" t="n"/>
+      <c r="I260" s="9" t="n"/>
+      <c r="K260" s="9" t="n"/>
+    </row>
+    <row r="261">
+      <c r="H261" s="9" t="n"/>
+      <c r="I261" s="9" t="n"/>
+      <c r="K261" s="9" t="n"/>
+    </row>
+    <row r="262">
+      <c r="H262" s="9" t="n"/>
+      <c r="I262" s="9" t="n"/>
+      <c r="K262" s="9" t="n"/>
+    </row>
+    <row r="263">
+      <c r="H263" s="9" t="n"/>
+      <c r="I263" s="9" t="n"/>
+      <c r="K263" s="9" t="n"/>
+    </row>
+    <row r="264">
+      <c r="H264" s="9" t="n"/>
+      <c r="I264" s="9" t="n"/>
+      <c r="K264" s="9" t="n"/>
+    </row>
+    <row r="265">
+      <c r="H265" s="9" t="n"/>
+      <c r="I265" s="9" t="n"/>
+      <c r="K265" s="9" t="n"/>
+    </row>
+    <row r="266">
+      <c r="H266" s="9" t="n"/>
+      <c r="I266" s="9" t="n"/>
+      <c r="K266" s="9" t="n"/>
+    </row>
+    <row r="267">
+      <c r="H267" s="9" t="n"/>
+      <c r="I267" s="9" t="n"/>
+      <c r="K267" s="9" t="n"/>
+    </row>
+    <row r="268">
+      <c r="H268" s="9" t="n"/>
+      <c r="I268" s="9" t="n"/>
+      <c r="K268" s="9" t="n"/>
+    </row>
+    <row r="269">
+      <c r="H269" s="9" t="n"/>
+      <c r="I269" s="9" t="n"/>
+      <c r="K269" s="9" t="n"/>
+    </row>
+    <row r="270">
+      <c r="H270" s="9" t="n"/>
+      <c r="I270" s="9" t="n"/>
+      <c r="K270" s="9" t="n"/>
+    </row>
+    <row r="271">
+      <c r="H271" s="9" t="n"/>
+      <c r="I271" s="9" t="n"/>
+      <c r="K271" s="9" t="n"/>
+    </row>
+    <row r="272">
+      <c r="H272" s="9" t="n"/>
+      <c r="I272" s="9" t="n"/>
+      <c r="K272" s="9" t="n"/>
+    </row>
+    <row r="273">
+      <c r="H273" s="9" t="n"/>
+      <c r="I273" s="9" t="n"/>
+      <c r="K273" s="9" t="n"/>
+    </row>
+    <row r="274">
+      <c r="H274" s="9" t="n"/>
+      <c r="I274" s="9" t="n"/>
+      <c r="K274" s="9" t="n"/>
+    </row>
+    <row r="275">
+      <c r="H275" s="9" t="n"/>
+      <c r="I275" s="9" t="n"/>
+      <c r="K275" s="9" t="n"/>
+    </row>
+    <row r="276">
+      <c r="H276" s="9" t="n"/>
+      <c r="I276" s="9" t="n"/>
+      <c r="K276" s="9" t="n"/>
+    </row>
+    <row r="277">
+      <c r="H277" s="9" t="n"/>
+      <c r="I277" s="9" t="n"/>
+      <c r="K277" s="9" t="n"/>
+    </row>
+    <row r="278">
+      <c r="H278" s="9" t="n"/>
+      <c r="I278" s="9" t="n"/>
+      <c r="K278" s="9" t="n"/>
+    </row>
+    <row r="279">
+      <c r="H279" s="9" t="n"/>
+      <c r="I279" s="9" t="n"/>
+      <c r="K279" s="9" t="n"/>
+    </row>
+    <row r="280">
+      <c r="H280" s="9" t="n"/>
+      <c r="I280" s="9" t="n"/>
+      <c r="K280" s="9" t="n"/>
+    </row>
+    <row r="281">
+      <c r="H281" s="9" t="n"/>
+      <c r="I281" s="9" t="n"/>
+      <c r="K281" s="9" t="n"/>
+    </row>
+    <row r="282">
+      <c r="H282" s="9" t="n"/>
+      <c r="I282" s="9" t="n"/>
+      <c r="K282" s="9" t="n"/>
+    </row>
+    <row r="283">
+      <c r="H283" s="9" t="n"/>
+      <c r="I283" s="9" t="n"/>
+      <c r="K283" s="9" t="n"/>
+    </row>
+    <row r="284">
+      <c r="H284" s="9" t="n"/>
+      <c r="I284" s="9" t="n"/>
+      <c r="K284" s="9" t="n"/>
+    </row>
+    <row r="285">
+      <c r="H285" s="9" t="n"/>
+      <c r="I285" s="9" t="n"/>
+      <c r="K285" s="9" t="n"/>
+    </row>
+    <row r="286">
+      <c r="H286" s="9" t="n"/>
+      <c r="I286" s="9" t="n"/>
+      <c r="K286" s="9" t="n"/>
+    </row>
+    <row r="287">
+      <c r="H287" s="9" t="n"/>
+      <c r="I287" s="9" t="n"/>
+      <c r="K287" s="9" t="n"/>
+    </row>
+    <row r="288">
+      <c r="H288" s="9" t="n"/>
+      <c r="I288" s="9" t="n"/>
+      <c r="K288" s="9" t="n"/>
+    </row>
+    <row r="289">
+      <c r="H289" s="9" t="n"/>
+      <c r="I289" s="9" t="n"/>
+      <c r="K289" s="9" t="n"/>
+    </row>
+    <row r="290">
+      <c r="H290" s="9" t="n"/>
+      <c r="I290" s="9" t="n"/>
+      <c r="K290" s="9" t="n"/>
+    </row>
+    <row r="291">
+      <c r="H291" s="9" t="n"/>
+      <c r="I291" s="9" t="n"/>
+      <c r="K291" s="9" t="n"/>
+    </row>
+    <row r="292">
+      <c r="H292" s="9" t="n"/>
+      <c r="I292" s="9" t="n"/>
+      <c r="K292" s="9" t="n"/>
+    </row>
+    <row r="293">
+      <c r="H293" s="9" t="n"/>
+      <c r="I293" s="9" t="n"/>
+      <c r="K293" s="9" t="n"/>
+    </row>
+    <row r="294">
+      <c r="H294" s="9" t="n"/>
+      <c r="I294" s="9" t="n"/>
+      <c r="K294" s="9" t="n"/>
+    </row>
+    <row r="295">
+      <c r="H295" s="9" t="n"/>
+      <c r="I295" s="9" t="n"/>
+      <c r="K295" s="9" t="n"/>
+    </row>
+    <row r="296">
+      <c r="H296" s="9" t="n"/>
+      <c r="I296" s="9" t="n"/>
+      <c r="K296" s="9" t="n"/>
+    </row>
+    <row r="297">
+      <c r="H297" s="9" t="n"/>
+      <c r="I297" s="9" t="n"/>
+      <c r="K297" s="9" t="n"/>
+    </row>
+    <row r="298">
+      <c r="H298" s="9" t="n"/>
+      <c r="I298" s="9" t="n"/>
+      <c r="K298" s="9" t="n"/>
+    </row>
+    <row r="299">
+      <c r="H299" s="9" t="n"/>
+      <c r="I299" s="9" t="n"/>
+      <c r="K299" s="9" t="n"/>
+    </row>
+    <row r="300">
+      <c r="H300" s="9" t="n"/>
+      <c r="I300" s="9" t="n"/>
+      <c r="K300" s="9" t="n"/>
+    </row>
+    <row r="301">
+      <c r="H301" s="9" t="n"/>
+      <c r="I301" s="9" t="n"/>
+      <c r="K301" s="9" t="n"/>
+    </row>
+    <row r="302">
+      <c r="H302" s="9" t="n"/>
+      <c r="I302" s="9" t="n"/>
+      <c r="K302" s="9" t="n"/>
+    </row>
+    <row r="303">
+      <c r="H303" s="9" t="n"/>
+      <c r="I303" s="9" t="n"/>
+      <c r="K303" s="9" t="n"/>
+    </row>
+    <row r="304">
+      <c r="H304" s="9" t="n"/>
+      <c r="I304" s="9" t="n"/>
+      <c r="K304" s="9" t="n"/>
+    </row>
+    <row r="305">
+      <c r="H305" s="9" t="n"/>
+      <c r="I305" s="9" t="n"/>
+      <c r="K305" s="9" t="n"/>
+    </row>
+    <row r="306">
+      <c r="H306" s="9" t="n"/>
+      <c r="I306" s="9" t="n"/>
+      <c r="K306" s="9" t="n"/>
+    </row>
+    <row r="307">
+      <c r="H307" s="9" t="n"/>
+      <c r="I307" s="9" t="n"/>
+      <c r="K307" s="9" t="n"/>
+    </row>
+    <row r="308">
+      <c r="H308" s="9" t="n"/>
+      <c r="I308" s="9" t="n"/>
+      <c r="K308" s="9" t="n"/>
+    </row>
+    <row r="309">
+      <c r="H309" s="9" t="n"/>
+      <c r="I309" s="9" t="n"/>
+      <c r="K309" s="9" t="n"/>
+    </row>
+    <row r="310">
+      <c r="H310" s="9" t="n"/>
+      <c r="I310" s="9" t="n"/>
+      <c r="K310" s="9" t="n"/>
+    </row>
+    <row r="311">
+      <c r="H311" s="9" t="n"/>
+      <c r="I311" s="9" t="n"/>
+      <c r="K311" s="9" t="n"/>
+    </row>
+    <row r="312">
+      <c r="H312" s="9" t="n"/>
+      <c r="I312" s="9" t="n"/>
+      <c r="K312" s="9" t="n"/>
+    </row>
+    <row r="313">
+      <c r="H313" s="9" t="n"/>
+      <c r="I313" s="9" t="n"/>
+      <c r="K313" s="9" t="n"/>
+    </row>
+    <row r="314">
+      <c r="H314" s="9" t="n"/>
+      <c r="I314" s="9" t="n"/>
+      <c r="K314" s="9" t="n"/>
+    </row>
+    <row r="315">
+      <c r="H315" s="9" t="n"/>
+      <c r="I315" s="9" t="n"/>
+      <c r="K315" s="9" t="n"/>
+    </row>
+    <row r="316">
+      <c r="H316" s="9" t="n"/>
+      <c r="I316" s="9" t="n"/>
+      <c r="K316" s="9" t="n"/>
+    </row>
+    <row r="317">
+      <c r="H317" s="9" t="n"/>
+      <c r="I317" s="9" t="n"/>
+      <c r="K317" s="9" t="n"/>
+    </row>
+    <row r="318">
+      <c r="H318" s="9" t="n"/>
+      <c r="I318" s="9" t="n"/>
+      <c r="K318" s="9" t="n"/>
+    </row>
+    <row r="319">
+      <c r="H319" s="9" t="n"/>
+      <c r="I319" s="9" t="n"/>
+      <c r="K319" s="9" t="n"/>
+    </row>
+    <row r="320">
+      <c r="H320" s="9" t="n"/>
+      <c r="I320" s="9" t="n"/>
+      <c r="K320" s="9" t="n"/>
+    </row>
+    <row r="321">
+      <c r="H321" s="9" t="n"/>
+      <c r="I321" s="9" t="n"/>
+      <c r="K321" s="9" t="n"/>
+    </row>
+    <row r="322">
+      <c r="H322" s="9" t="n"/>
+      <c r="I322" s="9" t="n"/>
+      <c r="K322" s="9" t="n"/>
+    </row>
+    <row r="323">
+      <c r="H323" s="9" t="n"/>
+      <c r="I323" s="9" t="n"/>
+      <c r="K323" s="9" t="n"/>
+    </row>
+    <row r="324">
+      <c r="H324" s="9" t="n"/>
+      <c r="I324" s="9" t="n"/>
+      <c r="K324" s="9" t="n"/>
+    </row>
+    <row r="325">
+      <c r="H325" s="9" t="n"/>
+      <c r="I325" s="9" t="n"/>
+      <c r="K325" s="9" t="n"/>
+    </row>
+    <row r="326">
+      <c r="H326" s="9" t="n"/>
+      <c r="I326" s="9" t="n"/>
+      <c r="K326" s="9" t="n"/>
+    </row>
+    <row r="327">
+      <c r="H327" s="9" t="n"/>
+      <c r="I327" s="9" t="n"/>
+      <c r="K327" s="9" t="n"/>
+    </row>
+    <row r="328">
+      <c r="H328" s="9" t="n"/>
+      <c r="I328" s="9" t="n"/>
+      <c r="K328" s="9" t="n"/>
+    </row>
+    <row r="329">
+      <c r="H329" s="9" t="n"/>
+      <c r="I329" s="9" t="n"/>
+      <c r="K329" s="9" t="n"/>
+    </row>
+    <row r="330">
+      <c r="H330" s="9" t="n"/>
+      <c r="I330" s="9" t="n"/>
+      <c r="K330" s="9" t="n"/>
+    </row>
+    <row r="331">
+      <c r="H331" s="9" t="n"/>
+      <c r="I331" s="9" t="n"/>
+      <c r="K331" s="9" t="n"/>
+    </row>
+    <row r="332">
+      <c r="H332" s="9" t="n"/>
+      <c r="I332" s="9" t="n"/>
+      <c r="K332" s="9" t="n"/>
+    </row>
+    <row r="333">
+      <c r="H333" s="9" t="n"/>
+      <c r="I333" s="9" t="n"/>
+      <c r="K333" s="9" t="n"/>
+    </row>
+    <row r="334">
+      <c r="H334" s="9" t="n"/>
+      <c r="I334" s="9" t="n"/>
+      <c r="K334" s="9" t="n"/>
+    </row>
+    <row r="335">
+      <c r="H335" s="9" t="n"/>
+      <c r="I335" s="9" t="n"/>
+      <c r="K335" s="9" t="n"/>
+    </row>
+    <row r="336">
+      <c r="H336" s="9" t="n"/>
+      <c r="I336" s="9" t="n"/>
+      <c r="K336" s="9" t="n"/>
+    </row>
+    <row r="337">
+      <c r="H337" s="9" t="n"/>
+      <c r="I337" s="9" t="n"/>
+      <c r="K337" s="9" t="n"/>
+    </row>
+    <row r="338">
+      <c r="H338" s="9" t="n"/>
+      <c r="I338" s="9" t="n"/>
+      <c r="K338" s="9" t="n"/>
+    </row>
+    <row r="339">
+      <c r="H339" s="9" t="n"/>
+      <c r="I339" s="9" t="n"/>
+      <c r="K339" s="9" t="n"/>
+    </row>
+    <row r="340">
+      <c r="H340" s="9" t="n"/>
+      <c r="I340" s="9" t="n"/>
+      <c r="K340" s="9" t="n"/>
+    </row>
+    <row r="341">
+      <c r="H341" s="9" t="n"/>
+      <c r="I341" s="9" t="n"/>
+      <c r="K341" s="9" t="n"/>
+    </row>
+    <row r="342">
+      <c r="H342" s="9" t="n"/>
+      <c r="I342" s="9" t="n"/>
+      <c r="K342" s="9" t="n"/>
+    </row>
+    <row r="343">
+      <c r="H343" s="9" t="n"/>
+      <c r="I343" s="9" t="n"/>
+      <c r="K343" s="9" t="n"/>
+    </row>
+    <row r="344">
+      <c r="H344" s="9" t="n"/>
+      <c r="I344" s="9" t="n"/>
+      <c r="K344" s="9" t="n"/>
+    </row>
+    <row r="345">
+      <c r="H345" s="9" t="n"/>
+      <c r="I345" s="9" t="n"/>
+      <c r="K345" s="9" t="n"/>
+    </row>
+    <row r="346">
+      <c r="H346" s="9" t="n"/>
+      <c r="I346" s="9" t="n"/>
+      <c r="K346" s="9" t="n"/>
+    </row>
+    <row r="347">
+      <c r="H347" s="9" t="n"/>
+      <c r="I347" s="9" t="n"/>
+      <c r="K347" s="9" t="n"/>
+    </row>
+    <row r="348">
+      <c r="H348" s="9" t="n"/>
+      <c r="I348" s="9" t="n"/>
+      <c r="K348" s="9" t="n"/>
+    </row>
+    <row r="349">
+      <c r="H349" s="9" t="n"/>
+      <c r="I349" s="9" t="n"/>
+      <c r="K349" s="9" t="n"/>
+    </row>
+    <row r="350">
+      <c r="H350" s="9" t="n"/>
+      <c r="I350" s="9" t="n"/>
+      <c r="K350" s="9" t="n"/>
+    </row>
+    <row r="351">
+      <c r="H351" s="9" t="n"/>
+      <c r="I351" s="9" t="n"/>
+      <c r="K351" s="9" t="n"/>
+    </row>
+    <row r="352">
+      <c r="H352" s="9" t="n"/>
+      <c r="I352" s="9" t="n"/>
+      <c r="K352" s="9" t="n"/>
+    </row>
+    <row r="353">
+      <c r="H353" s="9" t="n"/>
+      <c r="I353" s="9" t="n"/>
+      <c r="K353" s="9" t="n"/>
+    </row>
+    <row r="354">
+      <c r="H354" s="9" t="n"/>
+      <c r="I354" s="9" t="n"/>
+      <c r="K354" s="9" t="n"/>
+    </row>
+    <row r="355">
+      <c r="H355" s="9" t="n"/>
+      <c r="I355" s="9" t="n"/>
+      <c r="K355" s="9" t="n"/>
+    </row>
+    <row r="356">
+      <c r="H356" s="9" t="n"/>
+      <c r="I356" s="9" t="n"/>
+      <c r="K356" s="9" t="n"/>
+    </row>
+    <row r="357">
+      <c r="H357" s="9" t="n"/>
+      <c r="I357" s="9" t="n"/>
+      <c r="K357" s="9" t="n"/>
+    </row>
+    <row r="358">
+      <c r="H358" s="9" t="n"/>
+      <c r="I358" s="9" t="n"/>
+      <c r="K358" s="9" t="n"/>
+    </row>
+    <row r="359">
+      <c r="H359" s="9" t="n"/>
+      <c r="I359" s="9" t="n"/>
+      <c r="K359" s="9" t="n"/>
+    </row>
+    <row r="360">
+      <c r="H360" s="9" t="n"/>
+      <c r="I360" s="9" t="n"/>
+      <c r="K360" s="9" t="n"/>
+    </row>
+    <row r="361">
+      <c r="H361" s="9" t="n"/>
+      <c r="I361" s="9" t="n"/>
+      <c r="K361" s="9" t="n"/>
+    </row>
+    <row r="362">
+      <c r="H362" s="9" t="n"/>
+      <c r="I362" s="9" t="n"/>
+      <c r="K362" s="9" t="n"/>
+    </row>
+    <row r="363">
+      <c r="H363" s="9" t="n"/>
+      <c r="I363" s="9" t="n"/>
+      <c r="K363" s="9" t="n"/>
+    </row>
+    <row r="364">
+      <c r="H364" s="9" t="n"/>
+      <c r="I364" s="9" t="n"/>
+      <c r="K364" s="9" t="n"/>
+    </row>
+    <row r="365">
+      <c r="H365" s="9" t="n"/>
+      <c r="I365" s="9" t="n"/>
+      <c r="K365" s="9" t="n"/>
+    </row>
+    <row r="366">
+      <c r="H366" s="9" t="n"/>
+      <c r="I366" s="9" t="n"/>
+      <c r="K366" s="9" t="n"/>
+    </row>
+    <row r="367">
+      <c r="H367" s="9" t="n"/>
+      <c r="I367" s="9" t="n"/>
+      <c r="K367" s="9" t="n"/>
+    </row>
+    <row r="368">
+      <c r="H368" s="9" t="n"/>
+      <c r="I368" s="9" t="n"/>
+      <c r="K368" s="9" t="n"/>
+    </row>
+    <row r="369">
+      <c r="H369" s="9" t="n"/>
+      <c r="I369" s="9" t="n"/>
+      <c r="K369" s="9" t="n"/>
+    </row>
+    <row r="370">
+      <c r="H370" s="9" t="n"/>
+      <c r="I370" s="9" t="n"/>
+      <c r="K370" s="9" t="n"/>
+    </row>
+    <row r="371">
+      <c r="H371" s="9" t="n"/>
+      <c r="I371" s="9" t="n"/>
+      <c r="K371" s="9" t="n"/>
+    </row>
+    <row r="372">
+      <c r="H372" s="9" t="n"/>
+      <c r="I372" s="9" t="n"/>
+      <c r="K372" s="9" t="n"/>
+    </row>
+    <row r="373">
+      <c r="H373" s="9" t="n"/>
+      <c r="I373" s="9" t="n"/>
+      <c r="K373" s="9" t="n"/>
+    </row>
+    <row r="374">
+      <c r="H374" s="9" t="n"/>
+      <c r="I374" s="9" t="n"/>
+      <c r="K374" s="9" t="n"/>
+    </row>
+    <row r="375">
+      <c r="H375" s="9" t="n"/>
+      <c r="I375" s="9" t="n"/>
+      <c r="K375" s="9" t="n"/>
+    </row>
+    <row r="376">
+      <c r="H376" s="9" t="n"/>
+      <c r="I376" s="9" t="n"/>
+      <c r="K376" s="9" t="n"/>
+    </row>
+    <row r="377">
+      <c r="H377" s="9" t="n"/>
+      <c r="I377" s="9" t="n"/>
+      <c r="K377" s="9" t="n"/>
+    </row>
+    <row r="378">
+      <c r="H378" s="9" t="n"/>
+      <c r="I378" s="9" t="n"/>
+      <c r="K378" s="9" t="n"/>
+    </row>
+    <row r="379">
+      <c r="H379" s="9" t="n"/>
+      <c r="I379" s="9" t="n"/>
+      <c r="K379" s="9" t="n"/>
+    </row>
+    <row r="380">
+      <c r="H380" s="9" t="n"/>
+      <c r="I380" s="9" t="n"/>
+      <c r="K380" s="9" t="n"/>
+    </row>
+    <row r="381">
+      <c r="H381" s="9" t="n"/>
+      <c r="I381" s="9" t="n"/>
+      <c r="K381" s="9" t="n"/>
+    </row>
+    <row r="382">
+      <c r="H382" s="9" t="n"/>
+      <c r="I382" s="9" t="n"/>
+      <c r="K382" s="9" t="n"/>
+    </row>
+    <row r="383">
+      <c r="H383" s="9" t="n"/>
+      <c r="I383" s="9" t="n"/>
+      <c r="K383" s="9" t="n"/>
+    </row>
+    <row r="384">
+      <c r="H384" s="9" t="n"/>
+      <c r="I384" s="9" t="n"/>
+      <c r="K384" s="9" t="n"/>
+    </row>
+    <row r="385">
+      <c r="H385" s="9" t="n"/>
+      <c r="I385" s="9" t="n"/>
+      <c r="K385" s="9" t="n"/>
+    </row>
+    <row r="386">
+      <c r="H386" s="9" t="n"/>
+      <c r="I386" s="9" t="n"/>
+      <c r="K386" s="9" t="n"/>
+    </row>
+    <row r="387">
+      <c r="H387" s="9" t="n"/>
+      <c r="I387" s="9" t="n"/>
+      <c r="K387" s="9" t="n"/>
+    </row>
+    <row r="388">
+      <c r="H388" s="9" t="n"/>
+      <c r="I388" s="9" t="n"/>
+      <c r="K388" s="9" t="n"/>
+    </row>
+    <row r="389">
+      <c r="H389" s="9" t="n"/>
+      <c r="I389" s="9" t="n"/>
+      <c r="K389" s="9" t="n"/>
+    </row>
+    <row r="390">
+      <c r="H390" s="9" t="n"/>
+      <c r="I390" s="9" t="n"/>
+      <c r="K390" s="9" t="n"/>
+    </row>
+    <row r="391">
+      <c r="H391" s="9" t="n"/>
+      <c r="I391" s="9" t="n"/>
+      <c r="K391" s="9" t="n"/>
+    </row>
+    <row r="392">
+      <c r="H392" s="9" t="n"/>
+      <c r="I392" s="9" t="n"/>
+      <c r="K392" s="9" t="n"/>
+    </row>
+    <row r="393">
+      <c r="H393" s="9" t="n"/>
+      <c r="I393" s="9" t="n"/>
+      <c r="K393" s="9" t="n"/>
+    </row>
+    <row r="394">
+      <c r="H394" s="9" t="n"/>
+      <c r="I394" s="9" t="n"/>
+      <c r="K394" s="9" t="n"/>
+    </row>
+    <row r="395">
+      <c r="H395" s="9" t="n"/>
+      <c r="I395" s="9" t="n"/>
+      <c r="K395" s="9" t="n"/>
+    </row>
+    <row r="396">
+      <c r="H396" s="9" t="n"/>
+      <c r="I396" s="9" t="n"/>
+      <c r="K396" s="9" t="n"/>
+    </row>
+    <row r="397">
+      <c r="H397" s="9" t="n"/>
+      <c r="I397" s="9" t="n"/>
+      <c r="K397" s="9" t="n"/>
+    </row>
+    <row r="398">
+      <c r="H398" s="9" t="n"/>
+      <c r="I398" s="9" t="n"/>
+      <c r="K398" s="9" t="n"/>
+    </row>
+    <row r="399">
+      <c r="H399" s="9" t="n"/>
+      <c r="I399" s="9" t="n"/>
+      <c r="K399" s="9" t="n"/>
+    </row>
+    <row r="400">
+      <c r="H400" s="9" t="n"/>
+      <c r="I400" s="9" t="n"/>
+      <c r="K400" s="9" t="n"/>
+    </row>
+    <row r="401">
+      <c r="H401" s="9" t="n"/>
+      <c r="I401" s="9" t="n"/>
+      <c r="K401" s="9" t="n"/>
+    </row>
+    <row r="402">
+      <c r="H402" s="9" t="n"/>
+      <c r="I402" s="9" t="n"/>
+      <c r="K402" s="9" t="n"/>
+    </row>
+    <row r="403">
+      <c r="H403" s="9" t="n"/>
+      <c r="I403" s="9" t="n"/>
+      <c r="K403" s="9" t="n"/>
+    </row>
+    <row r="404">
+      <c r="H404" s="9" t="n"/>
+      <c r="I404" s="9" t="n"/>
+      <c r="K404" s="9" t="n"/>
+    </row>
+    <row r="405">
+      <c r="H405" s="9" t="n"/>
+      <c r="I405" s="9" t="n"/>
+      <c r="K405" s="9" t="n"/>
+    </row>
+    <row r="406">
+      <c r="H406" s="9" t="n"/>
+      <c r="I406" s="9" t="n"/>
+      <c r="K406" s="9" t="n"/>
+    </row>
+    <row r="407">
+      <c r="H407" s="9" t="n"/>
+      <c r="I407" s="9" t="n"/>
+      <c r="K407" s="9" t="n"/>
+    </row>
+    <row r="408">
+      <c r="H408" s="9" t="n"/>
+      <c r="I408" s="9" t="n"/>
+      <c r="K408" s="9" t="n"/>
+    </row>
+    <row r="409">
+      <c r="H409" s="9" t="n"/>
+      <c r="I409" s="9" t="n"/>
+      <c r="K409" s="9" t="n"/>
+    </row>
+    <row r="410">
+      <c r="H410" s="9" t="n"/>
+      <c r="I410" s="9" t="n"/>
+      <c r="K410" s="9" t="n"/>
+    </row>
+    <row r="411">
+      <c r="H411" s="9" t="n"/>
+      <c r="I411" s="9" t="n"/>
+      <c r="K411" s="9" t="n"/>
+    </row>
+    <row r="412">
+      <c r="H412" s="9" t="n"/>
+      <c r="I412" s="9" t="n"/>
+      <c r="K412" s="9" t="n"/>
+    </row>
+    <row r="413">
+      <c r="H413" s="9" t="n"/>
+      <c r="I413" s="9" t="n"/>
+      <c r="K413" s="9" t="n"/>
+    </row>
+    <row r="414">
+      <c r="H414" s="9" t="n"/>
+      <c r="I414" s="9" t="n"/>
+      <c r="K414" s="9" t="n"/>
+    </row>
+    <row r="415">
+      <c r="H415" s="9" t="n"/>
+      <c r="I415" s="9" t="n"/>
+      <c r="K415" s="9" t="n"/>
+    </row>
+    <row r="416">
+      <c r="H416" s="9" t="n"/>
+      <c r="I416" s="9" t="n"/>
+      <c r="K416" s="9" t="n"/>
+    </row>
+    <row r="417">
+      <c r="H417" s="9" t="n"/>
+      <c r="I417" s="9" t="n"/>
+      <c r="K417" s="9" t="n"/>
+    </row>
+    <row r="418">
+      <c r="H418" s="9" t="n"/>
+      <c r="I418" s="9" t="n"/>
+      <c r="K418" s="9" t="n"/>
+    </row>
+    <row r="419">
+      <c r="H419" s="9" t="n"/>
+      <c r="I419" s="9" t="n"/>
+      <c r="K419" s="9" t="n"/>
+    </row>
+    <row r="420">
+      <c r="H420" s="9" t="n"/>
+      <c r="I420" s="9" t="n"/>
+      <c r="K420" s="9" t="n"/>
+    </row>
+    <row r="421">
+      <c r="H421" s="9" t="n"/>
+      <c r="I421" s="9" t="n"/>
+      <c r="K421" s="9" t="n"/>
+    </row>
+    <row r="422">
+      <c r="H422" s="9" t="n"/>
+      <c r="I422" s="9" t="n"/>
+      <c r="K422" s="9" t="n"/>
+    </row>
+    <row r="423">
+      <c r="H423" s="9" t="n"/>
+      <c r="I423" s="9" t="n"/>
+      <c r="K423" s="9" t="n"/>
+    </row>
+    <row r="424">
+      <c r="H424" s="9" t="n"/>
+      <c r="I424" s="9" t="n"/>
+      <c r="K424" s="9" t="n"/>
+    </row>
+    <row r="425">
+      <c r="H425" s="9" t="n"/>
+      <c r="I425" s="9" t="n"/>
+      <c r="K425" s="9" t="n"/>
+    </row>
+    <row r="426">
+      <c r="H426" s="9" t="n"/>
+      <c r="I426" s="9" t="n"/>
+      <c r="K426" s="9" t="n"/>
+    </row>
+    <row r="427">
+      <c r="H427" s="9" t="n"/>
+      <c r="I427" s="9" t="n"/>
+      <c r="K427" s="9" t="n"/>
+    </row>
+    <row r="428">
+      <c r="H428" s="9" t="n"/>
+      <c r="I428" s="9" t="n"/>
+      <c r="K428" s="9" t="n"/>
+    </row>
+    <row r="429">
+      <c r="H429" s="9" t="n"/>
+      <c r="I429" s="9" t="n"/>
+      <c r="K429" s="9" t="n"/>
+    </row>
+    <row r="430">
+      <c r="H430" s="9" t="n"/>
+      <c r="I430" s="9" t="n"/>
+      <c r="K430" s="9" t="n"/>
+    </row>
+    <row r="431">
+      <c r="H431" s="9" t="n"/>
+      <c r="I431" s="9" t="n"/>
+      <c r="K431" s="9" t="n"/>
+    </row>
+    <row r="432">
+      <c r="H432" s="9" t="n"/>
+      <c r="I432" s="9" t="n"/>
+      <c r="K432" s="9" t="n"/>
+    </row>
+    <row r="433">
+      <c r="H433" s="9" t="n"/>
+      <c r="I433" s="9" t="n"/>
+      <c r="K433" s="9" t="n"/>
+    </row>
+    <row r="434">
+      <c r="H434" s="9" t="n"/>
+      <c r="I434" s="9" t="n"/>
+      <c r="K434" s="9" t="n"/>
+    </row>
+    <row r="435">
+      <c r="H435" s="9" t="n"/>
+      <c r="I435" s="9" t="n"/>
+      <c r="K435" s="9" t="n"/>
+    </row>
+    <row r="436">
+      <c r="H436" s="9" t="n"/>
+      <c r="I436" s="9" t="n"/>
+      <c r="K436" s="9" t="n"/>
+    </row>
+    <row r="437">
+      <c r="H437" s="9" t="n"/>
+      <c r="I437" s="9" t="n"/>
+      <c r="K437" s="9" t="n"/>
+    </row>
+    <row r="438">
+      <c r="H438" s="9" t="n"/>
+      <c r="I438" s="9" t="n"/>
+      <c r="K438" s="9" t="n"/>
+    </row>
+    <row r="439">
+      <c r="H439" s="9" t="n"/>
+      <c r="I439" s="9" t="n"/>
+      <c r="K439" s="9" t="n"/>
+    </row>
+    <row r="440">
+      <c r="H440" s="9" t="n"/>
+      <c r="I440" s="9" t="n"/>
+      <c r="K440" s="9" t="n"/>
+    </row>
+    <row r="441">
+      <c r="H441" s="9" t="n"/>
+      <c r="I441" s="9" t="n"/>
+      <c r="K441" s="9" t="n"/>
+    </row>
+    <row r="442">
+      <c r="H442" s="9" t="n"/>
+      <c r="I442" s="9" t="n"/>
+      <c r="K442" s="9" t="n"/>
+    </row>
+    <row r="443">
+      <c r="H443" s="9" t="n"/>
+      <c r="I443" s="9" t="n"/>
+      <c r="K443" s="9" t="n"/>
+    </row>
+    <row r="444">
+      <c r="H444" s="9" t="n"/>
+      <c r="I444" s="9" t="n"/>
+      <c r="K444" s="9" t="n"/>
+    </row>
+    <row r="445">
+      <c r="H445" s="9" t="n"/>
+      <c r="I445" s="9" t="n"/>
+      <c r="K445" s="9" t="n"/>
+    </row>
+    <row r="446">
+      <c r="H446" s="9" t="n"/>
+      <c r="I446" s="9" t="n"/>
+      <c r="K446" s="9" t="n"/>
+    </row>
+    <row r="447">
+      <c r="H447" s="9" t="n"/>
+      <c r="I447" s="9" t="n"/>
+      <c r="K447" s="9" t="n"/>
+    </row>
+    <row r="448">
+      <c r="H448" s="9" t="n"/>
+      <c r="I448" s="9" t="n"/>
+      <c r="K448" s="9" t="n"/>
+    </row>
+    <row r="449">
+      <c r="H449" s="9" t="n"/>
+      <c r="I449" s="9" t="n"/>
+      <c r="K449" s="9" t="n"/>
+    </row>
+    <row r="450">
+      <c r="H450" s="9" t="n"/>
+      <c r="I450" s="9" t="n"/>
+      <c r="K450" s="9" t="n"/>
+    </row>
+    <row r="451">
+      <c r="H451" s="9" t="n"/>
+      <c r="I451" s="9" t="n"/>
+      <c r="K451" s="9" t="n"/>
+    </row>
+    <row r="452">
+      <c r="H452" s="9" t="n"/>
+      <c r="I452" s="9" t="n"/>
+      <c r="K452" s="9" t="n"/>
+    </row>
+    <row r="453">
+      <c r="H453" s="9" t="n"/>
+      <c r="I453" s="9" t="n"/>
+      <c r="K453" s="9" t="n"/>
+    </row>
+    <row r="454">
+      <c r="H454" s="9" t="n"/>
+      <c r="I454" s="9" t="n"/>
+      <c r="K454" s="9" t="n"/>
+    </row>
+    <row r="455">
+      <c r="H455" s="9" t="n"/>
+      <c r="I455" s="9" t="n"/>
+      <c r="K455" s="9" t="n"/>
+    </row>
+    <row r="456">
+      <c r="H456" s="9" t="n"/>
+      <c r="I456" s="9" t="n"/>
+      <c r="K456" s="9" t="n"/>
+    </row>
+    <row r="457">
+      <c r="H457" s="9" t="n"/>
+      <c r="I457" s="9" t="n"/>
+      <c r="K457" s="9" t="n"/>
+    </row>
+    <row r="458">
+      <c r="H458" s="9" t="n"/>
+      <c r="I458" s="9" t="n"/>
+      <c r="K458" s="9" t="n"/>
+    </row>
+    <row r="459">
+      <c r="H459" s="9" t="n"/>
+      <c r="I459" s="9" t="n"/>
+      <c r="K459" s="9" t="n"/>
+    </row>
+    <row r="460">
+      <c r="H460" s="9" t="n"/>
+      <c r="I460" s="9" t="n"/>
+      <c r="K460" s="9" t="n"/>
+    </row>
+    <row r="461">
+      <c r="H461" s="9" t="n"/>
+      <c r="I461" s="9" t="n"/>
+      <c r="K461" s="9" t="n"/>
+    </row>
+    <row r="462">
+      <c r="H462" s="9" t="n"/>
+      <c r="I462" s="9" t="n"/>
+      <c r="K462" s="9" t="n"/>
+    </row>
+    <row r="463">
+      <c r="H463" s="9" t="n"/>
+      <c r="I463" s="9" t="n"/>
+      <c r="K463" s="9" t="n"/>
+    </row>
+    <row r="464">
+      <c r="H464" s="9" t="n"/>
+      <c r="I464" s="9" t="n"/>
+      <c r="K464" s="9" t="n"/>
+    </row>
+    <row r="465">
+      <c r="H465" s="9" t="n"/>
+      <c r="I465" s="9" t="n"/>
+      <c r="K465" s="9" t="n"/>
+    </row>
+    <row r="466">
+      <c r="H466" s="9" t="n"/>
+      <c r="I466" s="9" t="n"/>
+      <c r="K466" s="9" t="n"/>
+    </row>
+    <row r="467">
+      <c r="H467" s="9" t="n"/>
+      <c r="I467" s="9" t="n"/>
+      <c r="K467" s="9" t="n"/>
+    </row>
+    <row r="468">
+      <c r="H468" s="9" t="n"/>
+      <c r="I468" s="9" t="n"/>
+      <c r="K468" s="9" t="n"/>
+    </row>
+    <row r="469">
+      <c r="H469" s="9" t="n"/>
+      <c r="I469" s="9" t="n"/>
+      <c r="K469" s="9" t="n"/>
+    </row>
+    <row r="470">
+      <c r="H470" s="9" t="n"/>
+      <c r="I470" s="9" t="n"/>
+      <c r="K470" s="9" t="n"/>
+    </row>
+    <row r="471">
+      <c r="H471" s="9" t="n"/>
+      <c r="I471" s="9" t="n"/>
+      <c r="K471" s="9" t="n"/>
+    </row>
+    <row r="472">
+      <c r="H472" s="9" t="n"/>
+      <c r="I472" s="9" t="n"/>
+      <c r="K472" s="9" t="n"/>
+    </row>
+    <row r="473">
+      <c r="H473" s="9" t="n"/>
+      <c r="I473" s="9" t="n"/>
+      <c r="K473" s="9" t="n"/>
+    </row>
+    <row r="474">
+      <c r="H474" s="9" t="n"/>
+      <c r="I474" s="9" t="n"/>
+      <c r="K474" s="9" t="n"/>
+    </row>
+    <row r="475">
+      <c r="H475" s="9" t="n"/>
+      <c r="I475" s="9" t="n"/>
+      <c r="K475" s="9" t="n"/>
+    </row>
+    <row r="476">
+      <c r="H476" s="9" t="n"/>
+      <c r="I476" s="9" t="n"/>
+      <c r="K476" s="9" t="n"/>
+    </row>
+    <row r="477">
+      <c r="H477" s="9" t="n"/>
+      <c r="I477" s="9" t="n"/>
+      <c r="K477" s="9" t="n"/>
+    </row>
+    <row r="478">
+      <c r="H478" s="9" t="n"/>
+      <c r="I478" s="9" t="n"/>
+      <c r="K478" s="9" t="n"/>
+    </row>
+    <row r="479">
+      <c r="H479" s="9" t="n"/>
+      <c r="I479" s="9" t="n"/>
+      <c r="K479" s="9" t="n"/>
+    </row>
+    <row r="480">
+      <c r="H480" s="9" t="n"/>
+      <c r="I480" s="9" t="n"/>
+      <c r="K480" s="9" t="n"/>
+    </row>
+    <row r="481">
+      <c r="H481" s="9" t="n"/>
+      <c r="I481" s="9" t="n"/>
+      <c r="K481" s="9" t="n"/>
+    </row>
+    <row r="482">
+      <c r="H482" s="9" t="n"/>
+      <c r="I482" s="9" t="n"/>
+      <c r="K482" s="9" t="n"/>
+    </row>
+    <row r="483">
+      <c r="H483" s="9" t="n"/>
+      <c r="I483" s="9" t="n"/>
+      <c r="K483" s="9" t="n"/>
+    </row>
+    <row r="484">
+      <c r="H484" s="9" t="n"/>
+      <c r="I484" s="9" t="n"/>
+      <c r="K484" s="9" t="n"/>
+    </row>
+    <row r="485">
+      <c r="H485" s="9" t="n"/>
+      <c r="I485" s="9" t="n"/>
+      <c r="K485" s="9" t="n"/>
+    </row>
+    <row r="486">
+      <c r="H486" s="9" t="n"/>
+      <c r="I486" s="9" t="n"/>
+      <c r="K486" s="9" t="n"/>
+    </row>
+    <row r="487">
+      <c r="H487" s="9" t="n"/>
+      <c r="I487" s="9" t="n"/>
+      <c r="K487" s="9" t="n"/>
+    </row>
+    <row r="488">
+      <c r="H488" s="9" t="n"/>
+      <c r="I488" s="9" t="n"/>
+      <c r="K488" s="9" t="n"/>
+    </row>
+    <row r="489">
+      <c r="H489" s="9" t="n"/>
+      <c r="I489" s="9" t="n"/>
+      <c r="K489" s="9" t="n"/>
+    </row>
+    <row r="490">
+      <c r="H490" s="9" t="n"/>
+      <c r="I490" s="9" t="n"/>
+      <c r="K490" s="9" t="n"/>
+    </row>
+    <row r="491">
+      <c r="H491" s="9" t="n"/>
+      <c r="I491" s="9" t="n"/>
+      <c r="K491" s="9" t="n"/>
+    </row>
+    <row r="492">
+      <c r="H492" s="9" t="n"/>
+      <c r="I492" s="9" t="n"/>
+      <c r="K492" s="9" t="n"/>
+    </row>
+    <row r="493">
+      <c r="H493" s="9" t="n"/>
+      <c r="I493" s="9" t="n"/>
+      <c r="K493" s="9" t="n"/>
+    </row>
+    <row r="494">
+      <c r="H494" s="9" t="n"/>
+      <c r="I494" s="9" t="n"/>
+      <c r="K494" s="9" t="n"/>
+    </row>
+    <row r="495">
+      <c r="H495" s="9" t="n"/>
+      <c r="I495" s="9" t="n"/>
+      <c r="K495" s="9" t="n"/>
+    </row>
+    <row r="496">
+      <c r="H496" s="9" t="n"/>
+      <c r="I496" s="9" t="n"/>
+      <c r="K496" s="9" t="n"/>
+    </row>
+    <row r="497">
+      <c r="H497" s="9" t="n"/>
+      <c r="I497" s="9" t="n"/>
+      <c r="K497" s="9" t="n"/>
+    </row>
+    <row r="498">
+      <c r="H498" s="9" t="n"/>
+      <c r="I498" s="9" t="n"/>
+      <c r="K498" s="9" t="n"/>
+    </row>
+    <row r="499">
+      <c r="H499" s="9" t="n"/>
+      <c r="I499" s="9" t="n"/>
+      <c r="K499" s="9" t="n"/>
+    </row>
+    <row r="500">
+      <c r="H500" s="9" t="n"/>
+      <c r="I500" s="9" t="n"/>
+      <c r="K500" s="9" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:K21"/>
@@ -1533,7 +3928,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="6" t="inlineStr">
+      <c r="A2" s="8" t="inlineStr">
         <is>
           <t>Q001</t>
         </is>
@@ -1548,10 +3943,10 @@
           <t>homework는 셀 수 있는 명사라서 homeworks라고 쓸 수 있다.</t>
         </is>
       </c>
-      <c r="D2" s="6" t="n"/>
-      <c r="E2" s="6" t="n"/>
-      <c r="F2" s="6" t="n"/>
-      <c r="G2" s="6" t="n"/>
+      <c r="D2" s="8" t="n"/>
+      <c r="E2" s="8" t="n"/>
+      <c r="F2" s="8" t="n"/>
+      <c r="G2" s="8" t="n"/>
       <c r="H2" s="8" t="inlineStr">
         <is>
           <t>X</t>
@@ -1567,11 +3962,11 @@
       <c r="L2" s="7" t="n"/>
       <c r="M2" s="7" t="n"/>
       <c r="N2" s="6" t="n"/>
-      <c r="O2" s="6" t="n"/>
+      <c r="O2" s="8" t="n"/>
       <c r="P2" s="6" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="6" t="inlineStr">
+      <c r="A3" s="8" t="inlineStr">
         <is>
           <t>Q002</t>
         </is>
@@ -1586,22 +3981,22 @@
           <t>빈칸에 알맞은 것은? My sister ___ me her bike yesterday.</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D3" s="8" t="inlineStr">
         <is>
           <t>lent</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E3" s="8" t="inlineStr">
         <is>
           <t>borrowed</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F3" s="8" t="inlineStr">
         <is>
           <t>bought</t>
         </is>
       </c>
-      <c r="G3" s="6" t="inlineStr">
+      <c r="G3" s="8" t="inlineStr">
         <is>
           <t>brought</t>
         </is>
@@ -1633,1499 +4028,4481 @@
         </is>
       </c>
       <c r="N3" s="6" t="n"/>
-      <c r="O3" s="6" t="n"/>
+      <c r="O3" s="8" t="n"/>
       <c r="P3" s="6" t="n"/>
     </row>
     <row r="4">
+      <c r="A4" s="9" t="n"/>
+      <c r="D4" s="9" t="n"/>
+      <c r="E4" s="9" t="n"/>
+      <c r="F4" s="9" t="n"/>
+      <c r="G4" s="9" t="n"/>
       <c r="H4" s="9" t="n"/>
+      <c r="O4" s="9" t="n"/>
     </row>
     <row r="5">
+      <c r="A5" s="9" t="n"/>
+      <c r="D5" s="9" t="n"/>
+      <c r="E5" s="9" t="n"/>
+      <c r="F5" s="9" t="n"/>
+      <c r="G5" s="9" t="n"/>
       <c r="H5" s="9" t="n"/>
+      <c r="O5" s="9" t="n"/>
     </row>
     <row r="6">
+      <c r="A6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="9" t="n"/>
+      <c r="F6" s="9" t="n"/>
+      <c r="G6" s="9" t="n"/>
       <c r="H6" s="9" t="n"/>
+      <c r="O6" s="9" t="n"/>
     </row>
     <row r="7">
+      <c r="A7" s="9" t="n"/>
+      <c r="D7" s="9" t="n"/>
+      <c r="E7" s="9" t="n"/>
+      <c r="F7" s="9" t="n"/>
+      <c r="G7" s="9" t="n"/>
       <c r="H7" s="9" t="n"/>
+      <c r="O7" s="9" t="n"/>
     </row>
     <row r="8">
+      <c r="A8" s="9" t="n"/>
+      <c r="D8" s="9" t="n"/>
+      <c r="E8" s="9" t="n"/>
+      <c r="F8" s="9" t="n"/>
+      <c r="G8" s="9" t="n"/>
       <c r="H8" s="9" t="n"/>
+      <c r="O8" s="9" t="n"/>
     </row>
     <row r="9">
+      <c r="A9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="n"/>
+      <c r="G9" s="9" t="n"/>
       <c r="H9" s="9" t="n"/>
+      <c r="O9" s="9" t="n"/>
     </row>
     <row r="10">
+      <c r="A10" s="9" t="n"/>
+      <c r="D10" s="9" t="n"/>
+      <c r="E10" s="9" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
       <c r="H10" s="9" t="n"/>
+      <c r="O10" s="9" t="n"/>
     </row>
     <row r="11">
+      <c r="A11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="n"/>
+      <c r="G11" s="9" t="n"/>
       <c r="H11" s="9" t="n"/>
+      <c r="O11" s="9" t="n"/>
     </row>
     <row r="12">
+      <c r="A12" s="9" t="n"/>
+      <c r="D12" s="9" t="n"/>
+      <c r="E12" s="9" t="n"/>
+      <c r="F12" s="9" t="n"/>
+      <c r="G12" s="9" t="n"/>
       <c r="H12" s="9" t="n"/>
+      <c r="O12" s="9" t="n"/>
     </row>
     <row r="13">
+      <c r="A13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
       <c r="H13" s="9" t="n"/>
+      <c r="O13" s="9" t="n"/>
     </row>
     <row r="14">
+      <c r="A14" s="9" t="n"/>
+      <c r="D14" s="9" t="n"/>
+      <c r="E14" s="9" t="n"/>
+      <c r="F14" s="9" t="n"/>
+      <c r="G14" s="9" t="n"/>
       <c r="H14" s="9" t="n"/>
+      <c r="O14" s="9" t="n"/>
     </row>
     <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="n"/>
+      <c r="G15" s="9" t="n"/>
       <c r="H15" s="9" t="n"/>
+      <c r="O15" s="9" t="n"/>
     </row>
     <row r="16">
+      <c r="A16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="9" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
       <c r="H16" s="9" t="n"/>
+      <c r="O16" s="9" t="n"/>
     </row>
     <row r="17">
+      <c r="A17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+      <c r="E17" s="9" t="n"/>
+      <c r="F17" s="9" t="n"/>
+      <c r="G17" s="9" t="n"/>
       <c r="H17" s="9" t="n"/>
+      <c r="O17" s="9" t="n"/>
     </row>
     <row r="18">
+      <c r="A18" s="9" t="n"/>
+      <c r="D18" s="9" t="n"/>
+      <c r="E18" s="9" t="n"/>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="9" t="n"/>
       <c r="H18" s="9" t="n"/>
+      <c r="O18" s="9" t="n"/>
     </row>
     <row r="19">
+      <c r="A19" s="9" t="n"/>
+      <c r="D19" s="9" t="n"/>
+      <c r="E19" s="9" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
       <c r="H19" s="9" t="n"/>
+      <c r="O19" s="9" t="n"/>
     </row>
     <row r="20">
+      <c r="A20" s="9" t="n"/>
+      <c r="D20" s="9" t="n"/>
+      <c r="E20" s="9" t="n"/>
+      <c r="F20" s="9" t="n"/>
+      <c r="G20" s="9" t="n"/>
       <c r="H20" s="9" t="n"/>
+      <c r="O20" s="9" t="n"/>
     </row>
     <row r="21">
+      <c r="A21" s="9" t="n"/>
+      <c r="D21" s="9" t="n"/>
+      <c r="E21" s="9" t="n"/>
+      <c r="F21" s="9" t="n"/>
+      <c r="G21" s="9" t="n"/>
       <c r="H21" s="9" t="n"/>
+      <c r="O21" s="9" t="n"/>
     </row>
     <row r="22">
+      <c r="A22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
+      <c r="E22" s="9" t="n"/>
+      <c r="F22" s="9" t="n"/>
+      <c r="G22" s="9" t="n"/>
       <c r="H22" s="9" t="n"/>
+      <c r="O22" s="9" t="n"/>
     </row>
     <row r="23">
+      <c r="A23" s="9" t="n"/>
+      <c r="D23" s="9" t="n"/>
+      <c r="E23" s="9" t="n"/>
+      <c r="F23" s="9" t="n"/>
+      <c r="G23" s="9" t="n"/>
       <c r="H23" s="9" t="n"/>
+      <c r="O23" s="9" t="n"/>
     </row>
     <row r="24">
+      <c r="A24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
+      <c r="E24" s="9" t="n"/>
+      <c r="F24" s="9" t="n"/>
+      <c r="G24" s="9" t="n"/>
       <c r="H24" s="9" t="n"/>
+      <c r="O24" s="9" t="n"/>
     </row>
     <row r="25">
+      <c r="A25" s="9" t="n"/>
+      <c r="D25" s="9" t="n"/>
+      <c r="E25" s="9" t="n"/>
+      <c r="F25" s="9" t="n"/>
+      <c r="G25" s="9" t="n"/>
       <c r="H25" s="9" t="n"/>
+      <c r="O25" s="9" t="n"/>
     </row>
     <row r="26">
+      <c r="A26" s="9" t="n"/>
+      <c r="D26" s="9" t="n"/>
+      <c r="E26" s="9" t="n"/>
+      <c r="F26" s="9" t="n"/>
+      <c r="G26" s="9" t="n"/>
       <c r="H26" s="9" t="n"/>
+      <c r="O26" s="9" t="n"/>
     </row>
     <row r="27">
+      <c r="A27" s="9" t="n"/>
+      <c r="D27" s="9" t="n"/>
+      <c r="E27" s="9" t="n"/>
+      <c r="F27" s="9" t="n"/>
+      <c r="G27" s="9" t="n"/>
       <c r="H27" s="9" t="n"/>
+      <c r="O27" s="9" t="n"/>
     </row>
     <row r="28">
+      <c r="A28" s="9" t="n"/>
+      <c r="D28" s="9" t="n"/>
+      <c r="E28" s="9" t="n"/>
+      <c r="F28" s="9" t="n"/>
+      <c r="G28" s="9" t="n"/>
       <c r="H28" s="9" t="n"/>
+      <c r="O28" s="9" t="n"/>
     </row>
     <row r="29">
+      <c r="A29" s="9" t="n"/>
+      <c r="D29" s="9" t="n"/>
+      <c r="E29" s="9" t="n"/>
+      <c r="F29" s="9" t="n"/>
+      <c r="G29" s="9" t="n"/>
       <c r="H29" s="9" t="n"/>
+      <c r="O29" s="9" t="n"/>
     </row>
     <row r="30">
+      <c r="A30" s="9" t="n"/>
+      <c r="D30" s="9" t="n"/>
+      <c r="E30" s="9" t="n"/>
+      <c r="F30" s="9" t="n"/>
+      <c r="G30" s="9" t="n"/>
       <c r="H30" s="9" t="n"/>
+      <c r="O30" s="9" t="n"/>
     </row>
     <row r="31">
+      <c r="A31" s="9" t="n"/>
+      <c r="D31" s="9" t="n"/>
+      <c r="E31" s="9" t="n"/>
+      <c r="F31" s="9" t="n"/>
+      <c r="G31" s="9" t="n"/>
       <c r="H31" s="9" t="n"/>
+      <c r="O31" s="9" t="n"/>
     </row>
     <row r="32">
+      <c r="A32" s="9" t="n"/>
+      <c r="D32" s="9" t="n"/>
+      <c r="E32" s="9" t="n"/>
+      <c r="F32" s="9" t="n"/>
+      <c r="G32" s="9" t="n"/>
       <c r="H32" s="9" t="n"/>
+      <c r="O32" s="9" t="n"/>
     </row>
     <row r="33">
+      <c r="A33" s="9" t="n"/>
+      <c r="D33" s="9" t="n"/>
+      <c r="E33" s="9" t="n"/>
+      <c r="F33" s="9" t="n"/>
+      <c r="G33" s="9" t="n"/>
       <c r="H33" s="9" t="n"/>
+      <c r="O33" s="9" t="n"/>
     </row>
     <row r="34">
+      <c r="A34" s="9" t="n"/>
+      <c r="D34" s="9" t="n"/>
+      <c r="E34" s="9" t="n"/>
+      <c r="F34" s="9" t="n"/>
+      <c r="G34" s="9" t="n"/>
       <c r="H34" s="9" t="n"/>
+      <c r="O34" s="9" t="n"/>
     </row>
     <row r="35">
+      <c r="A35" s="9" t="n"/>
+      <c r="D35" s="9" t="n"/>
+      <c r="E35" s="9" t="n"/>
+      <c r="F35" s="9" t="n"/>
+      <c r="G35" s="9" t="n"/>
       <c r="H35" s="9" t="n"/>
+      <c r="O35" s="9" t="n"/>
     </row>
     <row r="36">
+      <c r="A36" s="9" t="n"/>
+      <c r="D36" s="9" t="n"/>
+      <c r="E36" s="9" t="n"/>
+      <c r="F36" s="9" t="n"/>
+      <c r="G36" s="9" t="n"/>
       <c r="H36" s="9" t="n"/>
+      <c r="O36" s="9" t="n"/>
     </row>
     <row r="37">
+      <c r="A37" s="9" t="n"/>
+      <c r="D37" s="9" t="n"/>
+      <c r="E37" s="9" t="n"/>
+      <c r="F37" s="9" t="n"/>
+      <c r="G37" s="9" t="n"/>
       <c r="H37" s="9" t="n"/>
+      <c r="O37" s="9" t="n"/>
     </row>
     <row r="38">
+      <c r="A38" s="9" t="n"/>
+      <c r="D38" s="9" t="n"/>
+      <c r="E38" s="9" t="n"/>
+      <c r="F38" s="9" t="n"/>
+      <c r="G38" s="9" t="n"/>
       <c r="H38" s="9" t="n"/>
+      <c r="O38" s="9" t="n"/>
     </row>
     <row r="39">
+      <c r="A39" s="9" t="n"/>
+      <c r="D39" s="9" t="n"/>
+      <c r="E39" s="9" t="n"/>
+      <c r="F39" s="9" t="n"/>
+      <c r="G39" s="9" t="n"/>
       <c r="H39" s="9" t="n"/>
+      <c r="O39" s="9" t="n"/>
     </row>
     <row r="40">
+      <c r="A40" s="9" t="n"/>
+      <c r="D40" s="9" t="n"/>
+      <c r="E40" s="9" t="n"/>
+      <c r="F40" s="9" t="n"/>
+      <c r="G40" s="9" t="n"/>
       <c r="H40" s="9" t="n"/>
+      <c r="O40" s="9" t="n"/>
     </row>
     <row r="41">
+      <c r="A41" s="9" t="n"/>
+      <c r="D41" s="9" t="n"/>
+      <c r="E41" s="9" t="n"/>
+      <c r="F41" s="9" t="n"/>
+      <c r="G41" s="9" t="n"/>
       <c r="H41" s="9" t="n"/>
+      <c r="O41" s="9" t="n"/>
     </row>
     <row r="42">
+      <c r="A42" s="9" t="n"/>
+      <c r="D42" s="9" t="n"/>
+      <c r="E42" s="9" t="n"/>
+      <c r="F42" s="9" t="n"/>
+      <c r="G42" s="9" t="n"/>
       <c r="H42" s="9" t="n"/>
+      <c r="O42" s="9" t="n"/>
     </row>
     <row r="43">
+      <c r="A43" s="9" t="n"/>
+      <c r="D43" s="9" t="n"/>
+      <c r="E43" s="9" t="n"/>
+      <c r="F43" s="9" t="n"/>
+      <c r="G43" s="9" t="n"/>
       <c r="H43" s="9" t="n"/>
+      <c r="O43" s="9" t="n"/>
     </row>
     <row r="44">
+      <c r="A44" s="9" t="n"/>
+      <c r="D44" s="9" t="n"/>
+      <c r="E44" s="9" t="n"/>
+      <c r="F44" s="9" t="n"/>
+      <c r="G44" s="9" t="n"/>
       <c r="H44" s="9" t="n"/>
+      <c r="O44" s="9" t="n"/>
     </row>
     <row r="45">
+      <c r="A45" s="9" t="n"/>
+      <c r="D45" s="9" t="n"/>
+      <c r="E45" s="9" t="n"/>
+      <c r="F45" s="9" t="n"/>
+      <c r="G45" s="9" t="n"/>
       <c r="H45" s="9" t="n"/>
+      <c r="O45" s="9" t="n"/>
     </row>
     <row r="46">
+      <c r="A46" s="9" t="n"/>
+      <c r="D46" s="9" t="n"/>
+      <c r="E46" s="9" t="n"/>
+      <c r="F46" s="9" t="n"/>
+      <c r="G46" s="9" t="n"/>
       <c r="H46" s="9" t="n"/>
+      <c r="O46" s="9" t="n"/>
     </row>
     <row r="47">
+      <c r="A47" s="9" t="n"/>
+      <c r="D47" s="9" t="n"/>
+      <c r="E47" s="9" t="n"/>
+      <c r="F47" s="9" t="n"/>
+      <c r="G47" s="9" t="n"/>
       <c r="H47" s="9" t="n"/>
+      <c r="O47" s="9" t="n"/>
     </row>
     <row r="48">
+      <c r="A48" s="9" t="n"/>
+      <c r="D48" s="9" t="n"/>
+      <c r="E48" s="9" t="n"/>
+      <c r="F48" s="9" t="n"/>
+      <c r="G48" s="9" t="n"/>
       <c r="H48" s="9" t="n"/>
+      <c r="O48" s="9" t="n"/>
     </row>
     <row r="49">
+      <c r="A49" s="9" t="n"/>
+      <c r="D49" s="9" t="n"/>
+      <c r="E49" s="9" t="n"/>
+      <c r="F49" s="9" t="n"/>
+      <c r="G49" s="9" t="n"/>
       <c r="H49" s="9" t="n"/>
+      <c r="O49" s="9" t="n"/>
     </row>
     <row r="50">
+      <c r="A50" s="9" t="n"/>
+      <c r="D50" s="9" t="n"/>
+      <c r="E50" s="9" t="n"/>
+      <c r="F50" s="9" t="n"/>
+      <c r="G50" s="9" t="n"/>
       <c r="H50" s="9" t="n"/>
+      <c r="O50" s="9" t="n"/>
     </row>
     <row r="51">
+      <c r="A51" s="9" t="n"/>
+      <c r="D51" s="9" t="n"/>
+      <c r="E51" s="9" t="n"/>
+      <c r="F51" s="9" t="n"/>
+      <c r="G51" s="9" t="n"/>
       <c r="H51" s="9" t="n"/>
+      <c r="O51" s="9" t="n"/>
     </row>
     <row r="52">
+      <c r="A52" s="9" t="n"/>
+      <c r="D52" s="9" t="n"/>
+      <c r="E52" s="9" t="n"/>
+      <c r="F52" s="9" t="n"/>
+      <c r="G52" s="9" t="n"/>
       <c r="H52" s="9" t="n"/>
+      <c r="O52" s="9" t="n"/>
     </row>
     <row r="53">
+      <c r="A53" s="9" t="n"/>
+      <c r="D53" s="9" t="n"/>
+      <c r="E53" s="9" t="n"/>
+      <c r="F53" s="9" t="n"/>
+      <c r="G53" s="9" t="n"/>
       <c r="H53" s="9" t="n"/>
+      <c r="O53" s="9" t="n"/>
     </row>
     <row r="54">
+      <c r="A54" s="9" t="n"/>
+      <c r="D54" s="9" t="n"/>
+      <c r="E54" s="9" t="n"/>
+      <c r="F54" s="9" t="n"/>
+      <c r="G54" s="9" t="n"/>
       <c r="H54" s="9" t="n"/>
+      <c r="O54" s="9" t="n"/>
     </row>
     <row r="55">
+      <c r="A55" s="9" t="n"/>
+      <c r="D55" s="9" t="n"/>
+      <c r="E55" s="9" t="n"/>
+      <c r="F55" s="9" t="n"/>
+      <c r="G55" s="9" t="n"/>
       <c r="H55" s="9" t="n"/>
+      <c r="O55" s="9" t="n"/>
     </row>
     <row r="56">
+      <c r="A56" s="9" t="n"/>
+      <c r="D56" s="9" t="n"/>
+      <c r="E56" s="9" t="n"/>
+      <c r="F56" s="9" t="n"/>
+      <c r="G56" s="9" t="n"/>
       <c r="H56" s="9" t="n"/>
+      <c r="O56" s="9" t="n"/>
     </row>
     <row r="57">
+      <c r="A57" s="9" t="n"/>
+      <c r="D57" s="9" t="n"/>
+      <c r="E57" s="9" t="n"/>
+      <c r="F57" s="9" t="n"/>
+      <c r="G57" s="9" t="n"/>
       <c r="H57" s="9" t="n"/>
+      <c r="O57" s="9" t="n"/>
     </row>
     <row r="58">
+      <c r="A58" s="9" t="n"/>
+      <c r="D58" s="9" t="n"/>
+      <c r="E58" s="9" t="n"/>
+      <c r="F58" s="9" t="n"/>
+      <c r="G58" s="9" t="n"/>
       <c r="H58" s="9" t="n"/>
+      <c r="O58" s="9" t="n"/>
     </row>
     <row r="59">
+      <c r="A59" s="9" t="n"/>
+      <c r="D59" s="9" t="n"/>
+      <c r="E59" s="9" t="n"/>
+      <c r="F59" s="9" t="n"/>
+      <c r="G59" s="9" t="n"/>
       <c r="H59" s="9" t="n"/>
+      <c r="O59" s="9" t="n"/>
     </row>
     <row r="60">
+      <c r="A60" s="9" t="n"/>
+      <c r="D60" s="9" t="n"/>
+      <c r="E60" s="9" t="n"/>
+      <c r="F60" s="9" t="n"/>
+      <c r="G60" s="9" t="n"/>
       <c r="H60" s="9" t="n"/>
+      <c r="O60" s="9" t="n"/>
     </row>
     <row r="61">
+      <c r="A61" s="9" t="n"/>
+      <c r="D61" s="9" t="n"/>
+      <c r="E61" s="9" t="n"/>
+      <c r="F61" s="9" t="n"/>
+      <c r="G61" s="9" t="n"/>
       <c r="H61" s="9" t="n"/>
+      <c r="O61" s="9" t="n"/>
     </row>
     <row r="62">
+      <c r="A62" s="9" t="n"/>
+      <c r="D62" s="9" t="n"/>
+      <c r="E62" s="9" t="n"/>
+      <c r="F62" s="9" t="n"/>
+      <c r="G62" s="9" t="n"/>
       <c r="H62" s="9" t="n"/>
+      <c r="O62" s="9" t="n"/>
     </row>
     <row r="63">
+      <c r="A63" s="9" t="n"/>
+      <c r="D63" s="9" t="n"/>
+      <c r="E63" s="9" t="n"/>
+      <c r="F63" s="9" t="n"/>
+      <c r="G63" s="9" t="n"/>
       <c r="H63" s="9" t="n"/>
+      <c r="O63" s="9" t="n"/>
     </row>
     <row r="64">
+      <c r="A64" s="9" t="n"/>
+      <c r="D64" s="9" t="n"/>
+      <c r="E64" s="9" t="n"/>
+      <c r="F64" s="9" t="n"/>
+      <c r="G64" s="9" t="n"/>
       <c r="H64" s="9" t="n"/>
+      <c r="O64" s="9" t="n"/>
     </row>
     <row r="65">
+      <c r="A65" s="9" t="n"/>
+      <c r="D65" s="9" t="n"/>
+      <c r="E65" s="9" t="n"/>
+      <c r="F65" s="9" t="n"/>
+      <c r="G65" s="9" t="n"/>
       <c r="H65" s="9" t="n"/>
+      <c r="O65" s="9" t="n"/>
     </row>
     <row r="66">
+      <c r="A66" s="9" t="n"/>
+      <c r="D66" s="9" t="n"/>
+      <c r="E66" s="9" t="n"/>
+      <c r="F66" s="9" t="n"/>
+      <c r="G66" s="9" t="n"/>
       <c r="H66" s="9" t="n"/>
+      <c r="O66" s="9" t="n"/>
     </row>
     <row r="67">
+      <c r="A67" s="9" t="n"/>
+      <c r="D67" s="9" t="n"/>
+      <c r="E67" s="9" t="n"/>
+      <c r="F67" s="9" t="n"/>
+      <c r="G67" s="9" t="n"/>
       <c r="H67" s="9" t="n"/>
+      <c r="O67" s="9" t="n"/>
     </row>
     <row r="68">
+      <c r="A68" s="9" t="n"/>
+      <c r="D68" s="9" t="n"/>
+      <c r="E68" s="9" t="n"/>
+      <c r="F68" s="9" t="n"/>
+      <c r="G68" s="9" t="n"/>
       <c r="H68" s="9" t="n"/>
+      <c r="O68" s="9" t="n"/>
     </row>
     <row r="69">
+      <c r="A69" s="9" t="n"/>
+      <c r="D69" s="9" t="n"/>
+      <c r="E69" s="9" t="n"/>
+      <c r="F69" s="9" t="n"/>
+      <c r="G69" s="9" t="n"/>
       <c r="H69" s="9" t="n"/>
+      <c r="O69" s="9" t="n"/>
     </row>
     <row r="70">
+      <c r="A70" s="9" t="n"/>
+      <c r="D70" s="9" t="n"/>
+      <c r="E70" s="9" t="n"/>
+      <c r="F70" s="9" t="n"/>
+      <c r="G70" s="9" t="n"/>
       <c r="H70" s="9" t="n"/>
+      <c r="O70" s="9" t="n"/>
     </row>
     <row r="71">
+      <c r="A71" s="9" t="n"/>
+      <c r="D71" s="9" t="n"/>
+      <c r="E71" s="9" t="n"/>
+      <c r="F71" s="9" t="n"/>
+      <c r="G71" s="9" t="n"/>
       <c r="H71" s="9" t="n"/>
+      <c r="O71" s="9" t="n"/>
     </row>
     <row r="72">
+      <c r="A72" s="9" t="n"/>
+      <c r="D72" s="9" t="n"/>
+      <c r="E72" s="9" t="n"/>
+      <c r="F72" s="9" t="n"/>
+      <c r="G72" s="9" t="n"/>
       <c r="H72" s="9" t="n"/>
+      <c r="O72" s="9" t="n"/>
     </row>
     <row r="73">
+      <c r="A73" s="9" t="n"/>
+      <c r="D73" s="9" t="n"/>
+      <c r="E73" s="9" t="n"/>
+      <c r="F73" s="9" t="n"/>
+      <c r="G73" s="9" t="n"/>
       <c r="H73" s="9" t="n"/>
+      <c r="O73" s="9" t="n"/>
     </row>
     <row r="74">
+      <c r="A74" s="9" t="n"/>
+      <c r="D74" s="9" t="n"/>
+      <c r="E74" s="9" t="n"/>
+      <c r="F74" s="9" t="n"/>
+      <c r="G74" s="9" t="n"/>
       <c r="H74" s="9" t="n"/>
+      <c r="O74" s="9" t="n"/>
     </row>
     <row r="75">
+      <c r="A75" s="9" t="n"/>
+      <c r="D75" s="9" t="n"/>
+      <c r="E75" s="9" t="n"/>
+      <c r="F75" s="9" t="n"/>
+      <c r="G75" s="9" t="n"/>
       <c r="H75" s="9" t="n"/>
+      <c r="O75" s="9" t="n"/>
     </row>
     <row r="76">
+      <c r="A76" s="9" t="n"/>
+      <c r="D76" s="9" t="n"/>
+      <c r="E76" s="9" t="n"/>
+      <c r="F76" s="9" t="n"/>
+      <c r="G76" s="9" t="n"/>
       <c r="H76" s="9" t="n"/>
+      <c r="O76" s="9" t="n"/>
     </row>
     <row r="77">
+      <c r="A77" s="9" t="n"/>
+      <c r="D77" s="9" t="n"/>
+      <c r="E77" s="9" t="n"/>
+      <c r="F77" s="9" t="n"/>
+      <c r="G77" s="9" t="n"/>
       <c r="H77" s="9" t="n"/>
+      <c r="O77" s="9" t="n"/>
     </row>
     <row r="78">
+      <c r="A78" s="9" t="n"/>
+      <c r="D78" s="9" t="n"/>
+      <c r="E78" s="9" t="n"/>
+      <c r="F78" s="9" t="n"/>
+      <c r="G78" s="9" t="n"/>
       <c r="H78" s="9" t="n"/>
+      <c r="O78" s="9" t="n"/>
     </row>
     <row r="79">
+      <c r="A79" s="9" t="n"/>
+      <c r="D79" s="9" t="n"/>
+      <c r="E79" s="9" t="n"/>
+      <c r="F79" s="9" t="n"/>
+      <c r="G79" s="9" t="n"/>
       <c r="H79" s="9" t="n"/>
+      <c r="O79" s="9" t="n"/>
     </row>
     <row r="80">
+      <c r="A80" s="9" t="n"/>
+      <c r="D80" s="9" t="n"/>
+      <c r="E80" s="9" t="n"/>
+      <c r="F80" s="9" t="n"/>
+      <c r="G80" s="9" t="n"/>
       <c r="H80" s="9" t="n"/>
+      <c r="O80" s="9" t="n"/>
     </row>
     <row r="81">
+      <c r="A81" s="9" t="n"/>
+      <c r="D81" s="9" t="n"/>
+      <c r="E81" s="9" t="n"/>
+      <c r="F81" s="9" t="n"/>
+      <c r="G81" s="9" t="n"/>
       <c r="H81" s="9" t="n"/>
+      <c r="O81" s="9" t="n"/>
     </row>
     <row r="82">
+      <c r="A82" s="9" t="n"/>
+      <c r="D82" s="9" t="n"/>
+      <c r="E82" s="9" t="n"/>
+      <c r="F82" s="9" t="n"/>
+      <c r="G82" s="9" t="n"/>
       <c r="H82" s="9" t="n"/>
+      <c r="O82" s="9" t="n"/>
     </row>
     <row r="83">
+      <c r="A83" s="9" t="n"/>
+      <c r="D83" s="9" t="n"/>
+      <c r="E83" s="9" t="n"/>
+      <c r="F83" s="9" t="n"/>
+      <c r="G83" s="9" t="n"/>
       <c r="H83" s="9" t="n"/>
+      <c r="O83" s="9" t="n"/>
     </row>
     <row r="84">
+      <c r="A84" s="9" t="n"/>
+      <c r="D84" s="9" t="n"/>
+      <c r="E84" s="9" t="n"/>
+      <c r="F84" s="9" t="n"/>
+      <c r="G84" s="9" t="n"/>
       <c r="H84" s="9" t="n"/>
+      <c r="O84" s="9" t="n"/>
     </row>
     <row r="85">
+      <c r="A85" s="9" t="n"/>
+      <c r="D85" s="9" t="n"/>
+      <c r="E85" s="9" t="n"/>
+      <c r="F85" s="9" t="n"/>
+      <c r="G85" s="9" t="n"/>
       <c r="H85" s="9" t="n"/>
+      <c r="O85" s="9" t="n"/>
     </row>
     <row r="86">
+      <c r="A86" s="9" t="n"/>
+      <c r="D86" s="9" t="n"/>
+      <c r="E86" s="9" t="n"/>
+      <c r="F86" s="9" t="n"/>
+      <c r="G86" s="9" t="n"/>
       <c r="H86" s="9" t="n"/>
+      <c r="O86" s="9" t="n"/>
     </row>
     <row r="87">
+      <c r="A87" s="9" t="n"/>
+      <c r="D87" s="9" t="n"/>
+      <c r="E87" s="9" t="n"/>
+      <c r="F87" s="9" t="n"/>
+      <c r="G87" s="9" t="n"/>
       <c r="H87" s="9" t="n"/>
+      <c r="O87" s="9" t="n"/>
     </row>
     <row r="88">
+      <c r="A88" s="9" t="n"/>
+      <c r="D88" s="9" t="n"/>
+      <c r="E88" s="9" t="n"/>
+      <c r="F88" s="9" t="n"/>
+      <c r="G88" s="9" t="n"/>
       <c r="H88" s="9" t="n"/>
+      <c r="O88" s="9" t="n"/>
     </row>
     <row r="89">
+      <c r="A89" s="9" t="n"/>
+      <c r="D89" s="9" t="n"/>
+      <c r="E89" s="9" t="n"/>
+      <c r="F89" s="9" t="n"/>
+      <c r="G89" s="9" t="n"/>
       <c r="H89" s="9" t="n"/>
+      <c r="O89" s="9" t="n"/>
     </row>
     <row r="90">
+      <c r="A90" s="9" t="n"/>
+      <c r="D90" s="9" t="n"/>
+      <c r="E90" s="9" t="n"/>
+      <c r="F90" s="9" t="n"/>
+      <c r="G90" s="9" t="n"/>
       <c r="H90" s="9" t="n"/>
+      <c r="O90" s="9" t="n"/>
     </row>
     <row r="91">
+      <c r="A91" s="9" t="n"/>
+      <c r="D91" s="9" t="n"/>
+      <c r="E91" s="9" t="n"/>
+      <c r="F91" s="9" t="n"/>
+      <c r="G91" s="9" t="n"/>
       <c r="H91" s="9" t="n"/>
+      <c r="O91" s="9" t="n"/>
     </row>
     <row r="92">
+      <c r="A92" s="9" t="n"/>
+      <c r="D92" s="9" t="n"/>
+      <c r="E92" s="9" t="n"/>
+      <c r="F92" s="9" t="n"/>
+      <c r="G92" s="9" t="n"/>
       <c r="H92" s="9" t="n"/>
+      <c r="O92" s="9" t="n"/>
     </row>
     <row r="93">
+      <c r="A93" s="9" t="n"/>
+      <c r="D93" s="9" t="n"/>
+      <c r="E93" s="9" t="n"/>
+      <c r="F93" s="9" t="n"/>
+      <c r="G93" s="9" t="n"/>
       <c r="H93" s="9" t="n"/>
+      <c r="O93" s="9" t="n"/>
     </row>
     <row r="94">
+      <c r="A94" s="9" t="n"/>
+      <c r="D94" s="9" t="n"/>
+      <c r="E94" s="9" t="n"/>
+      <c r="F94" s="9" t="n"/>
+      <c r="G94" s="9" t="n"/>
       <c r="H94" s="9" t="n"/>
+      <c r="O94" s="9" t="n"/>
     </row>
     <row r="95">
+      <c r="A95" s="9" t="n"/>
+      <c r="D95" s="9" t="n"/>
+      <c r="E95" s="9" t="n"/>
+      <c r="F95" s="9" t="n"/>
+      <c r="G95" s="9" t="n"/>
       <c r="H95" s="9" t="n"/>
+      <c r="O95" s="9" t="n"/>
     </row>
     <row r="96">
+      <c r="A96" s="9" t="n"/>
+      <c r="D96" s="9" t="n"/>
+      <c r="E96" s="9" t="n"/>
+      <c r="F96" s="9" t="n"/>
+      <c r="G96" s="9" t="n"/>
       <c r="H96" s="9" t="n"/>
+      <c r="O96" s="9" t="n"/>
     </row>
     <row r="97">
+      <c r="A97" s="9" t="n"/>
+      <c r="D97" s="9" t="n"/>
+      <c r="E97" s="9" t="n"/>
+      <c r="F97" s="9" t="n"/>
+      <c r="G97" s="9" t="n"/>
       <c r="H97" s="9" t="n"/>
+      <c r="O97" s="9" t="n"/>
     </row>
     <row r="98">
+      <c r="A98" s="9" t="n"/>
+      <c r="D98" s="9" t="n"/>
+      <c r="E98" s="9" t="n"/>
+      <c r="F98" s="9" t="n"/>
+      <c r="G98" s="9" t="n"/>
       <c r="H98" s="9" t="n"/>
+      <c r="O98" s="9" t="n"/>
     </row>
     <row r="99">
+      <c r="A99" s="9" t="n"/>
+      <c r="D99" s="9" t="n"/>
+      <c r="E99" s="9" t="n"/>
+      <c r="F99" s="9" t="n"/>
+      <c r="G99" s="9" t="n"/>
       <c r="H99" s="9" t="n"/>
+      <c r="O99" s="9" t="n"/>
     </row>
     <row r="100">
+      <c r="A100" s="9" t="n"/>
+      <c r="D100" s="9" t="n"/>
+      <c r="E100" s="9" t="n"/>
+      <c r="F100" s="9" t="n"/>
+      <c r="G100" s="9" t="n"/>
       <c r="H100" s="9" t="n"/>
+      <c r="O100" s="9" t="n"/>
     </row>
     <row r="101">
+      <c r="A101" s="9" t="n"/>
+      <c r="D101" s="9" t="n"/>
+      <c r="E101" s="9" t="n"/>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="9" t="n"/>
       <c r="H101" s="9" t="n"/>
+      <c r="O101" s="9" t="n"/>
     </row>
     <row r="102">
+      <c r="A102" s="9" t="n"/>
+      <c r="D102" s="9" t="n"/>
+      <c r="E102" s="9" t="n"/>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="9" t="n"/>
       <c r="H102" s="9" t="n"/>
+      <c r="O102" s="9" t="n"/>
     </row>
     <row r="103">
+      <c r="A103" s="9" t="n"/>
+      <c r="D103" s="9" t="n"/>
+      <c r="E103" s="9" t="n"/>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="9" t="n"/>
       <c r="H103" s="9" t="n"/>
+      <c r="O103" s="9" t="n"/>
     </row>
     <row r="104">
+      <c r="A104" s="9" t="n"/>
+      <c r="D104" s="9" t="n"/>
+      <c r="E104" s="9" t="n"/>
+      <c r="F104" s="9" t="n"/>
+      <c r="G104" s="9" t="n"/>
       <c r="H104" s="9" t="n"/>
+      <c r="O104" s="9" t="n"/>
     </row>
     <row r="105">
+      <c r="A105" s="9" t="n"/>
+      <c r="D105" s="9" t="n"/>
+      <c r="E105" s="9" t="n"/>
+      <c r="F105" s="9" t="n"/>
+      <c r="G105" s="9" t="n"/>
       <c r="H105" s="9" t="n"/>
+      <c r="O105" s="9" t="n"/>
     </row>
     <row r="106">
+      <c r="A106" s="9" t="n"/>
+      <c r="D106" s="9" t="n"/>
+      <c r="E106" s="9" t="n"/>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="9" t="n"/>
       <c r="H106" s="9" t="n"/>
+      <c r="O106" s="9" t="n"/>
     </row>
     <row r="107">
+      <c r="A107" s="9" t="n"/>
+      <c r="D107" s="9" t="n"/>
+      <c r="E107" s="9" t="n"/>
+      <c r="F107" s="9" t="n"/>
+      <c r="G107" s="9" t="n"/>
       <c r="H107" s="9" t="n"/>
+      <c r="O107" s="9" t="n"/>
     </row>
     <row r="108">
+      <c r="A108" s="9" t="n"/>
+      <c r="D108" s="9" t="n"/>
+      <c r="E108" s="9" t="n"/>
+      <c r="F108" s="9" t="n"/>
+      <c r="G108" s="9" t="n"/>
       <c r="H108" s="9" t="n"/>
+      <c r="O108" s="9" t="n"/>
     </row>
     <row r="109">
+      <c r="A109" s="9" t="n"/>
+      <c r="D109" s="9" t="n"/>
+      <c r="E109" s="9" t="n"/>
+      <c r="F109" s="9" t="n"/>
+      <c r="G109" s="9" t="n"/>
       <c r="H109" s="9" t="n"/>
+      <c r="O109" s="9" t="n"/>
     </row>
     <row r="110">
+      <c r="A110" s="9" t="n"/>
+      <c r="D110" s="9" t="n"/>
+      <c r="E110" s="9" t="n"/>
+      <c r="F110" s="9" t="n"/>
+      <c r="G110" s="9" t="n"/>
       <c r="H110" s="9" t="n"/>
+      <c r="O110" s="9" t="n"/>
     </row>
     <row r="111">
+      <c r="A111" s="9" t="n"/>
+      <c r="D111" s="9" t="n"/>
+      <c r="E111" s="9" t="n"/>
+      <c r="F111" s="9" t="n"/>
+      <c r="G111" s="9" t="n"/>
       <c r="H111" s="9" t="n"/>
+      <c r="O111" s="9" t="n"/>
     </row>
     <row r="112">
+      <c r="A112" s="9" t="n"/>
+      <c r="D112" s="9" t="n"/>
+      <c r="E112" s="9" t="n"/>
+      <c r="F112" s="9" t="n"/>
+      <c r="G112" s="9" t="n"/>
       <c r="H112" s="9" t="n"/>
+      <c r="O112" s="9" t="n"/>
     </row>
     <row r="113">
+      <c r="A113" s="9" t="n"/>
+      <c r="D113" s="9" t="n"/>
+      <c r="E113" s="9" t="n"/>
+      <c r="F113" s="9" t="n"/>
+      <c r="G113" s="9" t="n"/>
       <c r="H113" s="9" t="n"/>
+      <c r="O113" s="9" t="n"/>
     </row>
     <row r="114">
+      <c r="A114" s="9" t="n"/>
+      <c r="D114" s="9" t="n"/>
+      <c r="E114" s="9" t="n"/>
+      <c r="F114" s="9" t="n"/>
+      <c r="G114" s="9" t="n"/>
       <c r="H114" s="9" t="n"/>
+      <c r="O114" s="9" t="n"/>
     </row>
     <row r="115">
+      <c r="A115" s="9" t="n"/>
+      <c r="D115" s="9" t="n"/>
+      <c r="E115" s="9" t="n"/>
+      <c r="F115" s="9" t="n"/>
+      <c r="G115" s="9" t="n"/>
       <c r="H115" s="9" t="n"/>
+      <c r="O115" s="9" t="n"/>
     </row>
     <row r="116">
+      <c r="A116" s="9" t="n"/>
+      <c r="D116" s="9" t="n"/>
+      <c r="E116" s="9" t="n"/>
+      <c r="F116" s="9" t="n"/>
+      <c r="G116" s="9" t="n"/>
       <c r="H116" s="9" t="n"/>
+      <c r="O116" s="9" t="n"/>
     </row>
     <row r="117">
+      <c r="A117" s="9" t="n"/>
+      <c r="D117" s="9" t="n"/>
+      <c r="E117" s="9" t="n"/>
+      <c r="F117" s="9" t="n"/>
+      <c r="G117" s="9" t="n"/>
       <c r="H117" s="9" t="n"/>
+      <c r="O117" s="9" t="n"/>
     </row>
     <row r="118">
+      <c r="A118" s="9" t="n"/>
+      <c r="D118" s="9" t="n"/>
+      <c r="E118" s="9" t="n"/>
+      <c r="F118" s="9" t="n"/>
+      <c r="G118" s="9" t="n"/>
       <c r="H118" s="9" t="n"/>
+      <c r="O118" s="9" t="n"/>
     </row>
     <row r="119">
+      <c r="A119" s="9" t="n"/>
+      <c r="D119" s="9" t="n"/>
+      <c r="E119" s="9" t="n"/>
+      <c r="F119" s="9" t="n"/>
+      <c r="G119" s="9" t="n"/>
       <c r="H119" s="9" t="n"/>
+      <c r="O119" s="9" t="n"/>
     </row>
     <row r="120">
+      <c r="A120" s="9" t="n"/>
+      <c r="D120" s="9" t="n"/>
+      <c r="E120" s="9" t="n"/>
+      <c r="F120" s="9" t="n"/>
+      <c r="G120" s="9" t="n"/>
       <c r="H120" s="9" t="n"/>
+      <c r="O120" s="9" t="n"/>
     </row>
     <row r="121">
+      <c r="A121" s="9" t="n"/>
+      <c r="D121" s="9" t="n"/>
+      <c r="E121" s="9" t="n"/>
+      <c r="F121" s="9" t="n"/>
+      <c r="G121" s="9" t="n"/>
       <c r="H121" s="9" t="n"/>
+      <c r="O121" s="9" t="n"/>
     </row>
     <row r="122">
+      <c r="A122" s="9" t="n"/>
+      <c r="D122" s="9" t="n"/>
+      <c r="E122" s="9" t="n"/>
+      <c r="F122" s="9" t="n"/>
+      <c r="G122" s="9" t="n"/>
       <c r="H122" s="9" t="n"/>
+      <c r="O122" s="9" t="n"/>
     </row>
     <row r="123">
+      <c r="A123" s="9" t="n"/>
+      <c r="D123" s="9" t="n"/>
+      <c r="E123" s="9" t="n"/>
+      <c r="F123" s="9" t="n"/>
+      <c r="G123" s="9" t="n"/>
       <c r="H123" s="9" t="n"/>
+      <c r="O123" s="9" t="n"/>
     </row>
     <row r="124">
+      <c r="A124" s="9" t="n"/>
+      <c r="D124" s="9" t="n"/>
+      <c r="E124" s="9" t="n"/>
+      <c r="F124" s="9" t="n"/>
+      <c r="G124" s="9" t="n"/>
       <c r="H124" s="9" t="n"/>
+      <c r="O124" s="9" t="n"/>
     </row>
     <row r="125">
+      <c r="A125" s="9" t="n"/>
+      <c r="D125" s="9" t="n"/>
+      <c r="E125" s="9" t="n"/>
+      <c r="F125" s="9" t="n"/>
+      <c r="G125" s="9" t="n"/>
       <c r="H125" s="9" t="n"/>
+      <c r="O125" s="9" t="n"/>
     </row>
     <row r="126">
+      <c r="A126" s="9" t="n"/>
+      <c r="D126" s="9" t="n"/>
+      <c r="E126" s="9" t="n"/>
+      <c r="F126" s="9" t="n"/>
+      <c r="G126" s="9" t="n"/>
       <c r="H126" s="9" t="n"/>
+      <c r="O126" s="9" t="n"/>
     </row>
     <row r="127">
+      <c r="A127" s="9" t="n"/>
+      <c r="D127" s="9" t="n"/>
+      <c r="E127" s="9" t="n"/>
+      <c r="F127" s="9" t="n"/>
+      <c r="G127" s="9" t="n"/>
       <c r="H127" s="9" t="n"/>
+      <c r="O127" s="9" t="n"/>
     </row>
     <row r="128">
+      <c r="A128" s="9" t="n"/>
+      <c r="D128" s="9" t="n"/>
+      <c r="E128" s="9" t="n"/>
+      <c r="F128" s="9" t="n"/>
+      <c r="G128" s="9" t="n"/>
       <c r="H128" s="9" t="n"/>
+      <c r="O128" s="9" t="n"/>
     </row>
     <row r="129">
+      <c r="A129" s="9" t="n"/>
+      <c r="D129" s="9" t="n"/>
+      <c r="E129" s="9" t="n"/>
+      <c r="F129" s="9" t="n"/>
+      <c r="G129" s="9" t="n"/>
       <c r="H129" s="9" t="n"/>
+      <c r="O129" s="9" t="n"/>
     </row>
     <row r="130">
+      <c r="A130" s="9" t="n"/>
+      <c r="D130" s="9" t="n"/>
+      <c r="E130" s="9" t="n"/>
+      <c r="F130" s="9" t="n"/>
+      <c r="G130" s="9" t="n"/>
       <c r="H130" s="9" t="n"/>
+      <c r="O130" s="9" t="n"/>
     </row>
     <row r="131">
+      <c r="A131" s="9" t="n"/>
+      <c r="D131" s="9" t="n"/>
+      <c r="E131" s="9" t="n"/>
+      <c r="F131" s="9" t="n"/>
+      <c r="G131" s="9" t="n"/>
       <c r="H131" s="9" t="n"/>
+      <c r="O131" s="9" t="n"/>
     </row>
     <row r="132">
+      <c r="A132" s="9" t="n"/>
+      <c r="D132" s="9" t="n"/>
+      <c r="E132" s="9" t="n"/>
+      <c r="F132" s="9" t="n"/>
+      <c r="G132" s="9" t="n"/>
       <c r="H132" s="9" t="n"/>
+      <c r="O132" s="9" t="n"/>
     </row>
     <row r="133">
+      <c r="A133" s="9" t="n"/>
+      <c r="D133" s="9" t="n"/>
+      <c r="E133" s="9" t="n"/>
+      <c r="F133" s="9" t="n"/>
+      <c r="G133" s="9" t="n"/>
       <c r="H133" s="9" t="n"/>
+      <c r="O133" s="9" t="n"/>
     </row>
     <row r="134">
+      <c r="A134" s="9" t="n"/>
+      <c r="D134" s="9" t="n"/>
+      <c r="E134" s="9" t="n"/>
+      <c r="F134" s="9" t="n"/>
+      <c r="G134" s="9" t="n"/>
       <c r="H134" s="9" t="n"/>
+      <c r="O134" s="9" t="n"/>
     </row>
     <row r="135">
+      <c r="A135" s="9" t="n"/>
+      <c r="D135" s="9" t="n"/>
+      <c r="E135" s="9" t="n"/>
+      <c r="F135" s="9" t="n"/>
+      <c r="G135" s="9" t="n"/>
       <c r="H135" s="9" t="n"/>
+      <c r="O135" s="9" t="n"/>
     </row>
     <row r="136">
+      <c r="A136" s="9" t="n"/>
+      <c r="D136" s="9" t="n"/>
+      <c r="E136" s="9" t="n"/>
+      <c r="F136" s="9" t="n"/>
+      <c r="G136" s="9" t="n"/>
       <c r="H136" s="9" t="n"/>
+      <c r="O136" s="9" t="n"/>
     </row>
     <row r="137">
+      <c r="A137" s="9" t="n"/>
+      <c r="D137" s="9" t="n"/>
+      <c r="E137" s="9" t="n"/>
+      <c r="F137" s="9" t="n"/>
+      <c r="G137" s="9" t="n"/>
       <c r="H137" s="9" t="n"/>
+      <c r="O137" s="9" t="n"/>
     </row>
     <row r="138">
+      <c r="A138" s="9" t="n"/>
+      <c r="D138" s="9" t="n"/>
+      <c r="E138" s="9" t="n"/>
+      <c r="F138" s="9" t="n"/>
+      <c r="G138" s="9" t="n"/>
       <c r="H138" s="9" t="n"/>
+      <c r="O138" s="9" t="n"/>
     </row>
     <row r="139">
+      <c r="A139" s="9" t="n"/>
+      <c r="D139" s="9" t="n"/>
+      <c r="E139" s="9" t="n"/>
+      <c r="F139" s="9" t="n"/>
+      <c r="G139" s="9" t="n"/>
       <c r="H139" s="9" t="n"/>
+      <c r="O139" s="9" t="n"/>
     </row>
     <row r="140">
+      <c r="A140" s="9" t="n"/>
+      <c r="D140" s="9" t="n"/>
+      <c r="E140" s="9" t="n"/>
+      <c r="F140" s="9" t="n"/>
+      <c r="G140" s="9" t="n"/>
       <c r="H140" s="9" t="n"/>
+      <c r="O140" s="9" t="n"/>
     </row>
     <row r="141">
+      <c r="A141" s="9" t="n"/>
+      <c r="D141" s="9" t="n"/>
+      <c r="E141" s="9" t="n"/>
+      <c r="F141" s="9" t="n"/>
+      <c r="G141" s="9" t="n"/>
       <c r="H141" s="9" t="n"/>
+      <c r="O141" s="9" t="n"/>
     </row>
     <row r="142">
+      <c r="A142" s="9" t="n"/>
+      <c r="D142" s="9" t="n"/>
+      <c r="E142" s="9" t="n"/>
+      <c r="F142" s="9" t="n"/>
+      <c r="G142" s="9" t="n"/>
       <c r="H142" s="9" t="n"/>
+      <c r="O142" s="9" t="n"/>
     </row>
     <row r="143">
+      <c r="A143" s="9" t="n"/>
+      <c r="D143" s="9" t="n"/>
+      <c r="E143" s="9" t="n"/>
+      <c r="F143" s="9" t="n"/>
+      <c r="G143" s="9" t="n"/>
       <c r="H143" s="9" t="n"/>
+      <c r="O143" s="9" t="n"/>
     </row>
     <row r="144">
+      <c r="A144" s="9" t="n"/>
+      <c r="D144" s="9" t="n"/>
+      <c r="E144" s="9" t="n"/>
+      <c r="F144" s="9" t="n"/>
+      <c r="G144" s="9" t="n"/>
       <c r="H144" s="9" t="n"/>
+      <c r="O144" s="9" t="n"/>
     </row>
     <row r="145">
+      <c r="A145" s="9" t="n"/>
+      <c r="D145" s="9" t="n"/>
+      <c r="E145" s="9" t="n"/>
+      <c r="F145" s="9" t="n"/>
+      <c r="G145" s="9" t="n"/>
       <c r="H145" s="9" t="n"/>
+      <c r="O145" s="9" t="n"/>
     </row>
     <row r="146">
+      <c r="A146" s="9" t="n"/>
+      <c r="D146" s="9" t="n"/>
+      <c r="E146" s="9" t="n"/>
+      <c r="F146" s="9" t="n"/>
+      <c r="G146" s="9" t="n"/>
       <c r="H146" s="9" t="n"/>
+      <c r="O146" s="9" t="n"/>
     </row>
     <row r="147">
+      <c r="A147" s="9" t="n"/>
+      <c r="D147" s="9" t="n"/>
+      <c r="E147" s="9" t="n"/>
+      <c r="F147" s="9" t="n"/>
+      <c r="G147" s="9" t="n"/>
       <c r="H147" s="9" t="n"/>
+      <c r="O147" s="9" t="n"/>
     </row>
     <row r="148">
+      <c r="A148" s="9" t="n"/>
+      <c r="D148" s="9" t="n"/>
+      <c r="E148" s="9" t="n"/>
+      <c r="F148" s="9" t="n"/>
+      <c r="G148" s="9" t="n"/>
       <c r="H148" s="9" t="n"/>
+      <c r="O148" s="9" t="n"/>
     </row>
     <row r="149">
+      <c r="A149" s="9" t="n"/>
+      <c r="D149" s="9" t="n"/>
+      <c r="E149" s="9" t="n"/>
+      <c r="F149" s="9" t="n"/>
+      <c r="G149" s="9" t="n"/>
       <c r="H149" s="9" t="n"/>
+      <c r="O149" s="9" t="n"/>
     </row>
     <row r="150">
+      <c r="A150" s="9" t="n"/>
+      <c r="D150" s="9" t="n"/>
+      <c r="E150" s="9" t="n"/>
+      <c r="F150" s="9" t="n"/>
+      <c r="G150" s="9" t="n"/>
       <c r="H150" s="9" t="n"/>
+      <c r="O150" s="9" t="n"/>
     </row>
     <row r="151">
+      <c r="A151" s="9" t="n"/>
+      <c r="D151" s="9" t="n"/>
+      <c r="E151" s="9" t="n"/>
+      <c r="F151" s="9" t="n"/>
+      <c r="G151" s="9" t="n"/>
       <c r="H151" s="9" t="n"/>
+      <c r="O151" s="9" t="n"/>
     </row>
     <row r="152">
+      <c r="A152" s="9" t="n"/>
+      <c r="D152" s="9" t="n"/>
+      <c r="E152" s="9" t="n"/>
+      <c r="F152" s="9" t="n"/>
+      <c r="G152" s="9" t="n"/>
       <c r="H152" s="9" t="n"/>
+      <c r="O152" s="9" t="n"/>
     </row>
     <row r="153">
+      <c r="A153" s="9" t="n"/>
+      <c r="D153" s="9" t="n"/>
+      <c r="E153" s="9" t="n"/>
+      <c r="F153" s="9" t="n"/>
+      <c r="G153" s="9" t="n"/>
       <c r="H153" s="9" t="n"/>
+      <c r="O153" s="9" t="n"/>
     </row>
     <row r="154">
+      <c r="A154" s="9" t="n"/>
+      <c r="D154" s="9" t="n"/>
+      <c r="E154" s="9" t="n"/>
+      <c r="F154" s="9" t="n"/>
+      <c r="G154" s="9" t="n"/>
       <c r="H154" s="9" t="n"/>
+      <c r="O154" s="9" t="n"/>
     </row>
     <row r="155">
+      <c r="A155" s="9" t="n"/>
+      <c r="D155" s="9" t="n"/>
+      <c r="E155" s="9" t="n"/>
+      <c r="F155" s="9" t="n"/>
+      <c r="G155" s="9" t="n"/>
       <c r="H155" s="9" t="n"/>
+      <c r="O155" s="9" t="n"/>
     </row>
     <row r="156">
+      <c r="A156" s="9" t="n"/>
+      <c r="D156" s="9" t="n"/>
+      <c r="E156" s="9" t="n"/>
+      <c r="F156" s="9" t="n"/>
+      <c r="G156" s="9" t="n"/>
       <c r="H156" s="9" t="n"/>
+      <c r="O156" s="9" t="n"/>
     </row>
     <row r="157">
+      <c r="A157" s="9" t="n"/>
+      <c r="D157" s="9" t="n"/>
+      <c r="E157" s="9" t="n"/>
+      <c r="F157" s="9" t="n"/>
+      <c r="G157" s="9" t="n"/>
       <c r="H157" s="9" t="n"/>
+      <c r="O157" s="9" t="n"/>
     </row>
     <row r="158">
+      <c r="A158" s="9" t="n"/>
+      <c r="D158" s="9" t="n"/>
+      <c r="E158" s="9" t="n"/>
+      <c r="F158" s="9" t="n"/>
+      <c r="G158" s="9" t="n"/>
       <c r="H158" s="9" t="n"/>
+      <c r="O158" s="9" t="n"/>
     </row>
     <row r="159">
+      <c r="A159" s="9" t="n"/>
+      <c r="D159" s="9" t="n"/>
+      <c r="E159" s="9" t="n"/>
+      <c r="F159" s="9" t="n"/>
+      <c r="G159" s="9" t="n"/>
       <c r="H159" s="9" t="n"/>
+      <c r="O159" s="9" t="n"/>
     </row>
     <row r="160">
+      <c r="A160" s="9" t="n"/>
+      <c r="D160" s="9" t="n"/>
+      <c r="E160" s="9" t="n"/>
+      <c r="F160" s="9" t="n"/>
+      <c r="G160" s="9" t="n"/>
       <c r="H160" s="9" t="n"/>
+      <c r="O160" s="9" t="n"/>
     </row>
     <row r="161">
+      <c r="A161" s="9" t="n"/>
+      <c r="D161" s="9" t="n"/>
+      <c r="E161" s="9" t="n"/>
+      <c r="F161" s="9" t="n"/>
+      <c r="G161" s="9" t="n"/>
       <c r="H161" s="9" t="n"/>
+      <c r="O161" s="9" t="n"/>
     </row>
     <row r="162">
+      <c r="A162" s="9" t="n"/>
+      <c r="D162" s="9" t="n"/>
+      <c r="E162" s="9" t="n"/>
+      <c r="F162" s="9" t="n"/>
+      <c r="G162" s="9" t="n"/>
       <c r="H162" s="9" t="n"/>
+      <c r="O162" s="9" t="n"/>
     </row>
     <row r="163">
+      <c r="A163" s="9" t="n"/>
+      <c r="D163" s="9" t="n"/>
+      <c r="E163" s="9" t="n"/>
+      <c r="F163" s="9" t="n"/>
+      <c r="G163" s="9" t="n"/>
       <c r="H163" s="9" t="n"/>
+      <c r="O163" s="9" t="n"/>
     </row>
     <row r="164">
+      <c r="A164" s="9" t="n"/>
+      <c r="D164" s="9" t="n"/>
+      <c r="E164" s="9" t="n"/>
+      <c r="F164" s="9" t="n"/>
+      <c r="G164" s="9" t="n"/>
       <c r="H164" s="9" t="n"/>
+      <c r="O164" s="9" t="n"/>
     </row>
     <row r="165">
+      <c r="A165" s="9" t="n"/>
+      <c r="D165" s="9" t="n"/>
+      <c r="E165" s="9" t="n"/>
+      <c r="F165" s="9" t="n"/>
+      <c r="G165" s="9" t="n"/>
       <c r="H165" s="9" t="n"/>
+      <c r="O165" s="9" t="n"/>
     </row>
     <row r="166">
+      <c r="A166" s="9" t="n"/>
+      <c r="D166" s="9" t="n"/>
+      <c r="E166" s="9" t="n"/>
+      <c r="F166" s="9" t="n"/>
+      <c r="G166" s="9" t="n"/>
       <c r="H166" s="9" t="n"/>
+      <c r="O166" s="9" t="n"/>
     </row>
     <row r="167">
+      <c r="A167" s="9" t="n"/>
+      <c r="D167" s="9" t="n"/>
+      <c r="E167" s="9" t="n"/>
+      <c r="F167" s="9" t="n"/>
+      <c r="G167" s="9" t="n"/>
       <c r="H167" s="9" t="n"/>
+      <c r="O167" s="9" t="n"/>
     </row>
     <row r="168">
+      <c r="A168" s="9" t="n"/>
+      <c r="D168" s="9" t="n"/>
+      <c r="E168" s="9" t="n"/>
+      <c r="F168" s="9" t="n"/>
+      <c r="G168" s="9" t="n"/>
       <c r="H168" s="9" t="n"/>
+      <c r="O168" s="9" t="n"/>
     </row>
     <row r="169">
+      <c r="A169" s="9" t="n"/>
+      <c r="D169" s="9" t="n"/>
+      <c r="E169" s="9" t="n"/>
+      <c r="F169" s="9" t="n"/>
+      <c r="G169" s="9" t="n"/>
       <c r="H169" s="9" t="n"/>
+      <c r="O169" s="9" t="n"/>
     </row>
     <row r="170">
+      <c r="A170" s="9" t="n"/>
+      <c r="D170" s="9" t="n"/>
+      <c r="E170" s="9" t="n"/>
+      <c r="F170" s="9" t="n"/>
+      <c r="G170" s="9" t="n"/>
       <c r="H170" s="9" t="n"/>
+      <c r="O170" s="9" t="n"/>
     </row>
     <row r="171">
+      <c r="A171" s="9" t="n"/>
+      <c r="D171" s="9" t="n"/>
+      <c r="E171" s="9" t="n"/>
+      <c r="F171" s="9" t="n"/>
+      <c r="G171" s="9" t="n"/>
       <c r="H171" s="9" t="n"/>
+      <c r="O171" s="9" t="n"/>
     </row>
     <row r="172">
+      <c r="A172" s="9" t="n"/>
+      <c r="D172" s="9" t="n"/>
+      <c r="E172" s="9" t="n"/>
+      <c r="F172" s="9" t="n"/>
+      <c r="G172" s="9" t="n"/>
       <c r="H172" s="9" t="n"/>
+      <c r="O172" s="9" t="n"/>
     </row>
     <row r="173">
+      <c r="A173" s="9" t="n"/>
+      <c r="D173" s="9" t="n"/>
+      <c r="E173" s="9" t="n"/>
+      <c r="F173" s="9" t="n"/>
+      <c r="G173" s="9" t="n"/>
       <c r="H173" s="9" t="n"/>
+      <c r="O173" s="9" t="n"/>
     </row>
     <row r="174">
+      <c r="A174" s="9" t="n"/>
+      <c r="D174" s="9" t="n"/>
+      <c r="E174" s="9" t="n"/>
+      <c r="F174" s="9" t="n"/>
+      <c r="G174" s="9" t="n"/>
       <c r="H174" s="9" t="n"/>
+      <c r="O174" s="9" t="n"/>
     </row>
     <row r="175">
+      <c r="A175" s="9" t="n"/>
+      <c r="D175" s="9" t="n"/>
+      <c r="E175" s="9" t="n"/>
+      <c r="F175" s="9" t="n"/>
+      <c r="G175" s="9" t="n"/>
       <c r="H175" s="9" t="n"/>
+      <c r="O175" s="9" t="n"/>
     </row>
     <row r="176">
+      <c r="A176" s="9" t="n"/>
+      <c r="D176" s="9" t="n"/>
+      <c r="E176" s="9" t="n"/>
+      <c r="F176" s="9" t="n"/>
+      <c r="G176" s="9" t="n"/>
       <c r="H176" s="9" t="n"/>
+      <c r="O176" s="9" t="n"/>
     </row>
     <row r="177">
+      <c r="A177" s="9" t="n"/>
+      <c r="D177" s="9" t="n"/>
+      <c r="E177" s="9" t="n"/>
+      <c r="F177" s="9" t="n"/>
+      <c r="G177" s="9" t="n"/>
       <c r="H177" s="9" t="n"/>
+      <c r="O177" s="9" t="n"/>
     </row>
     <row r="178">
+      <c r="A178" s="9" t="n"/>
+      <c r="D178" s="9" t="n"/>
+      <c r="E178" s="9" t="n"/>
+      <c r="F178" s="9" t="n"/>
+      <c r="G178" s="9" t="n"/>
       <c r="H178" s="9" t="n"/>
+      <c r="O178" s="9" t="n"/>
     </row>
     <row r="179">
+      <c r="A179" s="9" t="n"/>
+      <c r="D179" s="9" t="n"/>
+      <c r="E179" s="9" t="n"/>
+      <c r="F179" s="9" t="n"/>
+      <c r="G179" s="9" t="n"/>
       <c r="H179" s="9" t="n"/>
+      <c r="O179" s="9" t="n"/>
     </row>
     <row r="180">
+      <c r="A180" s="9" t="n"/>
+      <c r="D180" s="9" t="n"/>
+      <c r="E180" s="9" t="n"/>
+      <c r="F180" s="9" t="n"/>
+      <c r="G180" s="9" t="n"/>
       <c r="H180" s="9" t="n"/>
+      <c r="O180" s="9" t="n"/>
     </row>
     <row r="181">
+      <c r="A181" s="9" t="n"/>
+      <c r="D181" s="9" t="n"/>
+      <c r="E181" s="9" t="n"/>
+      <c r="F181" s="9" t="n"/>
+      <c r="G181" s="9" t="n"/>
       <c r="H181" s="9" t="n"/>
+      <c r="O181" s="9" t="n"/>
     </row>
     <row r="182">
+      <c r="A182" s="9" t="n"/>
+      <c r="D182" s="9" t="n"/>
+      <c r="E182" s="9" t="n"/>
+      <c r="F182" s="9" t="n"/>
+      <c r="G182" s="9" t="n"/>
       <c r="H182" s="9" t="n"/>
+      <c r="O182" s="9" t="n"/>
     </row>
     <row r="183">
+      <c r="A183" s="9" t="n"/>
+      <c r="D183" s="9" t="n"/>
+      <c r="E183" s="9" t="n"/>
+      <c r="F183" s="9" t="n"/>
+      <c r="G183" s="9" t="n"/>
       <c r="H183" s="9" t="n"/>
+      <c r="O183" s="9" t="n"/>
     </row>
     <row r="184">
+      <c r="A184" s="9" t="n"/>
+      <c r="D184" s="9" t="n"/>
+      <c r="E184" s="9" t="n"/>
+      <c r="F184" s="9" t="n"/>
+      <c r="G184" s="9" t="n"/>
       <c r="H184" s="9" t="n"/>
+      <c r="O184" s="9" t="n"/>
     </row>
     <row r="185">
+      <c r="A185" s="9" t="n"/>
+      <c r="D185" s="9" t="n"/>
+      <c r="E185" s="9" t="n"/>
+      <c r="F185" s="9" t="n"/>
+      <c r="G185" s="9" t="n"/>
       <c r="H185" s="9" t="n"/>
+      <c r="O185" s="9" t="n"/>
     </row>
     <row r="186">
+      <c r="A186" s="9" t="n"/>
+      <c r="D186" s="9" t="n"/>
+      <c r="E186" s="9" t="n"/>
+      <c r="F186" s="9" t="n"/>
+      <c r="G186" s="9" t="n"/>
       <c r="H186" s="9" t="n"/>
+      <c r="O186" s="9" t="n"/>
     </row>
     <row r="187">
+      <c r="A187" s="9" t="n"/>
+      <c r="D187" s="9" t="n"/>
+      <c r="E187" s="9" t="n"/>
+      <c r="F187" s="9" t="n"/>
+      <c r="G187" s="9" t="n"/>
       <c r="H187" s="9" t="n"/>
+      <c r="O187" s="9" t="n"/>
     </row>
     <row r="188">
+      <c r="A188" s="9" t="n"/>
+      <c r="D188" s="9" t="n"/>
+      <c r="E188" s="9" t="n"/>
+      <c r="F188" s="9" t="n"/>
+      <c r="G188" s="9" t="n"/>
       <c r="H188" s="9" t="n"/>
+      <c r="O188" s="9" t="n"/>
     </row>
     <row r="189">
+      <c r="A189" s="9" t="n"/>
+      <c r="D189" s="9" t="n"/>
+      <c r="E189" s="9" t="n"/>
+      <c r="F189" s="9" t="n"/>
+      <c r="G189" s="9" t="n"/>
       <c r="H189" s="9" t="n"/>
+      <c r="O189" s="9" t="n"/>
     </row>
     <row r="190">
+      <c r="A190" s="9" t="n"/>
+      <c r="D190" s="9" t="n"/>
+      <c r="E190" s="9" t="n"/>
+      <c r="F190" s="9" t="n"/>
+      <c r="G190" s="9" t="n"/>
       <c r="H190" s="9" t="n"/>
+      <c r="O190" s="9" t="n"/>
     </row>
     <row r="191">
+      <c r="A191" s="9" t="n"/>
+      <c r="D191" s="9" t="n"/>
+      <c r="E191" s="9" t="n"/>
+      <c r="F191" s="9" t="n"/>
+      <c r="G191" s="9" t="n"/>
       <c r="H191" s="9" t="n"/>
+      <c r="O191" s="9" t="n"/>
     </row>
     <row r="192">
+      <c r="A192" s="9" t="n"/>
+      <c r="D192" s="9" t="n"/>
+      <c r="E192" s="9" t="n"/>
+      <c r="F192" s="9" t="n"/>
+      <c r="G192" s="9" t="n"/>
       <c r="H192" s="9" t="n"/>
+      <c r="O192" s="9" t="n"/>
     </row>
     <row r="193">
+      <c r="A193" s="9" t="n"/>
+      <c r="D193" s="9" t="n"/>
+      <c r="E193" s="9" t="n"/>
+      <c r="F193" s="9" t="n"/>
+      <c r="G193" s="9" t="n"/>
       <c r="H193" s="9" t="n"/>
+      <c r="O193" s="9" t="n"/>
     </row>
     <row r="194">
+      <c r="A194" s="9" t="n"/>
+      <c r="D194" s="9" t="n"/>
+      <c r="E194" s="9" t="n"/>
+      <c r="F194" s="9" t="n"/>
+      <c r="G194" s="9" t="n"/>
       <c r="H194" s="9" t="n"/>
+      <c r="O194" s="9" t="n"/>
     </row>
     <row r="195">
+      <c r="A195" s="9" t="n"/>
+      <c r="D195" s="9" t="n"/>
+      <c r="E195" s="9" t="n"/>
+      <c r="F195" s="9" t="n"/>
+      <c r="G195" s="9" t="n"/>
       <c r="H195" s="9" t="n"/>
+      <c r="O195" s="9" t="n"/>
     </row>
     <row r="196">
+      <c r="A196" s="9" t="n"/>
+      <c r="D196" s="9" t="n"/>
+      <c r="E196" s="9" t="n"/>
+      <c r="F196" s="9" t="n"/>
+      <c r="G196" s="9" t="n"/>
       <c r="H196" s="9" t="n"/>
+      <c r="O196" s="9" t="n"/>
     </row>
     <row r="197">
+      <c r="A197" s="9" t="n"/>
+      <c r="D197" s="9" t="n"/>
+      <c r="E197" s="9" t="n"/>
+      <c r="F197" s="9" t="n"/>
+      <c r="G197" s="9" t="n"/>
       <c r="H197" s="9" t="n"/>
+      <c r="O197" s="9" t="n"/>
     </row>
     <row r="198">
+      <c r="A198" s="9" t="n"/>
+      <c r="D198" s="9" t="n"/>
+      <c r="E198" s="9" t="n"/>
+      <c r="F198" s="9" t="n"/>
+      <c r="G198" s="9" t="n"/>
       <c r="H198" s="9" t="n"/>
+      <c r="O198" s="9" t="n"/>
     </row>
     <row r="199">
+      <c r="A199" s="9" t="n"/>
+      <c r="D199" s="9" t="n"/>
+      <c r="E199" s="9" t="n"/>
+      <c r="F199" s="9" t="n"/>
+      <c r="G199" s="9" t="n"/>
       <c r="H199" s="9" t="n"/>
+      <c r="O199" s="9" t="n"/>
     </row>
     <row r="200">
+      <c r="A200" s="9" t="n"/>
+      <c r="D200" s="9" t="n"/>
+      <c r="E200" s="9" t="n"/>
+      <c r="F200" s="9" t="n"/>
+      <c r="G200" s="9" t="n"/>
       <c r="H200" s="9" t="n"/>
+      <c r="O200" s="9" t="n"/>
     </row>
     <row r="201">
+      <c r="A201" s="9" t="n"/>
+      <c r="D201" s="9" t="n"/>
+      <c r="E201" s="9" t="n"/>
+      <c r="F201" s="9" t="n"/>
+      <c r="G201" s="9" t="n"/>
       <c r="H201" s="9" t="n"/>
+      <c r="O201" s="9" t="n"/>
     </row>
     <row r="202">
+      <c r="A202" s="9" t="n"/>
+      <c r="D202" s="9" t="n"/>
+      <c r="E202" s="9" t="n"/>
+      <c r="F202" s="9" t="n"/>
+      <c r="G202" s="9" t="n"/>
       <c r="H202" s="9" t="n"/>
+      <c r="O202" s="9" t="n"/>
     </row>
     <row r="203">
+      <c r="A203" s="9" t="n"/>
+      <c r="D203" s="9" t="n"/>
+      <c r="E203" s="9" t="n"/>
+      <c r="F203" s="9" t="n"/>
+      <c r="G203" s="9" t="n"/>
       <c r="H203" s="9" t="n"/>
+      <c r="O203" s="9" t="n"/>
     </row>
     <row r="204">
+      <c r="A204" s="9" t="n"/>
+      <c r="D204" s="9" t="n"/>
+      <c r="E204" s="9" t="n"/>
+      <c r="F204" s="9" t="n"/>
+      <c r="G204" s="9" t="n"/>
       <c r="H204" s="9" t="n"/>
+      <c r="O204" s="9" t="n"/>
     </row>
     <row r="205">
+      <c r="A205" s="9" t="n"/>
+      <c r="D205" s="9" t="n"/>
+      <c r="E205" s="9" t="n"/>
+      <c r="F205" s="9" t="n"/>
+      <c r="G205" s="9" t="n"/>
       <c r="H205" s="9" t="n"/>
+      <c r="O205" s="9" t="n"/>
     </row>
     <row r="206">
+      <c r="A206" s="9" t="n"/>
+      <c r="D206" s="9" t="n"/>
+      <c r="E206" s="9" t="n"/>
+      <c r="F206" s="9" t="n"/>
+      <c r="G206" s="9" t="n"/>
       <c r="H206" s="9" t="n"/>
+      <c r="O206" s="9" t="n"/>
     </row>
     <row r="207">
+      <c r="A207" s="9" t="n"/>
+      <c r="D207" s="9" t="n"/>
+      <c r="E207" s="9" t="n"/>
+      <c r="F207" s="9" t="n"/>
+      <c r="G207" s="9" t="n"/>
       <c r="H207" s="9" t="n"/>
+      <c r="O207" s="9" t="n"/>
     </row>
     <row r="208">
+      <c r="A208" s="9" t="n"/>
+      <c r="D208" s="9" t="n"/>
+      <c r="E208" s="9" t="n"/>
+      <c r="F208" s="9" t="n"/>
+      <c r="G208" s="9" t="n"/>
       <c r="H208" s="9" t="n"/>
+      <c r="O208" s="9" t="n"/>
     </row>
     <row r="209">
+      <c r="A209" s="9" t="n"/>
+      <c r="D209" s="9" t="n"/>
+      <c r="E209" s="9" t="n"/>
+      <c r="F209" s="9" t="n"/>
+      <c r="G209" s="9" t="n"/>
       <c r="H209" s="9" t="n"/>
+      <c r="O209" s="9" t="n"/>
     </row>
     <row r="210">
+      <c r="A210" s="9" t="n"/>
+      <c r="D210" s="9" t="n"/>
+      <c r="E210" s="9" t="n"/>
+      <c r="F210" s="9" t="n"/>
+      <c r="G210" s="9" t="n"/>
       <c r="H210" s="9" t="n"/>
+      <c r="O210" s="9" t="n"/>
     </row>
     <row r="211">
+      <c r="A211" s="9" t="n"/>
+      <c r="D211" s="9" t="n"/>
+      <c r="E211" s="9" t="n"/>
+      <c r="F211" s="9" t="n"/>
+      <c r="G211" s="9" t="n"/>
       <c r="H211" s="9" t="n"/>
+      <c r="O211" s="9" t="n"/>
     </row>
     <row r="212">
+      <c r="A212" s="9" t="n"/>
+      <c r="D212" s="9" t="n"/>
+      <c r="E212" s="9" t="n"/>
+      <c r="F212" s="9" t="n"/>
+      <c r="G212" s="9" t="n"/>
       <c r="H212" s="9" t="n"/>
+      <c r="O212" s="9" t="n"/>
     </row>
     <row r="213">
+      <c r="A213" s="9" t="n"/>
+      <c r="D213" s="9" t="n"/>
+      <c r="E213" s="9" t="n"/>
+      <c r="F213" s="9" t="n"/>
+      <c r="G213" s="9" t="n"/>
       <c r="H213" s="9" t="n"/>
+      <c r="O213" s="9" t="n"/>
     </row>
     <row r="214">
+      <c r="A214" s="9" t="n"/>
+      <c r="D214" s="9" t="n"/>
+      <c r="E214" s="9" t="n"/>
+      <c r="F214" s="9" t="n"/>
+      <c r="G214" s="9" t="n"/>
       <c r="H214" s="9" t="n"/>
+      <c r="O214" s="9" t="n"/>
     </row>
     <row r="215">
+      <c r="A215" s="9" t="n"/>
+      <c r="D215" s="9" t="n"/>
+      <c r="E215" s="9" t="n"/>
+      <c r="F215" s="9" t="n"/>
+      <c r="G215" s="9" t="n"/>
       <c r="H215" s="9" t="n"/>
+      <c r="O215" s="9" t="n"/>
     </row>
     <row r="216">
+      <c r="A216" s="9" t="n"/>
+      <c r="D216" s="9" t="n"/>
+      <c r="E216" s="9" t="n"/>
+      <c r="F216" s="9" t="n"/>
+      <c r="G216" s="9" t="n"/>
       <c r="H216" s="9" t="n"/>
+      <c r="O216" s="9" t="n"/>
     </row>
     <row r="217">
+      <c r="A217" s="9" t="n"/>
+      <c r="D217" s="9" t="n"/>
+      <c r="E217" s="9" t="n"/>
+      <c r="F217" s="9" t="n"/>
+      <c r="G217" s="9" t="n"/>
       <c r="H217" s="9" t="n"/>
+      <c r="O217" s="9" t="n"/>
     </row>
     <row r="218">
+      <c r="A218" s="9" t="n"/>
+      <c r="D218" s="9" t="n"/>
+      <c r="E218" s="9" t="n"/>
+      <c r="F218" s="9" t="n"/>
+      <c r="G218" s="9" t="n"/>
       <c r="H218" s="9" t="n"/>
+      <c r="O218" s="9" t="n"/>
     </row>
     <row r="219">
+      <c r="A219" s="9" t="n"/>
+      <c r="D219" s="9" t="n"/>
+      <c r="E219" s="9" t="n"/>
+      <c r="F219" s="9" t="n"/>
+      <c r="G219" s="9" t="n"/>
       <c r="H219" s="9" t="n"/>
+      <c r="O219" s="9" t="n"/>
     </row>
     <row r="220">
+      <c r="A220" s="9" t="n"/>
+      <c r="D220" s="9" t="n"/>
+      <c r="E220" s="9" t="n"/>
+      <c r="F220" s="9" t="n"/>
+      <c r="G220" s="9" t="n"/>
       <c r="H220" s="9" t="n"/>
+      <c r="O220" s="9" t="n"/>
     </row>
     <row r="221">
+      <c r="A221" s="9" t="n"/>
+      <c r="D221" s="9" t="n"/>
+      <c r="E221" s="9" t="n"/>
+      <c r="F221" s="9" t="n"/>
+      <c r="G221" s="9" t="n"/>
       <c r="H221" s="9" t="n"/>
+      <c r="O221" s="9" t="n"/>
     </row>
     <row r="222">
+      <c r="A222" s="9" t="n"/>
+      <c r="D222" s="9" t="n"/>
+      <c r="E222" s="9" t="n"/>
+      <c r="F222" s="9" t="n"/>
+      <c r="G222" s="9" t="n"/>
       <c r="H222" s="9" t="n"/>
+      <c r="O222" s="9" t="n"/>
     </row>
     <row r="223">
+      <c r="A223" s="9" t="n"/>
+      <c r="D223" s="9" t="n"/>
+      <c r="E223" s="9" t="n"/>
+      <c r="F223" s="9" t="n"/>
+      <c r="G223" s="9" t="n"/>
       <c r="H223" s="9" t="n"/>
+      <c r="O223" s="9" t="n"/>
     </row>
     <row r="224">
+      <c r="A224" s="9" t="n"/>
+      <c r="D224" s="9" t="n"/>
+      <c r="E224" s="9" t="n"/>
+      <c r="F224" s="9" t="n"/>
+      <c r="G224" s="9" t="n"/>
       <c r="H224" s="9" t="n"/>
+      <c r="O224" s="9" t="n"/>
     </row>
     <row r="225">
+      <c r="A225" s="9" t="n"/>
+      <c r="D225" s="9" t="n"/>
+      <c r="E225" s="9" t="n"/>
+      <c r="F225" s="9" t="n"/>
+      <c r="G225" s="9" t="n"/>
       <c r="H225" s="9" t="n"/>
+      <c r="O225" s="9" t="n"/>
     </row>
     <row r="226">
+      <c r="A226" s="9" t="n"/>
+      <c r="D226" s="9" t="n"/>
+      <c r="E226" s="9" t="n"/>
+      <c r="F226" s="9" t="n"/>
+      <c r="G226" s="9" t="n"/>
       <c r="H226" s="9" t="n"/>
+      <c r="O226" s="9" t="n"/>
     </row>
     <row r="227">
+      <c r="A227" s="9" t="n"/>
+      <c r="D227" s="9" t="n"/>
+      <c r="E227" s="9" t="n"/>
+      <c r="F227" s="9" t="n"/>
+      <c r="G227" s="9" t="n"/>
       <c r="H227" s="9" t="n"/>
+      <c r="O227" s="9" t="n"/>
     </row>
     <row r="228">
+      <c r="A228" s="9" t="n"/>
+      <c r="D228" s="9" t="n"/>
+      <c r="E228" s="9" t="n"/>
+      <c r="F228" s="9" t="n"/>
+      <c r="G228" s="9" t="n"/>
       <c r="H228" s="9" t="n"/>
+      <c r="O228" s="9" t="n"/>
     </row>
     <row r="229">
+      <c r="A229" s="9" t="n"/>
+      <c r="D229" s="9" t="n"/>
+      <c r="E229" s="9" t="n"/>
+      <c r="F229" s="9" t="n"/>
+      <c r="G229" s="9" t="n"/>
       <c r="H229" s="9" t="n"/>
+      <c r="O229" s="9" t="n"/>
     </row>
     <row r="230">
+      <c r="A230" s="9" t="n"/>
+      <c r="D230" s="9" t="n"/>
+      <c r="E230" s="9" t="n"/>
+      <c r="F230" s="9" t="n"/>
+      <c r="G230" s="9" t="n"/>
       <c r="H230" s="9" t="n"/>
+      <c r="O230" s="9" t="n"/>
     </row>
     <row r="231">
+      <c r="A231" s="9" t="n"/>
+      <c r="D231" s="9" t="n"/>
+      <c r="E231" s="9" t="n"/>
+      <c r="F231" s="9" t="n"/>
+      <c r="G231" s="9" t="n"/>
       <c r="H231" s="9" t="n"/>
+      <c r="O231" s="9" t="n"/>
     </row>
     <row r="232">
+      <c r="A232" s="9" t="n"/>
+      <c r="D232" s="9" t="n"/>
+      <c r="E232" s="9" t="n"/>
+      <c r="F232" s="9" t="n"/>
+      <c r="G232" s="9" t="n"/>
       <c r="H232" s="9" t="n"/>
+      <c r="O232" s="9" t="n"/>
     </row>
     <row r="233">
+      <c r="A233" s="9" t="n"/>
+      <c r="D233" s="9" t="n"/>
+      <c r="E233" s="9" t="n"/>
+      <c r="F233" s="9" t="n"/>
+      <c r="G233" s="9" t="n"/>
       <c r="H233" s="9" t="n"/>
+      <c r="O233" s="9" t="n"/>
     </row>
     <row r="234">
+      <c r="A234" s="9" t="n"/>
+      <c r="D234" s="9" t="n"/>
+      <c r="E234" s="9" t="n"/>
+      <c r="F234" s="9" t="n"/>
+      <c r="G234" s="9" t="n"/>
       <c r="H234" s="9" t="n"/>
+      <c r="O234" s="9" t="n"/>
     </row>
     <row r="235">
+      <c r="A235" s="9" t="n"/>
+      <c r="D235" s="9" t="n"/>
+      <c r="E235" s="9" t="n"/>
+      <c r="F235" s="9" t="n"/>
+      <c r="G235" s="9" t="n"/>
       <c r="H235" s="9" t="n"/>
+      <c r="O235" s="9" t="n"/>
     </row>
     <row r="236">
+      <c r="A236" s="9" t="n"/>
+      <c r="D236" s="9" t="n"/>
+      <c r="E236" s="9" t="n"/>
+      <c r="F236" s="9" t="n"/>
+      <c r="G236" s="9" t="n"/>
       <c r="H236" s="9" t="n"/>
+      <c r="O236" s="9" t="n"/>
     </row>
     <row r="237">
+      <c r="A237" s="9" t="n"/>
+      <c r="D237" s="9" t="n"/>
+      <c r="E237" s="9" t="n"/>
+      <c r="F237" s="9" t="n"/>
+      <c r="G237" s="9" t="n"/>
       <c r="H237" s="9" t="n"/>
+      <c r="O237" s="9" t="n"/>
     </row>
     <row r="238">
+      <c r="A238" s="9" t="n"/>
+      <c r="D238" s="9" t="n"/>
+      <c r="E238" s="9" t="n"/>
+      <c r="F238" s="9" t="n"/>
+      <c r="G238" s="9" t="n"/>
       <c r="H238" s="9" t="n"/>
+      <c r="O238" s="9" t="n"/>
     </row>
     <row r="239">
+      <c r="A239" s="9" t="n"/>
+      <c r="D239" s="9" t="n"/>
+      <c r="E239" s="9" t="n"/>
+      <c r="F239" s="9" t="n"/>
+      <c r="G239" s="9" t="n"/>
       <c r="H239" s="9" t="n"/>
+      <c r="O239" s="9" t="n"/>
     </row>
     <row r="240">
+      <c r="A240" s="9" t="n"/>
+      <c r="D240" s="9" t="n"/>
+      <c r="E240" s="9" t="n"/>
+      <c r="F240" s="9" t="n"/>
+      <c r="G240" s="9" t="n"/>
       <c r="H240" s="9" t="n"/>
+      <c r="O240" s="9" t="n"/>
     </row>
     <row r="241">
+      <c r="A241" s="9" t="n"/>
+      <c r="D241" s="9" t="n"/>
+      <c r="E241" s="9" t="n"/>
+      <c r="F241" s="9" t="n"/>
+      <c r="G241" s="9" t="n"/>
       <c r="H241" s="9" t="n"/>
+      <c r="O241" s="9" t="n"/>
     </row>
     <row r="242">
+      <c r="A242" s="9" t="n"/>
+      <c r="D242" s="9" t="n"/>
+      <c r="E242" s="9" t="n"/>
+      <c r="F242" s="9" t="n"/>
+      <c r="G242" s="9" t="n"/>
       <c r="H242" s="9" t="n"/>
+      <c r="O242" s="9" t="n"/>
     </row>
     <row r="243">
+      <c r="A243" s="9" t="n"/>
+      <c r="D243" s="9" t="n"/>
+      <c r="E243" s="9" t="n"/>
+      <c r="F243" s="9" t="n"/>
+      <c r="G243" s="9" t="n"/>
       <c r="H243" s="9" t="n"/>
+      <c r="O243" s="9" t="n"/>
     </row>
     <row r="244">
+      <c r="A244" s="9" t="n"/>
+      <c r="D244" s="9" t="n"/>
+      <c r="E244" s="9" t="n"/>
+      <c r="F244" s="9" t="n"/>
+      <c r="G244" s="9" t="n"/>
       <c r="H244" s="9" t="n"/>
+      <c r="O244" s="9" t="n"/>
     </row>
     <row r="245">
+      <c r="A245" s="9" t="n"/>
+      <c r="D245" s="9" t="n"/>
+      <c r="E245" s="9" t="n"/>
+      <c r="F245" s="9" t="n"/>
+      <c r="G245" s="9" t="n"/>
       <c r="H245" s="9" t="n"/>
+      <c r="O245" s="9" t="n"/>
     </row>
     <row r="246">
+      <c r="A246" s="9" t="n"/>
+      <c r="D246" s="9" t="n"/>
+      <c r="E246" s="9" t="n"/>
+      <c r="F246" s="9" t="n"/>
+      <c r="G246" s="9" t="n"/>
       <c r="H246" s="9" t="n"/>
+      <c r="O246" s="9" t="n"/>
     </row>
     <row r="247">
+      <c r="A247" s="9" t="n"/>
+      <c r="D247" s="9" t="n"/>
+      <c r="E247" s="9" t="n"/>
+      <c r="F247" s="9" t="n"/>
+      <c r="G247" s="9" t="n"/>
       <c r="H247" s="9" t="n"/>
+      <c r="O247" s="9" t="n"/>
     </row>
     <row r="248">
+      <c r="A248" s="9" t="n"/>
+      <c r="D248" s="9" t="n"/>
+      <c r="E248" s="9" t="n"/>
+      <c r="F248" s="9" t="n"/>
+      <c r="G248" s="9" t="n"/>
       <c r="H248" s="9" t="n"/>
+      <c r="O248" s="9" t="n"/>
     </row>
     <row r="249">
+      <c r="A249" s="9" t="n"/>
+      <c r="D249" s="9" t="n"/>
+      <c r="E249" s="9" t="n"/>
+      <c r="F249" s="9" t="n"/>
+      <c r="G249" s="9" t="n"/>
       <c r="H249" s="9" t="n"/>
+      <c r="O249" s="9" t="n"/>
     </row>
     <row r="250">
+      <c r="A250" s="9" t="n"/>
+      <c r="D250" s="9" t="n"/>
+      <c r="E250" s="9" t="n"/>
+      <c r="F250" s="9" t="n"/>
+      <c r="G250" s="9" t="n"/>
       <c r="H250" s="9" t="n"/>
+      <c r="O250" s="9" t="n"/>
     </row>
     <row r="251">
+      <c r="A251" s="9" t="n"/>
+      <c r="D251" s="9" t="n"/>
+      <c r="E251" s="9" t="n"/>
+      <c r="F251" s="9" t="n"/>
+      <c r="G251" s="9" t="n"/>
       <c r="H251" s="9" t="n"/>
+      <c r="O251" s="9" t="n"/>
     </row>
     <row r="252">
+      <c r="A252" s="9" t="n"/>
+      <c r="D252" s="9" t="n"/>
+      <c r="E252" s="9" t="n"/>
+      <c r="F252" s="9" t="n"/>
+      <c r="G252" s="9" t="n"/>
       <c r="H252" s="9" t="n"/>
+      <c r="O252" s="9" t="n"/>
     </row>
     <row r="253">
+      <c r="A253" s="9" t="n"/>
+      <c r="D253" s="9" t="n"/>
+      <c r="E253" s="9" t="n"/>
+      <c r="F253" s="9" t="n"/>
+      <c r="G253" s="9" t="n"/>
       <c r="H253" s="9" t="n"/>
+      <c r="O253" s="9" t="n"/>
     </row>
     <row r="254">
+      <c r="A254" s="9" t="n"/>
+      <c r="D254" s="9" t="n"/>
+      <c r="E254" s="9" t="n"/>
+      <c r="F254" s="9" t="n"/>
+      <c r="G254" s="9" t="n"/>
       <c r="H254" s="9" t="n"/>
+      <c r="O254" s="9" t="n"/>
     </row>
     <row r="255">
+      <c r="A255" s="9" t="n"/>
+      <c r="D255" s="9" t="n"/>
+      <c r="E255" s="9" t="n"/>
+      <c r="F255" s="9" t="n"/>
+      <c r="G255" s="9" t="n"/>
       <c r="H255" s="9" t="n"/>
+      <c r="O255" s="9" t="n"/>
     </row>
     <row r="256">
+      <c r="A256" s="9" t="n"/>
+      <c r="D256" s="9" t="n"/>
+      <c r="E256" s="9" t="n"/>
+      <c r="F256" s="9" t="n"/>
+      <c r="G256" s="9" t="n"/>
       <c r="H256" s="9" t="n"/>
+      <c r="O256" s="9" t="n"/>
     </row>
     <row r="257">
+      <c r="A257" s="9" t="n"/>
+      <c r="D257" s="9" t="n"/>
+      <c r="E257" s="9" t="n"/>
+      <c r="F257" s="9" t="n"/>
+      <c r="G257" s="9" t="n"/>
       <c r="H257" s="9" t="n"/>
+      <c r="O257" s="9" t="n"/>
     </row>
     <row r="258">
+      <c r="A258" s="9" t="n"/>
+      <c r="D258" s="9" t="n"/>
+      <c r="E258" s="9" t="n"/>
+      <c r="F258" s="9" t="n"/>
+      <c r="G258" s="9" t="n"/>
       <c r="H258" s="9" t="n"/>
+      <c r="O258" s="9" t="n"/>
     </row>
     <row r="259">
+      <c r="A259" s="9" t="n"/>
+      <c r="D259" s="9" t="n"/>
+      <c r="E259" s="9" t="n"/>
+      <c r="F259" s="9" t="n"/>
+      <c r="G259" s="9" t="n"/>
       <c r="H259" s="9" t="n"/>
+      <c r="O259" s="9" t="n"/>
     </row>
     <row r="260">
+      <c r="A260" s="9" t="n"/>
+      <c r="D260" s="9" t="n"/>
+      <c r="E260" s="9" t="n"/>
+      <c r="F260" s="9" t="n"/>
+      <c r="G260" s="9" t="n"/>
       <c r="H260" s="9" t="n"/>
+      <c r="O260" s="9" t="n"/>
     </row>
     <row r="261">
+      <c r="A261" s="9" t="n"/>
+      <c r="D261" s="9" t="n"/>
+      <c r="E261" s="9" t="n"/>
+      <c r="F261" s="9" t="n"/>
+      <c r="G261" s="9" t="n"/>
       <c r="H261" s="9" t="n"/>
+      <c r="O261" s="9" t="n"/>
     </row>
     <row r="262">
+      <c r="A262" s="9" t="n"/>
+      <c r="D262" s="9" t="n"/>
+      <c r="E262" s="9" t="n"/>
+      <c r="F262" s="9" t="n"/>
+      <c r="G262" s="9" t="n"/>
       <c r="H262" s="9" t="n"/>
+      <c r="O262" s="9" t="n"/>
     </row>
     <row r="263">
+      <c r="A263" s="9" t="n"/>
+      <c r="D263" s="9" t="n"/>
+      <c r="E263" s="9" t="n"/>
+      <c r="F263" s="9" t="n"/>
+      <c r="G263" s="9" t="n"/>
       <c r="H263" s="9" t="n"/>
+      <c r="O263" s="9" t="n"/>
     </row>
     <row r="264">
+      <c r="A264" s="9" t="n"/>
+      <c r="D264" s="9" t="n"/>
+      <c r="E264" s="9" t="n"/>
+      <c r="F264" s="9" t="n"/>
+      <c r="G264" s="9" t="n"/>
       <c r="H264" s="9" t="n"/>
+      <c r="O264" s="9" t="n"/>
     </row>
     <row r="265">
+      <c r="A265" s="9" t="n"/>
+      <c r="D265" s="9" t="n"/>
+      <c r="E265" s="9" t="n"/>
+      <c r="F265" s="9" t="n"/>
+      <c r="G265" s="9" t="n"/>
       <c r="H265" s="9" t="n"/>
+      <c r="O265" s="9" t="n"/>
     </row>
     <row r="266">
+      <c r="A266" s="9" t="n"/>
+      <c r="D266" s="9" t="n"/>
+      <c r="E266" s="9" t="n"/>
+      <c r="F266" s="9" t="n"/>
+      <c r="G266" s="9" t="n"/>
       <c r="H266" s="9" t="n"/>
+      <c r="O266" s="9" t="n"/>
     </row>
     <row r="267">
+      <c r="A267" s="9" t="n"/>
+      <c r="D267" s="9" t="n"/>
+      <c r="E267" s="9" t="n"/>
+      <c r="F267" s="9" t="n"/>
+      <c r="G267" s="9" t="n"/>
       <c r="H267" s="9" t="n"/>
+      <c r="O267" s="9" t="n"/>
     </row>
     <row r="268">
+      <c r="A268" s="9" t="n"/>
+      <c r="D268" s="9" t="n"/>
+      <c r="E268" s="9" t="n"/>
+      <c r="F268" s="9" t="n"/>
+      <c r="G268" s="9" t="n"/>
       <c r="H268" s="9" t="n"/>
+      <c r="O268" s="9" t="n"/>
     </row>
     <row r="269">
+      <c r="A269" s="9" t="n"/>
+      <c r="D269" s="9" t="n"/>
+      <c r="E269" s="9" t="n"/>
+      <c r="F269" s="9" t="n"/>
+      <c r="G269" s="9" t="n"/>
       <c r="H269" s="9" t="n"/>
+      <c r="O269" s="9" t="n"/>
     </row>
     <row r="270">
+      <c r="A270" s="9" t="n"/>
+      <c r="D270" s="9" t="n"/>
+      <c r="E270" s="9" t="n"/>
+      <c r="F270" s="9" t="n"/>
+      <c r="G270" s="9" t="n"/>
       <c r="H270" s="9" t="n"/>
+      <c r="O270" s="9" t="n"/>
     </row>
     <row r="271">
+      <c r="A271" s="9" t="n"/>
+      <c r="D271" s="9" t="n"/>
+      <c r="E271" s="9" t="n"/>
+      <c r="F271" s="9" t="n"/>
+      <c r="G271" s="9" t="n"/>
       <c r="H271" s="9" t="n"/>
+      <c r="O271" s="9" t="n"/>
     </row>
     <row r="272">
+      <c r="A272" s="9" t="n"/>
+      <c r="D272" s="9" t="n"/>
+      <c r="E272" s="9" t="n"/>
+      <c r="F272" s="9" t="n"/>
+      <c r="G272" s="9" t="n"/>
       <c r="H272" s="9" t="n"/>
+      <c r="O272" s="9" t="n"/>
     </row>
     <row r="273">
+      <c r="A273" s="9" t="n"/>
+      <c r="D273" s="9" t="n"/>
+      <c r="E273" s="9" t="n"/>
+      <c r="F273" s="9" t="n"/>
+      <c r="G273" s="9" t="n"/>
       <c r="H273" s="9" t="n"/>
+      <c r="O273" s="9" t="n"/>
     </row>
     <row r="274">
+      <c r="A274" s="9" t="n"/>
+      <c r="D274" s="9" t="n"/>
+      <c r="E274" s="9" t="n"/>
+      <c r="F274" s="9" t="n"/>
+      <c r="G274" s="9" t="n"/>
       <c r="H274" s="9" t="n"/>
+      <c r="O274" s="9" t="n"/>
     </row>
     <row r="275">
+      <c r="A275" s="9" t="n"/>
+      <c r="D275" s="9" t="n"/>
+      <c r="E275" s="9" t="n"/>
+      <c r="F275" s="9" t="n"/>
+      <c r="G275" s="9" t="n"/>
       <c r="H275" s="9" t="n"/>
+      <c r="O275" s="9" t="n"/>
     </row>
     <row r="276">
+      <c r="A276" s="9" t="n"/>
+      <c r="D276" s="9" t="n"/>
+      <c r="E276" s="9" t="n"/>
+      <c r="F276" s="9" t="n"/>
+      <c r="G276" s="9" t="n"/>
       <c r="H276" s="9" t="n"/>
+      <c r="O276" s="9" t="n"/>
     </row>
     <row r="277">
+      <c r="A277" s="9" t="n"/>
+      <c r="D277" s="9" t="n"/>
+      <c r="E277" s="9" t="n"/>
+      <c r="F277" s="9" t="n"/>
+      <c r="G277" s="9" t="n"/>
       <c r="H277" s="9" t="n"/>
+      <c r="O277" s="9" t="n"/>
     </row>
     <row r="278">
+      <c r="A278" s="9" t="n"/>
+      <c r="D278" s="9" t="n"/>
+      <c r="E278" s="9" t="n"/>
+      <c r="F278" s="9" t="n"/>
+      <c r="G278" s="9" t="n"/>
       <c r="H278" s="9" t="n"/>
+      <c r="O278" s="9" t="n"/>
     </row>
     <row r="279">
+      <c r="A279" s="9" t="n"/>
+      <c r="D279" s="9" t="n"/>
+      <c r="E279" s="9" t="n"/>
+      <c r="F279" s="9" t="n"/>
+      <c r="G279" s="9" t="n"/>
       <c r="H279" s="9" t="n"/>
+      <c r="O279" s="9" t="n"/>
     </row>
     <row r="280">
+      <c r="A280" s="9" t="n"/>
+      <c r="D280" s="9" t="n"/>
+      <c r="E280" s="9" t="n"/>
+      <c r="F280" s="9" t="n"/>
+      <c r="G280" s="9" t="n"/>
       <c r="H280" s="9" t="n"/>
+      <c r="O280" s="9" t="n"/>
     </row>
     <row r="281">
+      <c r="A281" s="9" t="n"/>
+      <c r="D281" s="9" t="n"/>
+      <c r="E281" s="9" t="n"/>
+      <c r="F281" s="9" t="n"/>
+      <c r="G281" s="9" t="n"/>
       <c r="H281" s="9" t="n"/>
+      <c r="O281" s="9" t="n"/>
     </row>
     <row r="282">
+      <c r="A282" s="9" t="n"/>
+      <c r="D282" s="9" t="n"/>
+      <c r="E282" s="9" t="n"/>
+      <c r="F282" s="9" t="n"/>
+      <c r="G282" s="9" t="n"/>
       <c r="H282" s="9" t="n"/>
+      <c r="O282" s="9" t="n"/>
     </row>
     <row r="283">
+      <c r="A283" s="9" t="n"/>
+      <c r="D283" s="9" t="n"/>
+      <c r="E283" s="9" t="n"/>
+      <c r="F283" s="9" t="n"/>
+      <c r="G283" s="9" t="n"/>
       <c r="H283" s="9" t="n"/>
+      <c r="O283" s="9" t="n"/>
     </row>
     <row r="284">
+      <c r="A284" s="9" t="n"/>
+      <c r="D284" s="9" t="n"/>
+      <c r="E284" s="9" t="n"/>
+      <c r="F284" s="9" t="n"/>
+      <c r="G284" s="9" t="n"/>
       <c r="H284" s="9" t="n"/>
+      <c r="O284" s="9" t="n"/>
     </row>
     <row r="285">
+      <c r="A285" s="9" t="n"/>
+      <c r="D285" s="9" t="n"/>
+      <c r="E285" s="9" t="n"/>
+      <c r="F285" s="9" t="n"/>
+      <c r="G285" s="9" t="n"/>
       <c r="H285" s="9" t="n"/>
+      <c r="O285" s="9" t="n"/>
     </row>
     <row r="286">
+      <c r="A286" s="9" t="n"/>
+      <c r="D286" s="9" t="n"/>
+      <c r="E286" s="9" t="n"/>
+      <c r="F286" s="9" t="n"/>
+      <c r="G286" s="9" t="n"/>
       <c r="H286" s="9" t="n"/>
+      <c r="O286" s="9" t="n"/>
     </row>
     <row r="287">
+      <c r="A287" s="9" t="n"/>
+      <c r="D287" s="9" t="n"/>
+      <c r="E287" s="9" t="n"/>
+      <c r="F287" s="9" t="n"/>
+      <c r="G287" s="9" t="n"/>
       <c r="H287" s="9" t="n"/>
+      <c r="O287" s="9" t="n"/>
     </row>
     <row r="288">
+      <c r="A288" s="9" t="n"/>
+      <c r="D288" s="9" t="n"/>
+      <c r="E288" s="9" t="n"/>
+      <c r="F288" s="9" t="n"/>
+      <c r="G288" s="9" t="n"/>
       <c r="H288" s="9" t="n"/>
+      <c r="O288" s="9" t="n"/>
     </row>
     <row r="289">
+      <c r="A289" s="9" t="n"/>
+      <c r="D289" s="9" t="n"/>
+      <c r="E289" s="9" t="n"/>
+      <c r="F289" s="9" t="n"/>
+      <c r="G289" s="9" t="n"/>
       <c r="H289" s="9" t="n"/>
+      <c r="O289" s="9" t="n"/>
     </row>
     <row r="290">
+      <c r="A290" s="9" t="n"/>
+      <c r="D290" s="9" t="n"/>
+      <c r="E290" s="9" t="n"/>
+      <c r="F290" s="9" t="n"/>
+      <c r="G290" s="9" t="n"/>
       <c r="H290" s="9" t="n"/>
+      <c r="O290" s="9" t="n"/>
     </row>
     <row r="291">
+      <c r="A291" s="9" t="n"/>
+      <c r="D291" s="9" t="n"/>
+      <c r="E291" s="9" t="n"/>
+      <c r="F291" s="9" t="n"/>
+      <c r="G291" s="9" t="n"/>
       <c r="H291" s="9" t="n"/>
+      <c r="O291" s="9" t="n"/>
     </row>
     <row r="292">
+      <c r="A292" s="9" t="n"/>
+      <c r="D292" s="9" t="n"/>
+      <c r="E292" s="9" t="n"/>
+      <c r="F292" s="9" t="n"/>
+      <c r="G292" s="9" t="n"/>
       <c r="H292" s="9" t="n"/>
+      <c r="O292" s="9" t="n"/>
     </row>
     <row r="293">
+      <c r="A293" s="9" t="n"/>
+      <c r="D293" s="9" t="n"/>
+      <c r="E293" s="9" t="n"/>
+      <c r="F293" s="9" t="n"/>
+      <c r="G293" s="9" t="n"/>
       <c r="H293" s="9" t="n"/>
+      <c r="O293" s="9" t="n"/>
     </row>
     <row r="294">
+      <c r="A294" s="9" t="n"/>
+      <c r="D294" s="9" t="n"/>
+      <c r="E294" s="9" t="n"/>
+      <c r="F294" s="9" t="n"/>
+      <c r="G294" s="9" t="n"/>
       <c r="H294" s="9" t="n"/>
+      <c r="O294" s="9" t="n"/>
     </row>
     <row r="295">
+      <c r="A295" s="9" t="n"/>
+      <c r="D295" s="9" t="n"/>
+      <c r="E295" s="9" t="n"/>
+      <c r="F295" s="9" t="n"/>
+      <c r="G295" s="9" t="n"/>
       <c r="H295" s="9" t="n"/>
+      <c r="O295" s="9" t="n"/>
     </row>
     <row r="296">
+      <c r="A296" s="9" t="n"/>
+      <c r="D296" s="9" t="n"/>
+      <c r="E296" s="9" t="n"/>
+      <c r="F296" s="9" t="n"/>
+      <c r="G296" s="9" t="n"/>
       <c r="H296" s="9" t="n"/>
+      <c r="O296" s="9" t="n"/>
     </row>
     <row r="297">
+      <c r="A297" s="9" t="n"/>
+      <c r="D297" s="9" t="n"/>
+      <c r="E297" s="9" t="n"/>
+      <c r="F297" s="9" t="n"/>
+      <c r="G297" s="9" t="n"/>
       <c r="H297" s="9" t="n"/>
+      <c r="O297" s="9" t="n"/>
     </row>
     <row r="298">
+      <c r="A298" s="9" t="n"/>
+      <c r="D298" s="9" t="n"/>
+      <c r="E298" s="9" t="n"/>
+      <c r="F298" s="9" t="n"/>
+      <c r="G298" s="9" t="n"/>
       <c r="H298" s="9" t="n"/>
+      <c r="O298" s="9" t="n"/>
     </row>
     <row r="299">
+      <c r="A299" s="9" t="n"/>
+      <c r="D299" s="9" t="n"/>
+      <c r="E299" s="9" t="n"/>
+      <c r="F299" s="9" t="n"/>
+      <c r="G299" s="9" t="n"/>
       <c r="H299" s="9" t="n"/>
+      <c r="O299" s="9" t="n"/>
     </row>
     <row r="300">
+      <c r="A300" s="9" t="n"/>
+      <c r="D300" s="9" t="n"/>
+      <c r="E300" s="9" t="n"/>
+      <c r="F300" s="9" t="n"/>
+      <c r="G300" s="9" t="n"/>
       <c r="H300" s="9" t="n"/>
+      <c r="O300" s="9" t="n"/>
     </row>
     <row r="301">
+      <c r="A301" s="9" t="n"/>
+      <c r="D301" s="9" t="n"/>
+      <c r="E301" s="9" t="n"/>
+      <c r="F301" s="9" t="n"/>
+      <c r="G301" s="9" t="n"/>
       <c r="H301" s="9" t="n"/>
+      <c r="O301" s="9" t="n"/>
     </row>
     <row r="302">
+      <c r="A302" s="9" t="n"/>
+      <c r="D302" s="9" t="n"/>
+      <c r="E302" s="9" t="n"/>
+      <c r="F302" s="9" t="n"/>
+      <c r="G302" s="9" t="n"/>
       <c r="H302" s="9" t="n"/>
+      <c r="O302" s="9" t="n"/>
     </row>
     <row r="303">
+      <c r="A303" s="9" t="n"/>
+      <c r="D303" s="9" t="n"/>
+      <c r="E303" s="9" t="n"/>
+      <c r="F303" s="9" t="n"/>
+      <c r="G303" s="9" t="n"/>
       <c r="H303" s="9" t="n"/>
+      <c r="O303" s="9" t="n"/>
     </row>
     <row r="304">
+      <c r="A304" s="9" t="n"/>
+      <c r="D304" s="9" t="n"/>
+      <c r="E304" s="9" t="n"/>
+      <c r="F304" s="9" t="n"/>
+      <c r="G304" s="9" t="n"/>
       <c r="H304" s="9" t="n"/>
+      <c r="O304" s="9" t="n"/>
     </row>
     <row r="305">
+      <c r="A305" s="9" t="n"/>
+      <c r="D305" s="9" t="n"/>
+      <c r="E305" s="9" t="n"/>
+      <c r="F305" s="9" t="n"/>
+      <c r="G305" s="9" t="n"/>
       <c r="H305" s="9" t="n"/>
+      <c r="O305" s="9" t="n"/>
     </row>
     <row r="306">
+      <c r="A306" s="9" t="n"/>
+      <c r="D306" s="9" t="n"/>
+      <c r="E306" s="9" t="n"/>
+      <c r="F306" s="9" t="n"/>
+      <c r="G306" s="9" t="n"/>
       <c r="H306" s="9" t="n"/>
+      <c r="O306" s="9" t="n"/>
     </row>
     <row r="307">
+      <c r="A307" s="9" t="n"/>
+      <c r="D307" s="9" t="n"/>
+      <c r="E307" s="9" t="n"/>
+      <c r="F307" s="9" t="n"/>
+      <c r="G307" s="9" t="n"/>
       <c r="H307" s="9" t="n"/>
+      <c r="O307" s="9" t="n"/>
     </row>
     <row r="308">
+      <c r="A308" s="9" t="n"/>
+      <c r="D308" s="9" t="n"/>
+      <c r="E308" s="9" t="n"/>
+      <c r="F308" s="9" t="n"/>
+      <c r="G308" s="9" t="n"/>
       <c r="H308" s="9" t="n"/>
+      <c r="O308" s="9" t="n"/>
     </row>
     <row r="309">
+      <c r="A309" s="9" t="n"/>
+      <c r="D309" s="9" t="n"/>
+      <c r="E309" s="9" t="n"/>
+      <c r="F309" s="9" t="n"/>
+      <c r="G309" s="9" t="n"/>
       <c r="H309" s="9" t="n"/>
+      <c r="O309" s="9" t="n"/>
     </row>
     <row r="310">
+      <c r="A310" s="9" t="n"/>
+      <c r="D310" s="9" t="n"/>
+      <c r="E310" s="9" t="n"/>
+      <c r="F310" s="9" t="n"/>
+      <c r="G310" s="9" t="n"/>
       <c r="H310" s="9" t="n"/>
+      <c r="O310" s="9" t="n"/>
     </row>
     <row r="311">
+      <c r="A311" s="9" t="n"/>
+      <c r="D311" s="9" t="n"/>
+      <c r="E311" s="9" t="n"/>
+      <c r="F311" s="9" t="n"/>
+      <c r="G311" s="9" t="n"/>
       <c r="H311" s="9" t="n"/>
+      <c r="O311" s="9" t="n"/>
     </row>
     <row r="312">
+      <c r="A312" s="9" t="n"/>
+      <c r="D312" s="9" t="n"/>
+      <c r="E312" s="9" t="n"/>
+      <c r="F312" s="9" t="n"/>
+      <c r="G312" s="9" t="n"/>
       <c r="H312" s="9" t="n"/>
+      <c r="O312" s="9" t="n"/>
     </row>
     <row r="313">
+      <c r="A313" s="9" t="n"/>
+      <c r="D313" s="9" t="n"/>
+      <c r="E313" s="9" t="n"/>
+      <c r="F313" s="9" t="n"/>
+      <c r="G313" s="9" t="n"/>
       <c r="H313" s="9" t="n"/>
+      <c r="O313" s="9" t="n"/>
     </row>
     <row r="314">
+      <c r="A314" s="9" t="n"/>
+      <c r="D314" s="9" t="n"/>
+      <c r="E314" s="9" t="n"/>
+      <c r="F314" s="9" t="n"/>
+      <c r="G314" s="9" t="n"/>
       <c r="H314" s="9" t="n"/>
+      <c r="O314" s="9" t="n"/>
     </row>
     <row r="315">
+      <c r="A315" s="9" t="n"/>
+      <c r="D315" s="9" t="n"/>
+      <c r="E315" s="9" t="n"/>
+      <c r="F315" s="9" t="n"/>
+      <c r="G315" s="9" t="n"/>
       <c r="H315" s="9" t="n"/>
+      <c r="O315" s="9" t="n"/>
     </row>
     <row r="316">
+      <c r="A316" s="9" t="n"/>
+      <c r="D316" s="9" t="n"/>
+      <c r="E316" s="9" t="n"/>
+      <c r="F316" s="9" t="n"/>
+      <c r="G316" s="9" t="n"/>
       <c r="H316" s="9" t="n"/>
+      <c r="O316" s="9" t="n"/>
     </row>
     <row r="317">
+      <c r="A317" s="9" t="n"/>
+      <c r="D317" s="9" t="n"/>
+      <c r="E317" s="9" t="n"/>
+      <c r="F317" s="9" t="n"/>
+      <c r="G317" s="9" t="n"/>
       <c r="H317" s="9" t="n"/>
+      <c r="O317" s="9" t="n"/>
     </row>
     <row r="318">
+      <c r="A318" s="9" t="n"/>
+      <c r="D318" s="9" t="n"/>
+      <c r="E318" s="9" t="n"/>
+      <c r="F318" s="9" t="n"/>
+      <c r="G318" s="9" t="n"/>
       <c r="H318" s="9" t="n"/>
+      <c r="O318" s="9" t="n"/>
     </row>
     <row r="319">
+      <c r="A319" s="9" t="n"/>
+      <c r="D319" s="9" t="n"/>
+      <c r="E319" s="9" t="n"/>
+      <c r="F319" s="9" t="n"/>
+      <c r="G319" s="9" t="n"/>
       <c r="H319" s="9" t="n"/>
+      <c r="O319" s="9" t="n"/>
     </row>
     <row r="320">
+      <c r="A320" s="9" t="n"/>
+      <c r="D320" s="9" t="n"/>
+      <c r="E320" s="9" t="n"/>
+      <c r="F320" s="9" t="n"/>
+      <c r="G320" s="9" t="n"/>
       <c r="H320" s="9" t="n"/>
+      <c r="O320" s="9" t="n"/>
     </row>
     <row r="321">
+      <c r="A321" s="9" t="n"/>
+      <c r="D321" s="9" t="n"/>
+      <c r="E321" s="9" t="n"/>
+      <c r="F321" s="9" t="n"/>
+      <c r="G321" s="9" t="n"/>
       <c r="H321" s="9" t="n"/>
+      <c r="O321" s="9" t="n"/>
     </row>
     <row r="322">
+      <c r="A322" s="9" t="n"/>
+      <c r="D322" s="9" t="n"/>
+      <c r="E322" s="9" t="n"/>
+      <c r="F322" s="9" t="n"/>
+      <c r="G322" s="9" t="n"/>
       <c r="H322" s="9" t="n"/>
+      <c r="O322" s="9" t="n"/>
     </row>
     <row r="323">
+      <c r="A323" s="9" t="n"/>
+      <c r="D323" s="9" t="n"/>
+      <c r="E323" s="9" t="n"/>
+      <c r="F323" s="9" t="n"/>
+      <c r="G323" s="9" t="n"/>
       <c r="H323" s="9" t="n"/>
+      <c r="O323" s="9" t="n"/>
     </row>
     <row r="324">
+      <c r="A324" s="9" t="n"/>
+      <c r="D324" s="9" t="n"/>
+      <c r="E324" s="9" t="n"/>
+      <c r="F324" s="9" t="n"/>
+      <c r="G324" s="9" t="n"/>
       <c r="H324" s="9" t="n"/>
+      <c r="O324" s="9" t="n"/>
     </row>
     <row r="325">
+      <c r="A325" s="9" t="n"/>
+      <c r="D325" s="9" t="n"/>
+      <c r="E325" s="9" t="n"/>
+      <c r="F325" s="9" t="n"/>
+      <c r="G325" s="9" t="n"/>
       <c r="H325" s="9" t="n"/>
+      <c r="O325" s="9" t="n"/>
     </row>
     <row r="326">
+      <c r="A326" s="9" t="n"/>
+      <c r="D326" s="9" t="n"/>
+      <c r="E326" s="9" t="n"/>
+      <c r="F326" s="9" t="n"/>
+      <c r="G326" s="9" t="n"/>
       <c r="H326" s="9" t="n"/>
+      <c r="O326" s="9" t="n"/>
     </row>
     <row r="327">
+      <c r="A327" s="9" t="n"/>
+      <c r="D327" s="9" t="n"/>
+      <c r="E327" s="9" t="n"/>
+      <c r="F327" s="9" t="n"/>
+      <c r="G327" s="9" t="n"/>
       <c r="H327" s="9" t="n"/>
+      <c r="O327" s="9" t="n"/>
     </row>
     <row r="328">
+      <c r="A328" s="9" t="n"/>
+      <c r="D328" s="9" t="n"/>
+      <c r="E328" s="9" t="n"/>
+      <c r="F328" s="9" t="n"/>
+      <c r="G328" s="9" t="n"/>
       <c r="H328" s="9" t="n"/>
+      <c r="O328" s="9" t="n"/>
     </row>
     <row r="329">
+      <c r="A329" s="9" t="n"/>
+      <c r="D329" s="9" t="n"/>
+      <c r="E329" s="9" t="n"/>
+      <c r="F329" s="9" t="n"/>
+      <c r="G329" s="9" t="n"/>
       <c r="H329" s="9" t="n"/>
+      <c r="O329" s="9" t="n"/>
     </row>
     <row r="330">
+      <c r="A330" s="9" t="n"/>
+      <c r="D330" s="9" t="n"/>
+      <c r="E330" s="9" t="n"/>
+      <c r="F330" s="9" t="n"/>
+      <c r="G330" s="9" t="n"/>
       <c r="H330" s="9" t="n"/>
+      <c r="O330" s="9" t="n"/>
     </row>
     <row r="331">
+      <c r="A331" s="9" t="n"/>
+      <c r="D331" s="9" t="n"/>
+      <c r="E331" s="9" t="n"/>
+      <c r="F331" s="9" t="n"/>
+      <c r="G331" s="9" t="n"/>
       <c r="H331" s="9" t="n"/>
+      <c r="O331" s="9" t="n"/>
     </row>
     <row r="332">
+      <c r="A332" s="9" t="n"/>
+      <c r="D332" s="9" t="n"/>
+      <c r="E332" s="9" t="n"/>
+      <c r="F332" s="9" t="n"/>
+      <c r="G332" s="9" t="n"/>
       <c r="H332" s="9" t="n"/>
+      <c r="O332" s="9" t="n"/>
     </row>
     <row r="333">
+      <c r="A333" s="9" t="n"/>
+      <c r="D333" s="9" t="n"/>
+      <c r="E333" s="9" t="n"/>
+      <c r="F333" s="9" t="n"/>
+      <c r="G333" s="9" t="n"/>
       <c r="H333" s="9" t="n"/>
+      <c r="O333" s="9" t="n"/>
     </row>
     <row r="334">
+      <c r="A334" s="9" t="n"/>
+      <c r="D334" s="9" t="n"/>
+      <c r="E334" s="9" t="n"/>
+      <c r="F334" s="9" t="n"/>
+      <c r="G334" s="9" t="n"/>
       <c r="H334" s="9" t="n"/>
+      <c r="O334" s="9" t="n"/>
     </row>
     <row r="335">
+      <c r="A335" s="9" t="n"/>
+      <c r="D335" s="9" t="n"/>
+      <c r="E335" s="9" t="n"/>
+      <c r="F335" s="9" t="n"/>
+      <c r="G335" s="9" t="n"/>
       <c r="H335" s="9" t="n"/>
+      <c r="O335" s="9" t="n"/>
     </row>
     <row r="336">
+      <c r="A336" s="9" t="n"/>
+      <c r="D336" s="9" t="n"/>
+      <c r="E336" s="9" t="n"/>
+      <c r="F336" s="9" t="n"/>
+      <c r="G336" s="9" t="n"/>
       <c r="H336" s="9" t="n"/>
+      <c r="O336" s="9" t="n"/>
     </row>
     <row r="337">
+      <c r="A337" s="9" t="n"/>
+      <c r="D337" s="9" t="n"/>
+      <c r="E337" s="9" t="n"/>
+      <c r="F337" s="9" t="n"/>
+      <c r="G337" s="9" t="n"/>
       <c r="H337" s="9" t="n"/>
+      <c r="O337" s="9" t="n"/>
     </row>
     <row r="338">
+      <c r="A338" s="9" t="n"/>
+      <c r="D338" s="9" t="n"/>
+      <c r="E338" s="9" t="n"/>
+      <c r="F338" s="9" t="n"/>
+      <c r="G338" s="9" t="n"/>
       <c r="H338" s="9" t="n"/>
+      <c r="O338" s="9" t="n"/>
     </row>
     <row r="339">
+      <c r="A339" s="9" t="n"/>
+      <c r="D339" s="9" t="n"/>
+      <c r="E339" s="9" t="n"/>
+      <c r="F339" s="9" t="n"/>
+      <c r="G339" s="9" t="n"/>
       <c r="H339" s="9" t="n"/>
+      <c r="O339" s="9" t="n"/>
     </row>
     <row r="340">
+      <c r="A340" s="9" t="n"/>
+      <c r="D340" s="9" t="n"/>
+      <c r="E340" s="9" t="n"/>
+      <c r="F340" s="9" t="n"/>
+      <c r="G340" s="9" t="n"/>
       <c r="H340" s="9" t="n"/>
+      <c r="O340" s="9" t="n"/>
     </row>
     <row r="341">
+      <c r="A341" s="9" t="n"/>
+      <c r="D341" s="9" t="n"/>
+      <c r="E341" s="9" t="n"/>
+      <c r="F341" s="9" t="n"/>
+      <c r="G341" s="9" t="n"/>
       <c r="H341" s="9" t="n"/>
+      <c r="O341" s="9" t="n"/>
     </row>
     <row r="342">
+      <c r="A342" s="9" t="n"/>
+      <c r="D342" s="9" t="n"/>
+      <c r="E342" s="9" t="n"/>
+      <c r="F342" s="9" t="n"/>
+      <c r="G342" s="9" t="n"/>
       <c r="H342" s="9" t="n"/>
+      <c r="O342" s="9" t="n"/>
     </row>
     <row r="343">
+      <c r="A343" s="9" t="n"/>
+      <c r="D343" s="9" t="n"/>
+      <c r="E343" s="9" t="n"/>
+      <c r="F343" s="9" t="n"/>
+      <c r="G343" s="9" t="n"/>
       <c r="H343" s="9" t="n"/>
+      <c r="O343" s="9" t="n"/>
     </row>
     <row r="344">
+      <c r="A344" s="9" t="n"/>
+      <c r="D344" s="9" t="n"/>
+      <c r="E344" s="9" t="n"/>
+      <c r="F344" s="9" t="n"/>
+      <c r="G344" s="9" t="n"/>
       <c r="H344" s="9" t="n"/>
+      <c r="O344" s="9" t="n"/>
     </row>
     <row r="345">
+      <c r="A345" s="9" t="n"/>
+      <c r="D345" s="9" t="n"/>
+      <c r="E345" s="9" t="n"/>
+      <c r="F345" s="9" t="n"/>
+      <c r="G345" s="9" t="n"/>
       <c r="H345" s="9" t="n"/>
+      <c r="O345" s="9" t="n"/>
     </row>
     <row r="346">
+      <c r="A346" s="9" t="n"/>
+      <c r="D346" s="9" t="n"/>
+      <c r="E346" s="9" t="n"/>
+      <c r="F346" s="9" t="n"/>
+      <c r="G346" s="9" t="n"/>
       <c r="H346" s="9" t="n"/>
+      <c r="O346" s="9" t="n"/>
     </row>
     <row r="347">
+      <c r="A347" s="9" t="n"/>
+      <c r="D347" s="9" t="n"/>
+      <c r="E347" s="9" t="n"/>
+      <c r="F347" s="9" t="n"/>
+      <c r="G347" s="9" t="n"/>
       <c r="H347" s="9" t="n"/>
+      <c r="O347" s="9" t="n"/>
     </row>
     <row r="348">
+      <c r="A348" s="9" t="n"/>
+      <c r="D348" s="9" t="n"/>
+      <c r="E348" s="9" t="n"/>
+      <c r="F348" s="9" t="n"/>
+      <c r="G348" s="9" t="n"/>
       <c r="H348" s="9" t="n"/>
+      <c r="O348" s="9" t="n"/>
     </row>
     <row r="349">
+      <c r="A349" s="9" t="n"/>
+      <c r="D349" s="9" t="n"/>
+      <c r="E349" s="9" t="n"/>
+      <c r="F349" s="9" t="n"/>
+      <c r="G349" s="9" t="n"/>
       <c r="H349" s="9" t="n"/>
+      <c r="O349" s="9" t="n"/>
     </row>
     <row r="350">
+      <c r="A350" s="9" t="n"/>
+      <c r="D350" s="9" t="n"/>
+      <c r="E350" s="9" t="n"/>
+      <c r="F350" s="9" t="n"/>
+      <c r="G350" s="9" t="n"/>
       <c r="H350" s="9" t="n"/>
+      <c r="O350" s="9" t="n"/>
     </row>
     <row r="351">
+      <c r="A351" s="9" t="n"/>
+      <c r="D351" s="9" t="n"/>
+      <c r="E351" s="9" t="n"/>
+      <c r="F351" s="9" t="n"/>
+      <c r="G351" s="9" t="n"/>
       <c r="H351" s="9" t="n"/>
+      <c r="O351" s="9" t="n"/>
     </row>
     <row r="352">
+      <c r="A352" s="9" t="n"/>
+      <c r="D352" s="9" t="n"/>
+      <c r="E352" s="9" t="n"/>
+      <c r="F352" s="9" t="n"/>
+      <c r="G352" s="9" t="n"/>
       <c r="H352" s="9" t="n"/>
+      <c r="O352" s="9" t="n"/>
     </row>
     <row r="353">
+      <c r="A353" s="9" t="n"/>
+      <c r="D353" s="9" t="n"/>
+      <c r="E353" s="9" t="n"/>
+      <c r="F353" s="9" t="n"/>
+      <c r="G353" s="9" t="n"/>
       <c r="H353" s="9" t="n"/>
+      <c r="O353" s="9" t="n"/>
     </row>
     <row r="354">
+      <c r="A354" s="9" t="n"/>
+      <c r="D354" s="9" t="n"/>
+      <c r="E354" s="9" t="n"/>
+      <c r="F354" s="9" t="n"/>
+      <c r="G354" s="9" t="n"/>
       <c r="H354" s="9" t="n"/>
+      <c r="O354" s="9" t="n"/>
     </row>
     <row r="355">
+      <c r="A355" s="9" t="n"/>
+      <c r="D355" s="9" t="n"/>
+      <c r="E355" s="9" t="n"/>
+      <c r="F355" s="9" t="n"/>
+      <c r="G355" s="9" t="n"/>
       <c r="H355" s="9" t="n"/>
+      <c r="O355" s="9" t="n"/>
     </row>
     <row r="356">
+      <c r="A356" s="9" t="n"/>
+      <c r="D356" s="9" t="n"/>
+      <c r="E356" s="9" t="n"/>
+      <c r="F356" s="9" t="n"/>
+      <c r="G356" s="9" t="n"/>
       <c r="H356" s="9" t="n"/>
+      <c r="O356" s="9" t="n"/>
     </row>
     <row r="357">
+      <c r="A357" s="9" t="n"/>
+      <c r="D357" s="9" t="n"/>
+      <c r="E357" s="9" t="n"/>
+      <c r="F357" s="9" t="n"/>
+      <c r="G357" s="9" t="n"/>
       <c r="H357" s="9" t="n"/>
+      <c r="O357" s="9" t="n"/>
     </row>
     <row r="358">
+      <c r="A358" s="9" t="n"/>
+      <c r="D358" s="9" t="n"/>
+      <c r="E358" s="9" t="n"/>
+      <c r="F358" s="9" t="n"/>
+      <c r="G358" s="9" t="n"/>
       <c r="H358" s="9" t="n"/>
+      <c r="O358" s="9" t="n"/>
     </row>
     <row r="359">
+      <c r="A359" s="9" t="n"/>
+      <c r="D359" s="9" t="n"/>
+      <c r="E359" s="9" t="n"/>
+      <c r="F359" s="9" t="n"/>
+      <c r="G359" s="9" t="n"/>
       <c r="H359" s="9" t="n"/>
+      <c r="O359" s="9" t="n"/>
     </row>
     <row r="360">
+      <c r="A360" s="9" t="n"/>
+      <c r="D360" s="9" t="n"/>
+      <c r="E360" s="9" t="n"/>
+      <c r="F360" s="9" t="n"/>
+      <c r="G360" s="9" t="n"/>
       <c r="H360" s="9" t="n"/>
+      <c r="O360" s="9" t="n"/>
     </row>
     <row r="361">
+      <c r="A361" s="9" t="n"/>
+      <c r="D361" s="9" t="n"/>
+      <c r="E361" s="9" t="n"/>
+      <c r="F361" s="9" t="n"/>
+      <c r="G361" s="9" t="n"/>
       <c r="H361" s="9" t="n"/>
+      <c r="O361" s="9" t="n"/>
     </row>
     <row r="362">
+      <c r="A362" s="9" t="n"/>
+      <c r="D362" s="9" t="n"/>
+      <c r="E362" s="9" t="n"/>
+      <c r="F362" s="9" t="n"/>
+      <c r="G362" s="9" t="n"/>
       <c r="H362" s="9" t="n"/>
+      <c r="O362" s="9" t="n"/>
     </row>
     <row r="363">
+      <c r="A363" s="9" t="n"/>
+      <c r="D363" s="9" t="n"/>
+      <c r="E363" s="9" t="n"/>
+      <c r="F363" s="9" t="n"/>
+      <c r="G363" s="9" t="n"/>
       <c r="H363" s="9" t="n"/>
+      <c r="O363" s="9" t="n"/>
     </row>
     <row r="364">
+      <c r="A364" s="9" t="n"/>
+      <c r="D364" s="9" t="n"/>
+      <c r="E364" s="9" t="n"/>
+      <c r="F364" s="9" t="n"/>
+      <c r="G364" s="9" t="n"/>
       <c r="H364" s="9" t="n"/>
+      <c r="O364" s="9" t="n"/>
     </row>
     <row r="365">
+      <c r="A365" s="9" t="n"/>
+      <c r="D365" s="9" t="n"/>
+      <c r="E365" s="9" t="n"/>
+      <c r="F365" s="9" t="n"/>
+      <c r="G365" s="9" t="n"/>
       <c r="H365" s="9" t="n"/>
+      <c r="O365" s="9" t="n"/>
     </row>
     <row r="366">
+      <c r="A366" s="9" t="n"/>
+      <c r="D366" s="9" t="n"/>
+      <c r="E366" s="9" t="n"/>
+      <c r="F366" s="9" t="n"/>
+      <c r="G366" s="9" t="n"/>
       <c r="H366" s="9" t="n"/>
+      <c r="O366" s="9" t="n"/>
     </row>
     <row r="367">
+      <c r="A367" s="9" t="n"/>
+      <c r="D367" s="9" t="n"/>
+      <c r="E367" s="9" t="n"/>
+      <c r="F367" s="9" t="n"/>
+      <c r="G367" s="9" t="n"/>
       <c r="H367" s="9" t="n"/>
+      <c r="O367" s="9" t="n"/>
     </row>
     <row r="368">
+      <c r="A368" s="9" t="n"/>
+      <c r="D368" s="9" t="n"/>
+      <c r="E368" s="9" t="n"/>
+      <c r="F368" s="9" t="n"/>
+      <c r="G368" s="9" t="n"/>
       <c r="H368" s="9" t="n"/>
+      <c r="O368" s="9" t="n"/>
     </row>
     <row r="369">
+      <c r="A369" s="9" t="n"/>
+      <c r="D369" s="9" t="n"/>
+      <c r="E369" s="9" t="n"/>
+      <c r="F369" s="9" t="n"/>
+      <c r="G369" s="9" t="n"/>
       <c r="H369" s="9" t="n"/>
+      <c r="O369" s="9" t="n"/>
     </row>
     <row r="370">
+      <c r="A370" s="9" t="n"/>
+      <c r="D370" s="9" t="n"/>
+      <c r="E370" s="9" t="n"/>
+      <c r="F370" s="9" t="n"/>
+      <c r="G370" s="9" t="n"/>
       <c r="H370" s="9" t="n"/>
+      <c r="O370" s="9" t="n"/>
     </row>
     <row r="371">
+      <c r="A371" s="9" t="n"/>
+      <c r="D371" s="9" t="n"/>
+      <c r="E371" s="9" t="n"/>
+      <c r="F371" s="9" t="n"/>
+      <c r="G371" s="9" t="n"/>
       <c r="H371" s="9" t="n"/>
+      <c r="O371" s="9" t="n"/>
     </row>
     <row r="372">
+      <c r="A372" s="9" t="n"/>
+      <c r="D372" s="9" t="n"/>
+      <c r="E372" s="9" t="n"/>
+      <c r="F372" s="9" t="n"/>
+      <c r="G372" s="9" t="n"/>
       <c r="H372" s="9" t="n"/>
+      <c r="O372" s="9" t="n"/>
     </row>
     <row r="373">
+      <c r="A373" s="9" t="n"/>
+      <c r="D373" s="9" t="n"/>
+      <c r="E373" s="9" t="n"/>
+      <c r="F373" s="9" t="n"/>
+      <c r="G373" s="9" t="n"/>
       <c r="H373" s="9" t="n"/>
+      <c r="O373" s="9" t="n"/>
     </row>
     <row r="374">
+      <c r="A374" s="9" t="n"/>
+      <c r="D374" s="9" t="n"/>
+      <c r="E374" s="9" t="n"/>
+      <c r="F374" s="9" t="n"/>
+      <c r="G374" s="9" t="n"/>
       <c r="H374" s="9" t="n"/>
+      <c r="O374" s="9" t="n"/>
     </row>
     <row r="375">
+      <c r="A375" s="9" t="n"/>
+      <c r="D375" s="9" t="n"/>
+      <c r="E375" s="9" t="n"/>
+      <c r="F375" s="9" t="n"/>
+      <c r="G375" s="9" t="n"/>
       <c r="H375" s="9" t="n"/>
+      <c r="O375" s="9" t="n"/>
     </row>
     <row r="376">
+      <c r="A376" s="9" t="n"/>
+      <c r="D376" s="9" t="n"/>
+      <c r="E376" s="9" t="n"/>
+      <c r="F376" s="9" t="n"/>
+      <c r="G376" s="9" t="n"/>
       <c r="H376" s="9" t="n"/>
+      <c r="O376" s="9" t="n"/>
     </row>
     <row r="377">
+      <c r="A377" s="9" t="n"/>
+      <c r="D377" s="9" t="n"/>
+      <c r="E377" s="9" t="n"/>
+      <c r="F377" s="9" t="n"/>
+      <c r="G377" s="9" t="n"/>
       <c r="H377" s="9" t="n"/>
+      <c r="O377" s="9" t="n"/>
     </row>
     <row r="378">
+      <c r="A378" s="9" t="n"/>
+      <c r="D378" s="9" t="n"/>
+      <c r="E378" s="9" t="n"/>
+      <c r="F378" s="9" t="n"/>
+      <c r="G378" s="9" t="n"/>
       <c r="H378" s="9" t="n"/>
+      <c r="O378" s="9" t="n"/>
     </row>
     <row r="379">
+      <c r="A379" s="9" t="n"/>
+      <c r="D379" s="9" t="n"/>
+      <c r="E379" s="9" t="n"/>
+      <c r="F379" s="9" t="n"/>
+      <c r="G379" s="9" t="n"/>
       <c r="H379" s="9" t="n"/>
+      <c r="O379" s="9" t="n"/>
     </row>
     <row r="380">
+      <c r="A380" s="9" t="n"/>
+      <c r="D380" s="9" t="n"/>
+      <c r="E380" s="9" t="n"/>
+      <c r="F380" s="9" t="n"/>
+      <c r="G380" s="9" t="n"/>
       <c r="H380" s="9" t="n"/>
+      <c r="O380" s="9" t="n"/>
     </row>
     <row r="381">
+      <c r="A381" s="9" t="n"/>
+      <c r="D381" s="9" t="n"/>
+      <c r="E381" s="9" t="n"/>
+      <c r="F381" s="9" t="n"/>
+      <c r="G381" s="9" t="n"/>
       <c r="H381" s="9" t="n"/>
+      <c r="O381" s="9" t="n"/>
     </row>
     <row r="382">
+      <c r="A382" s="9" t="n"/>
+      <c r="D382" s="9" t="n"/>
+      <c r="E382" s="9" t="n"/>
+      <c r="F382" s="9" t="n"/>
+      <c r="G382" s="9" t="n"/>
       <c r="H382" s="9" t="n"/>
+      <c r="O382" s="9" t="n"/>
     </row>
     <row r="383">
+      <c r="A383" s="9" t="n"/>
+      <c r="D383" s="9" t="n"/>
+      <c r="E383" s="9" t="n"/>
+      <c r="F383" s="9" t="n"/>
+      <c r="G383" s="9" t="n"/>
       <c r="H383" s="9" t="n"/>
+      <c r="O383" s="9" t="n"/>
     </row>
     <row r="384">
+      <c r="A384" s="9" t="n"/>
+      <c r="D384" s="9" t="n"/>
+      <c r="E384" s="9" t="n"/>
+      <c r="F384" s="9" t="n"/>
+      <c r="G384" s="9" t="n"/>
       <c r="H384" s="9" t="n"/>
+      <c r="O384" s="9" t="n"/>
     </row>
     <row r="385">
+      <c r="A385" s="9" t="n"/>
+      <c r="D385" s="9" t="n"/>
+      <c r="E385" s="9" t="n"/>
+      <c r="F385" s="9" t="n"/>
+      <c r="G385" s="9" t="n"/>
       <c r="H385" s="9" t="n"/>
+      <c r="O385" s="9" t="n"/>
     </row>
     <row r="386">
+      <c r="A386" s="9" t="n"/>
+      <c r="D386" s="9" t="n"/>
+      <c r="E386" s="9" t="n"/>
+      <c r="F386" s="9" t="n"/>
+      <c r="G386" s="9" t="n"/>
       <c r="H386" s="9" t="n"/>
+      <c r="O386" s="9" t="n"/>
     </row>
     <row r="387">
+      <c r="A387" s="9" t="n"/>
+      <c r="D387" s="9" t="n"/>
+      <c r="E387" s="9" t="n"/>
+      <c r="F387" s="9" t="n"/>
+      <c r="G387" s="9" t="n"/>
       <c r="H387" s="9" t="n"/>
+      <c r="O387" s="9" t="n"/>
     </row>
     <row r="388">
+      <c r="A388" s="9" t="n"/>
+      <c r="D388" s="9" t="n"/>
+      <c r="E388" s="9" t="n"/>
+      <c r="F388" s="9" t="n"/>
+      <c r="G388" s="9" t="n"/>
       <c r="H388" s="9" t="n"/>
+      <c r="O388" s="9" t="n"/>
     </row>
     <row r="389">
+      <c r="A389" s="9" t="n"/>
+      <c r="D389" s="9" t="n"/>
+      <c r="E389" s="9" t="n"/>
+      <c r="F389" s="9" t="n"/>
+      <c r="G389" s="9" t="n"/>
       <c r="H389" s="9" t="n"/>
+      <c r="O389" s="9" t="n"/>
     </row>
     <row r="390">
+      <c r="A390" s="9" t="n"/>
+      <c r="D390" s="9" t="n"/>
+      <c r="E390" s="9" t="n"/>
+      <c r="F390" s="9" t="n"/>
+      <c r="G390" s="9" t="n"/>
       <c r="H390" s="9" t="n"/>
+      <c r="O390" s="9" t="n"/>
     </row>
     <row r="391">
+      <c r="A391" s="9" t="n"/>
+      <c r="D391" s="9" t="n"/>
+      <c r="E391" s="9" t="n"/>
+      <c r="F391" s="9" t="n"/>
+      <c r="G391" s="9" t="n"/>
       <c r="H391" s="9" t="n"/>
+      <c r="O391" s="9" t="n"/>
     </row>
     <row r="392">
+      <c r="A392" s="9" t="n"/>
+      <c r="D392" s="9" t="n"/>
+      <c r="E392" s="9" t="n"/>
+      <c r="F392" s="9" t="n"/>
+      <c r="G392" s="9" t="n"/>
       <c r="H392" s="9" t="n"/>
+      <c r="O392" s="9" t="n"/>
     </row>
     <row r="393">
+      <c r="A393" s="9" t="n"/>
+      <c r="D393" s="9" t="n"/>
+      <c r="E393" s="9" t="n"/>
+      <c r="F393" s="9" t="n"/>
+      <c r="G393" s="9" t="n"/>
       <c r="H393" s="9" t="n"/>
+      <c r="O393" s="9" t="n"/>
     </row>
     <row r="394">
+      <c r="A394" s="9" t="n"/>
+      <c r="D394" s="9" t="n"/>
+      <c r="E394" s="9" t="n"/>
+      <c r="F394" s="9" t="n"/>
+      <c r="G394" s="9" t="n"/>
       <c r="H394" s="9" t="n"/>
+      <c r="O394" s="9" t="n"/>
     </row>
     <row r="395">
+      <c r="A395" s="9" t="n"/>
+      <c r="D395" s="9" t="n"/>
+      <c r="E395" s="9" t="n"/>
+      <c r="F395" s="9" t="n"/>
+      <c r="G395" s="9" t="n"/>
       <c r="H395" s="9" t="n"/>
+      <c r="O395" s="9" t="n"/>
     </row>
     <row r="396">
+      <c r="A396" s="9" t="n"/>
+      <c r="D396" s="9" t="n"/>
+      <c r="E396" s="9" t="n"/>
+      <c r="F396" s="9" t="n"/>
+      <c r="G396" s="9" t="n"/>
       <c r="H396" s="9" t="n"/>
+      <c r="O396" s="9" t="n"/>
     </row>
     <row r="397">
+      <c r="A397" s="9" t="n"/>
+      <c r="D397" s="9" t="n"/>
+      <c r="E397" s="9" t="n"/>
+      <c r="F397" s="9" t="n"/>
+      <c r="G397" s="9" t="n"/>
       <c r="H397" s="9" t="n"/>
+      <c r="O397" s="9" t="n"/>
     </row>
     <row r="398">
+      <c r="A398" s="9" t="n"/>
+      <c r="D398" s="9" t="n"/>
+      <c r="E398" s="9" t="n"/>
+      <c r="F398" s="9" t="n"/>
+      <c r="G398" s="9" t="n"/>
       <c r="H398" s="9" t="n"/>
+      <c r="O398" s="9" t="n"/>
     </row>
     <row r="399">
+      <c r="A399" s="9" t="n"/>
+      <c r="D399" s="9" t="n"/>
+      <c r="E399" s="9" t="n"/>
+      <c r="F399" s="9" t="n"/>
+      <c r="G399" s="9" t="n"/>
       <c r="H399" s="9" t="n"/>
+      <c r="O399" s="9" t="n"/>
     </row>
     <row r="400">
+      <c r="A400" s="9" t="n"/>
+      <c r="D400" s="9" t="n"/>
+      <c r="E400" s="9" t="n"/>
+      <c r="F400" s="9" t="n"/>
+      <c r="G400" s="9" t="n"/>
       <c r="H400" s="9" t="n"/>
+      <c r="O400" s="9" t="n"/>
     </row>
     <row r="401">
+      <c r="A401" s="9" t="n"/>
+      <c r="D401" s="9" t="n"/>
+      <c r="E401" s="9" t="n"/>
+      <c r="F401" s="9" t="n"/>
+      <c r="G401" s="9" t="n"/>
       <c r="H401" s="9" t="n"/>
+      <c r="O401" s="9" t="n"/>
     </row>
     <row r="402">
+      <c r="A402" s="9" t="n"/>
+      <c r="D402" s="9" t="n"/>
+      <c r="E402" s="9" t="n"/>
+      <c r="F402" s="9" t="n"/>
+      <c r="G402" s="9" t="n"/>
       <c r="H402" s="9" t="n"/>
+      <c r="O402" s="9" t="n"/>
     </row>
     <row r="403">
+      <c r="A403" s="9" t="n"/>
+      <c r="D403" s="9" t="n"/>
+      <c r="E403" s="9" t="n"/>
+      <c r="F403" s="9" t="n"/>
+      <c r="G403" s="9" t="n"/>
       <c r="H403" s="9" t="n"/>
+      <c r="O403" s="9" t="n"/>
     </row>
     <row r="404">
+      <c r="A404" s="9" t="n"/>
+      <c r="D404" s="9" t="n"/>
+      <c r="E404" s="9" t="n"/>
+      <c r="F404" s="9" t="n"/>
+      <c r="G404" s="9" t="n"/>
       <c r="H404" s="9" t="n"/>
+      <c r="O404" s="9" t="n"/>
     </row>
     <row r="405">
+      <c r="A405" s="9" t="n"/>
+      <c r="D405" s="9" t="n"/>
+      <c r="E405" s="9" t="n"/>
+      <c r="F405" s="9" t="n"/>
+      <c r="G405" s="9" t="n"/>
       <c r="H405" s="9" t="n"/>
+      <c r="O405" s="9" t="n"/>
     </row>
     <row r="406">
+      <c r="A406" s="9" t="n"/>
+      <c r="D406" s="9" t="n"/>
+      <c r="E406" s="9" t="n"/>
+      <c r="F406" s="9" t="n"/>
+      <c r="G406" s="9" t="n"/>
       <c r="H406" s="9" t="n"/>
+      <c r="O406" s="9" t="n"/>
     </row>
     <row r="407">
+      <c r="A407" s="9" t="n"/>
+      <c r="D407" s="9" t="n"/>
+      <c r="E407" s="9" t="n"/>
+      <c r="F407" s="9" t="n"/>
+      <c r="G407" s="9" t="n"/>
       <c r="H407" s="9" t="n"/>
+      <c r="O407" s="9" t="n"/>
     </row>
     <row r="408">
+      <c r="A408" s="9" t="n"/>
+      <c r="D408" s="9" t="n"/>
+      <c r="E408" s="9" t="n"/>
+      <c r="F408" s="9" t="n"/>
+      <c r="G408" s="9" t="n"/>
       <c r="H408" s="9" t="n"/>
+      <c r="O408" s="9" t="n"/>
     </row>
     <row r="409">
+      <c r="A409" s="9" t="n"/>
+      <c r="D409" s="9" t="n"/>
+      <c r="E409" s="9" t="n"/>
+      <c r="F409" s="9" t="n"/>
+      <c r="G409" s="9" t="n"/>
       <c r="H409" s="9" t="n"/>
+      <c r="O409" s="9" t="n"/>
     </row>
     <row r="410">
+      <c r="A410" s="9" t="n"/>
+      <c r="D410" s="9" t="n"/>
+      <c r="E410" s="9" t="n"/>
+      <c r="F410" s="9" t="n"/>
+      <c r="G410" s="9" t="n"/>
       <c r="H410" s="9" t="n"/>
+      <c r="O410" s="9" t="n"/>
     </row>
     <row r="411">
+      <c r="A411" s="9" t="n"/>
+      <c r="D411" s="9" t="n"/>
+      <c r="E411" s="9" t="n"/>
+      <c r="F411" s="9" t="n"/>
+      <c r="G411" s="9" t="n"/>
       <c r="H411" s="9" t="n"/>
+      <c r="O411" s="9" t="n"/>
     </row>
     <row r="412">
+      <c r="A412" s="9" t="n"/>
+      <c r="D412" s="9" t="n"/>
+      <c r="E412" s="9" t="n"/>
+      <c r="F412" s="9" t="n"/>
+      <c r="G412" s="9" t="n"/>
       <c r="H412" s="9" t="n"/>
+      <c r="O412" s="9" t="n"/>
     </row>
     <row r="413">
+      <c r="A413" s="9" t="n"/>
+      <c r="D413" s="9" t="n"/>
+      <c r="E413" s="9" t="n"/>
+      <c r="F413" s="9" t="n"/>
+      <c r="G413" s="9" t="n"/>
       <c r="H413" s="9" t="n"/>
+      <c r="O413" s="9" t="n"/>
     </row>
     <row r="414">
+      <c r="A414" s="9" t="n"/>
+      <c r="D414" s="9" t="n"/>
+      <c r="E414" s="9" t="n"/>
+      <c r="F414" s="9" t="n"/>
+      <c r="G414" s="9" t="n"/>
       <c r="H414" s="9" t="n"/>
+      <c r="O414" s="9" t="n"/>
     </row>
     <row r="415">
+      <c r="A415" s="9" t="n"/>
+      <c r="D415" s="9" t="n"/>
+      <c r="E415" s="9" t="n"/>
+      <c r="F415" s="9" t="n"/>
+      <c r="G415" s="9" t="n"/>
       <c r="H415" s="9" t="n"/>
+      <c r="O415" s="9" t="n"/>
     </row>
     <row r="416">
+      <c r="A416" s="9" t="n"/>
+      <c r="D416" s="9" t="n"/>
+      <c r="E416" s="9" t="n"/>
+      <c r="F416" s="9" t="n"/>
+      <c r="G416" s="9" t="n"/>
       <c r="H416" s="9" t="n"/>
+      <c r="O416" s="9" t="n"/>
     </row>
     <row r="417">
+      <c r="A417" s="9" t="n"/>
+      <c r="D417" s="9" t="n"/>
+      <c r="E417" s="9" t="n"/>
+      <c r="F417" s="9" t="n"/>
+      <c r="G417" s="9" t="n"/>
       <c r="H417" s="9" t="n"/>
+      <c r="O417" s="9" t="n"/>
     </row>
     <row r="418">
+      <c r="A418" s="9" t="n"/>
+      <c r="D418" s="9" t="n"/>
+      <c r="E418" s="9" t="n"/>
+      <c r="F418" s="9" t="n"/>
+      <c r="G418" s="9" t="n"/>
       <c r="H418" s="9" t="n"/>
+      <c r="O418" s="9" t="n"/>
     </row>
     <row r="419">
+      <c r="A419" s="9" t="n"/>
+      <c r="D419" s="9" t="n"/>
+      <c r="E419" s="9" t="n"/>
+      <c r="F419" s="9" t="n"/>
+      <c r="G419" s="9" t="n"/>
       <c r="H419" s="9" t="n"/>
+      <c r="O419" s="9" t="n"/>
     </row>
     <row r="420">
+      <c r="A420" s="9" t="n"/>
+      <c r="D420" s="9" t="n"/>
+      <c r="E420" s="9" t="n"/>
+      <c r="F420" s="9" t="n"/>
+      <c r="G420" s="9" t="n"/>
       <c r="H420" s="9" t="n"/>
+      <c r="O420" s="9" t="n"/>
     </row>
     <row r="421">
+      <c r="A421" s="9" t="n"/>
+      <c r="D421" s="9" t="n"/>
+      <c r="E421" s="9" t="n"/>
+      <c r="F421" s="9" t="n"/>
+      <c r="G421" s="9" t="n"/>
       <c r="H421" s="9" t="n"/>
+      <c r="O421" s="9" t="n"/>
     </row>
     <row r="422">
+      <c r="A422" s="9" t="n"/>
+      <c r="D422" s="9" t="n"/>
+      <c r="E422" s="9" t="n"/>
+      <c r="F422" s="9" t="n"/>
+      <c r="G422" s="9" t="n"/>
       <c r="H422" s="9" t="n"/>
+      <c r="O422" s="9" t="n"/>
     </row>
     <row r="423">
+      <c r="A423" s="9" t="n"/>
+      <c r="D423" s="9" t="n"/>
+      <c r="E423" s="9" t="n"/>
+      <c r="F423" s="9" t="n"/>
+      <c r="G423" s="9" t="n"/>
       <c r="H423" s="9" t="n"/>
+      <c r="O423" s="9" t="n"/>
     </row>
     <row r="424">
+      <c r="A424" s="9" t="n"/>
+      <c r="D424" s="9" t="n"/>
+      <c r="E424" s="9" t="n"/>
+      <c r="F424" s="9" t="n"/>
+      <c r="G424" s="9" t="n"/>
       <c r="H424" s="9" t="n"/>
+      <c r="O424" s="9" t="n"/>
     </row>
     <row r="425">
+      <c r="A425" s="9" t="n"/>
+      <c r="D425" s="9" t="n"/>
+      <c r="E425" s="9" t="n"/>
+      <c r="F425" s="9" t="n"/>
+      <c r="G425" s="9" t="n"/>
       <c r="H425" s="9" t="n"/>
+      <c r="O425" s="9" t="n"/>
     </row>
     <row r="426">
+      <c r="A426" s="9" t="n"/>
+      <c r="D426" s="9" t="n"/>
+      <c r="E426" s="9" t="n"/>
+      <c r="F426" s="9" t="n"/>
+      <c r="G426" s="9" t="n"/>
       <c r="H426" s="9" t="n"/>
+      <c r="O426" s="9" t="n"/>
     </row>
     <row r="427">
+      <c r="A427" s="9" t="n"/>
+      <c r="D427" s="9" t="n"/>
+      <c r="E427" s="9" t="n"/>
+      <c r="F427" s="9" t="n"/>
+      <c r="G427" s="9" t="n"/>
       <c r="H427" s="9" t="n"/>
+      <c r="O427" s="9" t="n"/>
     </row>
     <row r="428">
+      <c r="A428" s="9" t="n"/>
+      <c r="D428" s="9" t="n"/>
+      <c r="E428" s="9" t="n"/>
+      <c r="F428" s="9" t="n"/>
+      <c r="G428" s="9" t="n"/>
       <c r="H428" s="9" t="n"/>
+      <c r="O428" s="9" t="n"/>
     </row>
     <row r="429">
+      <c r="A429" s="9" t="n"/>
+      <c r="D429" s="9" t="n"/>
+      <c r="E429" s="9" t="n"/>
+      <c r="F429" s="9" t="n"/>
+      <c r="G429" s="9" t="n"/>
       <c r="H429" s="9" t="n"/>
+      <c r="O429" s="9" t="n"/>
     </row>
     <row r="430">
+      <c r="A430" s="9" t="n"/>
+      <c r="D430" s="9" t="n"/>
+      <c r="E430" s="9" t="n"/>
+      <c r="F430" s="9" t="n"/>
+      <c r="G430" s="9" t="n"/>
       <c r="H430" s="9" t="n"/>
+      <c r="O430" s="9" t="n"/>
     </row>
     <row r="431">
+      <c r="A431" s="9" t="n"/>
+      <c r="D431" s="9" t="n"/>
+      <c r="E431" s="9" t="n"/>
+      <c r="F431" s="9" t="n"/>
+      <c r="G431" s="9" t="n"/>
       <c r="H431" s="9" t="n"/>
+      <c r="O431" s="9" t="n"/>
     </row>
     <row r="432">
+      <c r="A432" s="9" t="n"/>
+      <c r="D432" s="9" t="n"/>
+      <c r="E432" s="9" t="n"/>
+      <c r="F432" s="9" t="n"/>
+      <c r="G432" s="9" t="n"/>
       <c r="H432" s="9" t="n"/>
+      <c r="O432" s="9" t="n"/>
     </row>
     <row r="433">
+      <c r="A433" s="9" t="n"/>
+      <c r="D433" s="9" t="n"/>
+      <c r="E433" s="9" t="n"/>
+      <c r="F433" s="9" t="n"/>
+      <c r="G433" s="9" t="n"/>
       <c r="H433" s="9" t="n"/>
+      <c r="O433" s="9" t="n"/>
     </row>
     <row r="434">
+      <c r="A434" s="9" t="n"/>
+      <c r="D434" s="9" t="n"/>
+      <c r="E434" s="9" t="n"/>
+      <c r="F434" s="9" t="n"/>
+      <c r="G434" s="9" t="n"/>
       <c r="H434" s="9" t="n"/>
+      <c r="O434" s="9" t="n"/>
     </row>
     <row r="435">
+      <c r="A435" s="9" t="n"/>
+      <c r="D435" s="9" t="n"/>
+      <c r="E435" s="9" t="n"/>
+      <c r="F435" s="9" t="n"/>
+      <c r="G435" s="9" t="n"/>
       <c r="H435" s="9" t="n"/>
+      <c r="O435" s="9" t="n"/>
     </row>
     <row r="436">
+      <c r="A436" s="9" t="n"/>
+      <c r="D436" s="9" t="n"/>
+      <c r="E436" s="9" t="n"/>
+      <c r="F436" s="9" t="n"/>
+      <c r="G436" s="9" t="n"/>
       <c r="H436" s="9" t="n"/>
+      <c r="O436" s="9" t="n"/>
     </row>
     <row r="437">
+      <c r="A437" s="9" t="n"/>
+      <c r="D437" s="9" t="n"/>
+      <c r="E437" s="9" t="n"/>
+      <c r="F437" s="9" t="n"/>
+      <c r="G437" s="9" t="n"/>
       <c r="H437" s="9" t="n"/>
+      <c r="O437" s="9" t="n"/>
     </row>
     <row r="438">
+      <c r="A438" s="9" t="n"/>
+      <c r="D438" s="9" t="n"/>
+      <c r="E438" s="9" t="n"/>
+      <c r="F438" s="9" t="n"/>
+      <c r="G438" s="9" t="n"/>
       <c r="H438" s="9" t="n"/>
+      <c r="O438" s="9" t="n"/>
     </row>
     <row r="439">
+      <c r="A439" s="9" t="n"/>
+      <c r="D439" s="9" t="n"/>
+      <c r="E439" s="9" t="n"/>
+      <c r="F439" s="9" t="n"/>
+      <c r="G439" s="9" t="n"/>
       <c r="H439" s="9" t="n"/>
+      <c r="O439" s="9" t="n"/>
     </row>
     <row r="440">
+      <c r="A440" s="9" t="n"/>
+      <c r="D440" s="9" t="n"/>
+      <c r="E440" s="9" t="n"/>
+      <c r="F440" s="9" t="n"/>
+      <c r="G440" s="9" t="n"/>
       <c r="H440" s="9" t="n"/>
+      <c r="O440" s="9" t="n"/>
     </row>
     <row r="441">
+      <c r="A441" s="9" t="n"/>
+      <c r="D441" s="9" t="n"/>
+      <c r="E441" s="9" t="n"/>
+      <c r="F441" s="9" t="n"/>
+      <c r="G441" s="9" t="n"/>
       <c r="H441" s="9" t="n"/>
+      <c r="O441" s="9" t="n"/>
     </row>
     <row r="442">
+      <c r="A442" s="9" t="n"/>
+      <c r="D442" s="9" t="n"/>
+      <c r="E442" s="9" t="n"/>
+      <c r="F442" s="9" t="n"/>
+      <c r="G442" s="9" t="n"/>
       <c r="H442" s="9" t="n"/>
+      <c r="O442" s="9" t="n"/>
     </row>
     <row r="443">
+      <c r="A443" s="9" t="n"/>
+      <c r="D443" s="9" t="n"/>
+      <c r="E443" s="9" t="n"/>
+      <c r="F443" s="9" t="n"/>
+      <c r="G443" s="9" t="n"/>
       <c r="H443" s="9" t="n"/>
+      <c r="O443" s="9" t="n"/>
     </row>
     <row r="444">
+      <c r="A444" s="9" t="n"/>
+      <c r="D444" s="9" t="n"/>
+      <c r="E444" s="9" t="n"/>
+      <c r="F444" s="9" t="n"/>
+      <c r="G444" s="9" t="n"/>
       <c r="H444" s="9" t="n"/>
+      <c r="O444" s="9" t="n"/>
     </row>
     <row r="445">
+      <c r="A445" s="9" t="n"/>
+      <c r="D445" s="9" t="n"/>
+      <c r="E445" s="9" t="n"/>
+      <c r="F445" s="9" t="n"/>
+      <c r="G445" s="9" t="n"/>
       <c r="H445" s="9" t="n"/>
+      <c r="O445" s="9" t="n"/>
     </row>
     <row r="446">
+      <c r="A446" s="9" t="n"/>
+      <c r="D446" s="9" t="n"/>
+      <c r="E446" s="9" t="n"/>
+      <c r="F446" s="9" t="n"/>
+      <c r="G446" s="9" t="n"/>
       <c r="H446" s="9" t="n"/>
+      <c r="O446" s="9" t="n"/>
     </row>
     <row r="447">
+      <c r="A447" s="9" t="n"/>
+      <c r="D447" s="9" t="n"/>
+      <c r="E447" s="9" t="n"/>
+      <c r="F447" s="9" t="n"/>
+      <c r="G447" s="9" t="n"/>
       <c r="H447" s="9" t="n"/>
+      <c r="O447" s="9" t="n"/>
     </row>
     <row r="448">
+      <c r="A448" s="9" t="n"/>
+      <c r="D448" s="9" t="n"/>
+      <c r="E448" s="9" t="n"/>
+      <c r="F448" s="9" t="n"/>
+      <c r="G448" s="9" t="n"/>
       <c r="H448" s="9" t="n"/>
+      <c r="O448" s="9" t="n"/>
     </row>
     <row r="449">
+      <c r="A449" s="9" t="n"/>
+      <c r="D449" s="9" t="n"/>
+      <c r="E449" s="9" t="n"/>
+      <c r="F449" s="9" t="n"/>
+      <c r="G449" s="9" t="n"/>
       <c r="H449" s="9" t="n"/>
+      <c r="O449" s="9" t="n"/>
     </row>
     <row r="450">
+      <c r="A450" s="9" t="n"/>
+      <c r="D450" s="9" t="n"/>
+      <c r="E450" s="9" t="n"/>
+      <c r="F450" s="9" t="n"/>
+      <c r="G450" s="9" t="n"/>
       <c r="H450" s="9" t="n"/>
+      <c r="O450" s="9" t="n"/>
     </row>
     <row r="451">
+      <c r="A451" s="9" t="n"/>
+      <c r="D451" s="9" t="n"/>
+      <c r="E451" s="9" t="n"/>
+      <c r="F451" s="9" t="n"/>
+      <c r="G451" s="9" t="n"/>
       <c r="H451" s="9" t="n"/>
+      <c r="O451" s="9" t="n"/>
     </row>
     <row r="452">
+      <c r="A452" s="9" t="n"/>
+      <c r="D452" s="9" t="n"/>
+      <c r="E452" s="9" t="n"/>
+      <c r="F452" s="9" t="n"/>
+      <c r="G452" s="9" t="n"/>
       <c r="H452" s="9" t="n"/>
+      <c r="O452" s="9" t="n"/>
     </row>
     <row r="453">
+      <c r="A453" s="9" t="n"/>
+      <c r="D453" s="9" t="n"/>
+      <c r="E453" s="9" t="n"/>
+      <c r="F453" s="9" t="n"/>
+      <c r="G453" s="9" t="n"/>
       <c r="H453" s="9" t="n"/>
+      <c r="O453" s="9" t="n"/>
     </row>
     <row r="454">
+      <c r="A454" s="9" t="n"/>
+      <c r="D454" s="9" t="n"/>
+      <c r="E454" s="9" t="n"/>
+      <c r="F454" s="9" t="n"/>
+      <c r="G454" s="9" t="n"/>
       <c r="H454" s="9" t="n"/>
+      <c r="O454" s="9" t="n"/>
     </row>
     <row r="455">
+      <c r="A455" s="9" t="n"/>
+      <c r="D455" s="9" t="n"/>
+      <c r="E455" s="9" t="n"/>
+      <c r="F455" s="9" t="n"/>
+      <c r="G455" s="9" t="n"/>
       <c r="H455" s="9" t="n"/>
+      <c r="O455" s="9" t="n"/>
     </row>
     <row r="456">
+      <c r="A456" s="9" t="n"/>
+      <c r="D456" s="9" t="n"/>
+      <c r="E456" s="9" t="n"/>
+      <c r="F456" s="9" t="n"/>
+      <c r="G456" s="9" t="n"/>
       <c r="H456" s="9" t="n"/>
+      <c r="O456" s="9" t="n"/>
     </row>
     <row r="457">
+      <c r="A457" s="9" t="n"/>
+      <c r="D457" s="9" t="n"/>
+      <c r="E457" s="9" t="n"/>
+      <c r="F457" s="9" t="n"/>
+      <c r="G457" s="9" t="n"/>
       <c r="H457" s="9" t="n"/>
+      <c r="O457" s="9" t="n"/>
     </row>
     <row r="458">
+      <c r="A458" s="9" t="n"/>
+      <c r="D458" s="9" t="n"/>
+      <c r="E458" s="9" t="n"/>
+      <c r="F458" s="9" t="n"/>
+      <c r="G458" s="9" t="n"/>
       <c r="H458" s="9" t="n"/>
+      <c r="O458" s="9" t="n"/>
     </row>
     <row r="459">
+      <c r="A459" s="9" t="n"/>
+      <c r="D459" s="9" t="n"/>
+      <c r="E459" s="9" t="n"/>
+      <c r="F459" s="9" t="n"/>
+      <c r="G459" s="9" t="n"/>
       <c r="H459" s="9" t="n"/>
+      <c r="O459" s="9" t="n"/>
     </row>
     <row r="460">
+      <c r="A460" s="9" t="n"/>
+      <c r="D460" s="9" t="n"/>
+      <c r="E460" s="9" t="n"/>
+      <c r="F460" s="9" t="n"/>
+      <c r="G460" s="9" t="n"/>
       <c r="H460" s="9" t="n"/>
+      <c r="O460" s="9" t="n"/>
     </row>
     <row r="461">
+      <c r="A461" s="9" t="n"/>
+      <c r="D461" s="9" t="n"/>
+      <c r="E461" s="9" t="n"/>
+      <c r="F461" s="9" t="n"/>
+      <c r="G461" s="9" t="n"/>
       <c r="H461" s="9" t="n"/>
+      <c r="O461" s="9" t="n"/>
     </row>
     <row r="462">
+      <c r="A462" s="9" t="n"/>
+      <c r="D462" s="9" t="n"/>
+      <c r="E462" s="9" t="n"/>
+      <c r="F462" s="9" t="n"/>
+      <c r="G462" s="9" t="n"/>
       <c r="H462" s="9" t="n"/>
+      <c r="O462" s="9" t="n"/>
     </row>
     <row r="463">
+      <c r="A463" s="9" t="n"/>
+      <c r="D463" s="9" t="n"/>
+      <c r="E463" s="9" t="n"/>
+      <c r="F463" s="9" t="n"/>
+      <c r="G463" s="9" t="n"/>
       <c r="H463" s="9" t="n"/>
+      <c r="O463" s="9" t="n"/>
     </row>
     <row r="464">
+      <c r="A464" s="9" t="n"/>
+      <c r="D464" s="9" t="n"/>
+      <c r="E464" s="9" t="n"/>
+      <c r="F464" s="9" t="n"/>
+      <c r="G464" s="9" t="n"/>
       <c r="H464" s="9" t="n"/>
+      <c r="O464" s="9" t="n"/>
     </row>
     <row r="465">
+      <c r="A465" s="9" t="n"/>
+      <c r="D465" s="9" t="n"/>
+      <c r="E465" s="9" t="n"/>
+      <c r="F465" s="9" t="n"/>
+      <c r="G465" s="9" t="n"/>
       <c r="H465" s="9" t="n"/>
+      <c r="O465" s="9" t="n"/>
     </row>
     <row r="466">
+      <c r="A466" s="9" t="n"/>
+      <c r="D466" s="9" t="n"/>
+      <c r="E466" s="9" t="n"/>
+      <c r="F466" s="9" t="n"/>
+      <c r="G466" s="9" t="n"/>
       <c r="H466" s="9" t="n"/>
+      <c r="O466" s="9" t="n"/>
     </row>
     <row r="467">
+      <c r="A467" s="9" t="n"/>
+      <c r="D467" s="9" t="n"/>
+      <c r="E467" s="9" t="n"/>
+      <c r="F467" s="9" t="n"/>
+      <c r="G467" s="9" t="n"/>
       <c r="H467" s="9" t="n"/>
+      <c r="O467" s="9" t="n"/>
     </row>
     <row r="468">
+      <c r="A468" s="9" t="n"/>
+      <c r="D468" s="9" t="n"/>
+      <c r="E468" s="9" t="n"/>
+      <c r="F468" s="9" t="n"/>
+      <c r="G468" s="9" t="n"/>
       <c r="H468" s="9" t="n"/>
+      <c r="O468" s="9" t="n"/>
     </row>
     <row r="469">
+      <c r="A469" s="9" t="n"/>
+      <c r="D469" s="9" t="n"/>
+      <c r="E469" s="9" t="n"/>
+      <c r="F469" s="9" t="n"/>
+      <c r="G469" s="9" t="n"/>
       <c r="H469" s="9" t="n"/>
+      <c r="O469" s="9" t="n"/>
     </row>
     <row r="470">
+      <c r="A470" s="9" t="n"/>
+      <c r="D470" s="9" t="n"/>
+      <c r="E470" s="9" t="n"/>
+      <c r="F470" s="9" t="n"/>
+      <c r="G470" s="9" t="n"/>
       <c r="H470" s="9" t="n"/>
+      <c r="O470" s="9" t="n"/>
     </row>
     <row r="471">
+      <c r="A471" s="9" t="n"/>
+      <c r="D471" s="9" t="n"/>
+      <c r="E471" s="9" t="n"/>
+      <c r="F471" s="9" t="n"/>
+      <c r="G471" s="9" t="n"/>
       <c r="H471" s="9" t="n"/>
+      <c r="O471" s="9" t="n"/>
     </row>
     <row r="472">
+      <c r="A472" s="9" t="n"/>
+      <c r="D472" s="9" t="n"/>
+      <c r="E472" s="9" t="n"/>
+      <c r="F472" s="9" t="n"/>
+      <c r="G472" s="9" t="n"/>
       <c r="H472" s="9" t="n"/>
+      <c r="O472" s="9" t="n"/>
     </row>
     <row r="473">
+      <c r="A473" s="9" t="n"/>
+      <c r="D473" s="9" t="n"/>
+      <c r="E473" s="9" t="n"/>
+      <c r="F473" s="9" t="n"/>
+      <c r="G473" s="9" t="n"/>
       <c r="H473" s="9" t="n"/>
+      <c r="O473" s="9" t="n"/>
     </row>
     <row r="474">
+      <c r="A474" s="9" t="n"/>
+      <c r="D474" s="9" t="n"/>
+      <c r="E474" s="9" t="n"/>
+      <c r="F474" s="9" t="n"/>
+      <c r="G474" s="9" t="n"/>
       <c r="H474" s="9" t="n"/>
+      <c r="O474" s="9" t="n"/>
     </row>
     <row r="475">
+      <c r="A475" s="9" t="n"/>
+      <c r="D475" s="9" t="n"/>
+      <c r="E475" s="9" t="n"/>
+      <c r="F475" s="9" t="n"/>
+      <c r="G475" s="9" t="n"/>
       <c r="H475" s="9" t="n"/>
+      <c r="O475" s="9" t="n"/>
     </row>
     <row r="476">
+      <c r="A476" s="9" t="n"/>
+      <c r="D476" s="9" t="n"/>
+      <c r="E476" s="9" t="n"/>
+      <c r="F476" s="9" t="n"/>
+      <c r="G476" s="9" t="n"/>
       <c r="H476" s="9" t="n"/>
+      <c r="O476" s="9" t="n"/>
     </row>
     <row r="477">
+      <c r="A477" s="9" t="n"/>
+      <c r="D477" s="9" t="n"/>
+      <c r="E477" s="9" t="n"/>
+      <c r="F477" s="9" t="n"/>
+      <c r="G477" s="9" t="n"/>
       <c r="H477" s="9" t="n"/>
+      <c r="O477" s="9" t="n"/>
     </row>
     <row r="478">
+      <c r="A478" s="9" t="n"/>
+      <c r="D478" s="9" t="n"/>
+      <c r="E478" s="9" t="n"/>
+      <c r="F478" s="9" t="n"/>
+      <c r="G478" s="9" t="n"/>
       <c r="H478" s="9" t="n"/>
+      <c r="O478" s="9" t="n"/>
     </row>
     <row r="479">
+      <c r="A479" s="9" t="n"/>
+      <c r="D479" s="9" t="n"/>
+      <c r="E479" s="9" t="n"/>
+      <c r="F479" s="9" t="n"/>
+      <c r="G479" s="9" t="n"/>
       <c r="H479" s="9" t="n"/>
+      <c r="O479" s="9" t="n"/>
     </row>
     <row r="480">
+      <c r="A480" s="9" t="n"/>
+      <c r="D480" s="9" t="n"/>
+      <c r="E480" s="9" t="n"/>
+      <c r="F480" s="9" t="n"/>
+      <c r="G480" s="9" t="n"/>
       <c r="H480" s="9" t="n"/>
+      <c r="O480" s="9" t="n"/>
     </row>
     <row r="481">
+      <c r="A481" s="9" t="n"/>
+      <c r="D481" s="9" t="n"/>
+      <c r="E481" s="9" t="n"/>
+      <c r="F481" s="9" t="n"/>
+      <c r="G481" s="9" t="n"/>
       <c r="H481" s="9" t="n"/>
+      <c r="O481" s="9" t="n"/>
     </row>
     <row r="482">
+      <c r="A482" s="9" t="n"/>
+      <c r="D482" s="9" t="n"/>
+      <c r="E482" s="9" t="n"/>
+      <c r="F482" s="9" t="n"/>
+      <c r="G482" s="9" t="n"/>
       <c r="H482" s="9" t="n"/>
+      <c r="O482" s="9" t="n"/>
     </row>
     <row r="483">
+      <c r="A483" s="9" t="n"/>
+      <c r="D483" s="9" t="n"/>
+      <c r="E483" s="9" t="n"/>
+      <c r="F483" s="9" t="n"/>
+      <c r="G483" s="9" t="n"/>
       <c r="H483" s="9" t="n"/>
+      <c r="O483" s="9" t="n"/>
     </row>
     <row r="484">
+      <c r="A484" s="9" t="n"/>
+      <c r="D484" s="9" t="n"/>
+      <c r="E484" s="9" t="n"/>
+      <c r="F484" s="9" t="n"/>
+      <c r="G484" s="9" t="n"/>
       <c r="H484" s="9" t="n"/>
+      <c r="O484" s="9" t="n"/>
     </row>
     <row r="485">
+      <c r="A485" s="9" t="n"/>
+      <c r="D485" s="9" t="n"/>
+      <c r="E485" s="9" t="n"/>
+      <c r="F485" s="9" t="n"/>
+      <c r="G485" s="9" t="n"/>
       <c r="H485" s="9" t="n"/>
+      <c r="O485" s="9" t="n"/>
     </row>
     <row r="486">
+      <c r="A486" s="9" t="n"/>
+      <c r="D486" s="9" t="n"/>
+      <c r="E486" s="9" t="n"/>
+      <c r="F486" s="9" t="n"/>
+      <c r="G486" s="9" t="n"/>
       <c r="H486" s="9" t="n"/>
+      <c r="O486" s="9" t="n"/>
     </row>
     <row r="487">
+      <c r="A487" s="9" t="n"/>
+      <c r="D487" s="9" t="n"/>
+      <c r="E487" s="9" t="n"/>
+      <c r="F487" s="9" t="n"/>
+      <c r="G487" s="9" t="n"/>
       <c r="H487" s="9" t="n"/>
+      <c r="O487" s="9" t="n"/>
     </row>
     <row r="488">
+      <c r="A488" s="9" t="n"/>
+      <c r="D488" s="9" t="n"/>
+      <c r="E488" s="9" t="n"/>
+      <c r="F488" s="9" t="n"/>
+      <c r="G488" s="9" t="n"/>
       <c r="H488" s="9" t="n"/>
+      <c r="O488" s="9" t="n"/>
     </row>
     <row r="489">
+      <c r="A489" s="9" t="n"/>
+      <c r="D489" s="9" t="n"/>
+      <c r="E489" s="9" t="n"/>
+      <c r="F489" s="9" t="n"/>
+      <c r="G489" s="9" t="n"/>
       <c r="H489" s="9" t="n"/>
+      <c r="O489" s="9" t="n"/>
     </row>
     <row r="490">
+      <c r="A490" s="9" t="n"/>
+      <c r="D490" s="9" t="n"/>
+      <c r="E490" s="9" t="n"/>
+      <c r="F490" s="9" t="n"/>
+      <c r="G490" s="9" t="n"/>
       <c r="H490" s="9" t="n"/>
+      <c r="O490" s="9" t="n"/>
     </row>
     <row r="491">
+      <c r="A491" s="9" t="n"/>
+      <c r="D491" s="9" t="n"/>
+      <c r="E491" s="9" t="n"/>
+      <c r="F491" s="9" t="n"/>
+      <c r="G491" s="9" t="n"/>
       <c r="H491" s="9" t="n"/>
+      <c r="O491" s="9" t="n"/>
     </row>
     <row r="492">
+      <c r="A492" s="9" t="n"/>
+      <c r="D492" s="9" t="n"/>
+      <c r="E492" s="9" t="n"/>
+      <c r="F492" s="9" t="n"/>
+      <c r="G492" s="9" t="n"/>
       <c r="H492" s="9" t="n"/>
+      <c r="O492" s="9" t="n"/>
     </row>
     <row r="493">
+      <c r="A493" s="9" t="n"/>
+      <c r="D493" s="9" t="n"/>
+      <c r="E493" s="9" t="n"/>
+      <c r="F493" s="9" t="n"/>
+      <c r="G493" s="9" t="n"/>
       <c r="H493" s="9" t="n"/>
+      <c r="O493" s="9" t="n"/>
     </row>
     <row r="494">
+      <c r="A494" s="9" t="n"/>
+      <c r="D494" s="9" t="n"/>
+      <c r="E494" s="9" t="n"/>
+      <c r="F494" s="9" t="n"/>
+      <c r="G494" s="9" t="n"/>
       <c r="H494" s="9" t="n"/>
+      <c r="O494" s="9" t="n"/>
     </row>
     <row r="495">
+      <c r="A495" s="9" t="n"/>
+      <c r="D495" s="9" t="n"/>
+      <c r="E495" s="9" t="n"/>
+      <c r="F495" s="9" t="n"/>
+      <c r="G495" s="9" t="n"/>
       <c r="H495" s="9" t="n"/>
+      <c r="O495" s="9" t="n"/>
     </row>
     <row r="496">
+      <c r="A496" s="9" t="n"/>
+      <c r="D496" s="9" t="n"/>
+      <c r="E496" s="9" t="n"/>
+      <c r="F496" s="9" t="n"/>
+      <c r="G496" s="9" t="n"/>
       <c r="H496" s="9" t="n"/>
+      <c r="O496" s="9" t="n"/>
     </row>
     <row r="497">
+      <c r="A497" s="9" t="n"/>
+      <c r="D497" s="9" t="n"/>
+      <c r="E497" s="9" t="n"/>
+      <c r="F497" s="9" t="n"/>
+      <c r="G497" s="9" t="n"/>
       <c r="H497" s="9" t="n"/>
+      <c r="O497" s="9" t="n"/>
     </row>
     <row r="498">
+      <c r="A498" s="9" t="n"/>
+      <c r="D498" s="9" t="n"/>
+      <c r="E498" s="9" t="n"/>
+      <c r="F498" s="9" t="n"/>
+      <c r="G498" s="9" t="n"/>
       <c r="H498" s="9" t="n"/>
+      <c r="O498" s="9" t="n"/>
     </row>
     <row r="499">
+      <c r="A499" s="9" t="n"/>
+      <c r="D499" s="9" t="n"/>
+      <c r="E499" s="9" t="n"/>
+      <c r="F499" s="9" t="n"/>
+      <c r="G499" s="9" t="n"/>
       <c r="H499" s="9" t="n"/>
+      <c r="O499" s="9" t="n"/>
     </row>
     <row r="500">
+      <c r="A500" s="9" t="n"/>
+      <c r="D500" s="9" t="n"/>
+      <c r="E500" s="9" t="n"/>
+      <c r="F500" s="9" t="n"/>
+      <c r="G500" s="9" t="n"/>
       <c r="H500" s="9" t="n"/>
+      <c r="O500" s="9" t="n"/>
     </row>
   </sheetData>
   <dataValidations count="3">

--- a/templates/classeum-vocab-week1.xlsx
+++ b/templates/classeum-vocab-week1.xlsx
@@ -665,7 +665,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>학생 명단은 이 파일에 넣지 않아요. 선생님 화면 [학생·기기]에서 '번호 이름'을 한 번만 붙여 넣으세요.</t>
+          <t>학생 명단은 이 파일에 넣지 않아요. 선생님 화면 [학생·기기]에서 반을 만들고, 반마다 '번호 이름'을 한 번만 붙여 넣으세요.</t>
         </is>
       </c>
     </row>

--- a/templates/classeum-vocab-week1.xlsx
+++ b/templates/classeum-vocab-week1.xlsx
@@ -665,7 +665,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>학생 명단은 이 파일에 넣지 않아요. 선생님 화면 [학생·기기]에서 반을 만들고, 반마다 '번호 이름'을 한 번만 붙여 넣으세요.</t>
+          <t>학생 명단은 이 파일에 넣지 않아요. 선생님 화면 [학생·기기]에서 반을 만들면, 학생이 처음 접속할 때 반·번호·이름을 직접 써서 등록해요.</t>
         </is>
       </c>
     </row>

--- a/templates/classeum-vocab-week1.xlsx
+++ b/templates/classeum-vocab-week1.xlsx
@@ -586,7 +586,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>시간(초) (선택): 비워 두면 15초입니다. 특별히 오래 걸리는 단어만 숫자를 쓰세요.</t>
+          <t>시간(초) (선택): 칸마다 10초가 미리 들어 있어요. 단어마다 바꿀 수 있고, 지우면 15초입니다.</t>
         </is>
       </c>
     </row>
@@ -780,7 +780,9 @@
           <t>나는 방과 후에 도서관에서 공부한다.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="n"/>
+      <c r="G2" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H2" s="8" t="n"/>
       <c r="I2" s="8" t="n"/>
       <c r="J2" s="6" t="n"/>
@@ -817,7 +819,9 @@
           <t>네 펜 좀 빌려도 될까?</t>
         </is>
       </c>
-      <c r="G3" s="6" t="n"/>
+      <c r="G3" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H3" s="8" t="n"/>
       <c r="I3" s="8" t="n"/>
       <c r="J3" s="6" t="n"/>
@@ -854,7 +858,9 @@
           <t>지우개 좀 빌려줄래?</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n"/>
+      <c r="G4" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="6" t="n"/>
@@ -887,7 +893,9 @@
           <t>내가 가장 좋아하는 과목은 수학이다.</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
+      <c r="G5" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="8" t="n"/>
       <c r="J5" s="6" t="n"/>
@@ -924,7 +932,9 @@
           <t>도서관에서는 조용히 해 주세요.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n"/>
+      <c r="G6" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H6" s="8" t="n"/>
       <c r="I6" s="8" t="n"/>
       <c r="J6" s="6" t="n"/>
@@ -961,7 +971,9 @@
           <t>나는 월요일에 일찍 일어난다.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n"/>
+      <c r="G7" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="8" t="n"/>
       <c r="J7" s="6" t="n"/>
@@ -998,7 +1010,9 @@
           <t>수업에 늦지 마.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
+      <c r="G8" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="6" t="n"/>
@@ -1031,7 +1045,9 @@
           <t>나는 숙제를 끝냈다.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n"/>
+      <c r="G9" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H9" s="8" t="n"/>
       <c r="I9" s="8" t="n"/>
       <c r="J9" s="6" t="n"/>
@@ -1056,7 +1072,9 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
-      <c r="G10" s="6" t="n"/>
+      <c r="G10" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H10" s="8" t="n"/>
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="6" t="n"/>
@@ -1081,7 +1099,9 @@
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
-      <c r="G11" s="6" t="n"/>
+      <c r="G11" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H11" s="8" t="n"/>
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="6" t="n"/>
@@ -1114,7 +1134,9 @@
           <t>오늘 수학 시험이 있다.</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n"/>
+      <c r="G12" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="6" t="n"/>
@@ -1151,7 +1173,9 @@
           <t>질문 하나 해도 될까요?</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n"/>
+      <c r="G13" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H13" s="8" t="n"/>
       <c r="I13" s="8" t="n"/>
       <c r="J13" s="6" t="n"/>
@@ -1188,7 +1212,9 @@
           <t>나는 답을 안다.</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
+      <c r="G14" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H14" s="8" t="n"/>
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="6" t="n"/>
@@ -1217,7 +1243,9 @@
       </c>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
-      <c r="G15" s="6" t="n"/>
+      <c r="G15" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H15" s="8" t="n"/>
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="6" t="n"/>
@@ -1246,7 +1274,9 @@
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="6" t="n"/>
+      <c r="G16" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H16" s="8" t="n"/>
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="6" t="n"/>
@@ -1275,7 +1305,9 @@
       </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
-      <c r="G17" s="6" t="n"/>
+      <c r="G17" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H17" s="8" t="n"/>
       <c r="I17" s="8" t="n"/>
       <c r="J17" s="6" t="n"/>
@@ -1304,7 +1336,9 @@
       </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
-      <c r="G18" s="6" t="n"/>
+      <c r="G18" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H18" s="8" t="n"/>
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="6" t="n"/>
@@ -1337,7 +1371,9 @@
           <t>나는 매일 영어를 연습한다.</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n"/>
+      <c r="G19" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H19" s="8" t="n"/>
       <c r="I19" s="8" t="n"/>
       <c r="J19" s="6" t="n"/>
@@ -1366,7 +1402,9 @@
       </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
-      <c r="G20" s="6" t="n"/>
+      <c r="G20" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="6" t="n"/>
@@ -1399,2403 +1437,3842 @@
           <t>쉬는 시간에 축구하자.</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n"/>
+      <c r="G21" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="H21" s="8" t="n"/>
       <c r="I21" s="8" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
+      <c r="G22" t="n">
+        <v>10</v>
+      </c>
       <c r="H22" s="9" t="n"/>
       <c r="I22" s="9" t="n"/>
       <c r="K22" s="9" t="n"/>
     </row>
     <row r="23">
+      <c r="G23" t="n">
+        <v>10</v>
+      </c>
       <c r="H23" s="9" t="n"/>
       <c r="I23" s="9" t="n"/>
       <c r="K23" s="9" t="n"/>
     </row>
     <row r="24">
+      <c r="G24" t="n">
+        <v>10</v>
+      </c>
       <c r="H24" s="9" t="n"/>
       <c r="I24" s="9" t="n"/>
       <c r="K24" s="9" t="n"/>
     </row>
     <row r="25">
+      <c r="G25" t="n">
+        <v>10</v>
+      </c>
       <c r="H25" s="9" t="n"/>
       <c r="I25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
     </row>
     <row r="26">
+      <c r="G26" t="n">
+        <v>10</v>
+      </c>
       <c r="H26" s="9" t="n"/>
       <c r="I26" s="9" t="n"/>
       <c r="K26" s="9" t="n"/>
     </row>
     <row r="27">
+      <c r="G27" t="n">
+        <v>10</v>
+      </c>
       <c r="H27" s="9" t="n"/>
       <c r="I27" s="9" t="n"/>
       <c r="K27" s="9" t="n"/>
     </row>
     <row r="28">
+      <c r="G28" t="n">
+        <v>10</v>
+      </c>
       <c r="H28" s="9" t="n"/>
       <c r="I28" s="9" t="n"/>
       <c r="K28" s="9" t="n"/>
     </row>
     <row r="29">
+      <c r="G29" t="n">
+        <v>10</v>
+      </c>
       <c r="H29" s="9" t="n"/>
       <c r="I29" s="9" t="n"/>
       <c r="K29" s="9" t="n"/>
     </row>
     <row r="30">
+      <c r="G30" t="n">
+        <v>10</v>
+      </c>
       <c r="H30" s="9" t="n"/>
       <c r="I30" s="9" t="n"/>
       <c r="K30" s="9" t="n"/>
     </row>
     <row r="31">
+      <c r="G31" t="n">
+        <v>10</v>
+      </c>
       <c r="H31" s="9" t="n"/>
       <c r="I31" s="9" t="n"/>
       <c r="K31" s="9" t="n"/>
     </row>
     <row r="32">
+      <c r="G32" t="n">
+        <v>10</v>
+      </c>
       <c r="H32" s="9" t="n"/>
       <c r="I32" s="9" t="n"/>
       <c r="K32" s="9" t="n"/>
     </row>
     <row r="33">
+      <c r="G33" t="n">
+        <v>10</v>
+      </c>
       <c r="H33" s="9" t="n"/>
       <c r="I33" s="9" t="n"/>
       <c r="K33" s="9" t="n"/>
     </row>
     <row r="34">
+      <c r="G34" t="n">
+        <v>10</v>
+      </c>
       <c r="H34" s="9" t="n"/>
       <c r="I34" s="9" t="n"/>
       <c r="K34" s="9" t="n"/>
     </row>
     <row r="35">
+      <c r="G35" t="n">
+        <v>10</v>
+      </c>
       <c r="H35" s="9" t="n"/>
       <c r="I35" s="9" t="n"/>
       <c r="K35" s="9" t="n"/>
     </row>
     <row r="36">
+      <c r="G36" t="n">
+        <v>10</v>
+      </c>
       <c r="H36" s="9" t="n"/>
       <c r="I36" s="9" t="n"/>
       <c r="K36" s="9" t="n"/>
     </row>
     <row r="37">
+      <c r="G37" t="n">
+        <v>10</v>
+      </c>
       <c r="H37" s="9" t="n"/>
       <c r="I37" s="9" t="n"/>
       <c r="K37" s="9" t="n"/>
     </row>
     <row r="38">
+      <c r="G38" t="n">
+        <v>10</v>
+      </c>
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="n"/>
       <c r="K38" s="9" t="n"/>
     </row>
     <row r="39">
+      <c r="G39" t="n">
+        <v>10</v>
+      </c>
       <c r="H39" s="9" t="n"/>
       <c r="I39" s="9" t="n"/>
       <c r="K39" s="9" t="n"/>
     </row>
     <row r="40">
+      <c r="G40" t="n">
+        <v>10</v>
+      </c>
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="n"/>
       <c r="K40" s="9" t="n"/>
     </row>
     <row r="41">
+      <c r="G41" t="n">
+        <v>10</v>
+      </c>
       <c r="H41" s="9" t="n"/>
       <c r="I41" s="9" t="n"/>
       <c r="K41" s="9" t="n"/>
     </row>
     <row r="42">
+      <c r="G42" t="n">
+        <v>10</v>
+      </c>
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
       <c r="K42" s="9" t="n"/>
     </row>
     <row r="43">
+      <c r="G43" t="n">
+        <v>10</v>
+      </c>
       <c r="H43" s="9" t="n"/>
       <c r="I43" s="9" t="n"/>
       <c r="K43" s="9" t="n"/>
     </row>
     <row r="44">
+      <c r="G44" t="n">
+        <v>10</v>
+      </c>
       <c r="H44" s="9" t="n"/>
       <c r="I44" s="9" t="n"/>
       <c r="K44" s="9" t="n"/>
     </row>
     <row r="45">
+      <c r="G45" t="n">
+        <v>10</v>
+      </c>
       <c r="H45" s="9" t="n"/>
       <c r="I45" s="9" t="n"/>
       <c r="K45" s="9" t="n"/>
     </row>
     <row r="46">
+      <c r="G46" t="n">
+        <v>10</v>
+      </c>
       <c r="H46" s="9" t="n"/>
       <c r="I46" s="9" t="n"/>
       <c r="K46" s="9" t="n"/>
     </row>
     <row r="47">
+      <c r="G47" t="n">
+        <v>10</v>
+      </c>
       <c r="H47" s="9" t="n"/>
       <c r="I47" s="9" t="n"/>
       <c r="K47" s="9" t="n"/>
     </row>
     <row r="48">
+      <c r="G48" t="n">
+        <v>10</v>
+      </c>
       <c r="H48" s="9" t="n"/>
       <c r="I48" s="9" t="n"/>
       <c r="K48" s="9" t="n"/>
     </row>
     <row r="49">
+      <c r="G49" t="n">
+        <v>10</v>
+      </c>
       <c r="H49" s="9" t="n"/>
       <c r="I49" s="9" t="n"/>
       <c r="K49" s="9" t="n"/>
     </row>
     <row r="50">
+      <c r="G50" t="n">
+        <v>10</v>
+      </c>
       <c r="H50" s="9" t="n"/>
       <c r="I50" s="9" t="n"/>
       <c r="K50" s="9" t="n"/>
     </row>
     <row r="51">
+      <c r="G51" t="n">
+        <v>10</v>
+      </c>
       <c r="H51" s="9" t="n"/>
       <c r="I51" s="9" t="n"/>
       <c r="K51" s="9" t="n"/>
     </row>
     <row r="52">
+      <c r="G52" t="n">
+        <v>10</v>
+      </c>
       <c r="H52" s="9" t="n"/>
       <c r="I52" s="9" t="n"/>
       <c r="K52" s="9" t="n"/>
     </row>
     <row r="53">
+      <c r="G53" t="n">
+        <v>10</v>
+      </c>
       <c r="H53" s="9" t="n"/>
       <c r="I53" s="9" t="n"/>
       <c r="K53" s="9" t="n"/>
     </row>
     <row r="54">
+      <c r="G54" t="n">
+        <v>10</v>
+      </c>
       <c r="H54" s="9" t="n"/>
       <c r="I54" s="9" t="n"/>
       <c r="K54" s="9" t="n"/>
     </row>
     <row r="55">
+      <c r="G55" t="n">
+        <v>10</v>
+      </c>
       <c r="H55" s="9" t="n"/>
       <c r="I55" s="9" t="n"/>
       <c r="K55" s="9" t="n"/>
     </row>
     <row r="56">
+      <c r="G56" t="n">
+        <v>10</v>
+      </c>
       <c r="H56" s="9" t="n"/>
       <c r="I56" s="9" t="n"/>
       <c r="K56" s="9" t="n"/>
     </row>
     <row r="57">
+      <c r="G57" t="n">
+        <v>10</v>
+      </c>
       <c r="H57" s="9" t="n"/>
       <c r="I57" s="9" t="n"/>
       <c r="K57" s="9" t="n"/>
     </row>
     <row r="58">
+      <c r="G58" t="n">
+        <v>10</v>
+      </c>
       <c r="H58" s="9" t="n"/>
       <c r="I58" s="9" t="n"/>
       <c r="K58" s="9" t="n"/>
     </row>
     <row r="59">
+      <c r="G59" t="n">
+        <v>10</v>
+      </c>
       <c r="H59" s="9" t="n"/>
       <c r="I59" s="9" t="n"/>
       <c r="K59" s="9" t="n"/>
     </row>
     <row r="60">
+      <c r="G60" t="n">
+        <v>10</v>
+      </c>
       <c r="H60" s="9" t="n"/>
       <c r="I60" s="9" t="n"/>
       <c r="K60" s="9" t="n"/>
     </row>
     <row r="61">
+      <c r="G61" t="n">
+        <v>10</v>
+      </c>
       <c r="H61" s="9" t="n"/>
       <c r="I61" s="9" t="n"/>
       <c r="K61" s="9" t="n"/>
     </row>
     <row r="62">
+      <c r="G62" t="n">
+        <v>10</v>
+      </c>
       <c r="H62" s="9" t="n"/>
       <c r="I62" s="9" t="n"/>
       <c r="K62" s="9" t="n"/>
     </row>
     <row r="63">
+      <c r="G63" t="n">
+        <v>10</v>
+      </c>
       <c r="H63" s="9" t="n"/>
       <c r="I63" s="9" t="n"/>
       <c r="K63" s="9" t="n"/>
     </row>
     <row r="64">
+      <c r="G64" t="n">
+        <v>10</v>
+      </c>
       <c r="H64" s="9" t="n"/>
       <c r="I64" s="9" t="n"/>
       <c r="K64" s="9" t="n"/>
     </row>
     <row r="65">
+      <c r="G65" t="n">
+        <v>10</v>
+      </c>
       <c r="H65" s="9" t="n"/>
       <c r="I65" s="9" t="n"/>
       <c r="K65" s="9" t="n"/>
     </row>
     <row r="66">
+      <c r="G66" t="n">
+        <v>10</v>
+      </c>
       <c r="H66" s="9" t="n"/>
       <c r="I66" s="9" t="n"/>
       <c r="K66" s="9" t="n"/>
     </row>
     <row r="67">
+      <c r="G67" t="n">
+        <v>10</v>
+      </c>
       <c r="H67" s="9" t="n"/>
       <c r="I67" s="9" t="n"/>
       <c r="K67" s="9" t="n"/>
     </row>
     <row r="68">
+      <c r="G68" t="n">
+        <v>10</v>
+      </c>
       <c r="H68" s="9" t="n"/>
       <c r="I68" s="9" t="n"/>
       <c r="K68" s="9" t="n"/>
     </row>
     <row r="69">
+      <c r="G69" t="n">
+        <v>10</v>
+      </c>
       <c r="H69" s="9" t="n"/>
       <c r="I69" s="9" t="n"/>
       <c r="K69" s="9" t="n"/>
     </row>
     <row r="70">
+      <c r="G70" t="n">
+        <v>10</v>
+      </c>
       <c r="H70" s="9" t="n"/>
       <c r="I70" s="9" t="n"/>
       <c r="K70" s="9" t="n"/>
     </row>
     <row r="71">
+      <c r="G71" t="n">
+        <v>10</v>
+      </c>
       <c r="H71" s="9" t="n"/>
       <c r="I71" s="9" t="n"/>
       <c r="K71" s="9" t="n"/>
     </row>
     <row r="72">
+      <c r="G72" t="n">
+        <v>10</v>
+      </c>
       <c r="H72" s="9" t="n"/>
       <c r="I72" s="9" t="n"/>
       <c r="K72" s="9" t="n"/>
     </row>
     <row r="73">
+      <c r="G73" t="n">
+        <v>10</v>
+      </c>
       <c r="H73" s="9" t="n"/>
       <c r="I73" s="9" t="n"/>
       <c r="K73" s="9" t="n"/>
     </row>
     <row r="74">
+      <c r="G74" t="n">
+        <v>10</v>
+      </c>
       <c r="H74" s="9" t="n"/>
       <c r="I74" s="9" t="n"/>
       <c r="K74" s="9" t="n"/>
     </row>
     <row r="75">
+      <c r="G75" t="n">
+        <v>10</v>
+      </c>
       <c r="H75" s="9" t="n"/>
       <c r="I75" s="9" t="n"/>
       <c r="K75" s="9" t="n"/>
     </row>
     <row r="76">
+      <c r="G76" t="n">
+        <v>10</v>
+      </c>
       <c r="H76" s="9" t="n"/>
       <c r="I76" s="9" t="n"/>
       <c r="K76" s="9" t="n"/>
     </row>
     <row r="77">
+      <c r="G77" t="n">
+        <v>10</v>
+      </c>
       <c r="H77" s="9" t="n"/>
       <c r="I77" s="9" t="n"/>
       <c r="K77" s="9" t="n"/>
     </row>
     <row r="78">
+      <c r="G78" t="n">
+        <v>10</v>
+      </c>
       <c r="H78" s="9" t="n"/>
       <c r="I78" s="9" t="n"/>
       <c r="K78" s="9" t="n"/>
     </row>
     <row r="79">
+      <c r="G79" t="n">
+        <v>10</v>
+      </c>
       <c r="H79" s="9" t="n"/>
       <c r="I79" s="9" t="n"/>
       <c r="K79" s="9" t="n"/>
     </row>
     <row r="80">
+      <c r="G80" t="n">
+        <v>10</v>
+      </c>
       <c r="H80" s="9" t="n"/>
       <c r="I80" s="9" t="n"/>
       <c r="K80" s="9" t="n"/>
     </row>
     <row r="81">
+      <c r="G81" t="n">
+        <v>10</v>
+      </c>
       <c r="H81" s="9" t="n"/>
       <c r="I81" s="9" t="n"/>
       <c r="K81" s="9" t="n"/>
     </row>
     <row r="82">
+      <c r="G82" t="n">
+        <v>10</v>
+      </c>
       <c r="H82" s="9" t="n"/>
       <c r="I82" s="9" t="n"/>
       <c r="K82" s="9" t="n"/>
     </row>
     <row r="83">
+      <c r="G83" t="n">
+        <v>10</v>
+      </c>
       <c r="H83" s="9" t="n"/>
       <c r="I83" s="9" t="n"/>
       <c r="K83" s="9" t="n"/>
     </row>
     <row r="84">
+      <c r="G84" t="n">
+        <v>10</v>
+      </c>
       <c r="H84" s="9" t="n"/>
       <c r="I84" s="9" t="n"/>
       <c r="K84" s="9" t="n"/>
     </row>
     <row r="85">
+      <c r="G85" t="n">
+        <v>10</v>
+      </c>
       <c r="H85" s="9" t="n"/>
       <c r="I85" s="9" t="n"/>
       <c r="K85" s="9" t="n"/>
     </row>
     <row r="86">
+      <c r="G86" t="n">
+        <v>10</v>
+      </c>
       <c r="H86" s="9" t="n"/>
       <c r="I86" s="9" t="n"/>
       <c r="K86" s="9" t="n"/>
     </row>
     <row r="87">
+      <c r="G87" t="n">
+        <v>10</v>
+      </c>
       <c r="H87" s="9" t="n"/>
       <c r="I87" s="9" t="n"/>
       <c r="K87" s="9" t="n"/>
     </row>
     <row r="88">
+      <c r="G88" t="n">
+        <v>10</v>
+      </c>
       <c r="H88" s="9" t="n"/>
       <c r="I88" s="9" t="n"/>
       <c r="K88" s="9" t="n"/>
     </row>
     <row r="89">
+      <c r="G89" t="n">
+        <v>10</v>
+      </c>
       <c r="H89" s="9" t="n"/>
       <c r="I89" s="9" t="n"/>
       <c r="K89" s="9" t="n"/>
     </row>
     <row r="90">
+      <c r="G90" t="n">
+        <v>10</v>
+      </c>
       <c r="H90" s="9" t="n"/>
       <c r="I90" s="9" t="n"/>
       <c r="K90" s="9" t="n"/>
     </row>
     <row r="91">
+      <c r="G91" t="n">
+        <v>10</v>
+      </c>
       <c r="H91" s="9" t="n"/>
       <c r="I91" s="9" t="n"/>
       <c r="K91" s="9" t="n"/>
     </row>
     <row r="92">
+      <c r="G92" t="n">
+        <v>10</v>
+      </c>
       <c r="H92" s="9" t="n"/>
       <c r="I92" s="9" t="n"/>
       <c r="K92" s="9" t="n"/>
     </row>
     <row r="93">
+      <c r="G93" t="n">
+        <v>10</v>
+      </c>
       <c r="H93" s="9" t="n"/>
       <c r="I93" s="9" t="n"/>
       <c r="K93" s="9" t="n"/>
     </row>
     <row r="94">
+      <c r="G94" t="n">
+        <v>10</v>
+      </c>
       <c r="H94" s="9" t="n"/>
       <c r="I94" s="9" t="n"/>
       <c r="K94" s="9" t="n"/>
     </row>
     <row r="95">
+      <c r="G95" t="n">
+        <v>10</v>
+      </c>
       <c r="H95" s="9" t="n"/>
       <c r="I95" s="9" t="n"/>
       <c r="K95" s="9" t="n"/>
     </row>
     <row r="96">
+      <c r="G96" t="n">
+        <v>10</v>
+      </c>
       <c r="H96" s="9" t="n"/>
       <c r="I96" s="9" t="n"/>
       <c r="K96" s="9" t="n"/>
     </row>
     <row r="97">
+      <c r="G97" t="n">
+        <v>10</v>
+      </c>
       <c r="H97" s="9" t="n"/>
       <c r="I97" s="9" t="n"/>
       <c r="K97" s="9" t="n"/>
     </row>
     <row r="98">
+      <c r="G98" t="n">
+        <v>10</v>
+      </c>
       <c r="H98" s="9" t="n"/>
       <c r="I98" s="9" t="n"/>
       <c r="K98" s="9" t="n"/>
     </row>
     <row r="99">
+      <c r="G99" t="n">
+        <v>10</v>
+      </c>
       <c r="H99" s="9" t="n"/>
       <c r="I99" s="9" t="n"/>
       <c r="K99" s="9" t="n"/>
     </row>
     <row r="100">
+      <c r="G100" t="n">
+        <v>10</v>
+      </c>
       <c r="H100" s="9" t="n"/>
       <c r="I100" s="9" t="n"/>
       <c r="K100" s="9" t="n"/>
     </row>
     <row r="101">
+      <c r="G101" t="n">
+        <v>10</v>
+      </c>
       <c r="H101" s="9" t="n"/>
       <c r="I101" s="9" t="n"/>
       <c r="K101" s="9" t="n"/>
     </row>
     <row r="102">
+      <c r="G102" t="n">
+        <v>10</v>
+      </c>
       <c r="H102" s="9" t="n"/>
       <c r="I102" s="9" t="n"/>
       <c r="K102" s="9" t="n"/>
     </row>
     <row r="103">
+      <c r="G103" t="n">
+        <v>10</v>
+      </c>
       <c r="H103" s="9" t="n"/>
       <c r="I103" s="9" t="n"/>
       <c r="K103" s="9" t="n"/>
     </row>
     <row r="104">
+      <c r="G104" t="n">
+        <v>10</v>
+      </c>
       <c r="H104" s="9" t="n"/>
       <c r="I104" s="9" t="n"/>
       <c r="K104" s="9" t="n"/>
     </row>
     <row r="105">
+      <c r="G105" t="n">
+        <v>10</v>
+      </c>
       <c r="H105" s="9" t="n"/>
       <c r="I105" s="9" t="n"/>
       <c r="K105" s="9" t="n"/>
     </row>
     <row r="106">
+      <c r="G106" t="n">
+        <v>10</v>
+      </c>
       <c r="H106" s="9" t="n"/>
       <c r="I106" s="9" t="n"/>
       <c r="K106" s="9" t="n"/>
     </row>
     <row r="107">
+      <c r="G107" t="n">
+        <v>10</v>
+      </c>
       <c r="H107" s="9" t="n"/>
       <c r="I107" s="9" t="n"/>
       <c r="K107" s="9" t="n"/>
     </row>
     <row r="108">
+      <c r="G108" t="n">
+        <v>10</v>
+      </c>
       <c r="H108" s="9" t="n"/>
       <c r="I108" s="9" t="n"/>
       <c r="K108" s="9" t="n"/>
     </row>
     <row r="109">
+      <c r="G109" t="n">
+        <v>10</v>
+      </c>
       <c r="H109" s="9" t="n"/>
       <c r="I109" s="9" t="n"/>
       <c r="K109" s="9" t="n"/>
     </row>
     <row r="110">
+      <c r="G110" t="n">
+        <v>10</v>
+      </c>
       <c r="H110" s="9" t="n"/>
       <c r="I110" s="9" t="n"/>
       <c r="K110" s="9" t="n"/>
     </row>
     <row r="111">
+      <c r="G111" t="n">
+        <v>10</v>
+      </c>
       <c r="H111" s="9" t="n"/>
       <c r="I111" s="9" t="n"/>
       <c r="K111" s="9" t="n"/>
     </row>
     <row r="112">
+      <c r="G112" t="n">
+        <v>10</v>
+      </c>
       <c r="H112" s="9" t="n"/>
       <c r="I112" s="9" t="n"/>
       <c r="K112" s="9" t="n"/>
     </row>
     <row r="113">
+      <c r="G113" t="n">
+        <v>10</v>
+      </c>
       <c r="H113" s="9" t="n"/>
       <c r="I113" s="9" t="n"/>
       <c r="K113" s="9" t="n"/>
     </row>
     <row r="114">
+      <c r="G114" t="n">
+        <v>10</v>
+      </c>
       <c r="H114" s="9" t="n"/>
       <c r="I114" s="9" t="n"/>
       <c r="K114" s="9" t="n"/>
     </row>
     <row r="115">
+      <c r="G115" t="n">
+        <v>10</v>
+      </c>
       <c r="H115" s="9" t="n"/>
       <c r="I115" s="9" t="n"/>
       <c r="K115" s="9" t="n"/>
     </row>
     <row r="116">
+      <c r="G116" t="n">
+        <v>10</v>
+      </c>
       <c r="H116" s="9" t="n"/>
       <c r="I116" s="9" t="n"/>
       <c r="K116" s="9" t="n"/>
     </row>
     <row r="117">
+      <c r="G117" t="n">
+        <v>10</v>
+      </c>
       <c r="H117" s="9" t="n"/>
       <c r="I117" s="9" t="n"/>
       <c r="K117" s="9" t="n"/>
     </row>
     <row r="118">
+      <c r="G118" t="n">
+        <v>10</v>
+      </c>
       <c r="H118" s="9" t="n"/>
       <c r="I118" s="9" t="n"/>
       <c r="K118" s="9" t="n"/>
     </row>
     <row r="119">
+      <c r="G119" t="n">
+        <v>10</v>
+      </c>
       <c r="H119" s="9" t="n"/>
       <c r="I119" s="9" t="n"/>
       <c r="K119" s="9" t="n"/>
     </row>
     <row r="120">
+      <c r="G120" t="n">
+        <v>10</v>
+      </c>
       <c r="H120" s="9" t="n"/>
       <c r="I120" s="9" t="n"/>
       <c r="K120" s="9" t="n"/>
     </row>
     <row r="121">
+      <c r="G121" t="n">
+        <v>10</v>
+      </c>
       <c r="H121" s="9" t="n"/>
       <c r="I121" s="9" t="n"/>
       <c r="K121" s="9" t="n"/>
     </row>
     <row r="122">
+      <c r="G122" t="n">
+        <v>10</v>
+      </c>
       <c r="H122" s="9" t="n"/>
       <c r="I122" s="9" t="n"/>
       <c r="K122" s="9" t="n"/>
     </row>
     <row r="123">
+      <c r="G123" t="n">
+        <v>10</v>
+      </c>
       <c r="H123" s="9" t="n"/>
       <c r="I123" s="9" t="n"/>
       <c r="K123" s="9" t="n"/>
     </row>
     <row r="124">
+      <c r="G124" t="n">
+        <v>10</v>
+      </c>
       <c r="H124" s="9" t="n"/>
       <c r="I124" s="9" t="n"/>
       <c r="K124" s="9" t="n"/>
     </row>
     <row r="125">
+      <c r="G125" t="n">
+        <v>10</v>
+      </c>
       <c r="H125" s="9" t="n"/>
       <c r="I125" s="9" t="n"/>
       <c r="K125" s="9" t="n"/>
     </row>
     <row r="126">
+      <c r="G126" t="n">
+        <v>10</v>
+      </c>
       <c r="H126" s="9" t="n"/>
       <c r="I126" s="9" t="n"/>
       <c r="K126" s="9" t="n"/>
     </row>
     <row r="127">
+      <c r="G127" t="n">
+        <v>10</v>
+      </c>
       <c r="H127" s="9" t="n"/>
       <c r="I127" s="9" t="n"/>
       <c r="K127" s="9" t="n"/>
     </row>
     <row r="128">
+      <c r="G128" t="n">
+        <v>10</v>
+      </c>
       <c r="H128" s="9" t="n"/>
       <c r="I128" s="9" t="n"/>
       <c r="K128" s="9" t="n"/>
     </row>
     <row r="129">
+      <c r="G129" t="n">
+        <v>10</v>
+      </c>
       <c r="H129" s="9" t="n"/>
       <c r="I129" s="9" t="n"/>
       <c r="K129" s="9" t="n"/>
     </row>
     <row r="130">
+      <c r="G130" t="n">
+        <v>10</v>
+      </c>
       <c r="H130" s="9" t="n"/>
       <c r="I130" s="9" t="n"/>
       <c r="K130" s="9" t="n"/>
     </row>
     <row r="131">
+      <c r="G131" t="n">
+        <v>10</v>
+      </c>
       <c r="H131" s="9" t="n"/>
       <c r="I131" s="9" t="n"/>
       <c r="K131" s="9" t="n"/>
     </row>
     <row r="132">
+      <c r="G132" t="n">
+        <v>10</v>
+      </c>
       <c r="H132" s="9" t="n"/>
       <c r="I132" s="9" t="n"/>
       <c r="K132" s="9" t="n"/>
     </row>
     <row r="133">
+      <c r="G133" t="n">
+        <v>10</v>
+      </c>
       <c r="H133" s="9" t="n"/>
       <c r="I133" s="9" t="n"/>
       <c r="K133" s="9" t="n"/>
     </row>
     <row r="134">
+      <c r="G134" t="n">
+        <v>10</v>
+      </c>
       <c r="H134" s="9" t="n"/>
       <c r="I134" s="9" t="n"/>
       <c r="K134" s="9" t="n"/>
     </row>
     <row r="135">
+      <c r="G135" t="n">
+        <v>10</v>
+      </c>
       <c r="H135" s="9" t="n"/>
       <c r="I135" s="9" t="n"/>
       <c r="K135" s="9" t="n"/>
     </row>
     <row r="136">
+      <c r="G136" t="n">
+        <v>10</v>
+      </c>
       <c r="H136" s="9" t="n"/>
       <c r="I136" s="9" t="n"/>
       <c r="K136" s="9" t="n"/>
     </row>
     <row r="137">
+      <c r="G137" t="n">
+        <v>10</v>
+      </c>
       <c r="H137" s="9" t="n"/>
       <c r="I137" s="9" t="n"/>
       <c r="K137" s="9" t="n"/>
     </row>
     <row r="138">
+      <c r="G138" t="n">
+        <v>10</v>
+      </c>
       <c r="H138" s="9" t="n"/>
       <c r="I138" s="9" t="n"/>
       <c r="K138" s="9" t="n"/>
     </row>
     <row r="139">
+      <c r="G139" t="n">
+        <v>10</v>
+      </c>
       <c r="H139" s="9" t="n"/>
       <c r="I139" s="9" t="n"/>
       <c r="K139" s="9" t="n"/>
     </row>
     <row r="140">
+      <c r="G140" t="n">
+        <v>10</v>
+      </c>
       <c r="H140" s="9" t="n"/>
       <c r="I140" s="9" t="n"/>
       <c r="K140" s="9" t="n"/>
     </row>
     <row r="141">
+      <c r="G141" t="n">
+        <v>10</v>
+      </c>
       <c r="H141" s="9" t="n"/>
       <c r="I141" s="9" t="n"/>
       <c r="K141" s="9" t="n"/>
     </row>
     <row r="142">
+      <c r="G142" t="n">
+        <v>10</v>
+      </c>
       <c r="H142" s="9" t="n"/>
       <c r="I142" s="9" t="n"/>
       <c r="K142" s="9" t="n"/>
     </row>
     <row r="143">
+      <c r="G143" t="n">
+        <v>10</v>
+      </c>
       <c r="H143" s="9" t="n"/>
       <c r="I143" s="9" t="n"/>
       <c r="K143" s="9" t="n"/>
     </row>
     <row r="144">
+      <c r="G144" t="n">
+        <v>10</v>
+      </c>
       <c r="H144" s="9" t="n"/>
       <c r="I144" s="9" t="n"/>
       <c r="K144" s="9" t="n"/>
     </row>
     <row r="145">
+      <c r="G145" t="n">
+        <v>10</v>
+      </c>
       <c r="H145" s="9" t="n"/>
       <c r="I145" s="9" t="n"/>
       <c r="K145" s="9" t="n"/>
     </row>
     <row r="146">
+      <c r="G146" t="n">
+        <v>10</v>
+      </c>
       <c r="H146" s="9" t="n"/>
       <c r="I146" s="9" t="n"/>
       <c r="K146" s="9" t="n"/>
     </row>
     <row r="147">
+      <c r="G147" t="n">
+        <v>10</v>
+      </c>
       <c r="H147" s="9" t="n"/>
       <c r="I147" s="9" t="n"/>
       <c r="K147" s="9" t="n"/>
     </row>
     <row r="148">
+      <c r="G148" t="n">
+        <v>10</v>
+      </c>
       <c r="H148" s="9" t="n"/>
       <c r="I148" s="9" t="n"/>
       <c r="K148" s="9" t="n"/>
     </row>
     <row r="149">
+      <c r="G149" t="n">
+        <v>10</v>
+      </c>
       <c r="H149" s="9" t="n"/>
       <c r="I149" s="9" t="n"/>
       <c r="K149" s="9" t="n"/>
     </row>
     <row r="150">
+      <c r="G150" t="n">
+        <v>10</v>
+      </c>
       <c r="H150" s="9" t="n"/>
       <c r="I150" s="9" t="n"/>
       <c r="K150" s="9" t="n"/>
     </row>
     <row r="151">
+      <c r="G151" t="n">
+        <v>10</v>
+      </c>
       <c r="H151" s="9" t="n"/>
       <c r="I151" s="9" t="n"/>
       <c r="K151" s="9" t="n"/>
     </row>
     <row r="152">
+      <c r="G152" t="n">
+        <v>10</v>
+      </c>
       <c r="H152" s="9" t="n"/>
       <c r="I152" s="9" t="n"/>
       <c r="K152" s="9" t="n"/>
     </row>
     <row r="153">
+      <c r="G153" t="n">
+        <v>10</v>
+      </c>
       <c r="H153" s="9" t="n"/>
       <c r="I153" s="9" t="n"/>
       <c r="K153" s="9" t="n"/>
     </row>
     <row r="154">
+      <c r="G154" t="n">
+        <v>10</v>
+      </c>
       <c r="H154" s="9" t="n"/>
       <c r="I154" s="9" t="n"/>
       <c r="K154" s="9" t="n"/>
     </row>
     <row r="155">
+      <c r="G155" t="n">
+        <v>10</v>
+      </c>
       <c r="H155" s="9" t="n"/>
       <c r="I155" s="9" t="n"/>
       <c r="K155" s="9" t="n"/>
     </row>
     <row r="156">
+      <c r="G156" t="n">
+        <v>10</v>
+      </c>
       <c r="H156" s="9" t="n"/>
       <c r="I156" s="9" t="n"/>
       <c r="K156" s="9" t="n"/>
     </row>
     <row r="157">
+      <c r="G157" t="n">
+        <v>10</v>
+      </c>
       <c r="H157" s="9" t="n"/>
       <c r="I157" s="9" t="n"/>
       <c r="K157" s="9" t="n"/>
     </row>
     <row r="158">
+      <c r="G158" t="n">
+        <v>10</v>
+      </c>
       <c r="H158" s="9" t="n"/>
       <c r="I158" s="9" t="n"/>
       <c r="K158" s="9" t="n"/>
     </row>
     <row r="159">
+      <c r="G159" t="n">
+        <v>10</v>
+      </c>
       <c r="H159" s="9" t="n"/>
       <c r="I159" s="9" t="n"/>
       <c r="K159" s="9" t="n"/>
     </row>
     <row r="160">
+      <c r="G160" t="n">
+        <v>10</v>
+      </c>
       <c r="H160" s="9" t="n"/>
       <c r="I160" s="9" t="n"/>
       <c r="K160" s="9" t="n"/>
     </row>
     <row r="161">
+      <c r="G161" t="n">
+        <v>10</v>
+      </c>
       <c r="H161" s="9" t="n"/>
       <c r="I161" s="9" t="n"/>
       <c r="K161" s="9" t="n"/>
     </row>
     <row r="162">
+      <c r="G162" t="n">
+        <v>10</v>
+      </c>
       <c r="H162" s="9" t="n"/>
       <c r="I162" s="9" t="n"/>
       <c r="K162" s="9" t="n"/>
     </row>
     <row r="163">
+      <c r="G163" t="n">
+        <v>10</v>
+      </c>
       <c r="H163" s="9" t="n"/>
       <c r="I163" s="9" t="n"/>
       <c r="K163" s="9" t="n"/>
     </row>
     <row r="164">
+      <c r="G164" t="n">
+        <v>10</v>
+      </c>
       <c r="H164" s="9" t="n"/>
       <c r="I164" s="9" t="n"/>
       <c r="K164" s="9" t="n"/>
     </row>
     <row r="165">
+      <c r="G165" t="n">
+        <v>10</v>
+      </c>
       <c r="H165" s="9" t="n"/>
       <c r="I165" s="9" t="n"/>
       <c r="K165" s="9" t="n"/>
     </row>
     <row r="166">
+      <c r="G166" t="n">
+        <v>10</v>
+      </c>
       <c r="H166" s="9" t="n"/>
       <c r="I166" s="9" t="n"/>
       <c r="K166" s="9" t="n"/>
     </row>
     <row r="167">
+      <c r="G167" t="n">
+        <v>10</v>
+      </c>
       <c r="H167" s="9" t="n"/>
       <c r="I167" s="9" t="n"/>
       <c r="K167" s="9" t="n"/>
     </row>
     <row r="168">
+      <c r="G168" t="n">
+        <v>10</v>
+      </c>
       <c r="H168" s="9" t="n"/>
       <c r="I168" s="9" t="n"/>
       <c r="K168" s="9" t="n"/>
     </row>
     <row r="169">
+      <c r="G169" t="n">
+        <v>10</v>
+      </c>
       <c r="H169" s="9" t="n"/>
       <c r="I169" s="9" t="n"/>
       <c r="K169" s="9" t="n"/>
     </row>
     <row r="170">
+      <c r="G170" t="n">
+        <v>10</v>
+      </c>
       <c r="H170" s="9" t="n"/>
       <c r="I170" s="9" t="n"/>
       <c r="K170" s="9" t="n"/>
     </row>
     <row r="171">
+      <c r="G171" t="n">
+        <v>10</v>
+      </c>
       <c r="H171" s="9" t="n"/>
       <c r="I171" s="9" t="n"/>
       <c r="K171" s="9" t="n"/>
     </row>
     <row r="172">
+      <c r="G172" t="n">
+        <v>10</v>
+      </c>
       <c r="H172" s="9" t="n"/>
       <c r="I172" s="9" t="n"/>
       <c r="K172" s="9" t="n"/>
     </row>
     <row r="173">
+      <c r="G173" t="n">
+        <v>10</v>
+      </c>
       <c r="H173" s="9" t="n"/>
       <c r="I173" s="9" t="n"/>
       <c r="K173" s="9" t="n"/>
     </row>
     <row r="174">
+      <c r="G174" t="n">
+        <v>10</v>
+      </c>
       <c r="H174" s="9" t="n"/>
       <c r="I174" s="9" t="n"/>
       <c r="K174" s="9" t="n"/>
     </row>
     <row r="175">
+      <c r="G175" t="n">
+        <v>10</v>
+      </c>
       <c r="H175" s="9" t="n"/>
       <c r="I175" s="9" t="n"/>
       <c r="K175" s="9" t="n"/>
     </row>
     <row r="176">
+      <c r="G176" t="n">
+        <v>10</v>
+      </c>
       <c r="H176" s="9" t="n"/>
       <c r="I176" s="9" t="n"/>
       <c r="K176" s="9" t="n"/>
     </row>
     <row r="177">
+      <c r="G177" t="n">
+        <v>10</v>
+      </c>
       <c r="H177" s="9" t="n"/>
       <c r="I177" s="9" t="n"/>
       <c r="K177" s="9" t="n"/>
     </row>
     <row r="178">
+      <c r="G178" t="n">
+        <v>10</v>
+      </c>
       <c r="H178" s="9" t="n"/>
       <c r="I178" s="9" t="n"/>
       <c r="K178" s="9" t="n"/>
     </row>
     <row r="179">
+      <c r="G179" t="n">
+        <v>10</v>
+      </c>
       <c r="H179" s="9" t="n"/>
       <c r="I179" s="9" t="n"/>
       <c r="K179" s="9" t="n"/>
     </row>
     <row r="180">
+      <c r="G180" t="n">
+        <v>10</v>
+      </c>
       <c r="H180" s="9" t="n"/>
       <c r="I180" s="9" t="n"/>
       <c r="K180" s="9" t="n"/>
     </row>
     <row r="181">
+      <c r="G181" t="n">
+        <v>10</v>
+      </c>
       <c r="H181" s="9" t="n"/>
       <c r="I181" s="9" t="n"/>
       <c r="K181" s="9" t="n"/>
     </row>
     <row r="182">
+      <c r="G182" t="n">
+        <v>10</v>
+      </c>
       <c r="H182" s="9" t="n"/>
       <c r="I182" s="9" t="n"/>
       <c r="K182" s="9" t="n"/>
     </row>
     <row r="183">
+      <c r="G183" t="n">
+        <v>10</v>
+      </c>
       <c r="H183" s="9" t="n"/>
       <c r="I183" s="9" t="n"/>
       <c r="K183" s="9" t="n"/>
     </row>
     <row r="184">
+      <c r="G184" t="n">
+        <v>10</v>
+      </c>
       <c r="H184" s="9" t="n"/>
       <c r="I184" s="9" t="n"/>
       <c r="K184" s="9" t="n"/>
     </row>
     <row r="185">
+      <c r="G185" t="n">
+        <v>10</v>
+      </c>
       <c r="H185" s="9" t="n"/>
       <c r="I185" s="9" t="n"/>
       <c r="K185" s="9" t="n"/>
     </row>
     <row r="186">
+      <c r="G186" t="n">
+        <v>10</v>
+      </c>
       <c r="H186" s="9" t="n"/>
       <c r="I186" s="9" t="n"/>
       <c r="K186" s="9" t="n"/>
     </row>
     <row r="187">
+      <c r="G187" t="n">
+        <v>10</v>
+      </c>
       <c r="H187" s="9" t="n"/>
       <c r="I187" s="9" t="n"/>
       <c r="K187" s="9" t="n"/>
     </row>
     <row r="188">
+      <c r="G188" t="n">
+        <v>10</v>
+      </c>
       <c r="H188" s="9" t="n"/>
       <c r="I188" s="9" t="n"/>
       <c r="K188" s="9" t="n"/>
     </row>
     <row r="189">
+      <c r="G189" t="n">
+        <v>10</v>
+      </c>
       <c r="H189" s="9" t="n"/>
       <c r="I189" s="9" t="n"/>
       <c r="K189" s="9" t="n"/>
     </row>
     <row r="190">
+      <c r="G190" t="n">
+        <v>10</v>
+      </c>
       <c r="H190" s="9" t="n"/>
       <c r="I190" s="9" t="n"/>
       <c r="K190" s="9" t="n"/>
     </row>
     <row r="191">
+      <c r="G191" t="n">
+        <v>10</v>
+      </c>
       <c r="H191" s="9" t="n"/>
       <c r="I191" s="9" t="n"/>
       <c r="K191" s="9" t="n"/>
     </row>
     <row r="192">
+      <c r="G192" t="n">
+        <v>10</v>
+      </c>
       <c r="H192" s="9" t="n"/>
       <c r="I192" s="9" t="n"/>
       <c r="K192" s="9" t="n"/>
     </row>
     <row r="193">
+      <c r="G193" t="n">
+        <v>10</v>
+      </c>
       <c r="H193" s="9" t="n"/>
       <c r="I193" s="9" t="n"/>
       <c r="K193" s="9" t="n"/>
     </row>
     <row r="194">
+      <c r="G194" t="n">
+        <v>10</v>
+      </c>
       <c r="H194" s="9" t="n"/>
       <c r="I194" s="9" t="n"/>
       <c r="K194" s="9" t="n"/>
     </row>
     <row r="195">
+      <c r="G195" t="n">
+        <v>10</v>
+      </c>
       <c r="H195" s="9" t="n"/>
       <c r="I195" s="9" t="n"/>
       <c r="K195" s="9" t="n"/>
     </row>
     <row r="196">
+      <c r="G196" t="n">
+        <v>10</v>
+      </c>
       <c r="H196" s="9" t="n"/>
       <c r="I196" s="9" t="n"/>
       <c r="K196" s="9" t="n"/>
     </row>
     <row r="197">
+      <c r="G197" t="n">
+        <v>10</v>
+      </c>
       <c r="H197" s="9" t="n"/>
       <c r="I197" s="9" t="n"/>
       <c r="K197" s="9" t="n"/>
     </row>
     <row r="198">
+      <c r="G198" t="n">
+        <v>10</v>
+      </c>
       <c r="H198" s="9" t="n"/>
       <c r="I198" s="9" t="n"/>
       <c r="K198" s="9" t="n"/>
     </row>
     <row r="199">
+      <c r="G199" t="n">
+        <v>10</v>
+      </c>
       <c r="H199" s="9" t="n"/>
       <c r="I199" s="9" t="n"/>
       <c r="K199" s="9" t="n"/>
     </row>
     <row r="200">
+      <c r="G200" t="n">
+        <v>10</v>
+      </c>
       <c r="H200" s="9" t="n"/>
       <c r="I200" s="9" t="n"/>
       <c r="K200" s="9" t="n"/>
     </row>
     <row r="201">
+      <c r="G201" t="n">
+        <v>10</v>
+      </c>
       <c r="H201" s="9" t="n"/>
       <c r="I201" s="9" t="n"/>
       <c r="K201" s="9" t="n"/>
     </row>
     <row r="202">
+      <c r="G202" t="n">
+        <v>10</v>
+      </c>
       <c r="H202" s="9" t="n"/>
       <c r="I202" s="9" t="n"/>
       <c r="K202" s="9" t="n"/>
     </row>
     <row r="203">
+      <c r="G203" t="n">
+        <v>10</v>
+      </c>
       <c r="H203" s="9" t="n"/>
       <c r="I203" s="9" t="n"/>
       <c r="K203" s="9" t="n"/>
     </row>
     <row r="204">
+      <c r="G204" t="n">
+        <v>10</v>
+      </c>
       <c r="H204" s="9" t="n"/>
       <c r="I204" s="9" t="n"/>
       <c r="K204" s="9" t="n"/>
     </row>
     <row r="205">
+      <c r="G205" t="n">
+        <v>10</v>
+      </c>
       <c r="H205" s="9" t="n"/>
       <c r="I205" s="9" t="n"/>
       <c r="K205" s="9" t="n"/>
     </row>
     <row r="206">
+      <c r="G206" t="n">
+        <v>10</v>
+      </c>
       <c r="H206" s="9" t="n"/>
       <c r="I206" s="9" t="n"/>
       <c r="K206" s="9" t="n"/>
     </row>
     <row r="207">
+      <c r="G207" t="n">
+        <v>10</v>
+      </c>
       <c r="H207" s="9" t="n"/>
       <c r="I207" s="9" t="n"/>
       <c r="K207" s="9" t="n"/>
     </row>
     <row r="208">
+      <c r="G208" t="n">
+        <v>10</v>
+      </c>
       <c r="H208" s="9" t="n"/>
       <c r="I208" s="9" t="n"/>
       <c r="K208" s="9" t="n"/>
     </row>
     <row r="209">
+      <c r="G209" t="n">
+        <v>10</v>
+      </c>
       <c r="H209" s="9" t="n"/>
       <c r="I209" s="9" t="n"/>
       <c r="K209" s="9" t="n"/>
     </row>
     <row r="210">
+      <c r="G210" t="n">
+        <v>10</v>
+      </c>
       <c r="H210" s="9" t="n"/>
       <c r="I210" s="9" t="n"/>
       <c r="K210" s="9" t="n"/>
     </row>
     <row r="211">
+      <c r="G211" t="n">
+        <v>10</v>
+      </c>
       <c r="H211" s="9" t="n"/>
       <c r="I211" s="9" t="n"/>
       <c r="K211" s="9" t="n"/>
     </row>
     <row r="212">
+      <c r="G212" t="n">
+        <v>10</v>
+      </c>
       <c r="H212" s="9" t="n"/>
       <c r="I212" s="9" t="n"/>
       <c r="K212" s="9" t="n"/>
     </row>
     <row r="213">
+      <c r="G213" t="n">
+        <v>10</v>
+      </c>
       <c r="H213" s="9" t="n"/>
       <c r="I213" s="9" t="n"/>
       <c r="K213" s="9" t="n"/>
     </row>
     <row r="214">
+      <c r="G214" t="n">
+        <v>10</v>
+      </c>
       <c r="H214" s="9" t="n"/>
       <c r="I214" s="9" t="n"/>
       <c r="K214" s="9" t="n"/>
     </row>
     <row r="215">
+      <c r="G215" t="n">
+        <v>10</v>
+      </c>
       <c r="H215" s="9" t="n"/>
       <c r="I215" s="9" t="n"/>
       <c r="K215" s="9" t="n"/>
     </row>
     <row r="216">
+      <c r="G216" t="n">
+        <v>10</v>
+      </c>
       <c r="H216" s="9" t="n"/>
       <c r="I216" s="9" t="n"/>
       <c r="K216" s="9" t="n"/>
     </row>
     <row r="217">
+      <c r="G217" t="n">
+        <v>10</v>
+      </c>
       <c r="H217" s="9" t="n"/>
       <c r="I217" s="9" t="n"/>
       <c r="K217" s="9" t="n"/>
     </row>
     <row r="218">
+      <c r="G218" t="n">
+        <v>10</v>
+      </c>
       <c r="H218" s="9" t="n"/>
       <c r="I218" s="9" t="n"/>
       <c r="K218" s="9" t="n"/>
     </row>
     <row r="219">
+      <c r="G219" t="n">
+        <v>10</v>
+      </c>
       <c r="H219" s="9" t="n"/>
       <c r="I219" s="9" t="n"/>
       <c r="K219" s="9" t="n"/>
     </row>
     <row r="220">
+      <c r="G220" t="n">
+        <v>10</v>
+      </c>
       <c r="H220" s="9" t="n"/>
       <c r="I220" s="9" t="n"/>
       <c r="K220" s="9" t="n"/>
     </row>
     <row r="221">
+      <c r="G221" t="n">
+        <v>10</v>
+      </c>
       <c r="H221" s="9" t="n"/>
       <c r="I221" s="9" t="n"/>
       <c r="K221" s="9" t="n"/>
     </row>
     <row r="222">
+      <c r="G222" t="n">
+        <v>10</v>
+      </c>
       <c r="H222" s="9" t="n"/>
       <c r="I222" s="9" t="n"/>
       <c r="K222" s="9" t="n"/>
     </row>
     <row r="223">
+      <c r="G223" t="n">
+        <v>10</v>
+      </c>
       <c r="H223" s="9" t="n"/>
       <c r="I223" s="9" t="n"/>
       <c r="K223" s="9" t="n"/>
     </row>
     <row r="224">
+      <c r="G224" t="n">
+        <v>10</v>
+      </c>
       <c r="H224" s="9" t="n"/>
       <c r="I224" s="9" t="n"/>
       <c r="K224" s="9" t="n"/>
     </row>
     <row r="225">
+      <c r="G225" t="n">
+        <v>10</v>
+      </c>
       <c r="H225" s="9" t="n"/>
       <c r="I225" s="9" t="n"/>
       <c r="K225" s="9" t="n"/>
     </row>
     <row r="226">
+      <c r="G226" t="n">
+        <v>10</v>
+      </c>
       <c r="H226" s="9" t="n"/>
       <c r="I226" s="9" t="n"/>
       <c r="K226" s="9" t="n"/>
     </row>
     <row r="227">
+      <c r="G227" t="n">
+        <v>10</v>
+      </c>
       <c r="H227" s="9" t="n"/>
       <c r="I227" s="9" t="n"/>
       <c r="K227" s="9" t="n"/>
     </row>
     <row r="228">
+      <c r="G228" t="n">
+        <v>10</v>
+      </c>
       <c r="H228" s="9" t="n"/>
       <c r="I228" s="9" t="n"/>
       <c r="K228" s="9" t="n"/>
     </row>
     <row r="229">
+      <c r="G229" t="n">
+        <v>10</v>
+      </c>
       <c r="H229" s="9" t="n"/>
       <c r="I229" s="9" t="n"/>
       <c r="K229" s="9" t="n"/>
     </row>
     <row r="230">
+      <c r="G230" t="n">
+        <v>10</v>
+      </c>
       <c r="H230" s="9" t="n"/>
       <c r="I230" s="9" t="n"/>
       <c r="K230" s="9" t="n"/>
     </row>
     <row r="231">
+      <c r="G231" t="n">
+        <v>10</v>
+      </c>
       <c r="H231" s="9" t="n"/>
       <c r="I231" s="9" t="n"/>
       <c r="K231" s="9" t="n"/>
     </row>
     <row r="232">
+      <c r="G232" t="n">
+        <v>10</v>
+      </c>
       <c r="H232" s="9" t="n"/>
       <c r="I232" s="9" t="n"/>
       <c r="K232" s="9" t="n"/>
     </row>
     <row r="233">
+      <c r="G233" t="n">
+        <v>10</v>
+      </c>
       <c r="H233" s="9" t="n"/>
       <c r="I233" s="9" t="n"/>
       <c r="K233" s="9" t="n"/>
     </row>
     <row r="234">
+      <c r="G234" t="n">
+        <v>10</v>
+      </c>
       <c r="H234" s="9" t="n"/>
       <c r="I234" s="9" t="n"/>
       <c r="K234" s="9" t="n"/>
     </row>
     <row r="235">
+      <c r="G235" t="n">
+        <v>10</v>
+      </c>
       <c r="H235" s="9" t="n"/>
       <c r="I235" s="9" t="n"/>
       <c r="K235" s="9" t="n"/>
     </row>
     <row r="236">
+      <c r="G236" t="n">
+        <v>10</v>
+      </c>
       <c r="H236" s="9" t="n"/>
       <c r="I236" s="9" t="n"/>
       <c r="K236" s="9" t="n"/>
     </row>
     <row r="237">
+      <c r="G237" t="n">
+        <v>10</v>
+      </c>
       <c r="H237" s="9" t="n"/>
       <c r="I237" s="9" t="n"/>
       <c r="K237" s="9" t="n"/>
     </row>
     <row r="238">
+      <c r="G238" t="n">
+        <v>10</v>
+      </c>
       <c r="H238" s="9" t="n"/>
       <c r="I238" s="9" t="n"/>
       <c r="K238" s="9" t="n"/>
     </row>
     <row r="239">
+      <c r="G239" t="n">
+        <v>10</v>
+      </c>
       <c r="H239" s="9" t="n"/>
       <c r="I239" s="9" t="n"/>
       <c r="K239" s="9" t="n"/>
     </row>
     <row r="240">
+      <c r="G240" t="n">
+        <v>10</v>
+      </c>
       <c r="H240" s="9" t="n"/>
       <c r="I240" s="9" t="n"/>
       <c r="K240" s="9" t="n"/>
     </row>
     <row r="241">
+      <c r="G241" t="n">
+        <v>10</v>
+      </c>
       <c r="H241" s="9" t="n"/>
       <c r="I241" s="9" t="n"/>
       <c r="K241" s="9" t="n"/>
     </row>
     <row r="242">
+      <c r="G242" t="n">
+        <v>10</v>
+      </c>
       <c r="H242" s="9" t="n"/>
       <c r="I242" s="9" t="n"/>
       <c r="K242" s="9" t="n"/>
     </row>
     <row r="243">
+      <c r="G243" t="n">
+        <v>10</v>
+      </c>
       <c r="H243" s="9" t="n"/>
       <c r="I243" s="9" t="n"/>
       <c r="K243" s="9" t="n"/>
     </row>
     <row r="244">
+      <c r="G244" t="n">
+        <v>10</v>
+      </c>
       <c r="H244" s="9" t="n"/>
       <c r="I244" s="9" t="n"/>
       <c r="K244" s="9" t="n"/>
     </row>
     <row r="245">
+      <c r="G245" t="n">
+        <v>10</v>
+      </c>
       <c r="H245" s="9" t="n"/>
       <c r="I245" s="9" t="n"/>
       <c r="K245" s="9" t="n"/>
     </row>
     <row r="246">
+      <c r="G246" t="n">
+        <v>10</v>
+      </c>
       <c r="H246" s="9" t="n"/>
       <c r="I246" s="9" t="n"/>
       <c r="K246" s="9" t="n"/>
     </row>
     <row r="247">
+      <c r="G247" t="n">
+        <v>10</v>
+      </c>
       <c r="H247" s="9" t="n"/>
       <c r="I247" s="9" t="n"/>
       <c r="K247" s="9" t="n"/>
     </row>
     <row r="248">
+      <c r="G248" t="n">
+        <v>10</v>
+      </c>
       <c r="H248" s="9" t="n"/>
       <c r="I248" s="9" t="n"/>
       <c r="K248" s="9" t="n"/>
     </row>
     <row r="249">
+      <c r="G249" t="n">
+        <v>10</v>
+      </c>
       <c r="H249" s="9" t="n"/>
       <c r="I249" s="9" t="n"/>
       <c r="K249" s="9" t="n"/>
     </row>
     <row r="250">
+      <c r="G250" t="n">
+        <v>10</v>
+      </c>
       <c r="H250" s="9" t="n"/>
       <c r="I250" s="9" t="n"/>
       <c r="K250" s="9" t="n"/>
     </row>
     <row r="251">
+      <c r="G251" t="n">
+        <v>10</v>
+      </c>
       <c r="H251" s="9" t="n"/>
       <c r="I251" s="9" t="n"/>
       <c r="K251" s="9" t="n"/>
     </row>
     <row r="252">
+      <c r="G252" t="n">
+        <v>10</v>
+      </c>
       <c r="H252" s="9" t="n"/>
       <c r="I252" s="9" t="n"/>
       <c r="K252" s="9" t="n"/>
     </row>
     <row r="253">
+      <c r="G253" t="n">
+        <v>10</v>
+      </c>
       <c r="H253" s="9" t="n"/>
       <c r="I253" s="9" t="n"/>
       <c r="K253" s="9" t="n"/>
     </row>
     <row r="254">
+      <c r="G254" t="n">
+        <v>10</v>
+      </c>
       <c r="H254" s="9" t="n"/>
       <c r="I254" s="9" t="n"/>
       <c r="K254" s="9" t="n"/>
     </row>
     <row r="255">
+      <c r="G255" t="n">
+        <v>10</v>
+      </c>
       <c r="H255" s="9" t="n"/>
       <c r="I255" s="9" t="n"/>
       <c r="K255" s="9" t="n"/>
     </row>
     <row r="256">
+      <c r="G256" t="n">
+        <v>10</v>
+      </c>
       <c r="H256" s="9" t="n"/>
       <c r="I256" s="9" t="n"/>
       <c r="K256" s="9" t="n"/>
     </row>
     <row r="257">
+      <c r="G257" t="n">
+        <v>10</v>
+      </c>
       <c r="H257" s="9" t="n"/>
       <c r="I257" s="9" t="n"/>
       <c r="K257" s="9" t="n"/>
     </row>
     <row r="258">
+      <c r="G258" t="n">
+        <v>10</v>
+      </c>
       <c r="H258" s="9" t="n"/>
       <c r="I258" s="9" t="n"/>
       <c r="K258" s="9" t="n"/>
     </row>
     <row r="259">
+      <c r="G259" t="n">
+        <v>10</v>
+      </c>
       <c r="H259" s="9" t="n"/>
       <c r="I259" s="9" t="n"/>
       <c r="K259" s="9" t="n"/>
     </row>
     <row r="260">
+      <c r="G260" t="n">
+        <v>10</v>
+      </c>
       <c r="H260" s="9" t="n"/>
       <c r="I260" s="9" t="n"/>
       <c r="K260" s="9" t="n"/>
     </row>
     <row r="261">
+      <c r="G261" t="n">
+        <v>10</v>
+      </c>
       <c r="H261" s="9" t="n"/>
       <c r="I261" s="9" t="n"/>
       <c r="K261" s="9" t="n"/>
     </row>
     <row r="262">
+      <c r="G262" t="n">
+        <v>10</v>
+      </c>
       <c r="H262" s="9" t="n"/>
       <c r="I262" s="9" t="n"/>
       <c r="K262" s="9" t="n"/>
     </row>
     <row r="263">
+      <c r="G263" t="n">
+        <v>10</v>
+      </c>
       <c r="H263" s="9" t="n"/>
       <c r="I263" s="9" t="n"/>
       <c r="K263" s="9" t="n"/>
     </row>
     <row r="264">
+      <c r="G264" t="n">
+        <v>10</v>
+      </c>
       <c r="H264" s="9" t="n"/>
       <c r="I264" s="9" t="n"/>
       <c r="K264" s="9" t="n"/>
     </row>
     <row r="265">
+      <c r="G265" t="n">
+        <v>10</v>
+      </c>
       <c r="H265" s="9" t="n"/>
       <c r="I265" s="9" t="n"/>
       <c r="K265" s="9" t="n"/>
     </row>
     <row r="266">
+      <c r="G266" t="n">
+        <v>10</v>
+      </c>
       <c r="H266" s="9" t="n"/>
       <c r="I266" s="9" t="n"/>
       <c r="K266" s="9" t="n"/>
     </row>
     <row r="267">
+      <c r="G267" t="n">
+        <v>10</v>
+      </c>
       <c r="H267" s="9" t="n"/>
       <c r="I267" s="9" t="n"/>
       <c r="K267" s="9" t="n"/>
     </row>
     <row r="268">
+      <c r="G268" t="n">
+        <v>10</v>
+      </c>
       <c r="H268" s="9" t="n"/>
       <c r="I268" s="9" t="n"/>
       <c r="K268" s="9" t="n"/>
     </row>
     <row r="269">
+      <c r="G269" t="n">
+        <v>10</v>
+      </c>
       <c r="H269" s="9" t="n"/>
       <c r="I269" s="9" t="n"/>
       <c r="K269" s="9" t="n"/>
     </row>
     <row r="270">
+      <c r="G270" t="n">
+        <v>10</v>
+      </c>
       <c r="H270" s="9" t="n"/>
       <c r="I270" s="9" t="n"/>
       <c r="K270" s="9" t="n"/>
     </row>
     <row r="271">
+      <c r="G271" t="n">
+        <v>10</v>
+      </c>
       <c r="H271" s="9" t="n"/>
       <c r="I271" s="9" t="n"/>
       <c r="K271" s="9" t="n"/>
     </row>
     <row r="272">
+      <c r="G272" t="n">
+        <v>10</v>
+      </c>
       <c r="H272" s="9" t="n"/>
       <c r="I272" s="9" t="n"/>
       <c r="K272" s="9" t="n"/>
     </row>
     <row r="273">
+      <c r="G273" t="n">
+        <v>10</v>
+      </c>
       <c r="H273" s="9" t="n"/>
       <c r="I273" s="9" t="n"/>
       <c r="K273" s="9" t="n"/>
     </row>
     <row r="274">
+      <c r="G274" t="n">
+        <v>10</v>
+      </c>
       <c r="H274" s="9" t="n"/>
       <c r="I274" s="9" t="n"/>
       <c r="K274" s="9" t="n"/>
     </row>
     <row r="275">
+      <c r="G275" t="n">
+        <v>10</v>
+      </c>
       <c r="H275" s="9" t="n"/>
       <c r="I275" s="9" t="n"/>
       <c r="K275" s="9" t="n"/>
     </row>
     <row r="276">
+      <c r="G276" t="n">
+        <v>10</v>
+      </c>
       <c r="H276" s="9" t="n"/>
       <c r="I276" s="9" t="n"/>
       <c r="K276" s="9" t="n"/>
     </row>
     <row r="277">
+      <c r="G277" t="n">
+        <v>10</v>
+      </c>
       <c r="H277" s="9" t="n"/>
       <c r="I277" s="9" t="n"/>
       <c r="K277" s="9" t="n"/>
     </row>
     <row r="278">
+      <c r="G278" t="n">
+        <v>10</v>
+      </c>
       <c r="H278" s="9" t="n"/>
       <c r="I278" s="9" t="n"/>
       <c r="K278" s="9" t="n"/>
     </row>
     <row r="279">
+      <c r="G279" t="n">
+        <v>10</v>
+      </c>
       <c r="H279" s="9" t="n"/>
       <c r="I279" s="9" t="n"/>
       <c r="K279" s="9" t="n"/>
     </row>
     <row r="280">
+      <c r="G280" t="n">
+        <v>10</v>
+      </c>
       <c r="H280" s="9" t="n"/>
       <c r="I280" s="9" t="n"/>
       <c r="K280" s="9" t="n"/>
     </row>
     <row r="281">
+      <c r="G281" t="n">
+        <v>10</v>
+      </c>
       <c r="H281" s="9" t="n"/>
       <c r="I281" s="9" t="n"/>
       <c r="K281" s="9" t="n"/>
     </row>
     <row r="282">
+      <c r="G282" t="n">
+        <v>10</v>
+      </c>
       <c r="H282" s="9" t="n"/>
       <c r="I282" s="9" t="n"/>
       <c r="K282" s="9" t="n"/>
     </row>
     <row r="283">
+      <c r="G283" t="n">
+        <v>10</v>
+      </c>
       <c r="H283" s="9" t="n"/>
       <c r="I283" s="9" t="n"/>
       <c r="K283" s="9" t="n"/>
     </row>
     <row r="284">
+      <c r="G284" t="n">
+        <v>10</v>
+      </c>
       <c r="H284" s="9" t="n"/>
       <c r="I284" s="9" t="n"/>
       <c r="K284" s="9" t="n"/>
     </row>
     <row r="285">
+      <c r="G285" t="n">
+        <v>10</v>
+      </c>
       <c r="H285" s="9" t="n"/>
       <c r="I285" s="9" t="n"/>
       <c r="K285" s="9" t="n"/>
     </row>
     <row r="286">
+      <c r="G286" t="n">
+        <v>10</v>
+      </c>
       <c r="H286" s="9" t="n"/>
       <c r="I286" s="9" t="n"/>
       <c r="K286" s="9" t="n"/>
     </row>
     <row r="287">
+      <c r="G287" t="n">
+        <v>10</v>
+      </c>
       <c r="H287" s="9" t="n"/>
       <c r="I287" s="9" t="n"/>
       <c r="K287" s="9" t="n"/>
     </row>
     <row r="288">
+      <c r="G288" t="n">
+        <v>10</v>
+      </c>
       <c r="H288" s="9" t="n"/>
       <c r="I288" s="9" t="n"/>
       <c r="K288" s="9" t="n"/>
     </row>
     <row r="289">
+      <c r="G289" t="n">
+        <v>10</v>
+      </c>
       <c r="H289" s="9" t="n"/>
       <c r="I289" s="9" t="n"/>
       <c r="K289" s="9" t="n"/>
     </row>
     <row r="290">
+      <c r="G290" t="n">
+        <v>10</v>
+      </c>
       <c r="H290" s="9" t="n"/>
       <c r="I290" s="9" t="n"/>
       <c r="K290" s="9" t="n"/>
     </row>
     <row r="291">
+      <c r="G291" t="n">
+        <v>10</v>
+      </c>
       <c r="H291" s="9" t="n"/>
       <c r="I291" s="9" t="n"/>
       <c r="K291" s="9" t="n"/>
     </row>
     <row r="292">
+      <c r="G292" t="n">
+        <v>10</v>
+      </c>
       <c r="H292" s="9" t="n"/>
       <c r="I292" s="9" t="n"/>
       <c r="K292" s="9" t="n"/>
     </row>
     <row r="293">
+      <c r="G293" t="n">
+        <v>10</v>
+      </c>
       <c r="H293" s="9" t="n"/>
       <c r="I293" s="9" t="n"/>
       <c r="K293" s="9" t="n"/>
     </row>
     <row r="294">
+      <c r="G294" t="n">
+        <v>10</v>
+      </c>
       <c r="H294" s="9" t="n"/>
       <c r="I294" s="9" t="n"/>
       <c r="K294" s="9" t="n"/>
     </row>
     <row r="295">
+      <c r="G295" t="n">
+        <v>10</v>
+      </c>
       <c r="H295" s="9" t="n"/>
       <c r="I295" s="9" t="n"/>
       <c r="K295" s="9" t="n"/>
     </row>
     <row r="296">
+      <c r="G296" t="n">
+        <v>10</v>
+      </c>
       <c r="H296" s="9" t="n"/>
       <c r="I296" s="9" t="n"/>
       <c r="K296" s="9" t="n"/>
     </row>
     <row r="297">
+      <c r="G297" t="n">
+        <v>10</v>
+      </c>
       <c r="H297" s="9" t="n"/>
       <c r="I297" s="9" t="n"/>
       <c r="K297" s="9" t="n"/>
     </row>
     <row r="298">
+      <c r="G298" t="n">
+        <v>10</v>
+      </c>
       <c r="H298" s="9" t="n"/>
       <c r="I298" s="9" t="n"/>
       <c r="K298" s="9" t="n"/>
     </row>
     <row r="299">
+      <c r="G299" t="n">
+        <v>10</v>
+      </c>
       <c r="H299" s="9" t="n"/>
       <c r="I299" s="9" t="n"/>
       <c r="K299" s="9" t="n"/>
     </row>
     <row r="300">
+      <c r="G300" t="n">
+        <v>10</v>
+      </c>
       <c r="H300" s="9" t="n"/>
       <c r="I300" s="9" t="n"/>
       <c r="K300" s="9" t="n"/>
     </row>
     <row r="301">
+      <c r="G301" t="n">
+        <v>10</v>
+      </c>
       <c r="H301" s="9" t="n"/>
       <c r="I301" s="9" t="n"/>
       <c r="K301" s="9" t="n"/>
     </row>
     <row r="302">
+      <c r="G302" t="n">
+        <v>10</v>
+      </c>
       <c r="H302" s="9" t="n"/>
       <c r="I302" s="9" t="n"/>
       <c r="K302" s="9" t="n"/>
     </row>
     <row r="303">
+      <c r="G303" t="n">
+        <v>10</v>
+      </c>
       <c r="H303" s="9" t="n"/>
       <c r="I303" s="9" t="n"/>
       <c r="K303" s="9" t="n"/>
     </row>
     <row r="304">
+      <c r="G304" t="n">
+        <v>10</v>
+      </c>
       <c r="H304" s="9" t="n"/>
       <c r="I304" s="9" t="n"/>
       <c r="K304" s="9" t="n"/>
     </row>
     <row r="305">
+      <c r="G305" t="n">
+        <v>10</v>
+      </c>
       <c r="H305" s="9" t="n"/>
       <c r="I305" s="9" t="n"/>
       <c r="K305" s="9" t="n"/>
     </row>
     <row r="306">
+      <c r="G306" t="n">
+        <v>10</v>
+      </c>
       <c r="H306" s="9" t="n"/>
       <c r="I306" s="9" t="n"/>
       <c r="K306" s="9" t="n"/>
     </row>
     <row r="307">
+      <c r="G307" t="n">
+        <v>10</v>
+      </c>
       <c r="H307" s="9" t="n"/>
       <c r="I307" s="9" t="n"/>
       <c r="K307" s="9" t="n"/>
     </row>
     <row r="308">
+      <c r="G308" t="n">
+        <v>10</v>
+      </c>
       <c r="H308" s="9" t="n"/>
       <c r="I308" s="9" t="n"/>
       <c r="K308" s="9" t="n"/>
     </row>
     <row r="309">
+      <c r="G309" t="n">
+        <v>10</v>
+      </c>
       <c r="H309" s="9" t="n"/>
       <c r="I309" s="9" t="n"/>
       <c r="K309" s="9" t="n"/>
     </row>
     <row r="310">
+      <c r="G310" t="n">
+        <v>10</v>
+      </c>
       <c r="H310" s="9" t="n"/>
       <c r="I310" s="9" t="n"/>
       <c r="K310" s="9" t="n"/>
     </row>
     <row r="311">
+      <c r="G311" t="n">
+        <v>10</v>
+      </c>
       <c r="H311" s="9" t="n"/>
       <c r="I311" s="9" t="n"/>
       <c r="K311" s="9" t="n"/>
     </row>
     <row r="312">
+      <c r="G312" t="n">
+        <v>10</v>
+      </c>
       <c r="H312" s="9" t="n"/>
       <c r="I312" s="9" t="n"/>
       <c r="K312" s="9" t="n"/>
     </row>
     <row r="313">
+      <c r="G313" t="n">
+        <v>10</v>
+      </c>
       <c r="H313" s="9" t="n"/>
       <c r="I313" s="9" t="n"/>
       <c r="K313" s="9" t="n"/>
     </row>
     <row r="314">
+      <c r="G314" t="n">
+        <v>10</v>
+      </c>
       <c r="H314" s="9" t="n"/>
       <c r="I314" s="9" t="n"/>
       <c r="K314" s="9" t="n"/>
     </row>
     <row r="315">
+      <c r="G315" t="n">
+        <v>10</v>
+      </c>
       <c r="H315" s="9" t="n"/>
       <c r="I315" s="9" t="n"/>
       <c r="K315" s="9" t="n"/>
     </row>
     <row r="316">
+      <c r="G316" t="n">
+        <v>10</v>
+      </c>
       <c r="H316" s="9" t="n"/>
       <c r="I316" s="9" t="n"/>
       <c r="K316" s="9" t="n"/>
     </row>
     <row r="317">
+      <c r="G317" t="n">
+        <v>10</v>
+      </c>
       <c r="H317" s="9" t="n"/>
       <c r="I317" s="9" t="n"/>
       <c r="K317" s="9" t="n"/>
     </row>
     <row r="318">
+      <c r="G318" t="n">
+        <v>10</v>
+      </c>
       <c r="H318" s="9" t="n"/>
       <c r="I318" s="9" t="n"/>
       <c r="K318" s="9" t="n"/>
     </row>
     <row r="319">
+      <c r="G319" t="n">
+        <v>10</v>
+      </c>
       <c r="H319" s="9" t="n"/>
       <c r="I319" s="9" t="n"/>
       <c r="K319" s="9" t="n"/>
     </row>
     <row r="320">
+      <c r="G320" t="n">
+        <v>10</v>
+      </c>
       <c r="H320" s="9" t="n"/>
       <c r="I320" s="9" t="n"/>
       <c r="K320" s="9" t="n"/>
     </row>
     <row r="321">
+      <c r="G321" t="n">
+        <v>10</v>
+      </c>
       <c r="H321" s="9" t="n"/>
       <c r="I321" s="9" t="n"/>
       <c r="K321" s="9" t="n"/>
     </row>
     <row r="322">
+      <c r="G322" t="n">
+        <v>10</v>
+      </c>
       <c r="H322" s="9" t="n"/>
       <c r="I322" s="9" t="n"/>
       <c r="K322" s="9" t="n"/>
     </row>
     <row r="323">
+      <c r="G323" t="n">
+        <v>10</v>
+      </c>
       <c r="H323" s="9" t="n"/>
       <c r="I323" s="9" t="n"/>
       <c r="K323" s="9" t="n"/>
     </row>
     <row r="324">
+      <c r="G324" t="n">
+        <v>10</v>
+      </c>
       <c r="H324" s="9" t="n"/>
       <c r="I324" s="9" t="n"/>
       <c r="K324" s="9" t="n"/>
     </row>
     <row r="325">
+      <c r="G325" t="n">
+        <v>10</v>
+      </c>
       <c r="H325" s="9" t="n"/>
       <c r="I325" s="9" t="n"/>
       <c r="K325" s="9" t="n"/>
     </row>
     <row r="326">
+      <c r="G326" t="n">
+        <v>10</v>
+      </c>
       <c r="H326" s="9" t="n"/>
       <c r="I326" s="9" t="n"/>
       <c r="K326" s="9" t="n"/>
     </row>
     <row r="327">
+      <c r="G327" t="n">
+        <v>10</v>
+      </c>
       <c r="H327" s="9" t="n"/>
       <c r="I327" s="9" t="n"/>
       <c r="K327" s="9" t="n"/>
     </row>
     <row r="328">
+      <c r="G328" t="n">
+        <v>10</v>
+      </c>
       <c r="H328" s="9" t="n"/>
       <c r="I328" s="9" t="n"/>
       <c r="K328" s="9" t="n"/>
     </row>
     <row r="329">
+      <c r="G329" t="n">
+        <v>10</v>
+      </c>
       <c r="H329" s="9" t="n"/>
       <c r="I329" s="9" t="n"/>
       <c r="K329" s="9" t="n"/>
     </row>
     <row r="330">
+      <c r="G330" t="n">
+        <v>10</v>
+      </c>
       <c r="H330" s="9" t="n"/>
       <c r="I330" s="9" t="n"/>
       <c r="K330" s="9" t="n"/>
     </row>
     <row r="331">
+      <c r="G331" t="n">
+        <v>10</v>
+      </c>
       <c r="H331" s="9" t="n"/>
       <c r="I331" s="9" t="n"/>
       <c r="K331" s="9" t="n"/>
     </row>
     <row r="332">
+      <c r="G332" t="n">
+        <v>10</v>
+      </c>
       <c r="H332" s="9" t="n"/>
       <c r="I332" s="9" t="n"/>
       <c r="K332" s="9" t="n"/>
     </row>
     <row r="333">
+      <c r="G333" t="n">
+        <v>10</v>
+      </c>
       <c r="H333" s="9" t="n"/>
       <c r="I333" s="9" t="n"/>
       <c r="K333" s="9" t="n"/>
     </row>
     <row r="334">
+      <c r="G334" t="n">
+        <v>10</v>
+      </c>
       <c r="H334" s="9" t="n"/>
       <c r="I334" s="9" t="n"/>
       <c r="K334" s="9" t="n"/>
     </row>
     <row r="335">
+      <c r="G335" t="n">
+        <v>10</v>
+      </c>
       <c r="H335" s="9" t="n"/>
       <c r="I335" s="9" t="n"/>
       <c r="K335" s="9" t="n"/>
     </row>
     <row r="336">
+      <c r="G336" t="n">
+        <v>10</v>
+      </c>
       <c r="H336" s="9" t="n"/>
       <c r="I336" s="9" t="n"/>
       <c r="K336" s="9" t="n"/>
     </row>
     <row r="337">
+      <c r="G337" t="n">
+        <v>10</v>
+      </c>
       <c r="H337" s="9" t="n"/>
       <c r="I337" s="9" t="n"/>
       <c r="K337" s="9" t="n"/>
     </row>
     <row r="338">
+      <c r="G338" t="n">
+        <v>10</v>
+      </c>
       <c r="H338" s="9" t="n"/>
       <c r="I338" s="9" t="n"/>
       <c r="K338" s="9" t="n"/>
     </row>
     <row r="339">
+      <c r="G339" t="n">
+        <v>10</v>
+      </c>
       <c r="H339" s="9" t="n"/>
       <c r="I339" s="9" t="n"/>
       <c r="K339" s="9" t="n"/>
     </row>
     <row r="340">
+      <c r="G340" t="n">
+        <v>10</v>
+      </c>
       <c r="H340" s="9" t="n"/>
       <c r="I340" s="9" t="n"/>
       <c r="K340" s="9" t="n"/>
     </row>
     <row r="341">
+      <c r="G341" t="n">
+        <v>10</v>
+      </c>
       <c r="H341" s="9" t="n"/>
       <c r="I341" s="9" t="n"/>
       <c r="K341" s="9" t="n"/>
     </row>
     <row r="342">
+      <c r="G342" t="n">
+        <v>10</v>
+      </c>
       <c r="H342" s="9" t="n"/>
       <c r="I342" s="9" t="n"/>
       <c r="K342" s="9" t="n"/>
     </row>
     <row r="343">
+      <c r="G343" t="n">
+        <v>10</v>
+      </c>
       <c r="H343" s="9" t="n"/>
       <c r="I343" s="9" t="n"/>
       <c r="K343" s="9" t="n"/>
     </row>
     <row r="344">
+      <c r="G344" t="n">
+        <v>10</v>
+      </c>
       <c r="H344" s="9" t="n"/>
       <c r="I344" s="9" t="n"/>
       <c r="K344" s="9" t="n"/>
     </row>
     <row r="345">
+      <c r="G345" t="n">
+        <v>10</v>
+      </c>
       <c r="H345" s="9" t="n"/>
       <c r="I345" s="9" t="n"/>
       <c r="K345" s="9" t="n"/>
     </row>
     <row r="346">
+      <c r="G346" t="n">
+        <v>10</v>
+      </c>
       <c r="H346" s="9" t="n"/>
       <c r="I346" s="9" t="n"/>
       <c r="K346" s="9" t="n"/>
     </row>
     <row r="347">
+      <c r="G347" t="n">
+        <v>10</v>
+      </c>
       <c r="H347" s="9" t="n"/>
       <c r="I347" s="9" t="n"/>
       <c r="K347" s="9" t="n"/>
     </row>
     <row r="348">
+      <c r="G348" t="n">
+        <v>10</v>
+      </c>
       <c r="H348" s="9" t="n"/>
       <c r="I348" s="9" t="n"/>
       <c r="K348" s="9" t="n"/>
     </row>
     <row r="349">
+      <c r="G349" t="n">
+        <v>10</v>
+      </c>
       <c r="H349" s="9" t="n"/>
       <c r="I349" s="9" t="n"/>
       <c r="K349" s="9" t="n"/>
     </row>
     <row r="350">
+      <c r="G350" t="n">
+        <v>10</v>
+      </c>
       <c r="H350" s="9" t="n"/>
       <c r="I350" s="9" t="n"/>
       <c r="K350" s="9" t="n"/>
     </row>
     <row r="351">
+      <c r="G351" t="n">
+        <v>10</v>
+      </c>
       <c r="H351" s="9" t="n"/>
       <c r="I351" s="9" t="n"/>
       <c r="K351" s="9" t="n"/>
     </row>
     <row r="352">
+      <c r="G352" t="n">
+        <v>10</v>
+      </c>
       <c r="H352" s="9" t="n"/>
       <c r="I352" s="9" t="n"/>
       <c r="K352" s="9" t="n"/>
     </row>
     <row r="353">
+      <c r="G353" t="n">
+        <v>10</v>
+      </c>
       <c r="H353" s="9" t="n"/>
       <c r="I353" s="9" t="n"/>
       <c r="K353" s="9" t="n"/>
     </row>
     <row r="354">
+      <c r="G354" t="n">
+        <v>10</v>
+      </c>
       <c r="H354" s="9" t="n"/>
       <c r="I354" s="9" t="n"/>
       <c r="K354" s="9" t="n"/>
     </row>
     <row r="355">
+      <c r="G355" t="n">
+        <v>10</v>
+      </c>
       <c r="H355" s="9" t="n"/>
       <c r="I355" s="9" t="n"/>
       <c r="K355" s="9" t="n"/>
     </row>
     <row r="356">
+      <c r="G356" t="n">
+        <v>10</v>
+      </c>
       <c r="H356" s="9" t="n"/>
       <c r="I356" s="9" t="n"/>
       <c r="K356" s="9" t="n"/>
     </row>
     <row r="357">
+      <c r="G357" t="n">
+        <v>10</v>
+      </c>
       <c r="H357" s="9" t="n"/>
       <c r="I357" s="9" t="n"/>
       <c r="K357" s="9" t="n"/>
     </row>
     <row r="358">
+      <c r="G358" t="n">
+        <v>10</v>
+      </c>
       <c r="H358" s="9" t="n"/>
       <c r="I358" s="9" t="n"/>
       <c r="K358" s="9" t="n"/>
     </row>
     <row r="359">
+      <c r="G359" t="n">
+        <v>10</v>
+      </c>
       <c r="H359" s="9" t="n"/>
       <c r="I359" s="9" t="n"/>
       <c r="K359" s="9" t="n"/>
     </row>
     <row r="360">
+      <c r="G360" t="n">
+        <v>10</v>
+      </c>
       <c r="H360" s="9" t="n"/>
       <c r="I360" s="9" t="n"/>
       <c r="K360" s="9" t="n"/>
     </row>
     <row r="361">
+      <c r="G361" t="n">
+        <v>10</v>
+      </c>
       <c r="H361" s="9" t="n"/>
       <c r="I361" s="9" t="n"/>
       <c r="K361" s="9" t="n"/>
     </row>
     <row r="362">
+      <c r="G362" t="n">
+        <v>10</v>
+      </c>
       <c r="H362" s="9" t="n"/>
       <c r="I362" s="9" t="n"/>
       <c r="K362" s="9" t="n"/>
     </row>
     <row r="363">
+      <c r="G363" t="n">
+        <v>10</v>
+      </c>
       <c r="H363" s="9" t="n"/>
       <c r="I363" s="9" t="n"/>
       <c r="K363" s="9" t="n"/>
     </row>
     <row r="364">
+      <c r="G364" t="n">
+        <v>10</v>
+      </c>
       <c r="H364" s="9" t="n"/>
       <c r="I364" s="9" t="n"/>
       <c r="K364" s="9" t="n"/>
     </row>
     <row r="365">
+      <c r="G365" t="n">
+        <v>10</v>
+      </c>
       <c r="H365" s="9" t="n"/>
       <c r="I365" s="9" t="n"/>
       <c r="K365" s="9" t="n"/>
     </row>
     <row r="366">
+      <c r="G366" t="n">
+        <v>10</v>
+      </c>
       <c r="H366" s="9" t="n"/>
       <c r="I366" s="9" t="n"/>
       <c r="K366" s="9" t="n"/>
     </row>
     <row r="367">
+      <c r="G367" t="n">
+        <v>10</v>
+      </c>
       <c r="H367" s="9" t="n"/>
       <c r="I367" s="9" t="n"/>
       <c r="K367" s="9" t="n"/>
     </row>
     <row r="368">
+      <c r="G368" t="n">
+        <v>10</v>
+      </c>
       <c r="H368" s="9" t="n"/>
       <c r="I368" s="9" t="n"/>
       <c r="K368" s="9" t="n"/>
     </row>
     <row r="369">
+      <c r="G369" t="n">
+        <v>10</v>
+      </c>
       <c r="H369" s="9" t="n"/>
       <c r="I369" s="9" t="n"/>
       <c r="K369" s="9" t="n"/>
     </row>
     <row r="370">
+      <c r="G370" t="n">
+        <v>10</v>
+      </c>
       <c r="H370" s="9" t="n"/>
       <c r="I370" s="9" t="n"/>
       <c r="K370" s="9" t="n"/>
     </row>
     <row r="371">
+      <c r="G371" t="n">
+        <v>10</v>
+      </c>
       <c r="H371" s="9" t="n"/>
       <c r="I371" s="9" t="n"/>
       <c r="K371" s="9" t="n"/>
     </row>
     <row r="372">
+      <c r="G372" t="n">
+        <v>10</v>
+      </c>
       <c r="H372" s="9" t="n"/>
       <c r="I372" s="9" t="n"/>
       <c r="K372" s="9" t="n"/>
     </row>
     <row r="373">
+      <c r="G373" t="n">
+        <v>10</v>
+      </c>
       <c r="H373" s="9" t="n"/>
       <c r="I373" s="9" t="n"/>
       <c r="K373" s="9" t="n"/>
     </row>
     <row r="374">
+      <c r="G374" t="n">
+        <v>10</v>
+      </c>
       <c r="H374" s="9" t="n"/>
       <c r="I374" s="9" t="n"/>
       <c r="K374" s="9" t="n"/>
     </row>
     <row r="375">
+      <c r="G375" t="n">
+        <v>10</v>
+      </c>
       <c r="H375" s="9" t="n"/>
       <c r="I375" s="9" t="n"/>
       <c r="K375" s="9" t="n"/>
     </row>
     <row r="376">
+      <c r="G376" t="n">
+        <v>10</v>
+      </c>
       <c r="H376" s="9" t="n"/>
       <c r="I376" s="9" t="n"/>
       <c r="K376" s="9" t="n"/>
     </row>
     <row r="377">
+      <c r="G377" t="n">
+        <v>10</v>
+      </c>
       <c r="H377" s="9" t="n"/>
       <c r="I377" s="9" t="n"/>
       <c r="K377" s="9" t="n"/>
     </row>
     <row r="378">
+      <c r="G378" t="n">
+        <v>10</v>
+      </c>
       <c r="H378" s="9" t="n"/>
       <c r="I378" s="9" t="n"/>
       <c r="K378" s="9" t="n"/>
     </row>
     <row r="379">
+      <c r="G379" t="n">
+        <v>10</v>
+      </c>
       <c r="H379" s="9" t="n"/>
       <c r="I379" s="9" t="n"/>
       <c r="K379" s="9" t="n"/>
     </row>
     <row r="380">
+      <c r="G380" t="n">
+        <v>10</v>
+      </c>
       <c r="H380" s="9" t="n"/>
       <c r="I380" s="9" t="n"/>
       <c r="K380" s="9" t="n"/>
     </row>
     <row r="381">
+      <c r="G381" t="n">
+        <v>10</v>
+      </c>
       <c r="H381" s="9" t="n"/>
       <c r="I381" s="9" t="n"/>
       <c r="K381" s="9" t="n"/>
     </row>
     <row r="382">
+      <c r="G382" t="n">
+        <v>10</v>
+      </c>
       <c r="H382" s="9" t="n"/>
       <c r="I382" s="9" t="n"/>
       <c r="K382" s="9" t="n"/>
     </row>
     <row r="383">
+      <c r="G383" t="n">
+        <v>10</v>
+      </c>
       <c r="H383" s="9" t="n"/>
       <c r="I383" s="9" t="n"/>
       <c r="K383" s="9" t="n"/>
     </row>
     <row r="384">
+      <c r="G384" t="n">
+        <v>10</v>
+      </c>
       <c r="H384" s="9" t="n"/>
       <c r="I384" s="9" t="n"/>
       <c r="K384" s="9" t="n"/>
     </row>
     <row r="385">
+      <c r="G385" t="n">
+        <v>10</v>
+      </c>
       <c r="H385" s="9" t="n"/>
       <c r="I385" s="9" t="n"/>
       <c r="K385" s="9" t="n"/>
     </row>
     <row r="386">
+      <c r="G386" t="n">
+        <v>10</v>
+      </c>
       <c r="H386" s="9" t="n"/>
       <c r="I386" s="9" t="n"/>
       <c r="K386" s="9" t="n"/>
     </row>
     <row r="387">
+      <c r="G387" t="n">
+        <v>10</v>
+      </c>
       <c r="H387" s="9" t="n"/>
       <c r="I387" s="9" t="n"/>
       <c r="K387" s="9" t="n"/>
     </row>
     <row r="388">
+      <c r="G388" t="n">
+        <v>10</v>
+      </c>
       <c r="H388" s="9" t="n"/>
       <c r="I388" s="9" t="n"/>
       <c r="K388" s="9" t="n"/>
     </row>
     <row r="389">
+      <c r="G389" t="n">
+        <v>10</v>
+      </c>
       <c r="H389" s="9" t="n"/>
       <c r="I389" s="9" t="n"/>
       <c r="K389" s="9" t="n"/>
     </row>
     <row r="390">
+      <c r="G390" t="n">
+        <v>10</v>
+      </c>
       <c r="H390" s="9" t="n"/>
       <c r="I390" s="9" t="n"/>
       <c r="K390" s="9" t="n"/>
     </row>
     <row r="391">
+      <c r="G391" t="n">
+        <v>10</v>
+      </c>
       <c r="H391" s="9" t="n"/>
       <c r="I391" s="9" t="n"/>
       <c r="K391" s="9" t="n"/>
     </row>
     <row r="392">
+      <c r="G392" t="n">
+        <v>10</v>
+      </c>
       <c r="H392" s="9" t="n"/>
       <c r="I392" s="9" t="n"/>
       <c r="K392" s="9" t="n"/>
     </row>
     <row r="393">
+      <c r="G393" t="n">
+        <v>10</v>
+      </c>
       <c r="H393" s="9" t="n"/>
       <c r="I393" s="9" t="n"/>
       <c r="K393" s="9" t="n"/>
     </row>
     <row r="394">
+      <c r="G394" t="n">
+        <v>10</v>
+      </c>
       <c r="H394" s="9" t="n"/>
       <c r="I394" s="9" t="n"/>
       <c r="K394" s="9" t="n"/>
     </row>
     <row r="395">
+      <c r="G395" t="n">
+        <v>10</v>
+      </c>
       <c r="H395" s="9" t="n"/>
       <c r="I395" s="9" t="n"/>
       <c r="K395" s="9" t="n"/>
     </row>
     <row r="396">
+      <c r="G396" t="n">
+        <v>10</v>
+      </c>
       <c r="H396" s="9" t="n"/>
       <c r="I396" s="9" t="n"/>
       <c r="K396" s="9" t="n"/>
     </row>
     <row r="397">
+      <c r="G397" t="n">
+        <v>10</v>
+      </c>
       <c r="H397" s="9" t="n"/>
       <c r="I397" s="9" t="n"/>
       <c r="K397" s="9" t="n"/>
     </row>
     <row r="398">
+      <c r="G398" t="n">
+        <v>10</v>
+      </c>
       <c r="H398" s="9" t="n"/>
       <c r="I398" s="9" t="n"/>
       <c r="K398" s="9" t="n"/>
     </row>
     <row r="399">
+      <c r="G399" t="n">
+        <v>10</v>
+      </c>
       <c r="H399" s="9" t="n"/>
       <c r="I399" s="9" t="n"/>
       <c r="K399" s="9" t="n"/>
     </row>
     <row r="400">
+      <c r="G400" t="n">
+        <v>10</v>
+      </c>
       <c r="H400" s="9" t="n"/>
       <c r="I400" s="9" t="n"/>
       <c r="K400" s="9" t="n"/>
     </row>
     <row r="401">
+      <c r="G401" t="n">
+        <v>10</v>
+      </c>
       <c r="H401" s="9" t="n"/>
       <c r="I401" s="9" t="n"/>
       <c r="K401" s="9" t="n"/>
     </row>
     <row r="402">
+      <c r="G402" t="n">
+        <v>10</v>
+      </c>
       <c r="H402" s="9" t="n"/>
       <c r="I402" s="9" t="n"/>
       <c r="K402" s="9" t="n"/>
     </row>
     <row r="403">
+      <c r="G403" t="n">
+        <v>10</v>
+      </c>
       <c r="H403" s="9" t="n"/>
       <c r="I403" s="9" t="n"/>
       <c r="K403" s="9" t="n"/>
     </row>
     <row r="404">
+      <c r="G404" t="n">
+        <v>10</v>
+      </c>
       <c r="H404" s="9" t="n"/>
       <c r="I404" s="9" t="n"/>
       <c r="K404" s="9" t="n"/>
     </row>
     <row r="405">
+      <c r="G405" t="n">
+        <v>10</v>
+      </c>
       <c r="H405" s="9" t="n"/>
       <c r="I405" s="9" t="n"/>
       <c r="K405" s="9" t="n"/>
     </row>
     <row r="406">
+      <c r="G406" t="n">
+        <v>10</v>
+      </c>
       <c r="H406" s="9" t="n"/>
       <c r="I406" s="9" t="n"/>
       <c r="K406" s="9" t="n"/>
     </row>
     <row r="407">
+      <c r="G407" t="n">
+        <v>10</v>
+      </c>
       <c r="H407" s="9" t="n"/>
       <c r="I407" s="9" t="n"/>
       <c r="K407" s="9" t="n"/>
     </row>
     <row r="408">
+      <c r="G408" t="n">
+        <v>10</v>
+      </c>
       <c r="H408" s="9" t="n"/>
       <c r="I408" s="9" t="n"/>
       <c r="K408" s="9" t="n"/>
     </row>
     <row r="409">
+      <c r="G409" t="n">
+        <v>10</v>
+      </c>
       <c r="H409" s="9" t="n"/>
       <c r="I409" s="9" t="n"/>
       <c r="K409" s="9" t="n"/>
     </row>
     <row r="410">
+      <c r="G410" t="n">
+        <v>10</v>
+      </c>
       <c r="H410" s="9" t="n"/>
       <c r="I410" s="9" t="n"/>
       <c r="K410" s="9" t="n"/>
     </row>
     <row r="411">
+      <c r="G411" t="n">
+        <v>10</v>
+      </c>
       <c r="H411" s="9" t="n"/>
       <c r="I411" s="9" t="n"/>
       <c r="K411" s="9" t="n"/>
     </row>
     <row r="412">
+      <c r="G412" t="n">
+        <v>10</v>
+      </c>
       <c r="H412" s="9" t="n"/>
       <c r="I412" s="9" t="n"/>
       <c r="K412" s="9" t="n"/>
     </row>
     <row r="413">
+      <c r="G413" t="n">
+        <v>10</v>
+      </c>
       <c r="H413" s="9" t="n"/>
       <c r="I413" s="9" t="n"/>
       <c r="K413" s="9" t="n"/>
     </row>
     <row r="414">
+      <c r="G414" t="n">
+        <v>10</v>
+      </c>
       <c r="H414" s="9" t="n"/>
       <c r="I414" s="9" t="n"/>
       <c r="K414" s="9" t="n"/>
     </row>
     <row r="415">
+      <c r="G415" t="n">
+        <v>10</v>
+      </c>
       <c r="H415" s="9" t="n"/>
       <c r="I415" s="9" t="n"/>
       <c r="K415" s="9" t="n"/>
     </row>
     <row r="416">
+      <c r="G416" t="n">
+        <v>10</v>
+      </c>
       <c r="H416" s="9" t="n"/>
       <c r="I416" s="9" t="n"/>
       <c r="K416" s="9" t="n"/>
     </row>
     <row r="417">
+      <c r="G417" t="n">
+        <v>10</v>
+      </c>
       <c r="H417" s="9" t="n"/>
       <c r="I417" s="9" t="n"/>
       <c r="K417" s="9" t="n"/>
     </row>
     <row r="418">
+      <c r="G418" t="n">
+        <v>10</v>
+      </c>
       <c r="H418" s="9" t="n"/>
       <c r="I418" s="9" t="n"/>
       <c r="K418" s="9" t="n"/>
     </row>
     <row r="419">
+      <c r="G419" t="n">
+        <v>10</v>
+      </c>
       <c r="H419" s="9" t="n"/>
       <c r="I419" s="9" t="n"/>
       <c r="K419" s="9" t="n"/>
     </row>
     <row r="420">
+      <c r="G420" t="n">
+        <v>10</v>
+      </c>
       <c r="H420" s="9" t="n"/>
       <c r="I420" s="9" t="n"/>
       <c r="K420" s="9" t="n"/>
     </row>
     <row r="421">
+      <c r="G421" t="n">
+        <v>10</v>
+      </c>
       <c r="H421" s="9" t="n"/>
       <c r="I421" s="9" t="n"/>
       <c r="K421" s="9" t="n"/>
     </row>
     <row r="422">
+      <c r="G422" t="n">
+        <v>10</v>
+      </c>
       <c r="H422" s="9" t="n"/>
       <c r="I422" s="9" t="n"/>
       <c r="K422" s="9" t="n"/>
     </row>
     <row r="423">
+      <c r="G423" t="n">
+        <v>10</v>
+      </c>
       <c r="H423" s="9" t="n"/>
       <c r="I423" s="9" t="n"/>
       <c r="K423" s="9" t="n"/>
     </row>
     <row r="424">
+      <c r="G424" t="n">
+        <v>10</v>
+      </c>
       <c r="H424" s="9" t="n"/>
       <c r="I424" s="9" t="n"/>
       <c r="K424" s="9" t="n"/>
     </row>
     <row r="425">
+      <c r="G425" t="n">
+        <v>10</v>
+      </c>
       <c r="H425" s="9" t="n"/>
       <c r="I425" s="9" t="n"/>
       <c r="K425" s="9" t="n"/>
     </row>
     <row r="426">
+      <c r="G426" t="n">
+        <v>10</v>
+      </c>
       <c r="H426" s="9" t="n"/>
       <c r="I426" s="9" t="n"/>
       <c r="K426" s="9" t="n"/>
     </row>
     <row r="427">
+      <c r="G427" t="n">
+        <v>10</v>
+      </c>
       <c r="H427" s="9" t="n"/>
       <c r="I427" s="9" t="n"/>
       <c r="K427" s="9" t="n"/>
     </row>
     <row r="428">
+      <c r="G428" t="n">
+        <v>10</v>
+      </c>
       <c r="H428" s="9" t="n"/>
       <c r="I428" s="9" t="n"/>
       <c r="K428" s="9" t="n"/>
     </row>
     <row r="429">
+      <c r="G429" t="n">
+        <v>10</v>
+      </c>
       <c r="H429" s="9" t="n"/>
       <c r="I429" s="9" t="n"/>
       <c r="K429" s="9" t="n"/>
     </row>
     <row r="430">
+      <c r="G430" t="n">
+        <v>10</v>
+      </c>
       <c r="H430" s="9" t="n"/>
       <c r="I430" s="9" t="n"/>
       <c r="K430" s="9" t="n"/>
     </row>
     <row r="431">
+      <c r="G431" t="n">
+        <v>10</v>
+      </c>
       <c r="H431" s="9" t="n"/>
       <c r="I431" s="9" t="n"/>
       <c r="K431" s="9" t="n"/>
     </row>
     <row r="432">
+      <c r="G432" t="n">
+        <v>10</v>
+      </c>
       <c r="H432" s="9" t="n"/>
       <c r="I432" s="9" t="n"/>
       <c r="K432" s="9" t="n"/>
     </row>
     <row r="433">
+      <c r="G433" t="n">
+        <v>10</v>
+      </c>
       <c r="H433" s="9" t="n"/>
       <c r="I433" s="9" t="n"/>
       <c r="K433" s="9" t="n"/>
     </row>
     <row r="434">
+      <c r="G434" t="n">
+        <v>10</v>
+      </c>
       <c r="H434" s="9" t="n"/>
       <c r="I434" s="9" t="n"/>
       <c r="K434" s="9" t="n"/>
     </row>
     <row r="435">
+      <c r="G435" t="n">
+        <v>10</v>
+      </c>
       <c r="H435" s="9" t="n"/>
       <c r="I435" s="9" t="n"/>
       <c r="K435" s="9" t="n"/>
     </row>
     <row r="436">
+      <c r="G436" t="n">
+        <v>10</v>
+      </c>
       <c r="H436" s="9" t="n"/>
       <c r="I436" s="9" t="n"/>
       <c r="K436" s="9" t="n"/>
     </row>
     <row r="437">
+      <c r="G437" t="n">
+        <v>10</v>
+      </c>
       <c r="H437" s="9" t="n"/>
       <c r="I437" s="9" t="n"/>
       <c r="K437" s="9" t="n"/>
     </row>
     <row r="438">
+      <c r="G438" t="n">
+        <v>10</v>
+      </c>
       <c r="H438" s="9" t="n"/>
       <c r="I438" s="9" t="n"/>
       <c r="K438" s="9" t="n"/>
     </row>
     <row r="439">
+      <c r="G439" t="n">
+        <v>10</v>
+      </c>
       <c r="H439" s="9" t="n"/>
       <c r="I439" s="9" t="n"/>
       <c r="K439" s="9" t="n"/>
     </row>
     <row r="440">
+      <c r="G440" t="n">
+        <v>10</v>
+      </c>
       <c r="H440" s="9" t="n"/>
       <c r="I440" s="9" t="n"/>
       <c r="K440" s="9" t="n"/>
     </row>
     <row r="441">
+      <c r="G441" t="n">
+        <v>10</v>
+      </c>
       <c r="H441" s="9" t="n"/>
       <c r="I441" s="9" t="n"/>
       <c r="K441" s="9" t="n"/>
     </row>
     <row r="442">
+      <c r="G442" t="n">
+        <v>10</v>
+      </c>
       <c r="H442" s="9" t="n"/>
       <c r="I442" s="9" t="n"/>
       <c r="K442" s="9" t="n"/>
     </row>
     <row r="443">
+      <c r="G443" t="n">
+        <v>10</v>
+      </c>
       <c r="H443" s="9" t="n"/>
       <c r="I443" s="9" t="n"/>
       <c r="K443" s="9" t="n"/>
     </row>
     <row r="444">
+      <c r="G444" t="n">
+        <v>10</v>
+      </c>
       <c r="H444" s="9" t="n"/>
       <c r="I444" s="9" t="n"/>
       <c r="K444" s="9" t="n"/>
     </row>
     <row r="445">
+      <c r="G445" t="n">
+        <v>10</v>
+      </c>
       <c r="H445" s="9" t="n"/>
       <c r="I445" s="9" t="n"/>
       <c r="K445" s="9" t="n"/>
     </row>
     <row r="446">
+      <c r="G446" t="n">
+        <v>10</v>
+      </c>
       <c r="H446" s="9" t="n"/>
       <c r="I446" s="9" t="n"/>
       <c r="K446" s="9" t="n"/>
     </row>
     <row r="447">
+      <c r="G447" t="n">
+        <v>10</v>
+      </c>
       <c r="H447" s="9" t="n"/>
       <c r="I447" s="9" t="n"/>
       <c r="K447" s="9" t="n"/>
     </row>
     <row r="448">
+      <c r="G448" t="n">
+        <v>10</v>
+      </c>
       <c r="H448" s="9" t="n"/>
       <c r="I448" s="9" t="n"/>
       <c r="K448" s="9" t="n"/>
     </row>
     <row r="449">
+      <c r="G449" t="n">
+        <v>10</v>
+      </c>
       <c r="H449" s="9" t="n"/>
       <c r="I449" s="9" t="n"/>
       <c r="K449" s="9" t="n"/>
     </row>
     <row r="450">
+      <c r="G450" t="n">
+        <v>10</v>
+      </c>
       <c r="H450" s="9" t="n"/>
       <c r="I450" s="9" t="n"/>
       <c r="K450" s="9" t="n"/>
     </row>
     <row r="451">
+      <c r="G451" t="n">
+        <v>10</v>
+      </c>
       <c r="H451" s="9" t="n"/>
       <c r="I451" s="9" t="n"/>
       <c r="K451" s="9" t="n"/>
     </row>
     <row r="452">
+      <c r="G452" t="n">
+        <v>10</v>
+      </c>
       <c r="H452" s="9" t="n"/>
       <c r="I452" s="9" t="n"/>
       <c r="K452" s="9" t="n"/>
     </row>
     <row r="453">
+      <c r="G453" t="n">
+        <v>10</v>
+      </c>
       <c r="H453" s="9" t="n"/>
       <c r="I453" s="9" t="n"/>
       <c r="K453" s="9" t="n"/>
     </row>
     <row r="454">
+      <c r="G454" t="n">
+        <v>10</v>
+      </c>
       <c r="H454" s="9" t="n"/>
       <c r="I454" s="9" t="n"/>
       <c r="K454" s="9" t="n"/>
     </row>
     <row r="455">
+      <c r="G455" t="n">
+        <v>10</v>
+      </c>
       <c r="H455" s="9" t="n"/>
       <c r="I455" s="9" t="n"/>
       <c r="K455" s="9" t="n"/>
     </row>
     <row r="456">
+      <c r="G456" t="n">
+        <v>10</v>
+      </c>
       <c r="H456" s="9" t="n"/>
       <c r="I456" s="9" t="n"/>
       <c r="K456" s="9" t="n"/>
     </row>
     <row r="457">
+      <c r="G457" t="n">
+        <v>10</v>
+      </c>
       <c r="H457" s="9" t="n"/>
       <c r="I457" s="9" t="n"/>
       <c r="K457" s="9" t="n"/>
     </row>
     <row r="458">
+      <c r="G458" t="n">
+        <v>10</v>
+      </c>
       <c r="H458" s="9" t="n"/>
       <c r="I458" s="9" t="n"/>
       <c r="K458" s="9" t="n"/>
     </row>
     <row r="459">
+      <c r="G459" t="n">
+        <v>10</v>
+      </c>
       <c r="H459" s="9" t="n"/>
       <c r="I459" s="9" t="n"/>
       <c r="K459" s="9" t="n"/>
     </row>
     <row r="460">
+      <c r="G460" t="n">
+        <v>10</v>
+      </c>
       <c r="H460" s="9" t="n"/>
       <c r="I460" s="9" t="n"/>
       <c r="K460" s="9" t="n"/>
     </row>
     <row r="461">
+      <c r="G461" t="n">
+        <v>10</v>
+      </c>
       <c r="H461" s="9" t="n"/>
       <c r="I461" s="9" t="n"/>
       <c r="K461" s="9" t="n"/>
     </row>
     <row r="462">
+      <c r="G462" t="n">
+        <v>10</v>
+      </c>
       <c r="H462" s="9" t="n"/>
       <c r="I462" s="9" t="n"/>
       <c r="K462" s="9" t="n"/>
     </row>
     <row r="463">
+      <c r="G463" t="n">
+        <v>10</v>
+      </c>
       <c r="H463" s="9" t="n"/>
       <c r="I463" s="9" t="n"/>
       <c r="K463" s="9" t="n"/>
     </row>
     <row r="464">
+      <c r="G464" t="n">
+        <v>10</v>
+      </c>
       <c r="H464" s="9" t="n"/>
       <c r="I464" s="9" t="n"/>
       <c r="K464" s="9" t="n"/>
     </row>
     <row r="465">
+      <c r="G465" t="n">
+        <v>10</v>
+      </c>
       <c r="H465" s="9" t="n"/>
       <c r="I465" s="9" t="n"/>
       <c r="K465" s="9" t="n"/>
     </row>
     <row r="466">
+      <c r="G466" t="n">
+        <v>10</v>
+      </c>
       <c r="H466" s="9" t="n"/>
       <c r="I466" s="9" t="n"/>
       <c r="K466" s="9" t="n"/>
     </row>
     <row r="467">
+      <c r="G467" t="n">
+        <v>10</v>
+      </c>
       <c r="H467" s="9" t="n"/>
       <c r="I467" s="9" t="n"/>
       <c r="K467" s="9" t="n"/>
     </row>
     <row r="468">
+      <c r="G468" t="n">
+        <v>10</v>
+      </c>
       <c r="H468" s="9" t="n"/>
       <c r="I468" s="9" t="n"/>
       <c r="K468" s="9" t="n"/>
     </row>
     <row r="469">
+      <c r="G469" t="n">
+        <v>10</v>
+      </c>
       <c r="H469" s="9" t="n"/>
       <c r="I469" s="9" t="n"/>
       <c r="K469" s="9" t="n"/>
     </row>
     <row r="470">
+      <c r="G470" t="n">
+        <v>10</v>
+      </c>
       <c r="H470" s="9" t="n"/>
       <c r="I470" s="9" t="n"/>
       <c r="K470" s="9" t="n"/>
     </row>
     <row r="471">
+      <c r="G471" t="n">
+        <v>10</v>
+      </c>
       <c r="H471" s="9" t="n"/>
       <c r="I471" s="9" t="n"/>
       <c r="K471" s="9" t="n"/>
     </row>
     <row r="472">
+      <c r="G472" t="n">
+        <v>10</v>
+      </c>
       <c r="H472" s="9" t="n"/>
       <c r="I472" s="9" t="n"/>
       <c r="K472" s="9" t="n"/>
     </row>
     <row r="473">
+      <c r="G473" t="n">
+        <v>10</v>
+      </c>
       <c r="H473" s="9" t="n"/>
       <c r="I473" s="9" t="n"/>
       <c r="K473" s="9" t="n"/>
     </row>
     <row r="474">
+      <c r="G474" t="n">
+        <v>10</v>
+      </c>
       <c r="H474" s="9" t="n"/>
       <c r="I474" s="9" t="n"/>
       <c r="K474" s="9" t="n"/>
     </row>
     <row r="475">
+      <c r="G475" t="n">
+        <v>10</v>
+      </c>
       <c r="H475" s="9" t="n"/>
       <c r="I475" s="9" t="n"/>
       <c r="K475" s="9" t="n"/>
     </row>
     <row r="476">
+      <c r="G476" t="n">
+        <v>10</v>
+      </c>
       <c r="H476" s="9" t="n"/>
       <c r="I476" s="9" t="n"/>
       <c r="K476" s="9" t="n"/>
     </row>
     <row r="477">
+      <c r="G477" t="n">
+        <v>10</v>
+      </c>
       <c r="H477" s="9" t="n"/>
       <c r="I477" s="9" t="n"/>
       <c r="K477" s="9" t="n"/>
     </row>
     <row r="478">
+      <c r="G478" t="n">
+        <v>10</v>
+      </c>
       <c r="H478" s="9" t="n"/>
       <c r="I478" s="9" t="n"/>
       <c r="K478" s="9" t="n"/>
     </row>
     <row r="479">
+      <c r="G479" t="n">
+        <v>10</v>
+      </c>
       <c r="H479" s="9" t="n"/>
       <c r="I479" s="9" t="n"/>
       <c r="K479" s="9" t="n"/>
     </row>
     <row r="480">
+      <c r="G480" t="n">
+        <v>10</v>
+      </c>
       <c r="H480" s="9" t="n"/>
       <c r="I480" s="9" t="n"/>
       <c r="K480" s="9" t="n"/>
     </row>
     <row r="481">
+      <c r="G481" t="n">
+        <v>10</v>
+      </c>
       <c r="H481" s="9" t="n"/>
       <c r="I481" s="9" t="n"/>
       <c r="K481" s="9" t="n"/>
     </row>
     <row r="482">
+      <c r="G482" t="n">
+        <v>10</v>
+      </c>
       <c r="H482" s="9" t="n"/>
       <c r="I482" s="9" t="n"/>
       <c r="K482" s="9" t="n"/>
     </row>
     <row r="483">
+      <c r="G483" t="n">
+        <v>10</v>
+      </c>
       <c r="H483" s="9" t="n"/>
       <c r="I483" s="9" t="n"/>
       <c r="K483" s="9" t="n"/>
     </row>
     <row r="484">
+      <c r="G484" t="n">
+        <v>10</v>
+      </c>
       <c r="H484" s="9" t="n"/>
       <c r="I484" s="9" t="n"/>
       <c r="K484" s="9" t="n"/>
     </row>
     <row r="485">
+      <c r="G485" t="n">
+        <v>10</v>
+      </c>
       <c r="H485" s="9" t="n"/>
       <c r="I485" s="9" t="n"/>
       <c r="K485" s="9" t="n"/>
     </row>
     <row r="486">
+      <c r="G486" t="n">
+        <v>10</v>
+      </c>
       <c r="H486" s="9" t="n"/>
       <c r="I486" s="9" t="n"/>
       <c r="K486" s="9" t="n"/>
     </row>
     <row r="487">
+      <c r="G487" t="n">
+        <v>10</v>
+      </c>
       <c r="H487" s="9" t="n"/>
       <c r="I487" s="9" t="n"/>
       <c r="K487" s="9" t="n"/>
     </row>
     <row r="488">
+      <c r="G488" t="n">
+        <v>10</v>
+      </c>
       <c r="H488" s="9" t="n"/>
       <c r="I488" s="9" t="n"/>
       <c r="K488" s="9" t="n"/>
     </row>
     <row r="489">
+      <c r="G489" t="n">
+        <v>10</v>
+      </c>
       <c r="H489" s="9" t="n"/>
       <c r="I489" s="9" t="n"/>
       <c r="K489" s="9" t="n"/>
     </row>
     <row r="490">
+      <c r="G490" t="n">
+        <v>10</v>
+      </c>
       <c r="H490" s="9" t="n"/>
       <c r="I490" s="9" t="n"/>
       <c r="K490" s="9" t="n"/>
     </row>
     <row r="491">
+      <c r="G491" t="n">
+        <v>10</v>
+      </c>
       <c r="H491" s="9" t="n"/>
       <c r="I491" s="9" t="n"/>
       <c r="K491" s="9" t="n"/>
     </row>
     <row r="492">
+      <c r="G492" t="n">
+        <v>10</v>
+      </c>
       <c r="H492" s="9" t="n"/>
       <c r="I492" s="9" t="n"/>
       <c r="K492" s="9" t="n"/>
     </row>
     <row r="493">
+      <c r="G493" t="n">
+        <v>10</v>
+      </c>
       <c r="H493" s="9" t="n"/>
       <c r="I493" s="9" t="n"/>
       <c r="K493" s="9" t="n"/>
     </row>
     <row r="494">
+      <c r="G494" t="n">
+        <v>10</v>
+      </c>
       <c r="H494" s="9" t="n"/>
       <c r="I494" s="9" t="n"/>
       <c r="K494" s="9" t="n"/>
     </row>
     <row r="495">
+      <c r="G495" t="n">
+        <v>10</v>
+      </c>
       <c r="H495" s="9" t="n"/>
       <c r="I495" s="9" t="n"/>
       <c r="K495" s="9" t="n"/>
     </row>
     <row r="496">
+      <c r="G496" t="n">
+        <v>10</v>
+      </c>
       <c r="H496" s="9" t="n"/>
       <c r="I496" s="9" t="n"/>
       <c r="K496" s="9" t="n"/>
     </row>
     <row r="497">
+      <c r="G497" t="n">
+        <v>10</v>
+      </c>
       <c r="H497" s="9" t="n"/>
       <c r="I497" s="9" t="n"/>
       <c r="K497" s="9" t="n"/>
     </row>
     <row r="498">
+      <c r="G498" t="n">
+        <v>10</v>
+      </c>
       <c r="H498" s="9" t="n"/>
       <c r="I498" s="9" t="n"/>
       <c r="K498" s="9" t="n"/>
     </row>
     <row r="499">
+      <c r="G499" t="n">
+        <v>10</v>
+      </c>
       <c r="H499" s="9" t="n"/>
       <c r="I499" s="9" t="n"/>
       <c r="K499" s="9" t="n"/>
     </row>
     <row r="500">
+      <c r="G500" t="n">
+        <v>10</v>
+      </c>
       <c r="H500" s="9" t="n"/>
       <c r="I500" s="9" t="n"/>
       <c r="K500" s="9" t="n"/>
@@ -3961,7 +5438,9 @@
       <c r="K2" s="7" t="n"/>
       <c r="L2" s="7" t="n"/>
       <c r="M2" s="7" t="n"/>
-      <c r="N2" s="6" t="n"/>
+      <c r="N2" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="O2" s="8" t="n"/>
       <c r="P2" s="6" t="n"/>
     </row>
@@ -4027,7 +5506,9 @@
           <t>brought는 '가져왔다'예요.</t>
         </is>
       </c>
-      <c r="N3" s="6" t="n"/>
+      <c r="N3" s="6" t="n">
+        <v>10</v>
+      </c>
       <c r="O3" s="8" t="n"/>
       <c r="P3" s="6" t="n"/>
     </row>

--- a/templates/classeum-vocab-week1.xlsx
+++ b/templates/classeum-vocab-week1.xlsx
@@ -593,7 +593,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>세트 (선택): 비워 두면 올린 날짜로 이벤트가 생겨요. (예: 10-29 퀴즈)</t>
+          <t>세트 (선택): 비워 두면 파일 이름으로 이벤트가 생겨요. (예: 3주차 단어장.xlsx → 3주차 단어장) 한 파일을 여러 퀴즈로 나눌 때만 쓰세요.</t>
         </is>
       </c>
     </row>

--- a/templates/classeum-vocab-week1.xlsx
+++ b/templates/classeum-vocab-week1.xlsx
@@ -586,7 +586,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>시간(초) (선택): 칸마다 10초가 미리 들어 있어요. 단어마다 바꿀 수 있고, 지우면 15초입니다.</t>
+          <t>시간(초) (선택): 비워 두면 10초예요. 오래 걸리는 단어만 숫자를 쓰세요.</t>
         </is>
       </c>
     </row>
@@ -780,9 +780,7 @@
           <t>나는 방과 후에 도서관에서 공부한다.</t>
         </is>
       </c>
-      <c r="G2" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G2" s="6" t="n"/>
       <c r="H2" s="8" t="n"/>
       <c r="I2" s="8" t="n"/>
       <c r="J2" s="6" t="n"/>
@@ -819,9 +817,7 @@
           <t>네 펜 좀 빌려도 될까?</t>
         </is>
       </c>
-      <c r="G3" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G3" s="6" t="n"/>
       <c r="H3" s="8" t="n"/>
       <c r="I3" s="8" t="n"/>
       <c r="J3" s="6" t="n"/>
@@ -858,9 +854,7 @@
           <t>지우개 좀 빌려줄래?</t>
         </is>
       </c>
-      <c r="G4" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G4" s="6" t="n"/>
       <c r="H4" s="8" t="n"/>
       <c r="I4" s="8" t="n"/>
       <c r="J4" s="6" t="n"/>
@@ -893,9 +887,7 @@
           <t>내가 가장 좋아하는 과목은 수학이다.</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G5" s="6" t="n"/>
       <c r="H5" s="8" t="n"/>
       <c r="I5" s="8" t="n"/>
       <c r="J5" s="6" t="n"/>
@@ -932,9 +924,7 @@
           <t>도서관에서는 조용히 해 주세요.</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G6" s="6" t="n"/>
       <c r="H6" s="8" t="n"/>
       <c r="I6" s="8" t="n"/>
       <c r="J6" s="6" t="n"/>
@@ -971,9 +961,7 @@
           <t>나는 월요일에 일찍 일어난다.</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G7" s="6" t="n"/>
       <c r="H7" s="8" t="n"/>
       <c r="I7" s="8" t="n"/>
       <c r="J7" s="6" t="n"/>
@@ -1010,9 +998,7 @@
           <t>수업에 늦지 마.</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G8" s="6" t="n"/>
       <c r="H8" s="8" t="n"/>
       <c r="I8" s="8" t="n"/>
       <c r="J8" s="6" t="n"/>
@@ -1045,9 +1031,7 @@
           <t>나는 숙제를 끝냈다.</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G9" s="6" t="n"/>
       <c r="H9" s="8" t="n"/>
       <c r="I9" s="8" t="n"/>
       <c r="J9" s="6" t="n"/>
@@ -1072,9 +1056,7 @@
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="7" t="n"/>
       <c r="F10" s="7" t="n"/>
-      <c r="G10" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G10" s="6" t="n"/>
       <c r="H10" s="8" t="n"/>
       <c r="I10" s="8" t="n"/>
       <c r="J10" s="6" t="n"/>
@@ -1099,9 +1081,7 @@
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="7" t="n"/>
       <c r="F11" s="7" t="n"/>
-      <c r="G11" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G11" s="6" t="n"/>
       <c r="H11" s="8" t="n"/>
       <c r="I11" s="8" t="n"/>
       <c r="J11" s="6" t="n"/>
@@ -1134,9 +1114,7 @@
           <t>오늘 수학 시험이 있다.</t>
         </is>
       </c>
-      <c r="G12" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G12" s="6" t="n"/>
       <c r="H12" s="8" t="n"/>
       <c r="I12" s="8" t="n"/>
       <c r="J12" s="6" t="n"/>
@@ -1173,9 +1151,7 @@
           <t>질문 하나 해도 될까요?</t>
         </is>
       </c>
-      <c r="G13" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G13" s="6" t="n"/>
       <c r="H13" s="8" t="n"/>
       <c r="I13" s="8" t="n"/>
       <c r="J13" s="6" t="n"/>
@@ -1212,9 +1188,7 @@
           <t>나는 답을 안다.</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G14" s="6" t="n"/>
       <c r="H14" s="8" t="n"/>
       <c r="I14" s="8" t="n"/>
       <c r="J14" s="6" t="n"/>
@@ -1243,9 +1217,7 @@
       </c>
       <c r="E15" s="7" t="n"/>
       <c r="F15" s="7" t="n"/>
-      <c r="G15" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G15" s="6" t="n"/>
       <c r="H15" s="8" t="n"/>
       <c r="I15" s="8" t="n"/>
       <c r="J15" s="6" t="n"/>
@@ -1274,9 +1246,7 @@
       </c>
       <c r="E16" s="7" t="n"/>
       <c r="F16" s="7" t="n"/>
-      <c r="G16" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G16" s="6" t="n"/>
       <c r="H16" s="8" t="n"/>
       <c r="I16" s="8" t="n"/>
       <c r="J16" s="6" t="n"/>
@@ -1305,9 +1275,7 @@
       </c>
       <c r="E17" s="7" t="n"/>
       <c r="F17" s="7" t="n"/>
-      <c r="G17" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G17" s="6" t="n"/>
       <c r="H17" s="8" t="n"/>
       <c r="I17" s="8" t="n"/>
       <c r="J17" s="6" t="n"/>
@@ -1336,9 +1304,7 @@
       </c>
       <c r="E18" s="7" t="n"/>
       <c r="F18" s="7" t="n"/>
-      <c r="G18" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G18" s="6" t="n"/>
       <c r="H18" s="8" t="n"/>
       <c r="I18" s="8" t="n"/>
       <c r="J18" s="6" t="n"/>
@@ -1371,9 +1337,7 @@
           <t>나는 매일 영어를 연습한다.</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G19" s="6" t="n"/>
       <c r="H19" s="8" t="n"/>
       <c r="I19" s="8" t="n"/>
       <c r="J19" s="6" t="n"/>
@@ -1402,9 +1366,7 @@
       </c>
       <c r="E20" s="7" t="n"/>
       <c r="F20" s="7" t="n"/>
-      <c r="G20" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G20" s="6" t="n"/>
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="8" t="n"/>
       <c r="J20" s="6" t="n"/>
@@ -1437,3842 +1399,2403 @@
           <t>쉬는 시간에 축구하자.</t>
         </is>
       </c>
-      <c r="G21" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="G21" s="6" t="n"/>
       <c r="H21" s="8" t="n"/>
       <c r="I21" s="8" t="n"/>
       <c r="J21" s="6" t="n"/>
       <c r="K21" s="8" t="n"/>
     </row>
     <row r="22">
-      <c r="G22" t="n">
-        <v>10</v>
-      </c>
       <c r="H22" s="9" t="n"/>
       <c r="I22" s="9" t="n"/>
       <c r="K22" s="9" t="n"/>
     </row>
     <row r="23">
-      <c r="G23" t="n">
-        <v>10</v>
-      </c>
       <c r="H23" s="9" t="n"/>
       <c r="I23" s="9" t="n"/>
       <c r="K23" s="9" t="n"/>
     </row>
     <row r="24">
-      <c r="G24" t="n">
-        <v>10</v>
-      </c>
       <c r="H24" s="9" t="n"/>
       <c r="I24" s="9" t="n"/>
       <c r="K24" s="9" t="n"/>
     </row>
     <row r="25">
-      <c r="G25" t="n">
-        <v>10</v>
-      </c>
       <c r="H25" s="9" t="n"/>
       <c r="I25" s="9" t="n"/>
       <c r="K25" s="9" t="n"/>
     </row>
     <row r="26">
-      <c r="G26" t="n">
-        <v>10</v>
-      </c>
       <c r="H26" s="9" t="n"/>
       <c r="I26" s="9" t="n"/>
       <c r="K26" s="9" t="n"/>
     </row>
     <row r="27">
-      <c r="G27" t="n">
-        <v>10</v>
-      </c>
       <c r="H27" s="9" t="n"/>
       <c r="I27" s="9" t="n"/>
       <c r="K27" s="9" t="n"/>
     </row>
     <row r="28">
-      <c r="G28" t="n">
-        <v>10</v>
-      </c>
       <c r="H28" s="9" t="n"/>
       <c r="I28" s="9" t="n"/>
       <c r="K28" s="9" t="n"/>
     </row>
     <row r="29">
-      <c r="G29" t="n">
-        <v>10</v>
-      </c>
       <c r="H29" s="9" t="n"/>
       <c r="I29" s="9" t="n"/>
       <c r="K29" s="9" t="n"/>
     </row>
     <row r="30">
-      <c r="G30" t="n">
-        <v>10</v>
-      </c>
       <c r="H30" s="9" t="n"/>
       <c r="I30" s="9" t="n"/>
       <c r="K30" s="9" t="n"/>
     </row>
     <row r="31">
-      <c r="G31" t="n">
-        <v>10</v>
-      </c>
       <c r="H31" s="9" t="n"/>
       <c r="I31" s="9" t="n"/>
       <c r="K31" s="9" t="n"/>
     </row>
     <row r="32">
-      <c r="G32" t="n">
-        <v>10</v>
-      </c>
       <c r="H32" s="9" t="n"/>
       <c r="I32" s="9" t="n"/>
       <c r="K32" s="9" t="n"/>
     </row>
     <row r="33">
-      <c r="G33" t="n">
-        <v>10</v>
-      </c>
       <c r="H33" s="9" t="n"/>
       <c r="I33" s="9" t="n"/>
       <c r="K33" s="9" t="n"/>
     </row>
     <row r="34">
-      <c r="G34" t="n">
-        <v>10</v>
-      </c>
       <c r="H34" s="9" t="n"/>
       <c r="I34" s="9" t="n"/>
       <c r="K34" s="9" t="n"/>
     </row>
     <row r="35">
-      <c r="G35" t="n">
-        <v>10</v>
-      </c>
       <c r="H35" s="9" t="n"/>
       <c r="I35" s="9" t="n"/>
       <c r="K35" s="9" t="n"/>
     </row>
     <row r="36">
-      <c r="G36" t="n">
-        <v>10</v>
-      </c>
       <c r="H36" s="9" t="n"/>
       <c r="I36" s="9" t="n"/>
       <c r="K36" s="9" t="n"/>
     </row>
     <row r="37">
-      <c r="G37" t="n">
-        <v>10</v>
-      </c>
       <c r="H37" s="9" t="n"/>
       <c r="I37" s="9" t="n"/>
       <c r="K37" s="9" t="n"/>
     </row>
     <row r="38">
-      <c r="G38" t="n">
-        <v>10</v>
-      </c>
       <c r="H38" s="9" t="n"/>
       <c r="I38" s="9" t="n"/>
       <c r="K38" s="9" t="n"/>
     </row>
     <row r="39">
-      <c r="G39" t="n">
-        <v>10</v>
-      </c>
       <c r="H39" s="9" t="n"/>
       <c r="I39" s="9" t="n"/>
       <c r="K39" s="9" t="n"/>
     </row>
     <row r="40">
-      <c r="G40" t="n">
-        <v>10</v>
-      </c>
       <c r="H40" s="9" t="n"/>
       <c r="I40" s="9" t="n"/>
       <c r="K40" s="9" t="n"/>
     </row>
     <row r="41">
-      <c r="G41" t="n">
-        <v>10</v>
-      </c>
       <c r="H41" s="9" t="n"/>
       <c r="I41" s="9" t="n"/>
       <c r="K41" s="9" t="n"/>
     </row>
     <row r="42">
-      <c r="G42" t="n">
-        <v>10</v>
-      </c>
       <c r="H42" s="9" t="n"/>
       <c r="I42" s="9" t="n"/>
       <c r="K42" s="9" t="n"/>
     </row>
     <row r="43">
-      <c r="G43" t="n">
-        <v>10</v>
-      </c>
       <c r="H43" s="9" t="n"/>
       <c r="I43" s="9" t="n"/>
       <c r="K43" s="9" t="n"/>
     </row>
     <row r="44">
-      <c r="G44" t="n">
-        <v>10</v>
-      </c>
       <c r="H44" s="9" t="n"/>
       <c r="I44" s="9" t="n"/>
       <c r="K44" s="9" t="n"/>
     </row>
     <row r="45">
-      <c r="G45" t="n">
-        <v>10</v>
-      </c>
       <c r="H45" s="9" t="n"/>
       <c r="I45" s="9" t="n"/>
       <c r="K45" s="9" t="n"/>
     </row>
     <row r="46">
-      <c r="G46" t="n">
-        <v>10</v>
-      </c>
       <c r="H46" s="9" t="n"/>
       <c r="I46" s="9" t="n"/>
       <c r="K46" s="9" t="n"/>
     </row>
     <row r="47">
-      <c r="G47" t="n">
-        <v>10</v>
-      </c>
       <c r="H47" s="9" t="n"/>
       <c r="I47" s="9" t="n"/>
       <c r="K47" s="9" t="n"/>
     </row>
     <row r="48">
-      <c r="G48" t="n">
-        <v>10</v>
-      </c>
       <c r="H48" s="9" t="n"/>
       <c r="I48" s="9" t="n"/>
       <c r="K48" s="9" t="n"/>
     </row>
     <row r="49">
-      <c r="G49" t="n">
-        <v>10</v>
-      </c>
       <c r="H49" s="9" t="n"/>
       <c r="I49" s="9" t="n"/>
       <c r="K49" s="9" t="n"/>
     </row>
     <row r="50">
-      <c r="G50" t="n">
-        <v>10</v>
-      </c>
       <c r="H50" s="9" t="n"/>
       <c r="I50" s="9" t="n"/>
       <c r="K50" s="9" t="n"/>
     </row>
     <row r="51">
-      <c r="G51" t="n">
-        <v>10</v>
-      </c>
       <c r="H51" s="9" t="n"/>
       <c r="I51" s="9" t="n"/>
       <c r="K51" s="9" t="n"/>
     </row>
     <row r="52">
-      <c r="G52" t="n">
-        <v>10</v>
-      </c>
       <c r="H52" s="9" t="n"/>
       <c r="I52" s="9" t="n"/>
       <c r="K52" s="9" t="n"/>
     </row>
     <row r="53">
-      <c r="G53" t="n">
-        <v>10</v>
-      </c>
       <c r="H53" s="9" t="n"/>
       <c r="I53" s="9" t="n"/>
       <c r="K53" s="9" t="n"/>
     </row>
     <row r="54">
-      <c r="G54" t="n">
-        <v>10</v>
-      </c>
       <c r="H54" s="9" t="n"/>
       <c r="I54" s="9" t="n"/>
       <c r="K54" s="9" t="n"/>
     </row>
     <row r="55">
-      <c r="G55" t="n">
-        <v>10</v>
-      </c>
       <c r="H55" s="9" t="n"/>
       <c r="I55" s="9" t="n"/>
       <c r="K55" s="9" t="n"/>
     </row>
     <row r="56">
-      <c r="G56" t="n">
-        <v>10</v>
-      </c>
       <c r="H56" s="9" t="n"/>
       <c r="I56" s="9" t="n"/>
       <c r="K56" s="9" t="n"/>
     </row>
     <row r="57">
-      <c r="G57" t="n">
-        <v>10</v>
-      </c>
       <c r="H57" s="9" t="n"/>
       <c r="I57" s="9" t="n"/>
       <c r="K57" s="9" t="n"/>
     </row>
     <row r="58">
-      <c r="G58" t="n">
-        <v>10</v>
-      </c>
       <c r="H58" s="9" t="n"/>
       <c r="I58" s="9" t="n"/>
       <c r="K58" s="9" t="n"/>
     </row>
     <row r="59">
-      <c r="G59" t="n">
-        <v>10</v>
-      </c>
       <c r="H59" s="9" t="n"/>
       <c r="I59" s="9" t="n"/>
       <c r="K59" s="9" t="n"/>
     </row>
     <row r="60">
-      <c r="G60" t="n">
-        <v>10</v>
-      </c>
       <c r="H60" s="9" t="n"/>
       <c r="I60" s="9" t="n"/>
       <c r="K60" s="9" t="n"/>
     </row>
     <row r="61">
-      <c r="G61" t="n">
-        <v>10</v>
-      </c>
       <c r="H61" s="9" t="n"/>
       <c r="I61" s="9" t="n"/>
       <c r="K61" s="9" t="n"/>
     </row>
     <row r="62">
-      <c r="G62" t="n">
-        <v>10</v>
-      </c>
       <c r="H62" s="9" t="n"/>
       <c r="I62" s="9" t="n"/>
       <c r="K62" s="9" t="n"/>
     </row>
     <row r="63">
-      <c r="G63" t="n">
-        <v>10</v>
-      </c>
       <c r="H63" s="9" t="n"/>
       <c r="I63" s="9" t="n"/>
       <c r="K63" s="9" t="n"/>
     </row>
     <row r="64">
-      <c r="G64" t="n">
-        <v>10</v>
-      </c>
       <c r="H64" s="9" t="n"/>
       <c r="I64" s="9" t="n"/>
       <c r="K64" s="9" t="n"/>
     </row>
     <row r="65">
-      <c r="G65" t="n">
-        <v>10</v>
-      </c>
       <c r="H65" s="9" t="n"/>
       <c r="I65" s="9" t="n"/>
       <c r="K65" s="9" t="n"/>
     </row>
     <row r="66">
-      <c r="G66" t="n">
-        <v>10</v>
-      </c>
       <c r="H66" s="9" t="n"/>
       <c r="I66" s="9" t="n"/>
       <c r="K66" s="9" t="n"/>
     </row>
     <row r="67">
-      <c r="G67" t="n">
-        <v>10</v>
-      </c>
       <c r="H67" s="9" t="n"/>
       <c r="I67" s="9" t="n"/>
       <c r="K67" s="9" t="n"/>
     </row>
     <row r="68">
-      <c r="G68" t="n">
-        <v>10</v>
-      </c>
       <c r="H68" s="9" t="n"/>
       <c r="I68" s="9" t="n"/>
       <c r="K68" s="9" t="n"/>
     </row>
     <row r="69">
-      <c r="G69" t="n">
-        <v>10</v>
-      </c>
       <c r="H69" s="9" t="n"/>
       <c r="I69" s="9" t="n"/>
       <c r="K69" s="9" t="n"/>
     </row>
     <row r="70">
-      <c r="G70" t="n">
-        <v>10</v>
-      </c>
       <c r="H70" s="9" t="n"/>
       <c r="I70" s="9" t="n"/>
       <c r="K70" s="9" t="n"/>
     </row>
     <row r="71">
-      <c r="G71" t="n">
-        <v>10</v>
-      </c>
       <c r="H71" s="9" t="n"/>
       <c r="I71" s="9" t="n"/>
       <c r="K71" s="9" t="n"/>
     </row>
     <row r="72">
-      <c r="G72" t="n">
-        <v>10</v>
-      </c>
       <c r="H72" s="9" t="n"/>
       <c r="I72" s="9" t="n"/>
       <c r="K72" s="9" t="n"/>
     </row>
     <row r="73">
-      <c r="G73" t="n">
-        <v>10</v>
-      </c>
       <c r="H73" s="9" t="n"/>
       <c r="I73" s="9" t="n"/>
       <c r="K73" s="9" t="n"/>
     </row>
     <row r="74">
-      <c r="G74" t="n">
-        <v>10</v>
-      </c>
       <c r="H74" s="9" t="n"/>
       <c r="I74" s="9" t="n"/>
       <c r="K74" s="9" t="n"/>
     </row>
     <row r="75">
-      <c r="G75" t="n">
-        <v>10</v>
-      </c>
       <c r="H75" s="9" t="n"/>
       <c r="I75" s="9" t="n"/>
       <c r="K75" s="9" t="n"/>
     </row>
     <row r="76">
-      <c r="G76" t="n">
-        <v>10</v>
-      </c>
       <c r="H76" s="9" t="n"/>
       <c r="I76" s="9" t="n"/>
       <c r="K76" s="9" t="n"/>
     </row>
     <row r="77">
-      <c r="G77" t="n">
-        <v>10</v>
-      </c>
       <c r="H77" s="9" t="n"/>
       <c r="I77" s="9" t="n"/>
       <c r="K77" s="9" t="n"/>
     </row>
     <row r="78">
-      <c r="G78" t="n">
-        <v>10</v>
-      </c>
       <c r="H78" s="9" t="n"/>
       <c r="I78" s="9" t="n"/>
       <c r="K78" s="9" t="n"/>
     </row>
     <row r="79">
-      <c r="G79" t="n">
-        <v>10</v>
-      </c>
       <c r="H79" s="9" t="n"/>
       <c r="I79" s="9" t="n"/>
       <c r="K79" s="9" t="n"/>
     </row>
     <row r="80">
-      <c r="G80" t="n">
-        <v>10</v>
-      </c>
       <c r="H80" s="9" t="n"/>
       <c r="I80" s="9" t="n"/>
       <c r="K80" s="9" t="n"/>
     </row>
     <row r="81">
-      <c r="G81" t="n">
-        <v>10</v>
-      </c>
       <c r="H81" s="9" t="n"/>
       <c r="I81" s="9" t="n"/>
       <c r="K81" s="9" t="n"/>
     </row>
     <row r="82">
-      <c r="G82" t="n">
-        <v>10</v>
-      </c>
       <c r="H82" s="9" t="n"/>
       <c r="I82" s="9" t="n"/>
       <c r="K82" s="9" t="n"/>
     </row>
     <row r="83">
-      <c r="G83" t="n">
-        <v>10</v>
-      </c>
       <c r="H83" s="9" t="n"/>
       <c r="I83" s="9" t="n"/>
       <c r="K83" s="9" t="n"/>
     </row>
     <row r="84">
-      <c r="G84" t="n">
-        <v>10</v>
-      </c>
       <c r="H84" s="9" t="n"/>
       <c r="I84" s="9" t="n"/>
       <c r="K84" s="9" t="n"/>
     </row>
     <row r="85">
-      <c r="G85" t="n">
-        <v>10</v>
-      </c>
       <c r="H85" s="9" t="n"/>
       <c r="I85" s="9" t="n"/>
       <c r="K85" s="9" t="n"/>
     </row>
     <row r="86">
-      <c r="G86" t="n">
-        <v>10</v>
-      </c>
       <c r="H86" s="9" t="n"/>
       <c r="I86" s="9" t="n"/>
       <c r="K86" s="9" t="n"/>
     </row>
     <row r="87">
-      <c r="G87" t="n">
-        <v>10</v>
-      </c>
       <c r="H87" s="9" t="n"/>
       <c r="I87" s="9" t="n"/>
       <c r="K87" s="9" t="n"/>
     </row>
     <row r="88">
-      <c r="G88" t="n">
-        <v>10</v>
-      </c>
       <c r="H88" s="9" t="n"/>
       <c r="I88" s="9" t="n"/>
       <c r="K88" s="9" t="n"/>
     </row>
     <row r="89">
-      <c r="G89" t="n">
-        <v>10</v>
-      </c>
       <c r="H89" s="9" t="n"/>
       <c r="I89" s="9" t="n"/>
       <c r="K89" s="9" t="n"/>
     </row>
     <row r="90">
-      <c r="G90" t="n">
-        <v>10</v>
-      </c>
       <c r="H90" s="9" t="n"/>
       <c r="I90" s="9" t="n"/>
       <c r="K90" s="9" t="n"/>
     </row>
     <row r="91">
-      <c r="G91" t="n">
-        <v>10</v>
-      </c>
       <c r="H91" s="9" t="n"/>
       <c r="I91" s="9" t="n"/>
       <c r="K91" s="9" t="n"/>
     </row>
     <row r="92">
-      <c r="G92" t="n">
-        <v>10</v>
-      </c>
       <c r="H92" s="9" t="n"/>
       <c r="I92" s="9" t="n"/>
       <c r="K92" s="9" t="n"/>
     </row>
     <row r="93">
-      <c r="G93" t="n">
-        <v>10</v>
-      </c>
       <c r="H93" s="9" t="n"/>
       <c r="I93" s="9" t="n"/>
       <c r="K93" s="9" t="n"/>
     </row>
     <row r="94">
-      <c r="G94" t="n">
-        <v>10</v>
-      </c>
       <c r="H94" s="9" t="n"/>
       <c r="I94" s="9" t="n"/>
       <c r="K94" s="9" t="n"/>
     </row>
     <row r="95">
-      <c r="G95" t="n">
-        <v>10</v>
-      </c>
       <c r="H95" s="9" t="n"/>
       <c r="I95" s="9" t="n"/>
       <c r="K95" s="9" t="n"/>
     </row>
     <row r="96">
-      <c r="G96" t="n">
-        <v>10</v>
-      </c>
       <c r="H96" s="9" t="n"/>
       <c r="I96" s="9" t="n"/>
       <c r="K96" s="9" t="n"/>
     </row>
     <row r="97">
-      <c r="G97" t="n">
-        <v>10</v>
-      </c>
       <c r="H97" s="9" t="n"/>
       <c r="I97" s="9" t="n"/>
       <c r="K97" s="9" t="n"/>
     </row>
     <row r="98">
-      <c r="G98" t="n">
-        <v>10</v>
-      </c>
       <c r="H98" s="9" t="n"/>
       <c r="I98" s="9" t="n"/>
       <c r="K98" s="9" t="n"/>
     </row>
     <row r="99">
-      <c r="G99" t="n">
-        <v>10</v>
-      </c>
       <c r="H99" s="9" t="n"/>
       <c r="I99" s="9" t="n"/>
       <c r="K99" s="9" t="n"/>
     </row>
     <row r="100">
-      <c r="G100" t="n">
-        <v>10</v>
-      </c>
       <c r="H100" s="9" t="n"/>
       <c r="I100" s="9" t="n"/>
       <c r="K100" s="9" t="n"/>
     </row>
     <row r="101">
-      <c r="G101" t="n">
-        <v>10</v>
-      </c>
       <c r="H101" s="9" t="n"/>
       <c r="I101" s="9" t="n"/>
       <c r="K101" s="9" t="n"/>
     </row>
     <row r="102">
-      <c r="G102" t="n">
-        <v>10</v>
-      </c>
       <c r="H102" s="9" t="n"/>
       <c r="I102" s="9" t="n"/>
       <c r="K102" s="9" t="n"/>
     </row>
     <row r="103">
-      <c r="G103" t="n">
-        <v>10</v>
-      </c>
       <c r="H103" s="9" t="n"/>
       <c r="I103" s="9" t="n"/>
       <c r="K103" s="9" t="n"/>
     </row>
     <row r="104">
-      <c r="G104" t="n">
-        <v>10</v>
-      </c>
       <c r="H104" s="9" t="n"/>
       <c r="I104" s="9" t="n"/>
       <c r="K104" s="9" t="n"/>
     </row>
     <row r="105">
-      <c r="G105" t="n">
-        <v>10</v>
-      </c>
       <c r="H105" s="9" t="n"/>
       <c r="I105" s="9" t="n"/>
       <c r="K105" s="9" t="n"/>
     </row>
     <row r="106">
-      <c r="G106" t="n">
-        <v>10</v>
-      </c>
       <c r="H106" s="9" t="n"/>
       <c r="I106" s="9" t="n"/>
       <c r="K106" s="9" t="n"/>
     </row>
     <row r="107">
-      <c r="G107" t="n">
-        <v>10</v>
-      </c>
       <c r="H107" s="9" t="n"/>
       <c r="I107" s="9" t="n"/>
       <c r="K107" s="9" t="n"/>
     </row>
     <row r="108">
-      <c r="G108" t="n">
-        <v>10</v>
-      </c>
       <c r="H108" s="9" t="n"/>
       <c r="I108" s="9" t="n"/>
       <c r="K108" s="9" t="n"/>
     </row>
     <row r="109">
-      <c r="G109" t="n">
-        <v>10</v>
-      </c>
       <c r="H109" s="9" t="n"/>
       <c r="I109" s="9" t="n"/>
       <c r="K109" s="9" t="n"/>
     </row>
     <row r="110">
-      <c r="G110" t="n">
-        <v>10</v>
-      </c>
       <c r="H110" s="9" t="n"/>
       <c r="I110" s="9" t="n"/>
       <c r="K110" s="9" t="n"/>
     </row>
     <row r="111">
-      <c r="G111" t="n">
-        <v>10</v>
-      </c>
       <c r="H111" s="9" t="n"/>
       <c r="I111" s="9" t="n"/>
       <c r="K111" s="9" t="n"/>
     </row>
     <row r="112">
-      <c r="G112" t="n">
-        <v>10</v>
-      </c>
       <c r="H112" s="9" t="n"/>
       <c r="I112" s="9" t="n"/>
       <c r="K112" s="9" t="n"/>
     </row>
     <row r="113">
-      <c r="G113" t="n">
-        <v>10</v>
-      </c>
       <c r="H113" s="9" t="n"/>
       <c r="I113" s="9" t="n"/>
       <c r="K113" s="9" t="n"/>
     </row>
     <row r="114">
-      <c r="G114" t="n">
-        <v>10</v>
-      </c>
       <c r="H114" s="9" t="n"/>
       <c r="I114" s="9" t="n"/>
       <c r="K114" s="9" t="n"/>
     </row>
     <row r="115">
-      <c r="G115" t="n">
-        <v>10</v>
-      </c>
       <c r="H115" s="9" t="n"/>
       <c r="I115" s="9" t="n"/>
       <c r="K115" s="9" t="n"/>
     </row>
     <row r="116">
-      <c r="G116" t="n">
-        <v>10</v>
-      </c>
       <c r="H116" s="9" t="n"/>
       <c r="I116" s="9" t="n"/>
       <c r="K116" s="9" t="n"/>
     </row>
     <row r="117">
-      <c r="G117" t="n">
-        <v>10</v>
-      </c>
       <c r="H117" s="9" t="n"/>
       <c r="I117" s="9" t="n"/>
       <c r="K117" s="9" t="n"/>
     </row>
     <row r="118">
-      <c r="G118" t="n">
-        <v>10</v>
-      </c>
       <c r="H118" s="9" t="n"/>
       <c r="I118" s="9" t="n"/>
       <c r="K118" s="9" t="n"/>
     </row>
     <row r="119">
-      <c r="G119" t="n">
-        <v>10</v>
-      </c>
       <c r="H119" s="9" t="n"/>
       <c r="I119" s="9" t="n"/>
       <c r="K119" s="9" t="n"/>
     </row>
     <row r="120">
-      <c r="G120" t="n">
-        <v>10</v>
-      </c>
       <c r="H120" s="9" t="n"/>
       <c r="I120" s="9" t="n"/>
       <c r="K120" s="9" t="n"/>
     </row>
     <row r="121">
-      <c r="G121" t="n">
-        <v>10</v>
-      </c>
       <c r="H121" s="9" t="n"/>
       <c r="I121" s="9" t="n"/>
       <c r="K121" s="9" t="n"/>
     </row>
     <row r="122">
-      <c r="G122" t="n">
-        <v>10</v>
-      </c>
       <c r="H122" s="9" t="n"/>
       <c r="I122" s="9" t="n"/>
       <c r="K122" s="9" t="n"/>
     </row>
     <row r="123">
-      <c r="G123" t="n">
-        <v>10</v>
-      </c>
       <c r="H123" s="9" t="n"/>
       <c r="I123" s="9" t="n"/>
       <c r="K123" s="9" t="n"/>
     </row>
     <row r="124">
-      <c r="G124" t="n">
-        <v>10</v>
-      </c>
       <c r="H124" s="9" t="n"/>
       <c r="I124" s="9" t="n"/>
       <c r="K124" s="9" t="n"/>
     </row>
     <row r="125">
-      <c r="G125" t="n">
-        <v>10</v>
-      </c>
       <c r="H125" s="9" t="n"/>
       <c r="I125" s="9" t="n"/>
       <c r="K125" s="9" t="n"/>
     </row>
     <row r="126">
-      <c r="G126" t="n">
-        <v>10</v>
-      </c>
       <c r="H126" s="9" t="n"/>
       <c r="I126" s="9" t="n"/>
       <c r="K126" s="9" t="n"/>
     </row>
     <row r="127">
-      <c r="G127" t="n">
-        <v>10</v>
-      </c>
       <c r="H127" s="9" t="n"/>
       <c r="I127" s="9" t="n"/>
       <c r="K127" s="9" t="n"/>
     </row>
     <row r="128">
-      <c r="G128" t="n">
-        <v>10</v>
-      </c>
       <c r="H128" s="9" t="n"/>
       <c r="I128" s="9" t="n"/>
       <c r="K128" s="9" t="n"/>
     </row>
     <row r="129">
-      <c r="G129" t="n">
-        <v>10</v>
-      </c>
       <c r="H129" s="9" t="n"/>
       <c r="I129" s="9" t="n"/>
       <c r="K129" s="9" t="n"/>
     </row>
     <row r="130">
-      <c r="G130" t="n">
-        <v>10</v>
-      </c>
       <c r="H130" s="9" t="n"/>
       <c r="I130" s="9" t="n"/>
       <c r="K130" s="9" t="n"/>
     </row>
     <row r="131">
-      <c r="G131" t="n">
-        <v>10</v>
-      </c>
       <c r="H131" s="9" t="n"/>
       <c r="I131" s="9" t="n"/>
       <c r="K131" s="9" t="n"/>
     </row>
     <row r="132">
-      <c r="G132" t="n">
-        <v>10</v>
-      </c>
       <c r="H132" s="9" t="n"/>
       <c r="I132" s="9" t="n"/>
       <c r="K132" s="9" t="n"/>
     </row>
     <row r="133">
-      <c r="G133" t="n">
-        <v>10</v>
-      </c>
       <c r="H133" s="9" t="n"/>
       <c r="I133" s="9" t="n"/>
       <c r="K133" s="9" t="n"/>
     </row>
     <row r="134">
-      <c r="G134" t="n">
-        <v>10</v>
-      </c>
       <c r="H134" s="9" t="n"/>
       <c r="I134" s="9" t="n"/>
       <c r="K134" s="9" t="n"/>
     </row>
     <row r="135">
-      <c r="G135" t="n">
-        <v>10</v>
-      </c>
       <c r="H135" s="9" t="n"/>
       <c r="I135" s="9" t="n"/>
       <c r="K135" s="9" t="n"/>
     </row>
     <row r="136">
-      <c r="G136" t="n">
-        <v>10</v>
-      </c>
       <c r="H136" s="9" t="n"/>
       <c r="I136" s="9" t="n"/>
       <c r="K136" s="9" t="n"/>
     </row>
     <row r="137">
-      <c r="G137" t="n">
-        <v>10</v>
-      </c>
       <c r="H137" s="9" t="n"/>
       <c r="I137" s="9" t="n"/>
       <c r="K137" s="9" t="n"/>
     </row>
     <row r="138">
-      <c r="G138" t="n">
-        <v>10</v>
-      </c>
       <c r="H138" s="9" t="n"/>
       <c r="I138" s="9" t="n"/>
       <c r="K138" s="9" t="n"/>
     </row>
     <row r="139">
-      <c r="G139" t="n">
-        <v>10</v>
-      </c>
       <c r="H139" s="9" t="n"/>
       <c r="I139" s="9" t="n"/>
       <c r="K139" s="9" t="n"/>
     </row>
     <row r="140">
-      <c r="G140" t="n">
-        <v>10</v>
-      </c>
       <c r="H140" s="9" t="n"/>
       <c r="I140" s="9" t="n"/>
       <c r="K140" s="9" t="n"/>
     </row>
     <row r="141">
-      <c r="G141" t="n">
-        <v>10</v>
-      </c>
       <c r="H141" s="9" t="n"/>
       <c r="I141" s="9" t="n"/>
       <c r="K141" s="9" t="n"/>
     </row>
     <row r="142">
-      <c r="G142" t="n">
-        <v>10</v>
-      </c>
       <c r="H142" s="9" t="n"/>
       <c r="I142" s="9" t="n"/>
       <c r="K142" s="9" t="n"/>
     </row>
     <row r="143">
-      <c r="G143" t="n">
-        <v>10</v>
-      </c>
       <c r="H143" s="9" t="n"/>
       <c r="I143" s="9" t="n"/>
       <c r="K143" s="9" t="n"/>
     </row>
     <row r="144">
-      <c r="G144" t="n">
-        <v>10</v>
-      </c>
       <c r="H144" s="9" t="n"/>
       <c r="I144" s="9" t="n"/>
       <c r="K144" s="9" t="n"/>
     </row>
     <row r="145">
-      <c r="G145" t="n">
-        <v>10</v>
-      </c>
       <c r="H145" s="9" t="n"/>
       <c r="I145" s="9" t="n"/>
       <c r="K145" s="9" t="n"/>
     </row>
     <row r="146">
-      <c r="G146" t="n">
-        <v>10</v>
-      </c>
       <c r="H146" s="9" t="n"/>
       <c r="I146" s="9" t="n"/>
       <c r="K146" s="9" t="n"/>
     </row>
     <row r="147">
-      <c r="G147" t="n">
-        <v>10</v>
-      </c>
       <c r="H147" s="9" t="n"/>
       <c r="I147" s="9" t="n"/>
       <c r="K147" s="9" t="n"/>
     </row>
     <row r="148">
-      <c r="G148" t="n">
-        <v>10</v>
-      </c>
       <c r="H148" s="9" t="n"/>
       <c r="I148" s="9" t="n"/>
       <c r="K148" s="9" t="n"/>
     </row>
     <row r="149">
-      <c r="G149" t="n">
-        <v>10</v>
-      </c>
       <c r="H149" s="9" t="n"/>
       <c r="I149" s="9" t="n"/>
       <c r="K149" s="9" t="n"/>
     </row>
     <row r="150">
-      <c r="G150" t="n">
-        <v>10</v>
-      </c>
       <c r="H150" s="9" t="n"/>
       <c r="I150" s="9" t="n"/>
       <c r="K150" s="9" t="n"/>
     </row>
     <row r="151">
-      <c r="G151" t="n">
-        <v>10</v>
-      </c>
       <c r="H151" s="9" t="n"/>
       <c r="I151" s="9" t="n"/>
       <c r="K151" s="9" t="n"/>
     </row>
     <row r="152">
-      <c r="G152" t="n">
-        <v>10</v>
-      </c>
       <c r="H152" s="9" t="n"/>
       <c r="I152" s="9" t="n"/>
       <c r="K152" s="9" t="n"/>
     </row>
     <row r="153">
-      <c r="G153" t="n">
-        <v>10</v>
-      </c>
       <c r="H153" s="9" t="n"/>
       <c r="I153" s="9" t="n"/>
       <c r="K153" s="9" t="n"/>
     </row>
     <row r="154">
-      <c r="G154" t="n">
-        <v>10</v>
-      </c>
       <c r="H154" s="9" t="n"/>
       <c r="I154" s="9" t="n"/>
       <c r="K154" s="9" t="n"/>
     </row>
     <row r="155">
-      <c r="G155" t="n">
-        <v>10</v>
-      </c>
       <c r="H155" s="9" t="n"/>
       <c r="I155" s="9" t="n"/>
       <c r="K155" s="9" t="n"/>
     </row>
     <row r="156">
-      <c r="G156" t="n">
-        <v>10</v>
-      </c>
       <c r="H156" s="9" t="n"/>
       <c r="I156" s="9" t="n"/>
       <c r="K156" s="9" t="n"/>
     </row>
     <row r="157">
-      <c r="G157" t="n">
-        <v>10</v>
-      </c>
       <c r="H157" s="9" t="n"/>
       <c r="I157" s="9" t="n"/>
       <c r="K157" s="9" t="n"/>
     </row>
     <row r="158">
-      <c r="G158" t="n">
-        <v>10</v>
-      </c>
       <c r="H158" s="9" t="n"/>
       <c r="I158" s="9" t="n"/>
       <c r="K158" s="9" t="n"/>
     </row>
     <row r="159">
-      <c r="G159" t="n">
-        <v>10</v>
-      </c>
       <c r="H159" s="9" t="n"/>
       <c r="I159" s="9" t="n"/>
       <c r="K159" s="9" t="n"/>
     </row>
     <row r="160">
-      <c r="G160" t="n">
-        <v>10</v>
-      </c>
       <c r="H160" s="9" t="n"/>
       <c r="I160" s="9" t="n"/>
       <c r="K160" s="9" t="n"/>
     </row>
     <row r="161">
-      <c r="G161" t="n">
-        <v>10</v>
-      </c>
       <c r="H161" s="9" t="n"/>
       <c r="I161" s="9" t="n"/>
       <c r="K161" s="9" t="n"/>
     </row>
     <row r="162">
-      <c r="G162" t="n">
-        <v>10</v>
-      </c>
       <c r="H162" s="9" t="n"/>
       <c r="I162" s="9" t="n"/>
       <c r="K162" s="9" t="n"/>
     </row>
     <row r="163">
-      <c r="G163" t="n">
-        <v>10</v>
-      </c>
       <c r="H163" s="9" t="n"/>
       <c r="I163" s="9" t="n"/>
       <c r="K163" s="9" t="n"/>
     </row>
     <row r="164">
-      <c r="G164" t="n">
-        <v>10</v>
-      </c>
       <c r="H164" s="9" t="n"/>
       <c r="I164" s="9" t="n"/>
       <c r="K164" s="9" t="n"/>
     </row>
     <row r="165">
-      <c r="G165" t="n">
-        <v>10</v>
-      </c>
       <c r="H165" s="9" t="n"/>
       <c r="I165" s="9" t="n"/>
       <c r="K165" s="9" t="n"/>
     </row>
     <row r="166">
-      <c r="G166" t="n">
-        <v>10</v>
-      </c>
       <c r="H166" s="9" t="n"/>
       <c r="I166" s="9" t="n"/>
       <c r="K166" s="9" t="n"/>
     </row>
     <row r="167">
-      <c r="G167" t="n">
-        <v>10</v>
-      </c>
       <c r="H167" s="9" t="n"/>
       <c r="I167" s="9" t="n"/>
       <c r="K167" s="9" t="n"/>
     </row>
     <row r="168">
-      <c r="G168" t="n">
-        <v>10</v>
-      </c>
       <c r="H168" s="9" t="n"/>
       <c r="I168" s="9" t="n"/>
       <c r="K168" s="9" t="n"/>
     </row>
     <row r="169">
-      <c r="G169" t="n">
-        <v>10</v>
-      </c>
       <c r="H169" s="9" t="n"/>
       <c r="I169" s="9" t="n"/>
       <c r="K169" s="9" t="n"/>
     </row>
     <row r="170">
-      <c r="G170" t="n">
-        <v>10</v>
-      </c>
       <c r="H170" s="9" t="n"/>
       <c r="I170" s="9" t="n"/>
       <c r="K170" s="9" t="n"/>
     </row>
     <row r="171">
-      <c r="G171" t="n">
-        <v>10</v>
-      </c>
       <c r="H171" s="9" t="n"/>
       <c r="I171" s="9" t="n"/>
       <c r="K171" s="9" t="n"/>
     </row>
     <row r="172">
-      <c r="G172" t="n">
-        <v>10</v>
-      </c>
       <c r="H172" s="9" t="n"/>
       <c r="I172" s="9" t="n"/>
       <c r="K172" s="9" t="n"/>
     </row>
     <row r="173">
-      <c r="G173" t="n">
-        <v>10</v>
-      </c>
       <c r="H173" s="9" t="n"/>
       <c r="I173" s="9" t="n"/>
       <c r="K173" s="9" t="n"/>
     </row>
     <row r="174">
-      <c r="G174" t="n">
-        <v>10</v>
-      </c>
       <c r="H174" s="9" t="n"/>
       <c r="I174" s="9" t="n"/>
       <c r="K174" s="9" t="n"/>
     </row>
     <row r="175">
-      <c r="G175" t="n">
-        <v>10</v>
-      </c>
       <c r="H175" s="9" t="n"/>
       <c r="I175" s="9" t="n"/>
       <c r="K175" s="9" t="n"/>
     </row>
     <row r="176">
-      <c r="G176" t="n">
-        <v>10</v>
-      </c>
       <c r="H176" s="9" t="n"/>
       <c r="I176" s="9" t="n"/>
       <c r="K176" s="9" t="n"/>
     </row>
     <row r="177">
-      <c r="G177" t="n">
-        <v>10</v>
-      </c>
       <c r="H177" s="9" t="n"/>
       <c r="I177" s="9" t="n"/>
       <c r="K177" s="9" t="n"/>
     </row>
     <row r="178">
-      <c r="G178" t="n">
-        <v>10</v>
-      </c>
       <c r="H178" s="9" t="n"/>
       <c r="I178" s="9" t="n"/>
       <c r="K178" s="9" t="n"/>
     </row>
     <row r="179">
-      <c r="G179" t="n">
-        <v>10</v>
-      </c>
       <c r="H179" s="9" t="n"/>
       <c r="I179" s="9" t="n"/>
       <c r="K179" s="9" t="n"/>
     </row>
     <row r="180">
-      <c r="G180" t="n">
-        <v>10</v>
-      </c>
       <c r="H180" s="9" t="n"/>
       <c r="I180" s="9" t="n"/>
       <c r="K180" s="9" t="n"/>
     </row>
     <row r="181">
-      <c r="G181" t="n">
-        <v>10</v>
-      </c>
       <c r="H181" s="9" t="n"/>
       <c r="I181" s="9" t="n"/>
       <c r="K181" s="9" t="n"/>
     </row>
     <row r="182">
-      <c r="G182" t="n">
-        <v>10</v>
-      </c>
       <c r="H182" s="9" t="n"/>
       <c r="I182" s="9" t="n"/>
       <c r="K182" s="9" t="n"/>
     </row>
     <row r="183">
-      <c r="G183" t="n">
-        <v>10</v>
-      </c>
       <c r="H183" s="9" t="n"/>
       <c r="I183" s="9" t="n"/>
       <c r="K183" s="9" t="n"/>
     </row>
     <row r="184">
-      <c r="G184" t="n">
-        <v>10</v>
-      </c>
       <c r="H184" s="9" t="n"/>
       <c r="I184" s="9" t="n"/>
       <c r="K184" s="9" t="n"/>
     </row>
     <row r="185">
-      <c r="G185" t="n">
-        <v>10</v>
-      </c>
       <c r="H185" s="9" t="n"/>
       <c r="I185" s="9" t="n"/>
       <c r="K185" s="9" t="n"/>
     </row>
     <row r="186">
-      <c r="G186" t="n">
-        <v>10</v>
-      </c>
       <c r="H186" s="9" t="n"/>
       <c r="I186" s="9" t="n"/>
       <c r="K186" s="9" t="n"/>
     </row>
     <row r="187">
-      <c r="G187" t="n">
-        <v>10</v>
-      </c>
       <c r="H187" s="9" t="n"/>
       <c r="I187" s="9" t="n"/>
       <c r="K187" s="9" t="n"/>
     </row>
     <row r="188">
-      <c r="G188" t="n">
-        <v>10</v>
-      </c>
       <c r="H188" s="9" t="n"/>
       <c r="I188" s="9" t="n"/>
       <c r="K188" s="9" t="n"/>
     </row>
     <row r="189">
-      <c r="G189" t="n">
-        <v>10</v>
-      </c>
       <c r="H189" s="9" t="n"/>
       <c r="I189" s="9" t="n"/>
       <c r="K189" s="9" t="n"/>
     </row>
     <row r="190">
-      <c r="G190" t="n">
-        <v>10</v>
-      </c>
       <c r="H190" s="9" t="n"/>
       <c r="I190" s="9" t="n"/>
       <c r="K190" s="9" t="n"/>
     </row>
     <row r="191">
-      <c r="G191" t="n">
-        <v>10</v>
-      </c>
       <c r="H191" s="9" t="n"/>
       <c r="I191" s="9" t="n"/>
       <c r="K191" s="9" t="n"/>
     </row>
     <row r="192">
-      <c r="G192" t="n">
-        <v>10</v>
-      </c>
       <c r="H192" s="9" t="n"/>
       <c r="I192" s="9" t="n"/>
       <c r="K192" s="9" t="n"/>
     </row>
     <row r="193">
-      <c r="G193" t="n">
-        <v>10</v>
-      </c>
       <c r="H193" s="9" t="n"/>
       <c r="I193" s="9" t="n"/>
       <c r="K193" s="9" t="n"/>
     </row>
     <row r="194">
-      <c r="G194" t="n">
-        <v>10</v>
-      </c>
       <c r="H194" s="9" t="n"/>
       <c r="I194" s="9" t="n"/>
       <c r="K194" s="9" t="n"/>
     </row>
     <row r="195">
-      <c r="G195" t="n">
-        <v>10</v>
-      </c>
       <c r="H195" s="9" t="n"/>
       <c r="I195" s="9" t="n"/>
       <c r="K195" s="9" t="n"/>
     </row>
     <row r="196">
-      <c r="G196" t="n">
-        <v>10</v>
-      </c>
       <c r="H196" s="9" t="n"/>
       <c r="I196" s="9" t="n"/>
       <c r="K196" s="9" t="n"/>
     </row>
     <row r="197">
-      <c r="G197" t="n">
-        <v>10</v>
-      </c>
       <c r="H197" s="9" t="n"/>
       <c r="I197" s="9" t="n"/>
       <c r="K197" s="9" t="n"/>
     </row>
     <row r="198">
-      <c r="G198" t="n">
-        <v>10</v>
-      </c>
       <c r="H198" s="9" t="n"/>
       <c r="I198" s="9" t="n"/>
       <c r="K198" s="9" t="n"/>
     </row>
     <row r="199">
-      <c r="G199" t="n">
-        <v>10</v>
-      </c>
       <c r="H199" s="9" t="n"/>
       <c r="I199" s="9" t="n"/>
       <c r="K199" s="9" t="n"/>
     </row>
     <row r="200">
-      <c r="G200" t="n">
-        <v>10</v>
-      </c>
       <c r="H200" s="9" t="n"/>
       <c r="I200" s="9" t="n"/>
       <c r="K200" s="9" t="n"/>
     </row>
     <row r="201">
-      <c r="G201" t="n">
-        <v>10</v>
-      </c>
       <c r="H201" s="9" t="n"/>
       <c r="I201" s="9" t="n"/>
       <c r="K201" s="9" t="n"/>
     </row>
     <row r="202">
-      <c r="G202" t="n">
-        <v>10</v>
-      </c>
       <c r="H202" s="9" t="n"/>
       <c r="I202" s="9" t="n"/>
       <c r="K202" s="9" t="n"/>
     </row>
     <row r="203">
-      <c r="G203" t="n">
-        <v>10</v>
-      </c>
       <c r="H203" s="9" t="n"/>
       <c r="I203" s="9" t="n"/>
       <c r="K203" s="9" t="n"/>
     </row>
     <row r="204">
-      <c r="G204" t="n">
-        <v>10</v>
-      </c>
       <c r="H204" s="9" t="n"/>
       <c r="I204" s="9" t="n"/>
       <c r="K204" s="9" t="n"/>
     </row>
     <row r="205">
-      <c r="G205" t="n">
-        <v>10</v>
-      </c>
       <c r="H205" s="9" t="n"/>
       <c r="I205" s="9" t="n"/>
       <c r="K205" s="9" t="n"/>
     </row>
     <row r="206">
-      <c r="G206" t="n">
-        <v>10</v>
-      </c>
       <c r="H206" s="9" t="n"/>
       <c r="I206" s="9" t="n"/>
       <c r="K206" s="9" t="n"/>
     </row>
     <row r="207">
-      <c r="G207" t="n">
-        <v>10</v>
-      </c>
       <c r="H207" s="9" t="n"/>
       <c r="I207" s="9" t="n"/>
       <c r="K207" s="9" t="n"/>
     </row>
     <row r="208">
-      <c r="G208" t="n">
-        <v>10</v>
-      </c>
       <c r="H208" s="9" t="n"/>
       <c r="I208" s="9" t="n"/>
       <c r="K208" s="9" t="n"/>
     </row>
     <row r="209">
-      <c r="G209" t="n">
-        <v>10</v>
-      </c>
       <c r="H209" s="9" t="n"/>
       <c r="I209" s="9" t="n"/>
       <c r="K209" s="9" t="n"/>
     </row>
     <row r="210">
-      <c r="G210" t="n">
-        <v>10</v>
-      </c>
       <c r="H210" s="9" t="n"/>
       <c r="I210" s="9" t="n"/>
       <c r="K210" s="9" t="n"/>
     </row>
     <row r="211">
-      <c r="G211" t="n">
-        <v>10</v>
-      </c>
       <c r="H211" s="9" t="n"/>
       <c r="I211" s="9" t="n"/>
       <c r="K211" s="9" t="n"/>
     </row>
     <row r="212">
-      <c r="G212" t="n">
-        <v>10</v>
-      </c>
       <c r="H212" s="9" t="n"/>
       <c r="I212" s="9" t="n"/>
       <c r="K212" s="9" t="n"/>
     </row>
     <row r="213">
-      <c r="G213" t="n">
-        <v>10</v>
-      </c>
       <c r="H213" s="9" t="n"/>
       <c r="I213" s="9" t="n"/>
       <c r="K213" s="9" t="n"/>
     </row>
     <row r="214">
-      <c r="G214" t="n">
-        <v>10</v>
-      </c>
       <c r="H214" s="9" t="n"/>
       <c r="I214" s="9" t="n"/>
       <c r="K214" s="9" t="n"/>
     </row>
     <row r="215">
-      <c r="G215" t="n">
-        <v>10</v>
-      </c>
       <c r="H215" s="9" t="n"/>
       <c r="I215" s="9" t="n"/>
       <c r="K215" s="9" t="n"/>
     </row>
     <row r="216">
-      <c r="G216" t="n">
-        <v>10</v>
-      </c>
       <c r="H216" s="9" t="n"/>
       <c r="I216" s="9" t="n"/>
       <c r="K216" s="9" t="n"/>
     </row>
     <row r="217">
-      <c r="G217" t="n">
-        <v>10</v>
-      </c>
       <c r="H217" s="9" t="n"/>
       <c r="I217" s="9" t="n"/>
       <c r="K217" s="9" t="n"/>
     </row>
     <row r="218">
-      <c r="G218" t="n">
-        <v>10</v>
-      </c>
       <c r="H218" s="9" t="n"/>
       <c r="I218" s="9" t="n"/>
       <c r="K218" s="9" t="n"/>
     </row>
     <row r="219">
-      <c r="G219" t="n">
-        <v>10</v>
-      </c>
       <c r="H219" s="9" t="n"/>
       <c r="I219" s="9" t="n"/>
       <c r="K219" s="9" t="n"/>
     </row>
     <row r="220">
-      <c r="G220" t="n">
-        <v>10</v>
-      </c>
       <c r="H220" s="9" t="n"/>
       <c r="I220" s="9" t="n"/>
       <c r="K220" s="9" t="n"/>
     </row>
     <row r="221">
-      <c r="G221" t="n">
-        <v>10</v>
-      </c>
       <c r="H221" s="9" t="n"/>
       <c r="I221" s="9" t="n"/>
       <c r="K221" s="9" t="n"/>
     </row>
     <row r="222">
-      <c r="G222" t="n">
-        <v>10</v>
-      </c>
       <c r="H222" s="9" t="n"/>
       <c r="I222" s="9" t="n"/>
       <c r="K222" s="9" t="n"/>
     </row>
     <row r="223">
-      <c r="G223" t="n">
-        <v>10</v>
-      </c>
       <c r="H223" s="9" t="n"/>
       <c r="I223" s="9" t="n"/>
       <c r="K223" s="9" t="n"/>
     </row>
     <row r="224">
-      <c r="G224" t="n">
-        <v>10</v>
-      </c>
       <c r="H224" s="9" t="n"/>
       <c r="I224" s="9" t="n"/>
       <c r="K224" s="9" t="n"/>
     </row>
     <row r="225">
-      <c r="G225" t="n">
-        <v>10</v>
-      </c>
       <c r="H225" s="9" t="n"/>
       <c r="I225" s="9" t="n"/>
       <c r="K225" s="9" t="n"/>
     </row>
     <row r="226">
-      <c r="G226" t="n">
-        <v>10</v>
-      </c>
       <c r="H226" s="9" t="n"/>
       <c r="I226" s="9" t="n"/>
       <c r="K226" s="9" t="n"/>
     </row>
     <row r="227">
-      <c r="G227" t="n">
-        <v>10</v>
-      </c>
       <c r="H227" s="9" t="n"/>
       <c r="I227" s="9" t="n"/>
       <c r="K227" s="9" t="n"/>
     </row>
     <row r="228">
-      <c r="G228" t="n">
-        <v>10</v>
-      </c>
       <c r="H228" s="9" t="n"/>
       <c r="I228" s="9" t="n"/>
       <c r="K228" s="9" t="n"/>
     </row>
     <row r="229">
-      <c r="G229" t="n">
-        <v>10</v>
-      </c>
       <c r="H229" s="9" t="n"/>
       <c r="I229" s="9" t="n"/>
       <c r="K229" s="9" t="n"/>
     </row>
     <row r="230">
-      <c r="G230" t="n">
-        <v>10</v>
-      </c>
       <c r="H230" s="9" t="n"/>
       <c r="I230" s="9" t="n"/>
       <c r="K230" s="9" t="n"/>
     </row>
     <row r="231">
-      <c r="G231" t="n">
-        <v>10</v>
-      </c>
       <c r="H231" s="9" t="n"/>
       <c r="I231" s="9" t="n"/>
       <c r="K231" s="9" t="n"/>
     </row>
     <row r="232">
-      <c r="G232" t="n">
-        <v>10</v>
-      </c>
       <c r="H232" s="9" t="n"/>
       <c r="I232" s="9" t="n"/>
       <c r="K232" s="9" t="n"/>
     </row>
     <row r="233">
-      <c r="G233" t="n">
-        <v>10</v>
-      </c>
       <c r="H233" s="9" t="n"/>
       <c r="I233" s="9" t="n"/>
       <c r="K233" s="9" t="n"/>
     </row>
     <row r="234">
-      <c r="G234" t="n">
-        <v>10</v>
-      </c>
       <c r="H234" s="9" t="n"/>
       <c r="I234" s="9" t="n"/>
       <c r="K234" s="9" t="n"/>
     </row>
     <row r="235">
-      <c r="G235" t="n">
-        <v>10</v>
-      </c>
       <c r="H235" s="9" t="n"/>
       <c r="I235" s="9" t="n"/>
       <c r="K235" s="9" t="n"/>
     </row>
     <row r="236">
-      <c r="G236" t="n">
-        <v>10</v>
-      </c>
       <c r="H236" s="9" t="n"/>
       <c r="I236" s="9" t="n"/>
       <c r="K236" s="9" t="n"/>
     </row>
     <row r="237">
-      <c r="G237" t="n">
-        <v>10</v>
-      </c>
       <c r="H237" s="9" t="n"/>
       <c r="I237" s="9" t="n"/>
       <c r="K237" s="9" t="n"/>
     </row>
     <row r="238">
-      <c r="G238" t="n">
-        <v>10</v>
-      </c>
       <c r="H238" s="9" t="n"/>
       <c r="I238" s="9" t="n"/>
       <c r="K238" s="9" t="n"/>
     </row>
     <row r="239">
-      <c r="G239" t="n">
-        <v>10</v>
-      </c>
       <c r="H239" s="9" t="n"/>
       <c r="I239" s="9" t="n"/>
       <c r="K239" s="9" t="n"/>
     </row>
     <row r="240">
-      <c r="G240" t="n">
-        <v>10</v>
-      </c>
       <c r="H240" s="9" t="n"/>
       <c r="I240" s="9" t="n"/>
       <c r="K240" s="9" t="n"/>
     </row>
     <row r="241">
-      <c r="G241" t="n">
-        <v>10</v>
-      </c>
       <c r="H241" s="9" t="n"/>
       <c r="I241" s="9" t="n"/>
       <c r="K241" s="9" t="n"/>
     </row>
     <row r="242">
-      <c r="G242" t="n">
-        <v>10</v>
-      </c>
       <c r="H242" s="9" t="n"/>
       <c r="I242" s="9" t="n"/>
       <c r="K242" s="9" t="n"/>
     </row>
     <row r="243">
-      <c r="G243" t="n">
-        <v>10</v>
-      </c>
       <c r="H243" s="9" t="n"/>
       <c r="I243" s="9" t="n"/>
       <c r="K243" s="9" t="n"/>
     </row>
     <row r="244">
-      <c r="G244" t="n">
-        <v>10</v>
-      </c>
       <c r="H244" s="9" t="n"/>
       <c r="I244" s="9" t="n"/>
       <c r="K244" s="9" t="n"/>
     </row>
     <row r="245">
-      <c r="G245" t="n">
-        <v>10</v>
-      </c>
       <c r="H245" s="9" t="n"/>
       <c r="I245" s="9" t="n"/>
       <c r="K245" s="9" t="n"/>
     </row>
     <row r="246">
-      <c r="G246" t="n">
-        <v>10</v>
-      </c>
       <c r="H246" s="9" t="n"/>
       <c r="I246" s="9" t="n"/>
       <c r="K246" s="9" t="n"/>
     </row>
     <row r="247">
-      <c r="G247" t="n">
-        <v>10</v>
-      </c>
       <c r="H247" s="9" t="n"/>
       <c r="I247" s="9" t="n"/>
       <c r="K247" s="9" t="n"/>
     </row>
     <row r="248">
-      <c r="G248" t="n">
-        <v>10</v>
-      </c>
       <c r="H248" s="9" t="n"/>
       <c r="I248" s="9" t="n"/>
       <c r="K248" s="9" t="n"/>
     </row>
     <row r="249">
-      <c r="G249" t="n">
-        <v>10</v>
-      </c>
       <c r="H249" s="9" t="n"/>
       <c r="I249" s="9" t="n"/>
       <c r="K249" s="9" t="n"/>
     </row>
     <row r="250">
-      <c r="G250" t="n">
-        <v>10</v>
-      </c>
       <c r="H250" s="9" t="n"/>
       <c r="I250" s="9" t="n"/>
       <c r="K250" s="9" t="n"/>
     </row>
     <row r="251">
-      <c r="G251" t="n">
-        <v>10</v>
-      </c>
       <c r="H251" s="9" t="n"/>
       <c r="I251" s="9" t="n"/>
       <c r="K251" s="9" t="n"/>
     </row>
     <row r="252">
-      <c r="G252" t="n">
-        <v>10</v>
-      </c>
       <c r="H252" s="9" t="n"/>
       <c r="I252" s="9" t="n"/>
       <c r="K252" s="9" t="n"/>
     </row>
     <row r="253">
-      <c r="G253" t="n">
-        <v>10</v>
-      </c>
       <c r="H253" s="9" t="n"/>
       <c r="I253" s="9" t="n"/>
       <c r="K253" s="9" t="n"/>
     </row>
     <row r="254">
-      <c r="G254" t="n">
-        <v>10</v>
-      </c>
       <c r="H254" s="9" t="n"/>
       <c r="I254" s="9" t="n"/>
       <c r="K254" s="9" t="n"/>
     </row>
     <row r="255">
-      <c r="G255" t="n">
-        <v>10</v>
-      </c>
       <c r="H255" s="9" t="n"/>
       <c r="I255" s="9" t="n"/>
       <c r="K255" s="9" t="n"/>
     </row>
     <row r="256">
-      <c r="G256" t="n">
-        <v>10</v>
-      </c>
       <c r="H256" s="9" t="n"/>
       <c r="I256" s="9" t="n"/>
       <c r="K256" s="9" t="n"/>
     </row>
     <row r="257">
-      <c r="G257" t="n">
-        <v>10</v>
-      </c>
       <c r="H257" s="9" t="n"/>
       <c r="I257" s="9" t="n"/>
       <c r="K257" s="9" t="n"/>
     </row>
     <row r="258">
-      <c r="G258" t="n">
-        <v>10</v>
-      </c>
       <c r="H258" s="9" t="n"/>
       <c r="I258" s="9" t="n"/>
       <c r="K258" s="9" t="n"/>
     </row>
     <row r="259">
-      <c r="G259" t="n">
-        <v>10</v>
-      </c>
       <c r="H259" s="9" t="n"/>
       <c r="I259" s="9" t="n"/>
       <c r="K259" s="9" t="n"/>
     </row>
     <row r="260">
-      <c r="G260" t="n">
-        <v>10</v>
-      </c>
       <c r="H260" s="9" t="n"/>
       <c r="I260" s="9" t="n"/>
       <c r="K260" s="9" t="n"/>
     </row>
     <row r="261">
-      <c r="G261" t="n">
-        <v>10</v>
-      </c>
       <c r="H261" s="9" t="n"/>
       <c r="I261" s="9" t="n"/>
       <c r="K261" s="9" t="n"/>
     </row>
     <row r="262">
-      <c r="G262" t="n">
-        <v>10</v>
-      </c>
       <c r="H262" s="9" t="n"/>
       <c r="I262" s="9" t="n"/>
       <c r="K262" s="9" t="n"/>
     </row>
     <row r="263">
-      <c r="G263" t="n">
-        <v>10</v>
-      </c>
       <c r="H263" s="9" t="n"/>
       <c r="I263" s="9" t="n"/>
       <c r="K263" s="9" t="n"/>
     </row>
     <row r="264">
-      <c r="G264" t="n">
-        <v>10</v>
-      </c>
       <c r="H264" s="9" t="n"/>
       <c r="I264" s="9" t="n"/>
       <c r="K264" s="9" t="n"/>
     </row>
     <row r="265">
-      <c r="G265" t="n">
-        <v>10</v>
-      </c>
       <c r="H265" s="9" t="n"/>
       <c r="I265" s="9" t="n"/>
       <c r="K265" s="9" t="n"/>
     </row>
     <row r="266">
-      <c r="G266" t="n">
-        <v>10</v>
-      </c>
       <c r="H266" s="9" t="n"/>
       <c r="I266" s="9" t="n"/>
       <c r="K266" s="9" t="n"/>
     </row>
     <row r="267">
-      <c r="G267" t="n">
-        <v>10</v>
-      </c>
       <c r="H267" s="9" t="n"/>
       <c r="I267" s="9" t="n"/>
       <c r="K267" s="9" t="n"/>
     </row>
     <row r="268">
-      <c r="G268" t="n">
-        <v>10</v>
-      </c>
       <c r="H268" s="9" t="n"/>
       <c r="I268" s="9" t="n"/>
       <c r="K268" s="9" t="n"/>
     </row>
     <row r="269">
-      <c r="G269" t="n">
-        <v>10</v>
-      </c>
       <c r="H269" s="9" t="n"/>
       <c r="I269" s="9" t="n"/>
       <c r="K269" s="9" t="n"/>
     </row>
     <row r="270">
-      <c r="G270" t="n">
-        <v>10</v>
-      </c>
       <c r="H270" s="9" t="n"/>
       <c r="I270" s="9" t="n"/>
       <c r="K270" s="9" t="n"/>
     </row>
     <row r="271">
-      <c r="G271" t="n">
-        <v>10</v>
-      </c>
       <c r="H271" s="9" t="n"/>
       <c r="I271" s="9" t="n"/>
       <c r="K271" s="9" t="n"/>
     </row>
     <row r="272">
-      <c r="G272" t="n">
-        <v>10</v>
-      </c>
       <c r="H272" s="9" t="n"/>
       <c r="I272" s="9" t="n"/>
       <c r="K272" s="9" t="n"/>
     </row>
     <row r="273">
-      <c r="G273" t="n">
-        <v>10</v>
-      </c>
       <c r="H273" s="9" t="n"/>
       <c r="I273" s="9" t="n"/>
       <c r="K273" s="9" t="n"/>
     </row>
     <row r="274">
-      <c r="G274" t="n">
-        <v>10</v>
-      </c>
       <c r="H274" s="9" t="n"/>
       <c r="I274" s="9" t="n"/>
       <c r="K274" s="9" t="n"/>
     </row>
     <row r="275">
-      <c r="G275" t="n">
-        <v>10</v>
-      </c>
       <c r="H275" s="9" t="n"/>
       <c r="I275" s="9" t="n"/>
       <c r="K275" s="9" t="n"/>
     </row>
     <row r="276">
-      <c r="G276" t="n">
-        <v>10</v>
-      </c>
       <c r="H276" s="9" t="n"/>
       <c r="I276" s="9" t="n"/>
       <c r="K276" s="9" t="n"/>
     </row>
     <row r="277">
-      <c r="G277" t="n">
-        <v>10</v>
-      </c>
       <c r="H277" s="9" t="n"/>
       <c r="I277" s="9" t="n"/>
       <c r="K277" s="9" t="n"/>
     </row>
     <row r="278">
-      <c r="G278" t="n">
-        <v>10</v>
-      </c>
       <c r="H278" s="9" t="n"/>
       <c r="I278" s="9" t="n"/>
       <c r="K278" s="9" t="n"/>
     </row>
     <row r="279">
-      <c r="G279" t="n">
-        <v>10</v>
-      </c>
       <c r="H279" s="9" t="n"/>
       <c r="I279" s="9" t="n"/>
       <c r="K279" s="9" t="n"/>
     </row>
     <row r="280">
-      <c r="G280" t="n">
-        <v>10</v>
-      </c>
       <c r="H280" s="9" t="n"/>
       <c r="I280" s="9" t="n"/>
       <c r="K280" s="9" t="n"/>
     </row>
     <row r="281">
-      <c r="G281" t="n">
-        <v>10</v>
-      </c>
       <c r="H281" s="9" t="n"/>
       <c r="I281" s="9" t="n"/>
       <c r="K281" s="9" t="n"/>
     </row>
     <row r="282">
-      <c r="G282" t="n">
-        <v>10</v>
-      </c>
       <c r="H282" s="9" t="n"/>
       <c r="I282" s="9" t="n"/>
       <c r="K282" s="9" t="n"/>
     </row>
     <row r="283">
-      <c r="G283" t="n">
-        <v>10</v>
-      </c>
       <c r="H283" s="9" t="n"/>
       <c r="I283" s="9" t="n"/>
       <c r="K283" s="9" t="n"/>
     </row>
     <row r="284">
-      <c r="G284" t="n">
-        <v>10</v>
-      </c>
       <c r="H284" s="9" t="n"/>
       <c r="I284" s="9" t="n"/>
       <c r="K284" s="9" t="n"/>
     </row>
     <row r="285">
-      <c r="G285" t="n">
-        <v>10</v>
-      </c>
       <c r="H285" s="9" t="n"/>
       <c r="I285" s="9" t="n"/>
       <c r="K285" s="9" t="n"/>
     </row>
     <row r="286">
-      <c r="G286" t="n">
-        <v>10</v>
-      </c>
       <c r="H286" s="9" t="n"/>
       <c r="I286" s="9" t="n"/>
       <c r="K286" s="9" t="n"/>
     </row>
     <row r="287">
-      <c r="G287" t="n">
-        <v>10</v>
-      </c>
       <c r="H287" s="9" t="n"/>
       <c r="I287" s="9" t="n"/>
       <c r="K287" s="9" t="n"/>
     </row>
     <row r="288">
-      <c r="G288" t="n">
-        <v>10</v>
-      </c>
       <c r="H288" s="9" t="n"/>
       <c r="I288" s="9" t="n"/>
       <c r="K288" s="9" t="n"/>
     </row>
     <row r="289">
-      <c r="G289" t="n">
-        <v>10</v>
-      </c>
       <c r="H289" s="9" t="n"/>
       <c r="I289" s="9" t="n"/>
       <c r="K289" s="9" t="n"/>
     </row>
     <row r="290">
-      <c r="G290" t="n">
-        <v>10</v>
-      </c>
       <c r="H290" s="9" t="n"/>
       <c r="I290" s="9" t="n"/>
       <c r="K290" s="9" t="n"/>
     </row>
     <row r="291">
-      <c r="G291" t="n">
-        <v>10</v>
-      </c>
       <c r="H291" s="9" t="n"/>
       <c r="I291" s="9" t="n"/>
       <c r="K291" s="9" t="n"/>
     </row>
     <row r="292">
-      <c r="G292" t="n">
-        <v>10</v>
-      </c>
       <c r="H292" s="9" t="n"/>
       <c r="I292" s="9" t="n"/>
       <c r="K292" s="9" t="n"/>
     </row>
     <row r="293">
-      <c r="G293" t="n">
-        <v>10</v>
-      </c>
       <c r="H293" s="9" t="n"/>
       <c r="I293" s="9" t="n"/>
       <c r="K293" s="9" t="n"/>
     </row>
     <row r="294">
-      <c r="G294" t="n">
-        <v>10</v>
-      </c>
       <c r="H294" s="9" t="n"/>
       <c r="I294" s="9" t="n"/>
       <c r="K294" s="9" t="n"/>
     </row>
     <row r="295">
-      <c r="G295" t="n">
-        <v>10</v>
-      </c>
       <c r="H295" s="9" t="n"/>
       <c r="I295" s="9" t="n"/>
       <c r="K295" s="9" t="n"/>
     </row>
     <row r="296">
-      <c r="G296" t="n">
-        <v>10</v>
-      </c>
       <c r="H296" s="9" t="n"/>
       <c r="I296" s="9" t="n"/>
       <c r="K296" s="9" t="n"/>
     </row>
     <row r="297">
-      <c r="G297" t="n">
-        <v>10</v>
-      </c>
       <c r="H297" s="9" t="n"/>
       <c r="I297" s="9" t="n"/>
       <c r="K297" s="9" t="n"/>
     </row>
     <row r="298">
-      <c r="G298" t="n">
-        <v>10</v>
-      </c>
       <c r="H298" s="9" t="n"/>
       <c r="I298" s="9" t="n"/>
       <c r="K298" s="9" t="n"/>
     </row>
     <row r="299">
-      <c r="G299" t="n">
-        <v>10</v>
-      </c>
       <c r="H299" s="9" t="n"/>
       <c r="I299" s="9" t="n"/>
       <c r="K299" s="9" t="n"/>
     </row>
     <row r="300">
-      <c r="G300" t="n">
-        <v>10</v>
-      </c>
       <c r="H300" s="9" t="n"/>
       <c r="I300" s="9" t="n"/>
       <c r="K300" s="9" t="n"/>
     </row>
     <row r="301">
-      <c r="G301" t="n">
-        <v>10</v>
-      </c>
       <c r="H301" s="9" t="n"/>
       <c r="I301" s="9" t="n"/>
       <c r="K301" s="9" t="n"/>
     </row>
     <row r="302">
-      <c r="G302" t="n">
-        <v>10</v>
-      </c>
       <c r="H302" s="9" t="n"/>
       <c r="I302" s="9" t="n"/>
       <c r="K302" s="9" t="n"/>
     </row>
     <row r="303">
-      <c r="G303" t="n">
-        <v>10</v>
-      </c>
       <c r="H303" s="9" t="n"/>
       <c r="I303" s="9" t="n"/>
       <c r="K303" s="9" t="n"/>
     </row>
     <row r="304">
-      <c r="G304" t="n">
-        <v>10</v>
-      </c>
       <c r="H304" s="9" t="n"/>
       <c r="I304" s="9" t="n"/>
       <c r="K304" s="9" t="n"/>
     </row>
     <row r="305">
-      <c r="G305" t="n">
-        <v>10</v>
-      </c>
       <c r="H305" s="9" t="n"/>
       <c r="I305" s="9" t="n"/>
       <c r="K305" s="9" t="n"/>
     </row>
     <row r="306">
-      <c r="G306" t="n">
-        <v>10</v>
-      </c>
       <c r="H306" s="9" t="n"/>
       <c r="I306" s="9" t="n"/>
       <c r="K306" s="9" t="n"/>
     </row>
     <row r="307">
-      <c r="G307" t="n">
-        <v>10</v>
-      </c>
       <c r="H307" s="9" t="n"/>
       <c r="I307" s="9" t="n"/>
       <c r="K307" s="9" t="n"/>
     </row>
     <row r="308">
-      <c r="G308" t="n">
-        <v>10</v>
-      </c>
       <c r="H308" s="9" t="n"/>
       <c r="I308" s="9" t="n"/>
       <c r="K308" s="9" t="n"/>
     </row>
     <row r="309">
-      <c r="G309" t="n">
-        <v>10</v>
-      </c>
       <c r="H309" s="9" t="n"/>
       <c r="I309" s="9" t="n"/>
       <c r="K309" s="9" t="n"/>
     </row>
     <row r="310">
-      <c r="G310" t="n">
-        <v>10</v>
-      </c>
       <c r="H310" s="9" t="n"/>
       <c r="I310" s="9" t="n"/>
       <c r="K310" s="9" t="n"/>
     </row>
     <row r="311">
-      <c r="G311" t="n">
-        <v>10</v>
-      </c>
       <c r="H311" s="9" t="n"/>
       <c r="I311" s="9" t="n"/>
       <c r="K311" s="9" t="n"/>
     </row>
     <row r="312">
-      <c r="G312" t="n">
-        <v>10</v>
-      </c>
       <c r="H312" s="9" t="n"/>
       <c r="I312" s="9" t="n"/>
       <c r="K312" s="9" t="n"/>
     </row>
     <row r="313">
-      <c r="G313" t="n">
-        <v>10</v>
-      </c>
       <c r="H313" s="9" t="n"/>
       <c r="I313" s="9" t="n"/>
       <c r="K313" s="9" t="n"/>
     </row>
     <row r="314">
-      <c r="G314" t="n">
-        <v>10</v>
-      </c>
       <c r="H314" s="9" t="n"/>
       <c r="I314" s="9" t="n"/>
       <c r="K314" s="9" t="n"/>
     </row>
     <row r="315">
-      <c r="G315" t="n">
-        <v>10</v>
-      </c>
       <c r="H315" s="9" t="n"/>
       <c r="I315" s="9" t="n"/>
       <c r="K315" s="9" t="n"/>
     </row>
     <row r="316">
-      <c r="G316" t="n">
-        <v>10</v>
-      </c>
       <c r="H316" s="9" t="n"/>
       <c r="I316" s="9" t="n"/>
       <c r="K316" s="9" t="n"/>
     </row>
     <row r="317">
-      <c r="G317" t="n">
-        <v>10</v>
-      </c>
       <c r="H317" s="9" t="n"/>
       <c r="I317" s="9" t="n"/>
       <c r="K317" s="9" t="n"/>
     </row>
     <row r="318">
-      <c r="G318" t="n">
-        <v>10</v>
-      </c>
       <c r="H318" s="9" t="n"/>
       <c r="I318" s="9" t="n"/>
       <c r="K318" s="9" t="n"/>
     </row>
     <row r="319">
-      <c r="G319" t="n">
-        <v>10</v>
-      </c>
       <c r="H319" s="9" t="n"/>
       <c r="I319" s="9" t="n"/>
       <c r="K319" s="9" t="n"/>
     </row>
     <row r="320">
-      <c r="G320" t="n">
-        <v>10</v>
-      </c>
       <c r="H320" s="9" t="n"/>
       <c r="I320" s="9" t="n"/>
       <c r="K320" s="9" t="n"/>
     </row>
     <row r="321">
-      <c r="G321" t="n">
-        <v>10</v>
-      </c>
       <c r="H321" s="9" t="n"/>
       <c r="I321" s="9" t="n"/>
       <c r="K321" s="9" t="n"/>
     </row>
     <row r="322">
-      <c r="G322" t="n">
-        <v>10</v>
-      </c>
       <c r="H322" s="9" t="n"/>
       <c r="I322" s="9" t="n"/>
       <c r="K322" s="9" t="n"/>
     </row>
     <row r="323">
-      <c r="G323" t="n">
-        <v>10</v>
-      </c>
       <c r="H323" s="9" t="n"/>
       <c r="I323" s="9" t="n"/>
       <c r="K323" s="9" t="n"/>
     </row>
     <row r="324">
-      <c r="G324" t="n">
-        <v>10</v>
-      </c>
       <c r="H324" s="9" t="n"/>
       <c r="I324" s="9" t="n"/>
       <c r="K324" s="9" t="n"/>
     </row>
     <row r="325">
-      <c r="G325" t="n">
-        <v>10</v>
-      </c>
       <c r="H325" s="9" t="n"/>
       <c r="I325" s="9" t="n"/>
       <c r="K325" s="9" t="n"/>
     </row>
     <row r="326">
-      <c r="G326" t="n">
-        <v>10</v>
-      </c>
       <c r="H326" s="9" t="n"/>
       <c r="I326" s="9" t="n"/>
       <c r="K326" s="9" t="n"/>
     </row>
     <row r="327">
-      <c r="G327" t="n">
-        <v>10</v>
-      </c>
       <c r="H327" s="9" t="n"/>
       <c r="I327" s="9" t="n"/>
       <c r="K327" s="9" t="n"/>
     </row>
     <row r="328">
-      <c r="G328" t="n">
-        <v>10</v>
-      </c>
       <c r="H328" s="9" t="n"/>
       <c r="I328" s="9" t="n"/>
       <c r="K328" s="9" t="n"/>
     </row>
     <row r="329">
-      <c r="G329" t="n">
-        <v>10</v>
-      </c>
       <c r="H329" s="9" t="n"/>
       <c r="I329" s="9" t="n"/>
       <c r="K329" s="9" t="n"/>
     </row>
     <row r="330">
-      <c r="G330" t="n">
-        <v>10</v>
-      </c>
       <c r="H330" s="9" t="n"/>
       <c r="I330" s="9" t="n"/>
       <c r="K330" s="9" t="n"/>
     </row>
     <row r="331">
-      <c r="G331" t="n">
-        <v>10</v>
-      </c>
       <c r="H331" s="9" t="n"/>
       <c r="I331" s="9" t="n"/>
       <c r="K331" s="9" t="n"/>
     </row>
     <row r="332">
-      <c r="G332" t="n">
-        <v>10</v>
-      </c>
       <c r="H332" s="9" t="n"/>
       <c r="I332" s="9" t="n"/>
       <c r="K332" s="9" t="n"/>
     </row>
     <row r="333">
-      <c r="G333" t="n">
-        <v>10</v>
-      </c>
       <c r="H333" s="9" t="n"/>
       <c r="I333" s="9" t="n"/>
       <c r="K333" s="9" t="n"/>
     </row>
     <row r="334">
-      <c r="G334" t="n">
-        <v>10</v>
-      </c>
       <c r="H334" s="9" t="n"/>
       <c r="I334" s="9" t="n"/>
       <c r="K334" s="9" t="n"/>
     </row>
     <row r="335">
-      <c r="G335" t="n">
-        <v>10</v>
-      </c>
       <c r="H335" s="9" t="n"/>
       <c r="I335" s="9" t="n"/>
       <c r="K335" s="9" t="n"/>
     </row>
     <row r="336">
-      <c r="G336" t="n">
-        <v>10</v>
-      </c>
       <c r="H336" s="9" t="n"/>
       <c r="I336" s="9" t="n"/>
       <c r="K336" s="9" t="n"/>
     </row>
     <row r="337">
-      <c r="G337" t="n">
-        <v>10</v>
-      </c>
       <c r="H337" s="9" t="n"/>
       <c r="I337" s="9" t="n"/>
       <c r="K337" s="9" t="n"/>
     </row>
     <row r="338">
-      <c r="G338" t="n">
-        <v>10</v>
-      </c>
       <c r="H338" s="9" t="n"/>
       <c r="I338" s="9" t="n"/>
       <c r="K338" s="9" t="n"/>
     </row>
     <row r="339">
-      <c r="G339" t="n">
-        <v>10</v>
-      </c>
       <c r="H339" s="9" t="n"/>
       <c r="I339" s="9" t="n"/>
       <c r="K339" s="9" t="n"/>
     </row>
     <row r="340">
-      <c r="G340" t="n">
-        <v>10</v>
-      </c>
       <c r="H340" s="9" t="n"/>
       <c r="I340" s="9" t="n"/>
       <c r="K340" s="9" t="n"/>
     </row>
     <row r="341">
-      <c r="G341" t="n">
-        <v>10</v>
-      </c>
       <c r="H341" s="9" t="n"/>
       <c r="I341" s="9" t="n"/>
       <c r="K341" s="9" t="n"/>
     </row>
     <row r="342">
-      <c r="G342" t="n">
-        <v>10</v>
-      </c>
       <c r="H342" s="9" t="n"/>
       <c r="I342" s="9" t="n"/>
       <c r="K342" s="9" t="n"/>
     </row>
     <row r="343">
-      <c r="G343" t="n">
-        <v>10</v>
-      </c>
       <c r="H343" s="9" t="n"/>
       <c r="I343" s="9" t="n"/>
       <c r="K343" s="9" t="n"/>
     </row>
     <row r="344">
-      <c r="G344" t="n">
-        <v>10</v>
-      </c>
       <c r="H344" s="9" t="n"/>
       <c r="I344" s="9" t="n"/>
       <c r="K344" s="9" t="n"/>
     </row>
     <row r="345">
-      <c r="G345" t="n">
-        <v>10</v>
-      </c>
       <c r="H345" s="9" t="n"/>
       <c r="I345" s="9" t="n"/>
       <c r="K345" s="9" t="n"/>
     </row>
     <row r="346">
-      <c r="G346" t="n">
-        <v>10</v>
-      </c>
       <c r="H346" s="9" t="n"/>
       <c r="I346" s="9" t="n"/>
       <c r="K346" s="9" t="n"/>
     </row>
     <row r="347">
-      <c r="G347" t="n">
-        <v>10</v>
-      </c>
       <c r="H347" s="9" t="n"/>
       <c r="I347" s="9" t="n"/>
       <c r="K347" s="9" t="n"/>
     </row>
     <row r="348">
-      <c r="G348" t="n">
-        <v>10</v>
-      </c>
       <c r="H348" s="9" t="n"/>
       <c r="I348" s="9" t="n"/>
       <c r="K348" s="9" t="n"/>
     </row>
     <row r="349">
-      <c r="G349" t="n">
-        <v>10</v>
-      </c>
       <c r="H349" s="9" t="n"/>
       <c r="I349" s="9" t="n"/>
       <c r="K349" s="9" t="n"/>
     </row>
     <row r="350">
-      <c r="G350" t="n">
-        <v>10</v>
-      </c>
       <c r="H350" s="9" t="n"/>
       <c r="I350" s="9" t="n"/>
       <c r="K350" s="9" t="n"/>
     </row>
     <row r="351">
-      <c r="G351" t="n">
-        <v>10</v>
-      </c>
       <c r="H351" s="9" t="n"/>
       <c r="I351" s="9" t="n"/>
       <c r="K351" s="9" t="n"/>
     </row>
     <row r="352">
-      <c r="G352" t="n">
-        <v>10</v>
-      </c>
       <c r="H352" s="9" t="n"/>
       <c r="I352" s="9" t="n"/>
       <c r="K352" s="9" t="n"/>
     </row>
     <row r="353">
-      <c r="G353" t="n">
-        <v>10</v>
-      </c>
       <c r="H353" s="9" t="n"/>
       <c r="I353" s="9" t="n"/>
       <c r="K353" s="9" t="n"/>
     </row>
     <row r="354">
-      <c r="G354" t="n">
-        <v>10</v>
-      </c>
       <c r="H354" s="9" t="n"/>
       <c r="I354" s="9" t="n"/>
       <c r="K354" s="9" t="n"/>
     </row>
     <row r="355">
-      <c r="G355" t="n">
-        <v>10</v>
-      </c>
       <c r="H355" s="9" t="n"/>
       <c r="I355" s="9" t="n"/>
       <c r="K355" s="9" t="n"/>
     </row>
     <row r="356">
-      <c r="G356" t="n">
-        <v>10</v>
-      </c>
       <c r="H356" s="9" t="n"/>
       <c r="I356" s="9" t="n"/>
       <c r="K356" s="9" t="n"/>
     </row>
     <row r="357">
-      <c r="G357" t="n">
-        <v>10</v>
-      </c>
       <c r="H357" s="9" t="n"/>
       <c r="I357" s="9" t="n"/>
       <c r="K357" s="9" t="n"/>
     </row>
     <row r="358">
-      <c r="G358" t="n">
-        <v>10</v>
-      </c>
       <c r="H358" s="9" t="n"/>
       <c r="I358" s="9" t="n"/>
       <c r="K358" s="9" t="n"/>
     </row>
     <row r="359">
-      <c r="G359" t="n">
-        <v>10</v>
-      </c>
       <c r="H359" s="9" t="n"/>
       <c r="I359" s="9" t="n"/>
       <c r="K359" s="9" t="n"/>
     </row>
     <row r="360">
-      <c r="G360" t="n">
-        <v>10</v>
-      </c>
       <c r="H360" s="9" t="n"/>
       <c r="I360" s="9" t="n"/>
       <c r="K360" s="9" t="n"/>
     </row>
     <row r="361">
-      <c r="G361" t="n">
-        <v>10</v>
-      </c>
       <c r="H361" s="9" t="n"/>
       <c r="I361" s="9" t="n"/>
       <c r="K361" s="9" t="n"/>
     </row>
     <row r="362">
-      <c r="G362" t="n">
-        <v>10</v>
-      </c>
       <c r="H362" s="9" t="n"/>
       <c r="I362" s="9" t="n"/>
       <c r="K362" s="9" t="n"/>
     </row>
     <row r="363">
-      <c r="G363" t="n">
-        <v>10</v>
-      </c>
       <c r="H363" s="9" t="n"/>
       <c r="I363" s="9" t="n"/>
       <c r="K363" s="9" t="n"/>
     </row>
     <row r="364">
-      <c r="G364" t="n">
-        <v>10</v>
-      </c>
       <c r="H364" s="9" t="n"/>
       <c r="I364" s="9" t="n"/>
       <c r="K364" s="9" t="n"/>
     </row>
     <row r="365">
-      <c r="G365" t="n">
-        <v>10</v>
-      </c>
       <c r="H365" s="9" t="n"/>
       <c r="I365" s="9" t="n"/>
       <c r="K365" s="9" t="n"/>
     </row>
     <row r="366">
-      <c r="G366" t="n">
-        <v>10</v>
-      </c>
       <c r="H366" s="9" t="n"/>
       <c r="I366" s="9" t="n"/>
       <c r="K366" s="9" t="n"/>
     </row>
     <row r="367">
-      <c r="G367" t="n">
-        <v>10</v>
-      </c>
       <c r="H367" s="9" t="n"/>
       <c r="I367" s="9" t="n"/>
       <c r="K367" s="9" t="n"/>
     </row>
     <row r="368">
-      <c r="G368" t="n">
-        <v>10</v>
-      </c>
       <c r="H368" s="9" t="n"/>
       <c r="I368" s="9" t="n"/>
       <c r="K368" s="9" t="n"/>
     </row>
     <row r="369">
-      <c r="G369" t="n">
-        <v>10</v>
-      </c>
       <c r="H369" s="9" t="n"/>
       <c r="I369" s="9" t="n"/>
       <c r="K369" s="9" t="n"/>
     </row>
     <row r="370">
-      <c r="G370" t="n">
-        <v>10</v>
-      </c>
       <c r="H370" s="9" t="n"/>
       <c r="I370" s="9" t="n"/>
       <c r="K370" s="9" t="n"/>
     </row>
     <row r="371">
-      <c r="G371" t="n">
-        <v>10</v>
-      </c>
       <c r="H371" s="9" t="n"/>
       <c r="I371" s="9" t="n"/>
       <c r="K371" s="9" t="n"/>
     </row>
     <row r="372">
-      <c r="G372" t="n">
-        <v>10</v>
-      </c>
       <c r="H372" s="9" t="n"/>
       <c r="I372" s="9" t="n"/>
       <c r="K372" s="9" t="n"/>
     </row>
     <row r="373">
-      <c r="G373" t="n">
-        <v>10</v>
-      </c>
       <c r="H373" s="9" t="n"/>
       <c r="I373" s="9" t="n"/>
       <c r="K373" s="9" t="n"/>
     </row>
     <row r="374">
-      <c r="G374" t="n">
-        <v>10</v>
-      </c>
       <c r="H374" s="9" t="n"/>
       <c r="I374" s="9" t="n"/>
       <c r="K374" s="9" t="n"/>
     </row>
     <row r="375">
-      <c r="G375" t="n">
-        <v>10</v>
-      </c>
       <c r="H375" s="9" t="n"/>
       <c r="I375" s="9" t="n"/>
       <c r="K375" s="9" t="n"/>
     </row>
     <row r="376">
-      <c r="G376" t="n">
-        <v>10</v>
-      </c>
       <c r="H376" s="9" t="n"/>
       <c r="I376" s="9" t="n"/>
       <c r="K376" s="9" t="n"/>
     </row>
     <row r="377">
-      <c r="G377" t="n">
-        <v>10</v>
-      </c>
       <c r="H377" s="9" t="n"/>
       <c r="I377" s="9" t="n"/>
       <c r="K377" s="9" t="n"/>
     </row>
     <row r="378">
-      <c r="G378" t="n">
-        <v>10</v>
-      </c>
       <c r="H378" s="9" t="n"/>
       <c r="I378" s="9" t="n"/>
       <c r="K378" s="9" t="n"/>
     </row>
     <row r="379">
-      <c r="G379" t="n">
-        <v>10</v>
-      </c>
       <c r="H379" s="9" t="n"/>
       <c r="I379" s="9" t="n"/>
       <c r="K379" s="9" t="n"/>
     </row>
     <row r="380">
-      <c r="G380" t="n">
-        <v>10</v>
-      </c>
       <c r="H380" s="9" t="n"/>
       <c r="I380" s="9" t="n"/>
       <c r="K380" s="9" t="n"/>
     </row>
     <row r="381">
-      <c r="G381" t="n">
-        <v>10</v>
-      </c>
       <c r="H381" s="9" t="n"/>
       <c r="I381" s="9" t="n"/>
       <c r="K381" s="9" t="n"/>
     </row>
     <row r="382">
-      <c r="G382" t="n">
-        <v>10</v>
-      </c>
       <c r="H382" s="9" t="n"/>
       <c r="I382" s="9" t="n"/>
       <c r="K382" s="9" t="n"/>
     </row>
     <row r="383">
-      <c r="G383" t="n">
-        <v>10</v>
-      </c>
       <c r="H383" s="9" t="n"/>
       <c r="I383" s="9" t="n"/>
       <c r="K383" s="9" t="n"/>
     </row>
     <row r="384">
-      <c r="G384" t="n">
-        <v>10</v>
-      </c>
       <c r="H384" s="9" t="n"/>
       <c r="I384" s="9" t="n"/>
       <c r="K384" s="9" t="n"/>
     </row>
     <row r="385">
-      <c r="G385" t="n">
-        <v>10</v>
-      </c>
       <c r="H385" s="9" t="n"/>
       <c r="I385" s="9" t="n"/>
       <c r="K385" s="9" t="n"/>
     </row>
     <row r="386">
-      <c r="G386" t="n">
-        <v>10</v>
-      </c>
       <c r="H386" s="9" t="n"/>
       <c r="I386" s="9" t="n"/>
       <c r="K386" s="9" t="n"/>
     </row>
     <row r="387">
-      <c r="G387" t="n">
-        <v>10</v>
-      </c>
       <c r="H387" s="9" t="n"/>
       <c r="I387" s="9" t="n"/>
       <c r="K387" s="9" t="n"/>
     </row>
     <row r="388">
-      <c r="G388" t="n">
-        <v>10</v>
-      </c>
       <c r="H388" s="9" t="n"/>
       <c r="I388" s="9" t="n"/>
       <c r="K388" s="9" t="n"/>
     </row>
     <row r="389">
-      <c r="G389" t="n">
-        <v>10</v>
-      </c>
       <c r="H389" s="9" t="n"/>
       <c r="I389" s="9" t="n"/>
       <c r="K389" s="9" t="n"/>
     </row>
     <row r="390">
-      <c r="G390" t="n">
-        <v>10</v>
-      </c>
       <c r="H390" s="9" t="n"/>
       <c r="I390" s="9" t="n"/>
       <c r="K390" s="9" t="n"/>
     </row>
     <row r="391">
-      <c r="G391" t="n">
-        <v>10</v>
-      </c>
       <c r="H391" s="9" t="n"/>
       <c r="I391" s="9" t="n"/>
       <c r="K391" s="9" t="n"/>
     </row>
     <row r="392">
-      <c r="G392" t="n">
-        <v>10</v>
-      </c>
       <c r="H392" s="9" t="n"/>
       <c r="I392" s="9" t="n"/>
       <c r="K392" s="9" t="n"/>
     </row>
     <row r="393">
-      <c r="G393" t="n">
-        <v>10</v>
-      </c>
       <c r="H393" s="9" t="n"/>
       <c r="I393" s="9" t="n"/>
       <c r="K393" s="9" t="n"/>
     </row>
     <row r="394">
-      <c r="G394" t="n">
-        <v>10</v>
-      </c>
       <c r="H394" s="9" t="n"/>
       <c r="I394" s="9" t="n"/>
       <c r="K394" s="9" t="n"/>
     </row>
     <row r="395">
-      <c r="G395" t="n">
-        <v>10</v>
-      </c>
       <c r="H395" s="9" t="n"/>
       <c r="I395" s="9" t="n"/>
       <c r="K395" s="9" t="n"/>
     </row>
     <row r="396">
-      <c r="G396" t="n">
-        <v>10</v>
-      </c>
       <c r="H396" s="9" t="n"/>
       <c r="I396" s="9" t="n"/>
       <c r="K396" s="9" t="n"/>
     </row>
     <row r="397">
-      <c r="G397" t="n">
-        <v>10</v>
-      </c>
       <c r="H397" s="9" t="n"/>
       <c r="I397" s="9" t="n"/>
       <c r="K397" s="9" t="n"/>
     </row>
     <row r="398">
-      <c r="G398" t="n">
-        <v>10</v>
-      </c>
       <c r="H398" s="9" t="n"/>
       <c r="I398" s="9" t="n"/>
       <c r="K398" s="9" t="n"/>
     </row>
     <row r="399">
-      <c r="G399" t="n">
-        <v>10</v>
-      </c>
       <c r="H399" s="9" t="n"/>
       <c r="I399" s="9" t="n"/>
       <c r="K399" s="9" t="n"/>
     </row>
     <row r="400">
-      <c r="G400" t="n">
-        <v>10</v>
-      </c>
       <c r="H400" s="9" t="n"/>
       <c r="I400" s="9" t="n"/>
       <c r="K400" s="9" t="n"/>
     </row>
     <row r="401">
-      <c r="G401" t="n">
-        <v>10</v>
-      </c>
       <c r="H401" s="9" t="n"/>
       <c r="I401" s="9" t="n"/>
       <c r="K401" s="9" t="n"/>
     </row>
     <row r="402">
-      <c r="G402" t="n">
-        <v>10</v>
-      </c>
       <c r="H402" s="9" t="n"/>
       <c r="I402" s="9" t="n"/>
       <c r="K402" s="9" t="n"/>
     </row>
     <row r="403">
-      <c r="G403" t="n">
-        <v>10</v>
-      </c>
       <c r="H403" s="9" t="n"/>
       <c r="I403" s="9" t="n"/>
       <c r="K403" s="9" t="n"/>
     </row>
     <row r="404">
-      <c r="G404" t="n">
-        <v>10</v>
-      </c>
       <c r="H404" s="9" t="n"/>
       <c r="I404" s="9" t="n"/>
       <c r="K404" s="9" t="n"/>
     </row>
     <row r="405">
-      <c r="G405" t="n">
-        <v>10</v>
-      </c>
       <c r="H405" s="9" t="n"/>
       <c r="I405" s="9" t="n"/>
       <c r="K405" s="9" t="n"/>
     </row>
     <row r="406">
-      <c r="G406" t="n">
-        <v>10</v>
-      </c>
       <c r="H406" s="9" t="n"/>
       <c r="I406" s="9" t="n"/>
       <c r="K406" s="9" t="n"/>
     </row>
     <row r="407">
-      <c r="G407" t="n">
-        <v>10</v>
-      </c>
       <c r="H407" s="9" t="n"/>
       <c r="I407" s="9" t="n"/>
       <c r="K407" s="9" t="n"/>
     </row>
     <row r="408">
-      <c r="G408" t="n">
-        <v>10</v>
-      </c>
       <c r="H408" s="9" t="n"/>
       <c r="I408" s="9" t="n"/>
       <c r="K408" s="9" t="n"/>
     </row>
     <row r="409">
-      <c r="G409" t="n">
-        <v>10</v>
-      </c>
       <c r="H409" s="9" t="n"/>
       <c r="I409" s="9" t="n"/>
       <c r="K409" s="9" t="n"/>
     </row>
     <row r="410">
-      <c r="G410" t="n">
-        <v>10</v>
-      </c>
       <c r="H410" s="9" t="n"/>
       <c r="I410" s="9" t="n"/>
       <c r="K410" s="9" t="n"/>
     </row>
     <row r="411">
-      <c r="G411" t="n">
-        <v>10</v>
-      </c>
       <c r="H411" s="9" t="n"/>
       <c r="I411" s="9" t="n"/>
       <c r="K411" s="9" t="n"/>
     </row>
     <row r="412">
-      <c r="G412" t="n">
-        <v>10</v>
-      </c>
       <c r="H412" s="9" t="n"/>
       <c r="I412" s="9" t="n"/>
       <c r="K412" s="9" t="n"/>
     </row>
     <row r="413">
-      <c r="G413" t="n">
-        <v>10</v>
-      </c>
       <c r="H413" s="9" t="n"/>
       <c r="I413" s="9" t="n"/>
       <c r="K413" s="9" t="n"/>
     </row>
     <row r="414">
-      <c r="G414" t="n">
-        <v>10</v>
-      </c>
       <c r="H414" s="9" t="n"/>
       <c r="I414" s="9" t="n"/>
       <c r="K414" s="9" t="n"/>
     </row>
     <row r="415">
-      <c r="G415" t="n">
-        <v>10</v>
-      </c>
       <c r="H415" s="9" t="n"/>
       <c r="I415" s="9" t="n"/>
       <c r="K415" s="9" t="n"/>
     </row>
     <row r="416">
-      <c r="G416" t="n">
-        <v>10</v>
-      </c>
       <c r="H416" s="9" t="n"/>
       <c r="I416" s="9" t="n"/>
       <c r="K416" s="9" t="n"/>
     </row>
     <row r="417">
-      <c r="G417" t="n">
-        <v>10</v>
-      </c>
       <c r="H417" s="9" t="n"/>
       <c r="I417" s="9" t="n"/>
       <c r="K417" s="9" t="n"/>
     </row>
     <row r="418">
-      <c r="G418" t="n">
-        <v>10</v>
-      </c>
       <c r="H418" s="9" t="n"/>
       <c r="I418" s="9" t="n"/>
       <c r="K418" s="9" t="n"/>
     </row>
     <row r="419">
-      <c r="G419" t="n">
-        <v>10</v>
-      </c>
       <c r="H419" s="9" t="n"/>
       <c r="I419" s="9" t="n"/>
       <c r="K419" s="9" t="n"/>
     </row>
     <row r="420">
-      <c r="G420" t="n">
-        <v>10</v>
-      </c>
       <c r="H420" s="9" t="n"/>
       <c r="I420" s="9" t="n"/>
       <c r="K420" s="9" t="n"/>
     </row>
     <row r="421">
-      <c r="G421" t="n">
-        <v>10</v>
-      </c>
       <c r="H421" s="9" t="n"/>
       <c r="I421" s="9" t="n"/>
       <c r="K421" s="9" t="n"/>
     </row>
     <row r="422">
-      <c r="G422" t="n">
-        <v>10</v>
-      </c>
       <c r="H422" s="9" t="n"/>
       <c r="I422" s="9" t="n"/>
       <c r="K422" s="9" t="n"/>
     </row>
     <row r="423">
-      <c r="G423" t="n">
-        <v>10</v>
-      </c>
       <c r="H423" s="9" t="n"/>
       <c r="I423" s="9" t="n"/>
       <c r="K423" s="9" t="n"/>
     </row>
     <row r="424">
-      <c r="G424" t="n">
-        <v>10</v>
-      </c>
       <c r="H424" s="9" t="n"/>
       <c r="I424" s="9" t="n"/>
       <c r="K424" s="9" t="n"/>
     </row>
     <row r="425">
-      <c r="G425" t="n">
-        <v>10</v>
-      </c>
       <c r="H425" s="9" t="n"/>
       <c r="I425" s="9" t="n"/>
       <c r="K425" s="9" t="n"/>
     </row>
     <row r="426">
-      <c r="G426" t="n">
-        <v>10</v>
-      </c>
       <c r="H426" s="9" t="n"/>
       <c r="I426" s="9" t="n"/>
       <c r="K426" s="9" t="n"/>
     </row>
     <row r="427">
-      <c r="G427" t="n">
-        <v>10</v>
-      </c>
       <c r="H427" s="9" t="n"/>
       <c r="I427" s="9" t="n"/>
       <c r="K427" s="9" t="n"/>
     </row>
     <row r="428">
-      <c r="G428" t="n">
-        <v>10</v>
-      </c>
       <c r="H428" s="9" t="n"/>
       <c r="I428" s="9" t="n"/>
       <c r="K428" s="9" t="n"/>
     </row>
     <row r="429">
-      <c r="G429" t="n">
-        <v>10</v>
-      </c>
       <c r="H429" s="9" t="n"/>
       <c r="I429" s="9" t="n"/>
       <c r="K429" s="9" t="n"/>
     </row>
     <row r="430">
-      <c r="G430" t="n">
-        <v>10</v>
-      </c>
       <c r="H430" s="9" t="n"/>
       <c r="I430" s="9" t="n"/>
       <c r="K430" s="9" t="n"/>
     </row>
     <row r="431">
-      <c r="G431" t="n">
-        <v>10</v>
-      </c>
       <c r="H431" s="9" t="n"/>
       <c r="I431" s="9" t="n"/>
       <c r="K431" s="9" t="n"/>
     </row>
     <row r="432">
-      <c r="G432" t="n">
-        <v>10</v>
-      </c>
       <c r="H432" s="9" t="n"/>
       <c r="I432" s="9" t="n"/>
       <c r="K432" s="9" t="n"/>
     </row>
     <row r="433">
-      <c r="G433" t="n">
-        <v>10</v>
-      </c>
       <c r="H433" s="9" t="n"/>
       <c r="I433" s="9" t="n"/>
       <c r="K433" s="9" t="n"/>
     </row>
     <row r="434">
-      <c r="G434" t="n">
-        <v>10</v>
-      </c>
       <c r="H434" s="9" t="n"/>
       <c r="I434" s="9" t="n"/>
       <c r="K434" s="9" t="n"/>
     </row>
     <row r="435">
-      <c r="G435" t="n">
-        <v>10</v>
-      </c>
       <c r="H435" s="9" t="n"/>
       <c r="I435" s="9" t="n"/>
       <c r="K435" s="9" t="n"/>
     </row>
     <row r="436">
-      <c r="G436" t="n">
-        <v>10</v>
-      </c>
       <c r="H436" s="9" t="n"/>
       <c r="I436" s="9" t="n"/>
       <c r="K436" s="9" t="n"/>
     </row>
     <row r="437">
-      <c r="G437" t="n">
-        <v>10</v>
-      </c>
       <c r="H437" s="9" t="n"/>
       <c r="I437" s="9" t="n"/>
       <c r="K437" s="9" t="n"/>
     </row>
     <row r="438">
-      <c r="G438" t="n">
-        <v>10</v>
-      </c>
       <c r="H438" s="9" t="n"/>
       <c r="I438" s="9" t="n"/>
       <c r="K438" s="9" t="n"/>
     </row>
     <row r="439">
-      <c r="G439" t="n">
-        <v>10</v>
-      </c>
       <c r="H439" s="9" t="n"/>
       <c r="I439" s="9" t="n"/>
       <c r="K439" s="9" t="n"/>
     </row>
     <row r="440">
-      <c r="G440" t="n">
-        <v>10</v>
-      </c>
       <c r="H440" s="9" t="n"/>
       <c r="I440" s="9" t="n"/>
       <c r="K440" s="9" t="n"/>
     </row>
     <row r="441">
-      <c r="G441" t="n">
-        <v>10</v>
-      </c>
       <c r="H441" s="9" t="n"/>
       <c r="I441" s="9" t="n"/>
       <c r="K441" s="9" t="n"/>
     </row>
     <row r="442">
-      <c r="G442" t="n">
-        <v>10</v>
-      </c>
       <c r="H442" s="9" t="n"/>
       <c r="I442" s="9" t="n"/>
       <c r="K442" s="9" t="n"/>
     </row>
     <row r="443">
-      <c r="G443" t="n">
-        <v>10</v>
-      </c>
       <c r="H443" s="9" t="n"/>
       <c r="I443" s="9" t="n"/>
       <c r="K443" s="9" t="n"/>
     </row>
     <row r="444">
-      <c r="G444" t="n">
-        <v>10</v>
-      </c>
       <c r="H444" s="9" t="n"/>
       <c r="I444" s="9" t="n"/>
       <c r="K444" s="9" t="n"/>
     </row>
     <row r="445">
-      <c r="G445" t="n">
-        <v>10</v>
-      </c>
       <c r="H445" s="9" t="n"/>
       <c r="I445" s="9" t="n"/>
       <c r="K445" s="9" t="n"/>
     </row>
     <row r="446">
-      <c r="G446" t="n">
-        <v>10</v>
-      </c>
       <c r="H446" s="9" t="n"/>
       <c r="I446" s="9" t="n"/>
       <c r="K446" s="9" t="n"/>
     </row>
     <row r="447">
-      <c r="G447" t="n">
-        <v>10</v>
-      </c>
       <c r="H447" s="9" t="n"/>
       <c r="I447" s="9" t="n"/>
       <c r="K447" s="9" t="n"/>
     </row>
     <row r="448">
-      <c r="G448" t="n">
-        <v>10</v>
-      </c>
       <c r="H448" s="9" t="n"/>
       <c r="I448" s="9" t="n"/>
       <c r="K448" s="9" t="n"/>
     </row>
     <row r="449">
-      <c r="G449" t="n">
-        <v>10</v>
-      </c>
       <c r="H449" s="9" t="n"/>
       <c r="I449" s="9" t="n"/>
       <c r="K449" s="9" t="n"/>
     </row>
     <row r="450">
-      <c r="G450" t="n">
-        <v>10</v>
-      </c>
       <c r="H450" s="9" t="n"/>
       <c r="I450" s="9" t="n"/>
       <c r="K450" s="9" t="n"/>
     </row>
     <row r="451">
-      <c r="G451" t="n">
-        <v>10</v>
-      </c>
       <c r="H451" s="9" t="n"/>
       <c r="I451" s="9" t="n"/>
       <c r="K451" s="9" t="n"/>
     </row>
     <row r="452">
-      <c r="G452" t="n">
-        <v>10</v>
-      </c>
       <c r="H452" s="9" t="n"/>
       <c r="I452" s="9" t="n"/>
       <c r="K452" s="9" t="n"/>
     </row>
     <row r="453">
-      <c r="G453" t="n">
-        <v>10</v>
-      </c>
       <c r="H453" s="9" t="n"/>
       <c r="I453" s="9" t="n"/>
       <c r="K453" s="9" t="n"/>
     </row>
     <row r="454">
-      <c r="G454" t="n">
-        <v>10</v>
-      </c>
       <c r="H454" s="9" t="n"/>
       <c r="I454" s="9" t="n"/>
       <c r="K454" s="9" t="n"/>
     </row>
     <row r="455">
-      <c r="G455" t="n">
-        <v>10</v>
-      </c>
       <c r="H455" s="9" t="n"/>
       <c r="I455" s="9" t="n"/>
       <c r="K455" s="9" t="n"/>
     </row>
     <row r="456">
-      <c r="G456" t="n">
-        <v>10</v>
-      </c>
       <c r="H456" s="9" t="n"/>
       <c r="I456" s="9" t="n"/>
       <c r="K456" s="9" t="n"/>
     </row>
     <row r="457">
-      <c r="G457" t="n">
-        <v>10</v>
-      </c>
       <c r="H457" s="9" t="n"/>
       <c r="I457" s="9" t="n"/>
       <c r="K457" s="9" t="n"/>
     </row>
     <row r="458">
-      <c r="G458" t="n">
-        <v>10</v>
-      </c>
       <c r="H458" s="9" t="n"/>
       <c r="I458" s="9" t="n"/>
       <c r="K458" s="9" t="n"/>
     </row>
     <row r="459">
-      <c r="G459" t="n">
-        <v>10</v>
-      </c>
       <c r="H459" s="9" t="n"/>
       <c r="I459" s="9" t="n"/>
       <c r="K459" s="9" t="n"/>
     </row>
     <row r="460">
-      <c r="G460" t="n">
-        <v>10</v>
-      </c>
       <c r="H460" s="9" t="n"/>
       <c r="I460" s="9" t="n"/>
       <c r="K460" s="9" t="n"/>
     </row>
     <row r="461">
-      <c r="G461" t="n">
-        <v>10</v>
-      </c>
       <c r="H461" s="9" t="n"/>
       <c r="I461" s="9" t="n"/>
       <c r="K461" s="9" t="n"/>
     </row>
     <row r="462">
-      <c r="G462" t="n">
-        <v>10</v>
-      </c>
       <c r="H462" s="9" t="n"/>
       <c r="I462" s="9" t="n"/>
       <c r="K462" s="9" t="n"/>
     </row>
     <row r="463">
-      <c r="G463" t="n">
-        <v>10</v>
-      </c>
       <c r="H463" s="9" t="n"/>
       <c r="I463" s="9" t="n"/>
       <c r="K463" s="9" t="n"/>
     </row>
     <row r="464">
-      <c r="G464" t="n">
-        <v>10</v>
-      </c>
       <c r="H464" s="9" t="n"/>
       <c r="I464" s="9" t="n"/>
       <c r="K464" s="9" t="n"/>
     </row>
     <row r="465">
-      <c r="G465" t="n">
-        <v>10</v>
-      </c>
       <c r="H465" s="9" t="n"/>
       <c r="I465" s="9" t="n"/>
       <c r="K465" s="9" t="n"/>
     </row>
     <row r="466">
-      <c r="G466" t="n">
-        <v>10</v>
-      </c>
       <c r="H466" s="9" t="n"/>
       <c r="I466" s="9" t="n"/>
       <c r="K466" s="9" t="n"/>
     </row>
     <row r="467">
-      <c r="G467" t="n">
-        <v>10</v>
-      </c>
       <c r="H467" s="9" t="n"/>
       <c r="I467" s="9" t="n"/>
       <c r="K467" s="9" t="n"/>
     </row>
     <row r="468">
-      <c r="G468" t="n">
-        <v>10</v>
-      </c>
       <c r="H468" s="9" t="n"/>
       <c r="I468" s="9" t="n"/>
       <c r="K468" s="9" t="n"/>
     </row>
     <row r="469">
-      <c r="G469" t="n">
-        <v>10</v>
-      </c>
       <c r="H469" s="9" t="n"/>
       <c r="I469" s="9" t="n"/>
       <c r="K469" s="9" t="n"/>
     </row>
     <row r="470">
-      <c r="G470" t="n">
-        <v>10</v>
-      </c>
       <c r="H470" s="9" t="n"/>
       <c r="I470" s="9" t="n"/>
       <c r="K470" s="9" t="n"/>
     </row>
     <row r="471">
-      <c r="G471" t="n">
-        <v>10</v>
-      </c>
       <c r="H471" s="9" t="n"/>
       <c r="I471" s="9" t="n"/>
       <c r="K471" s="9" t="n"/>
     </row>
     <row r="472">
-      <c r="G472" t="n">
-        <v>10</v>
-      </c>
       <c r="H472" s="9" t="n"/>
       <c r="I472" s="9" t="n"/>
       <c r="K472" s="9" t="n"/>
     </row>
     <row r="473">
-      <c r="G473" t="n">
-        <v>10</v>
-      </c>
       <c r="H473" s="9" t="n"/>
       <c r="I473" s="9" t="n"/>
       <c r="K473" s="9" t="n"/>
     </row>
     <row r="474">
-      <c r="G474" t="n">
-        <v>10</v>
-      </c>
       <c r="H474" s="9" t="n"/>
       <c r="I474" s="9" t="n"/>
       <c r="K474" s="9" t="n"/>
     </row>
     <row r="475">
-      <c r="G475" t="n">
-        <v>10</v>
-      </c>
       <c r="H475" s="9" t="n"/>
       <c r="I475" s="9" t="n"/>
       <c r="K475" s="9" t="n"/>
     </row>
     <row r="476">
-      <c r="G476" t="n">
-        <v>10</v>
-      </c>
       <c r="H476" s="9" t="n"/>
       <c r="I476" s="9" t="n"/>
       <c r="K476" s="9" t="n"/>
     </row>
     <row r="477">
-      <c r="G477" t="n">
-        <v>10</v>
-      </c>
       <c r="H477" s="9" t="n"/>
       <c r="I477" s="9" t="n"/>
       <c r="K477" s="9" t="n"/>
     </row>
     <row r="478">
-      <c r="G478" t="n">
-        <v>10</v>
-      </c>
       <c r="H478" s="9" t="n"/>
       <c r="I478" s="9" t="n"/>
       <c r="K478" s="9" t="n"/>
     </row>
     <row r="479">
-      <c r="G479" t="n">
-        <v>10</v>
-      </c>
       <c r="H479" s="9" t="n"/>
       <c r="I479" s="9" t="n"/>
       <c r="K479" s="9" t="n"/>
     </row>
     <row r="480">
-      <c r="G480" t="n">
-        <v>10</v>
-      </c>
       <c r="H480" s="9" t="n"/>
       <c r="I480" s="9" t="n"/>
       <c r="K480" s="9" t="n"/>
     </row>
     <row r="481">
-      <c r="G481" t="n">
-        <v>10</v>
-      </c>
       <c r="H481" s="9" t="n"/>
       <c r="I481" s="9" t="n"/>
       <c r="K481" s="9" t="n"/>
     </row>
     <row r="482">
-      <c r="G482" t="n">
-        <v>10</v>
-      </c>
       <c r="H482" s="9" t="n"/>
       <c r="I482" s="9" t="n"/>
       <c r="K482" s="9" t="n"/>
     </row>
     <row r="483">
-      <c r="G483" t="n">
-        <v>10</v>
-      </c>
       <c r="H483" s="9" t="n"/>
       <c r="I483" s="9" t="n"/>
       <c r="K483" s="9" t="n"/>
     </row>
     <row r="484">
-      <c r="G484" t="n">
-        <v>10</v>
-      </c>
       <c r="H484" s="9" t="n"/>
       <c r="I484" s="9" t="n"/>
       <c r="K484" s="9" t="n"/>
     </row>
     <row r="485">
-      <c r="G485" t="n">
-        <v>10</v>
-      </c>
       <c r="H485" s="9" t="n"/>
       <c r="I485" s="9" t="n"/>
       <c r="K485" s="9" t="n"/>
     </row>
     <row r="486">
-      <c r="G486" t="n">
-        <v>10</v>
-      </c>
       <c r="H486" s="9" t="n"/>
       <c r="I486" s="9" t="n"/>
       <c r="K486" s="9" t="n"/>
     </row>
     <row r="487">
-      <c r="G487" t="n">
-        <v>10</v>
-      </c>
       <c r="H487" s="9" t="n"/>
       <c r="I487" s="9" t="n"/>
       <c r="K487" s="9" t="n"/>
     </row>
     <row r="488">
-      <c r="G488" t="n">
-        <v>10</v>
-      </c>
       <c r="H488" s="9" t="n"/>
       <c r="I488" s="9" t="n"/>
       <c r="K488" s="9" t="n"/>
     </row>
     <row r="489">
-      <c r="G489" t="n">
-        <v>10</v>
-      </c>
       <c r="H489" s="9" t="n"/>
       <c r="I489" s="9" t="n"/>
       <c r="K489" s="9" t="n"/>
     </row>
     <row r="490">
-      <c r="G490" t="n">
-        <v>10</v>
-      </c>
       <c r="H490" s="9" t="n"/>
       <c r="I490" s="9" t="n"/>
       <c r="K490" s="9" t="n"/>
     </row>
     <row r="491">
-      <c r="G491" t="n">
-        <v>10</v>
-      </c>
       <c r="H491" s="9" t="n"/>
       <c r="I491" s="9" t="n"/>
       <c r="K491" s="9" t="n"/>
     </row>
     <row r="492">
-      <c r="G492" t="n">
-        <v>10</v>
-      </c>
       <c r="H492" s="9" t="n"/>
       <c r="I492" s="9" t="n"/>
       <c r="K492" s="9" t="n"/>
     </row>
     <row r="493">
-      <c r="G493" t="n">
-        <v>10</v>
-      </c>
       <c r="H493" s="9" t="n"/>
       <c r="I493" s="9" t="n"/>
       <c r="K493" s="9" t="n"/>
     </row>
     <row r="494">
-      <c r="G494" t="n">
-        <v>10</v>
-      </c>
       <c r="H494" s="9" t="n"/>
       <c r="I494" s="9" t="n"/>
       <c r="K494" s="9" t="n"/>
     </row>
     <row r="495">
-      <c r="G495" t="n">
-        <v>10</v>
-      </c>
       <c r="H495" s="9" t="n"/>
       <c r="I495" s="9" t="n"/>
       <c r="K495" s="9" t="n"/>
     </row>
     <row r="496">
-      <c r="G496" t="n">
-        <v>10</v>
-      </c>
       <c r="H496" s="9" t="n"/>
       <c r="I496" s="9" t="n"/>
       <c r="K496" s="9" t="n"/>
     </row>
     <row r="497">
-      <c r="G497" t="n">
-        <v>10</v>
-      </c>
       <c r="H497" s="9" t="n"/>
       <c r="I497" s="9" t="n"/>
       <c r="K497" s="9" t="n"/>
     </row>
     <row r="498">
-      <c r="G498" t="n">
-        <v>10</v>
-      </c>
       <c r="H498" s="9" t="n"/>
       <c r="I498" s="9" t="n"/>
       <c r="K498" s="9" t="n"/>
     </row>
     <row r="499">
-      <c r="G499" t="n">
-        <v>10</v>
-      </c>
       <c r="H499" s="9" t="n"/>
       <c r="I499" s="9" t="n"/>
       <c r="K499" s="9" t="n"/>
     </row>
     <row r="500">
-      <c r="G500" t="n">
-        <v>10</v>
-      </c>
       <c r="H500" s="9" t="n"/>
       <c r="I500" s="9" t="n"/>
       <c r="K500" s="9" t="n"/>
@@ -5438,9 +3961,7 @@
       <c r="K2" s="7" t="n"/>
       <c r="L2" s="7" t="n"/>
       <c r="M2" s="7" t="n"/>
-      <c r="N2" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="N2" s="6" t="n"/>
       <c r="O2" s="8" t="n"/>
       <c r="P2" s="6" t="n"/>
     </row>
@@ -5506,9 +4027,7 @@
           <t>brought는 '가져왔다'예요.</t>
         </is>
       </c>
-      <c r="N3" s="6" t="n">
-        <v>10</v>
-      </c>
+      <c r="N3" s="6" t="n"/>
       <c r="O3" s="8" t="n"/>
       <c r="P3" s="6" t="n"/>
     </row>
